--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -7,9 +7,10 @@
     <sheet state="visible" name="Lanes" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Balls" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Stamps" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Black" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Trials" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="Judgement" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Ideas" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Aims" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Ideas" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="221">
   <si>
     <t>Discards</t>
   </si>
@@ -190,37 +191,46 @@
     <t>Effect</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Lane 1</t>
   </si>
   <si>
     <t>lane_deck</t>
   </si>
   <si>
-    <t xml:space="preserve">All balls in this Lane are Retained after they are Scored. </t>
+    <t xml:space="preserve">All balls in this Lane are Retained after this Lane has Scored. </t>
   </si>
   <si>
     <t>Lane 2</t>
   </si>
   <si>
-    <t>You must Discard one ball from this Lane before you Score it.</t>
+    <t xml:space="preserve">You may discard 3 Colored balls to Discard one Black ball from this Lane when this Lane is Scored. </t>
   </si>
   <si>
     <t>Lane 3</t>
   </si>
   <si>
-    <t>You may move one ball from this Lane to your other Lane after it has Scored.</t>
+    <t>You may move one ball from this Lane to an open Lane after this Lane has Scored.</t>
+  </si>
+  <si>
+    <t>1?</t>
   </si>
   <si>
     <t>Lane 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Any Life lost from balls in this Lane is also gained as Points. </t>
+    <t xml:space="preserve">Black balls scores points equal to the damage they dealt when this Lane is Scored. </t>
+  </si>
+  <si>
+    <t>2?</t>
   </si>
   <si>
     <t>Lane 5</t>
   </si>
   <si>
-    <t xml:space="preserve">You may draw a Discarded ball when this is Scored. </t>
+    <t xml:space="preserve">You may draw a Discarded ball when this Lane is about to get Scored. </t>
   </si>
   <si>
     <t>Lane 6</t>
@@ -262,134 +272,172 @@
     <t>ball_deck</t>
   </si>
   <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
-Reveal a ball. Draw it if it is Yellow. </t>
+    <t xml:space="preserve">When Scored:&lt;/br&gt;
+Gain 1 Yellow if Yellow is the majority Color in this Lane. </t>
+  </si>
+  <si>
+    <t>- 1 / 3</t>
   </si>
   <si>
     <t>Common Yellow 2</t>
   </si>
   <si>
-    <t>Score:&lt;/br&gt;
-Gain 1 Retains</t>
+    <t>When Scored:&lt;/br&gt;
+Gain 1 Reclaims</t>
   </si>
   <si>
     <t>Common Blue 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 1 Blue when hit by a Blue ball. </t>
+    <t xml:space="preserve">On Hit:&lt;/br&gt;
+Gain 1 Shield if the ball was Black. </t>
+  </si>
+  <si>
+    <t>0.75 * 0.5</t>
   </si>
   <si>
     <t>Common Blue 2</t>
-  </si>
-  <si>
-    <t>Score:&lt;/br&gt;
-Gain 1 Discards</t>
-  </si>
-  <si>
-    <t>Common Green 1</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain 1 Bounces when hit. </t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
-Gain 1 Yellow. </t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score:&lt;/br&gt;
-Retain one discarded Black ball to gain 1 Green. </t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain 1 Point whenever this is moved to the Combola. </t>
-  </si>
-  <si>
-    <t>Uncommon Blue 1</t>
-  </si>
-  <si>
-    <t>Gain 1 Shield when this hits or is hit by a Black ball.</t>
-  </si>
-  <si>
-    <t>Uncommon Blue 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
-Discard a Black ball from the Combola. </t>
-  </si>
-  <si>
-    <t>Uncommon Blue 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
-You may Discard a non-black ball from a Lane to gain 1 Green.  </t>
-  </si>
-  <si>
-    <t>Uncommon Blue 4</t>
   </si>
   <si>
     <t xml:space="preserve">On Draw:&lt;/br&gt;
 Draw a random Discarded ball.  </t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Common Green 1</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When Scored:&lt;/br&gt;
+Gain 1 Green if adjacent to two different colors. </t>
+  </si>
+  <si>
+    <t>1.0 * 0.5</t>
+  </si>
+  <si>
+    <t>Uncommon Yellow 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Hit:&lt;/br&gt;
+Gain 1 Bounces. </t>
+  </si>
+  <si>
+    <t>1.5 - 3.0</t>
+  </si>
+  <si>
+    <t>Uncommon Yellow 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Draw:&lt;/br&gt;
+Gain 1 Yellow for each Yellow ball in the Draw area. </t>
+  </si>
+  <si>
+    <t>1.0 - 3.0</t>
+  </si>
+  <si>
+    <t>Uncommon Yellow 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Draw:&lt;/br&gt;
+Reveal a ball. Draw it and repeat this effect if it was Yellow. </t>
+  </si>
+  <si>
+    <t>Uncommon Yellow 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw this ball when it is Retained or Redeemed. </t>
+  </si>
+  <si>
+    <t>Uncommon Blue 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 1 Blue whenever this hits or is hit by a Blue ball. </t>
+  </si>
+  <si>
+    <t>2 * x</t>
+  </si>
+  <si>
+    <t>Uncommon Blue 2</t>
+  </si>
+  <si>
+    <t>When Placed:&lt;/br&gt;
+Gain 1 Redeem. You may Discard a colored ball from this Lane to get 1 additional Redeem.</t>
+  </si>
+  <si>
+    <t>Uncommon Blue 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redeem this ball at the start of a Trial. </t>
+  </si>
+  <si>
+    <t>Uncommon Blue 4</t>
+  </si>
+  <si>
+    <t>On Hit:&lt;/br&gt;
+If the hit ball matches the majority color in this Lane, Redeem it. If the hit ball is Black and Black is the majority color in this Lane, Discard the hit ball and this ball instead.</t>
+  </si>
+  <si>
+    <t>2.0 if black is majority. Need exhausted?</t>
+  </si>
+  <si>
     <t>Uncommon Green 1</t>
   </si>
   <si>
-    <t>Score any balls hit by this.</t>
+    <t>On Hit:&lt;/br&gt;
+Score the hit ball.</t>
+  </si>
+  <si>
+    <t>1.0 - ?</t>
   </si>
   <si>
     <t>Uncommon Green 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Score:&lt;/br&gt;
-Gain 1 Green if adjacent to both a Blue and Yellow ball. </t>
+    <t xml:space="preserve">On Hit:&lt;/br&gt;
+Gain 1 Bounces if the ball was Yellow.&lt;/br&gt;
+Gain 1 Redeems if the ball was Blue.&lt;/br&gt;
+Gain both if it was Green. </t>
   </si>
   <si>
     <t>Rare Yellow 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Score:&lt;/br&gt;
-Gain 1 Yellow for each Black ball in the Combola. </t>
+    <t xml:space="preserve">When Placed:&lt;/br&gt;
+Score all balls in this Lane if there are fewer balls in this Lane than the other Lane. </t>
   </si>
   <si>
     <t>Rare Yellow 2</t>
   </si>
   <si>
-    <t xml:space="preserve">You may Bounce any ball hit by this. </t>
+    <t xml:space="preserve">When Scored:&lt;/br&gt;
+Gain 1 Green for each ball of the majority color in this Lane. </t>
   </si>
   <si>
     <t>Rare Blue 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Score:&lt;br&gt;
-Gain 1 Blue for each Discarded ball in excess of balls in both Lanes. </t>
+    <t xml:space="preserve">When a ball is Redeemed you may Draw it and place it in this Lane instead. </t>
   </si>
   <si>
     <t>Rare Blue 2</t>
   </si>
   <si>
+    <t xml:space="preserve">When Scored:&lt;/br&gt;
+Gain 3 Blue. </t>
+  </si>
+  <si>
+    <t>Rare Green 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">On Draw:&lt;/br&gt;
-You may Discard this ball to Discard all balls in a Lane. </t>
-  </si>
-  <si>
-    <t>Rare Green 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score:&lt;/br&gt;
-Gain 1 Key and lose 1 Health. </t>
+Discard a Black ball from a Lane if you have 5 or less Health. </t>
+  </si>
+  <si>
+    <t>2.0</t>
   </si>
   <si>
     <t>Common Stamp 1</t>
@@ -398,41 +446,53 @@
     <t>stamp_deck</t>
   </si>
   <si>
-    <t>2+X</t>
+    <t>1+X</t>
   </si>
   <si>
     <t>Gain X Retains</t>
   </si>
   <si>
+    <t>0.75 / x</t>
+  </si>
+  <si>
     <t>Common Stamp 2</t>
   </si>
   <si>
-    <t>Add X temporary Yellow balls to the Combola.</t>
+    <t>Add 1 + X temporary Yellow balls to the Combola.</t>
+  </si>
+  <si>
+    <t>0.5 + 0.5 / x</t>
   </si>
   <si>
     <t>Common Stamp 3</t>
   </si>
   <si>
-    <t>Gain X Discards</t>
+    <t>Gain X Shield</t>
   </si>
   <si>
     <t>Common Stamp 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Discard X random balls from the Combola. </t>
+    <t xml:space="preserve">Draw X balls. You may Discard all of them. </t>
+  </si>
+  <si>
+    <t>x=1 --&gt; 1 but then weaker?</t>
   </si>
   <si>
     <t>Common Stamp 5</t>
   </si>
   <si>
     <t>Gain X Retains&lt;/br&gt;
-Gain X Discards</t>
+Gain X Shield</t>
+  </si>
+  <si>
+    <t>1.5 / x</t>
   </si>
   <si>
     <t>Uncommon Stamp 1</t>
   </si>
   <si>
-    <t>4+X</t>
+    <t>3+X</t>
   </si>
   <si>
     <t>Gain X Bounces</t>
@@ -441,61 +501,82 @@
     <t>Uncommon Stamp 2</t>
   </si>
   <si>
-    <t>Draw X balls.</t>
+    <t xml:space="preserve">Gain 3X Yellow if you have a Lane with at least that many balls. </t>
   </si>
   <si>
     <t>Uncommon Stamp 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain X Yellow if you have a Lane with at least twice that many balls. </t>
+    <t xml:space="preserve">Draw X balls from an open Lane. </t>
   </si>
   <si>
     <t>Uncommon Stamp 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Bounce the first X balls of a Lane.  </t>
+  </si>
+  <si>
     <t>Uncommon Stamp 5</t>
   </si>
   <si>
-    <t>Gain X Shield</t>
+    <t>Gain 1 + X Redeems</t>
+  </si>
+  <si>
+    <t>1 + 1 / x</t>
   </si>
   <si>
     <t>Uncommon Stamp 6</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain X Blue if you have at least that many Black balls among your Lanes. </t>
+    <t xml:space="preserve">You may draw 1 + X Discarded balls at random. </t>
+  </si>
+  <si>
+    <t>Maybe 2X?</t>
   </si>
   <si>
     <t>Uncommon Stamp 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Discard X different balls from an open Lane. </t>
+    <t xml:space="preserve">Score all balls in a Lane with no more than 2X balls. </t>
+  </si>
+  <si>
+    <t>50%: 2 / x</t>
   </si>
   <si>
     <t>Uncommon Stamp 8</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw X random Discarded balls. </t>
+    <t>Gain X Health</t>
+  </si>
+  <si>
+    <t>Premium shield</t>
   </si>
   <si>
     <t>Uncommon Stamp 9</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain X Shield for each Black ball in a Lane. </t>
+    <t xml:space="preserve">Gain the effect from a Stamp at level X or less thrice. </t>
+  </si>
+  <si>
+    <t>~3 / x</t>
   </si>
   <si>
     <t>Uncommon Stamp 10</t>
   </si>
   <si>
-    <t xml:space="preserve">Score a Lane with no more than X balls. </t>
+    <t xml:space="preserve">Gain 2X Green. You score no points for levels gained by this. </t>
+  </si>
+  <si>
+    <t>3 / x</t>
   </si>
   <si>
     <t>Rare Stamp 1</t>
   </si>
   <si>
-    <t>8+X</t>
-  </si>
-  <si>
-    <t>Draw balls and place them in an open Lane until that Lane contains X balls in total. Then bounce any Black balls placed this way.</t>
+    <t>7+X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw and then place balls in an open Lane until it has X balls. Then Bounce any Black balls placed by this effect. </t>
   </si>
   <si>
     <t>Rare Stamp 2</t>
@@ -504,24 +585,27 @@
     <t>Gain X Gold</t>
   </si>
   <si>
+    <t>2.4 / x</t>
+  </si>
+  <si>
     <t>Rare Stamp 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain X Keys and Discard X non-black balls from the Combola. </t>
+    <t xml:space="preserve">Gain X Keys and lose X Health. </t>
   </si>
   <si>
     <t>Rare Stamp 4</t>
   </si>
   <si>
-    <t>Gain X Health</t>
-  </si>
-  <si>
     <t>Rare Stamp 5</t>
   </si>
   <si>
     <t>Discard X Black balls from the Combola.</t>
   </si>
   <si>
+    <t>Can be game breaking</t>
+  </si>
+  <si>
     <t>Strength</t>
   </si>
   <si>
@@ -531,19 +615,25 @@
     <t>black_deck</t>
   </si>
   <si>
-    <t xml:space="preserve">Add X temporary Black balls to the Combola at the start of the game. </t>
+    <t xml:space="preserve">Add X / 2 (rounded down) temporary Black balls to the Combola at the start of the Trial. </t>
+  </si>
+  <si>
+    <t>1.5*x</t>
   </si>
   <si>
     <t>Black 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Lose 1 Health when Bouncing a Black ball. </t>
+    <t>Discard X colored balls at the start of the Trial.</t>
   </si>
   <si>
     <t>Black 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Remove one of your highest level Stamps for this game. </t>
+    <t>Exhaust one of your highest level Stamps at the start of this game.</t>
+  </si>
+  <si>
+    <t>3?</t>
   </si>
   <si>
     <t>Black 4</t>
@@ -555,7 +645,7 @@
     <t>Black 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw a Black ball whenever you open a Lane. </t>
+    <t xml:space="preserve">Draw a Black ball and gain 1 Shield whenever you open a Lane. </t>
   </si>
   <si>
     <t>Judgement 1</t>
@@ -636,12 +726,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -650,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -668,6 +764,16 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,6 +808,10 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1193,90 +1303,107 @@
       <c r="D1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1">
         <v>1.0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1">
         <v>1.0</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -4271,7 +4398,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.38"/>
-    <col customWidth="1" min="7" max="7" width="27.38"/>
+    <col customWidth="1" min="7" max="7" width="34.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4285,93 +4412,97 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="H1" s="6"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1">
         <v>8.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="H2" s="6"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C3" s="1">
         <v>8.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="H3" s="6"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1">
         <v>6.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="H4" s="6"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C5" s="1">
         <v>10.0</v>
@@ -4380,21 +4511,24 @@
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" s="1">
         <v>2.0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -4403,21 +4537,22 @@
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1">
         <v>2.0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="H6" s="7"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1">
         <v>10.0</v>
@@ -4426,21 +4561,24 @@
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F7" s="1">
         <v>2.0</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>85</v>
+      <c r="G7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1">
         <v>10.0</v>
@@ -4449,21 +4587,25 @@
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F8" s="1">
         <v>2.0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>87</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1">
         <v>10.0</v>
@@ -4472,21 +4614,25 @@
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
         <v>2.0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1">
         <v>3.0</v>
@@ -4495,21 +4641,25 @@
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1">
         <v>4.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1">
         <v>3.0</v>
@@ -4518,21 +4668,25 @@
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F11" s="1">
         <v>4.0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>93</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -4541,21 +4695,23 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F12" s="1">
         <v>4.0</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>95</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="J12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1">
         <v>3.0</v>
@@ -4564,21 +4720,23 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1">
         <v>4.0</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>97</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="J13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1">
         <v>3.0</v>
@@ -4587,21 +4745,25 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F14" s="1">
         <v>4.0</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C15" s="1">
         <v>3.0</v>
@@ -4610,21 +4772,23 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>101</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="J15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C16" s="1">
         <v>3.0</v>
@@ -4633,21 +4797,23 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F16" s="1">
         <v>4.0</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="G16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1">
         <v>3.0</v>
@@ -4656,21 +4822,25 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F17" s="1">
         <v>4.0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>105</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1">
         <v>3.0</v>
@@ -4679,21 +4849,25 @@
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1">
         <v>4.0</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1">
         <v>3.0</v>
@@ -4702,21 +4876,23 @@
         <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F19" s="1">
         <v>4.0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>109</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="J19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1">
         <v>1.0</v>
@@ -4725,21 +4901,22 @@
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1">
         <v>8.0</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>111</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="H20" s="7"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" s="1">
         <v>1.0</v>
@@ -4748,21 +4925,22 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1">
         <v>8.0</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>113</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="H21" s="7"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1">
         <v>1.0</v>
@@ -4771,21 +4949,22 @@
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>115</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="H22" s="6"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1">
         <v>1.0</v>
@@ -4794,21 +4973,22 @@
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F23" s="1">
         <v>8.0</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>117</v>
-      </c>
+      <c r="G23" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="6"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1">
         <v>1.0</v>
@@ -4817,2942 +4997,3921 @@
         <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F24" s="1">
         <v>8.0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>119</v>
+        <v>132</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="25">
       <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26">
       <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
     </row>
     <row r="27">
       <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28">
       <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29">
       <c r="G29" s="5"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30">
       <c r="G30" s="5"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31">
       <c r="G31" s="5"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32">
       <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33">
       <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34">
       <c r="G34" s="5"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35">
       <c r="G35" s="5"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36">
       <c r="G36" s="5"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37">
       <c r="G37" s="5"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38">
       <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
     </row>
     <row r="39">
       <c r="G39" s="5"/>
+      <c r="H39" s="6"/>
     </row>
     <row r="40">
       <c r="G40" s="5"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41">
       <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
     </row>
     <row r="42">
       <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43">
       <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44">
       <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45">
       <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46">
       <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
     </row>
     <row r="47">
       <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48">
       <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49">
       <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
     </row>
     <row r="50">
       <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
     </row>
     <row r="51">
       <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52">
       <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53">
       <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
     </row>
     <row r="54">
       <c r="G54" s="5"/>
+      <c r="H54" s="6"/>
     </row>
     <row r="55">
       <c r="G55" s="5"/>
+      <c r="H55" s="6"/>
     </row>
     <row r="56">
       <c r="G56" s="5"/>
+      <c r="H56" s="6"/>
     </row>
     <row r="57">
       <c r="G57" s="5"/>
+      <c r="H57" s="6"/>
     </row>
     <row r="58">
       <c r="G58" s="5"/>
+      <c r="H58" s="6"/>
     </row>
     <row r="59">
       <c r="G59" s="5"/>
+      <c r="H59" s="6"/>
     </row>
     <row r="60">
       <c r="G60" s="5"/>
+      <c r="H60" s="6"/>
     </row>
     <row r="61">
       <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
     </row>
     <row r="62">
       <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
     </row>
     <row r="63">
       <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
     </row>
     <row r="64">
       <c r="G64" s="5"/>
+      <c r="H64" s="6"/>
     </row>
     <row r="65">
       <c r="G65" s="5"/>
+      <c r="H65" s="6"/>
     </row>
     <row r="66">
       <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
     </row>
     <row r="67">
       <c r="G67" s="5"/>
+      <c r="H67" s="6"/>
     </row>
     <row r="68">
       <c r="G68" s="5"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69">
       <c r="G69" s="5"/>
+      <c r="H69" s="6"/>
     </row>
     <row r="70">
       <c r="G70" s="5"/>
+      <c r="H70" s="6"/>
     </row>
     <row r="71">
       <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72">
       <c r="G72" s="5"/>
+      <c r="H72" s="6"/>
     </row>
     <row r="73">
       <c r="G73" s="5"/>
+      <c r="H73" s="6"/>
     </row>
     <row r="74">
       <c r="G74" s="5"/>
+      <c r="H74" s="6"/>
     </row>
     <row r="75">
       <c r="G75" s="5"/>
+      <c r="H75" s="6"/>
     </row>
     <row r="76">
       <c r="G76" s="5"/>
+      <c r="H76" s="6"/>
     </row>
     <row r="77">
       <c r="G77" s="5"/>
+      <c r="H77" s="6"/>
     </row>
     <row r="78">
       <c r="G78" s="5"/>
+      <c r="H78" s="6"/>
     </row>
     <row r="79">
       <c r="G79" s="5"/>
+      <c r="H79" s="6"/>
     </row>
     <row r="80">
       <c r="G80" s="5"/>
+      <c r="H80" s="6"/>
     </row>
     <row r="81">
       <c r="G81" s="5"/>
+      <c r="H81" s="6"/>
     </row>
     <row r="82">
       <c r="G82" s="5"/>
+      <c r="H82" s="6"/>
     </row>
     <row r="83">
       <c r="G83" s="5"/>
+      <c r="H83" s="6"/>
     </row>
     <row r="84">
       <c r="G84" s="5"/>
+      <c r="H84" s="6"/>
     </row>
     <row r="85">
       <c r="G85" s="5"/>
+      <c r="H85" s="6"/>
     </row>
     <row r="86">
       <c r="G86" s="5"/>
+      <c r="H86" s="6"/>
     </row>
     <row r="87">
       <c r="G87" s="5"/>
+      <c r="H87" s="6"/>
     </row>
     <row r="88">
       <c r="G88" s="5"/>
+      <c r="H88" s="6"/>
     </row>
     <row r="89">
       <c r="G89" s="5"/>
+      <c r="H89" s="6"/>
     </row>
     <row r="90">
       <c r="G90" s="5"/>
+      <c r="H90" s="6"/>
     </row>
     <row r="91">
       <c r="G91" s="5"/>
+      <c r="H91" s="6"/>
     </row>
     <row r="92">
       <c r="G92" s="5"/>
+      <c r="H92" s="6"/>
     </row>
     <row r="93">
       <c r="G93" s="5"/>
+      <c r="H93" s="6"/>
     </row>
     <row r="94">
       <c r="G94" s="5"/>
+      <c r="H94" s="6"/>
     </row>
     <row r="95">
       <c r="G95" s="5"/>
+      <c r="H95" s="6"/>
     </row>
     <row r="96">
       <c r="G96" s="5"/>
+      <c r="H96" s="6"/>
     </row>
     <row r="97">
       <c r="G97" s="5"/>
+      <c r="H97" s="6"/>
     </row>
     <row r="98">
       <c r="G98" s="5"/>
+      <c r="H98" s="6"/>
     </row>
     <row r="99">
       <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
     </row>
     <row r="100">
       <c r="G100" s="5"/>
+      <c r="H100" s="6"/>
     </row>
     <row r="101">
       <c r="G101" s="5"/>
+      <c r="H101" s="6"/>
     </row>
     <row r="102">
       <c r="G102" s="5"/>
+      <c r="H102" s="6"/>
     </row>
     <row r="103">
       <c r="G103" s="5"/>
+      <c r="H103" s="6"/>
     </row>
     <row r="104">
       <c r="G104" s="5"/>
+      <c r="H104" s="6"/>
     </row>
     <row r="105">
       <c r="G105" s="5"/>
+      <c r="H105" s="6"/>
     </row>
     <row r="106">
       <c r="G106" s="5"/>
+      <c r="H106" s="6"/>
     </row>
     <row r="107">
       <c r="G107" s="5"/>
+      <c r="H107" s="6"/>
     </row>
     <row r="108">
       <c r="G108" s="5"/>
+      <c r="H108" s="6"/>
     </row>
     <row r="109">
       <c r="G109" s="5"/>
+      <c r="H109" s="6"/>
     </row>
     <row r="110">
       <c r="G110" s="5"/>
+      <c r="H110" s="6"/>
     </row>
     <row r="111">
       <c r="G111" s="5"/>
+      <c r="H111" s="6"/>
     </row>
     <row r="112">
       <c r="G112" s="5"/>
+      <c r="H112" s="6"/>
     </row>
     <row r="113">
       <c r="G113" s="5"/>
+      <c r="H113" s="6"/>
     </row>
     <row r="114">
       <c r="G114" s="5"/>
+      <c r="H114" s="6"/>
     </row>
     <row r="115">
       <c r="G115" s="5"/>
+      <c r="H115" s="6"/>
     </row>
     <row r="116">
       <c r="G116" s="5"/>
+      <c r="H116" s="6"/>
     </row>
     <row r="117">
       <c r="G117" s="5"/>
+      <c r="H117" s="6"/>
     </row>
     <row r="118">
       <c r="G118" s="5"/>
+      <c r="H118" s="6"/>
     </row>
     <row r="119">
       <c r="G119" s="5"/>
+      <c r="H119" s="6"/>
     </row>
     <row r="120">
       <c r="G120" s="5"/>
+      <c r="H120" s="6"/>
     </row>
     <row r="121">
       <c r="G121" s="5"/>
+      <c r="H121" s="6"/>
     </row>
     <row r="122">
       <c r="G122" s="5"/>
+      <c r="H122" s="6"/>
     </row>
     <row r="123">
       <c r="G123" s="5"/>
+      <c r="H123" s="6"/>
     </row>
     <row r="124">
       <c r="G124" s="5"/>
+      <c r="H124" s="6"/>
     </row>
     <row r="125">
       <c r="G125" s="5"/>
+      <c r="H125" s="6"/>
     </row>
     <row r="126">
       <c r="G126" s="5"/>
+      <c r="H126" s="6"/>
     </row>
     <row r="127">
       <c r="G127" s="5"/>
+      <c r="H127" s="6"/>
     </row>
     <row r="128">
       <c r="G128" s="5"/>
+      <c r="H128" s="6"/>
     </row>
     <row r="129">
       <c r="G129" s="5"/>
+      <c r="H129" s="6"/>
     </row>
     <row r="130">
       <c r="G130" s="5"/>
+      <c r="H130" s="6"/>
     </row>
     <row r="131">
       <c r="G131" s="5"/>
+      <c r="H131" s="6"/>
     </row>
     <row r="132">
       <c r="G132" s="5"/>
+      <c r="H132" s="6"/>
     </row>
     <row r="133">
       <c r="G133" s="5"/>
+      <c r="H133" s="6"/>
     </row>
     <row r="134">
       <c r="G134" s="5"/>
+      <c r="H134" s="6"/>
     </row>
     <row r="135">
       <c r="G135" s="5"/>
+      <c r="H135" s="6"/>
     </row>
     <row r="136">
       <c r="G136" s="5"/>
+      <c r="H136" s="6"/>
     </row>
     <row r="137">
       <c r="G137" s="5"/>
+      <c r="H137" s="6"/>
     </row>
     <row r="138">
       <c r="G138" s="5"/>
+      <c r="H138" s="6"/>
     </row>
     <row r="139">
       <c r="G139" s="5"/>
+      <c r="H139" s="6"/>
     </row>
     <row r="140">
       <c r="G140" s="5"/>
+      <c r="H140" s="6"/>
     </row>
     <row r="141">
       <c r="G141" s="5"/>
+      <c r="H141" s="6"/>
     </row>
     <row r="142">
       <c r="G142" s="5"/>
+      <c r="H142" s="6"/>
     </row>
     <row r="143">
       <c r="G143" s="5"/>
+      <c r="H143" s="6"/>
     </row>
     <row r="144">
       <c r="G144" s="5"/>
+      <c r="H144" s="6"/>
     </row>
     <row r="145">
       <c r="G145" s="5"/>
+      <c r="H145" s="6"/>
     </row>
     <row r="146">
       <c r="G146" s="5"/>
+      <c r="H146" s="6"/>
     </row>
     <row r="147">
       <c r="G147" s="5"/>
+      <c r="H147" s="6"/>
     </row>
     <row r="148">
       <c r="G148" s="5"/>
+      <c r="H148" s="6"/>
     </row>
     <row r="149">
       <c r="G149" s="5"/>
+      <c r="H149" s="6"/>
     </row>
     <row r="150">
       <c r="G150" s="5"/>
+      <c r="H150" s="6"/>
     </row>
     <row r="151">
       <c r="G151" s="5"/>
+      <c r="H151" s="6"/>
     </row>
     <row r="152">
       <c r="G152" s="5"/>
+      <c r="H152" s="6"/>
     </row>
     <row r="153">
       <c r="G153" s="5"/>
+      <c r="H153" s="6"/>
     </row>
     <row r="154">
       <c r="G154" s="5"/>
+      <c r="H154" s="6"/>
     </row>
     <row r="155">
       <c r="G155" s="5"/>
+      <c r="H155" s="6"/>
     </row>
     <row r="156">
       <c r="G156" s="5"/>
+      <c r="H156" s="6"/>
     </row>
     <row r="157">
       <c r="G157" s="5"/>
+      <c r="H157" s="6"/>
     </row>
     <row r="158">
       <c r="G158" s="5"/>
+      <c r="H158" s="6"/>
     </row>
     <row r="159">
       <c r="G159" s="5"/>
+      <c r="H159" s="6"/>
     </row>
     <row r="160">
       <c r="G160" s="5"/>
+      <c r="H160" s="6"/>
     </row>
     <row r="161">
       <c r="G161" s="5"/>
+      <c r="H161" s="6"/>
     </row>
     <row r="162">
       <c r="G162" s="5"/>
+      <c r="H162" s="6"/>
     </row>
     <row r="163">
       <c r="G163" s="5"/>
+      <c r="H163" s="6"/>
     </row>
     <row r="164">
       <c r="G164" s="5"/>
+      <c r="H164" s="6"/>
     </row>
     <row r="165">
       <c r="G165" s="5"/>
+      <c r="H165" s="6"/>
     </row>
     <row r="166">
       <c r="G166" s="5"/>
+      <c r="H166" s="6"/>
     </row>
     <row r="167">
       <c r="G167" s="5"/>
+      <c r="H167" s="6"/>
     </row>
     <row r="168">
       <c r="G168" s="5"/>
+      <c r="H168" s="6"/>
     </row>
     <row r="169">
       <c r="G169" s="5"/>
+      <c r="H169" s="6"/>
     </row>
     <row r="170">
       <c r="G170" s="5"/>
+      <c r="H170" s="6"/>
     </row>
     <row r="171">
       <c r="G171" s="5"/>
+      <c r="H171" s="6"/>
     </row>
     <row r="172">
       <c r="G172" s="5"/>
+      <c r="H172" s="6"/>
     </row>
     <row r="173">
       <c r="G173" s="5"/>
+      <c r="H173" s="6"/>
     </row>
     <row r="174">
       <c r="G174" s="5"/>
+      <c r="H174" s="6"/>
     </row>
     <row r="175">
       <c r="G175" s="5"/>
+      <c r="H175" s="6"/>
     </row>
     <row r="176">
       <c r="G176" s="5"/>
+      <c r="H176" s="6"/>
     </row>
     <row r="177">
       <c r="G177" s="5"/>
+      <c r="H177" s="6"/>
     </row>
     <row r="178">
       <c r="G178" s="5"/>
+      <c r="H178" s="6"/>
     </row>
     <row r="179">
       <c r="G179" s="5"/>
+      <c r="H179" s="6"/>
     </row>
     <row r="180">
       <c r="G180" s="5"/>
+      <c r="H180" s="6"/>
     </row>
     <row r="181">
       <c r="G181" s="5"/>
+      <c r="H181" s="6"/>
     </row>
     <row r="182">
       <c r="G182" s="5"/>
+      <c r="H182" s="6"/>
     </row>
     <row r="183">
       <c r="G183" s="5"/>
+      <c r="H183" s="6"/>
     </row>
     <row r="184">
       <c r="G184" s="5"/>
+      <c r="H184" s="6"/>
     </row>
     <row r="185">
       <c r="G185" s="5"/>
+      <c r="H185" s="6"/>
     </row>
     <row r="186">
       <c r="G186" s="5"/>
+      <c r="H186" s="6"/>
     </row>
     <row r="187">
       <c r="G187" s="5"/>
+      <c r="H187" s="6"/>
     </row>
     <row r="188">
       <c r="G188" s="5"/>
+      <c r="H188" s="6"/>
     </row>
     <row r="189">
       <c r="G189" s="5"/>
+      <c r="H189" s="6"/>
     </row>
     <row r="190">
       <c r="G190" s="5"/>
+      <c r="H190" s="6"/>
     </row>
     <row r="191">
       <c r="G191" s="5"/>
+      <c r="H191" s="6"/>
     </row>
     <row r="192">
       <c r="G192" s="5"/>
+      <c r="H192" s="6"/>
     </row>
     <row r="193">
       <c r="G193" s="5"/>
+      <c r="H193" s="6"/>
     </row>
     <row r="194">
       <c r="G194" s="5"/>
+      <c r="H194" s="6"/>
     </row>
     <row r="195">
       <c r="G195" s="5"/>
+      <c r="H195" s="6"/>
     </row>
     <row r="196">
       <c r="G196" s="5"/>
+      <c r="H196" s="6"/>
     </row>
     <row r="197">
       <c r="G197" s="5"/>
+      <c r="H197" s="6"/>
     </row>
     <row r="198">
       <c r="G198" s="5"/>
+      <c r="H198" s="6"/>
     </row>
     <row r="199">
       <c r="G199" s="5"/>
+      <c r="H199" s="6"/>
     </row>
     <row r="200">
       <c r="G200" s="5"/>
+      <c r="H200" s="6"/>
     </row>
     <row r="201">
       <c r="G201" s="5"/>
+      <c r="H201" s="6"/>
     </row>
     <row r="202">
       <c r="G202" s="5"/>
+      <c r="H202" s="6"/>
     </row>
     <row r="203">
       <c r="G203" s="5"/>
+      <c r="H203" s="6"/>
     </row>
     <row r="204">
       <c r="G204" s="5"/>
+      <c r="H204" s="6"/>
     </row>
     <row r="205">
       <c r="G205" s="5"/>
+      <c r="H205" s="6"/>
     </row>
     <row r="206">
       <c r="G206" s="5"/>
+      <c r="H206" s="6"/>
     </row>
     <row r="207">
       <c r="G207" s="5"/>
+      <c r="H207" s="6"/>
     </row>
     <row r="208">
       <c r="G208" s="5"/>
+      <c r="H208" s="6"/>
     </row>
     <row r="209">
       <c r="G209" s="5"/>
+      <c r="H209" s="6"/>
     </row>
     <row r="210">
       <c r="G210" s="5"/>
+      <c r="H210" s="6"/>
     </row>
     <row r="211">
       <c r="G211" s="5"/>
+      <c r="H211" s="6"/>
     </row>
     <row r="212">
       <c r="G212" s="5"/>
+      <c r="H212" s="6"/>
     </row>
     <row r="213">
       <c r="G213" s="5"/>
+      <c r="H213" s="6"/>
     </row>
     <row r="214">
       <c r="G214" s="5"/>
+      <c r="H214" s="6"/>
     </row>
     <row r="215">
       <c r="G215" s="5"/>
+      <c r="H215" s="6"/>
     </row>
     <row r="216">
       <c r="G216" s="5"/>
+      <c r="H216" s="6"/>
     </row>
     <row r="217">
       <c r="G217" s="5"/>
+      <c r="H217" s="6"/>
     </row>
     <row r="218">
       <c r="G218" s="5"/>
+      <c r="H218" s="6"/>
     </row>
     <row r="219">
       <c r="G219" s="5"/>
+      <c r="H219" s="6"/>
     </row>
     <row r="220">
       <c r="G220" s="5"/>
+      <c r="H220" s="6"/>
     </row>
     <row r="221">
       <c r="G221" s="5"/>
+      <c r="H221" s="6"/>
     </row>
     <row r="222">
       <c r="G222" s="5"/>
+      <c r="H222" s="6"/>
     </row>
     <row r="223">
       <c r="G223" s="5"/>
+      <c r="H223" s="6"/>
     </row>
     <row r="224">
       <c r="G224" s="5"/>
+      <c r="H224" s="6"/>
     </row>
     <row r="225">
       <c r="G225" s="5"/>
+      <c r="H225" s="6"/>
     </row>
     <row r="226">
       <c r="G226" s="5"/>
+      <c r="H226" s="6"/>
     </row>
     <row r="227">
       <c r="G227" s="5"/>
+      <c r="H227" s="6"/>
     </row>
     <row r="228">
       <c r="G228" s="5"/>
+      <c r="H228" s="6"/>
     </row>
     <row r="229">
       <c r="G229" s="5"/>
+      <c r="H229" s="6"/>
     </row>
     <row r="230">
       <c r="G230" s="5"/>
+      <c r="H230" s="6"/>
     </row>
     <row r="231">
       <c r="G231" s="5"/>
+      <c r="H231" s="6"/>
     </row>
     <row r="232">
       <c r="G232" s="5"/>
+      <c r="H232" s="6"/>
     </row>
     <row r="233">
       <c r="G233" s="5"/>
+      <c r="H233" s="6"/>
     </row>
     <row r="234">
       <c r="G234" s="5"/>
+      <c r="H234" s="6"/>
     </row>
     <row r="235">
       <c r="G235" s="5"/>
+      <c r="H235" s="6"/>
     </row>
     <row r="236">
       <c r="G236" s="5"/>
+      <c r="H236" s="6"/>
     </row>
     <row r="237">
       <c r="G237" s="5"/>
+      <c r="H237" s="6"/>
     </row>
     <row r="238">
       <c r="G238" s="5"/>
+      <c r="H238" s="6"/>
     </row>
     <row r="239">
       <c r="G239" s="5"/>
+      <c r="H239" s="6"/>
     </row>
     <row r="240">
       <c r="G240" s="5"/>
+      <c r="H240" s="6"/>
     </row>
     <row r="241">
       <c r="G241" s="5"/>
+      <c r="H241" s="6"/>
     </row>
     <row r="242">
       <c r="G242" s="5"/>
+      <c r="H242" s="6"/>
     </row>
     <row r="243">
       <c r="G243" s="5"/>
+      <c r="H243" s="6"/>
     </row>
     <row r="244">
       <c r="G244" s="5"/>
+      <c r="H244" s="6"/>
     </row>
     <row r="245">
       <c r="G245" s="5"/>
+      <c r="H245" s="6"/>
     </row>
     <row r="246">
       <c r="G246" s="5"/>
+      <c r="H246" s="6"/>
     </row>
     <row r="247">
       <c r="G247" s="5"/>
+      <c r="H247" s="6"/>
     </row>
     <row r="248">
       <c r="G248" s="5"/>
+      <c r="H248" s="6"/>
     </row>
     <row r="249">
       <c r="G249" s="5"/>
+      <c r="H249" s="6"/>
     </row>
     <row r="250">
       <c r="G250" s="5"/>
+      <c r="H250" s="6"/>
     </row>
     <row r="251">
       <c r="G251" s="5"/>
+      <c r="H251" s="6"/>
     </row>
     <row r="252">
       <c r="G252" s="5"/>
+      <c r="H252" s="6"/>
     </row>
     <row r="253">
       <c r="G253" s="5"/>
+      <c r="H253" s="6"/>
     </row>
     <row r="254">
       <c r="G254" s="5"/>
+      <c r="H254" s="6"/>
     </row>
     <row r="255">
       <c r="G255" s="5"/>
+      <c r="H255" s="6"/>
     </row>
     <row r="256">
       <c r="G256" s="5"/>
+      <c r="H256" s="6"/>
     </row>
     <row r="257">
       <c r="G257" s="5"/>
+      <c r="H257" s="6"/>
     </row>
     <row r="258">
       <c r="G258" s="5"/>
+      <c r="H258" s="6"/>
     </row>
     <row r="259">
       <c r="G259" s="5"/>
+      <c r="H259" s="6"/>
     </row>
     <row r="260">
       <c r="G260" s="5"/>
+      <c r="H260" s="6"/>
     </row>
     <row r="261">
       <c r="G261" s="5"/>
+      <c r="H261" s="6"/>
     </row>
     <row r="262">
       <c r="G262" s="5"/>
+      <c r="H262" s="6"/>
     </row>
     <row r="263">
       <c r="G263" s="5"/>
+      <c r="H263" s="6"/>
     </row>
     <row r="264">
       <c r="G264" s="5"/>
+      <c r="H264" s="6"/>
     </row>
     <row r="265">
       <c r="G265" s="5"/>
+      <c r="H265" s="6"/>
     </row>
     <row r="266">
       <c r="G266" s="5"/>
+      <c r="H266" s="6"/>
     </row>
     <row r="267">
       <c r="G267" s="5"/>
+      <c r="H267" s="6"/>
     </row>
     <row r="268">
       <c r="G268" s="5"/>
+      <c r="H268" s="6"/>
     </row>
     <row r="269">
       <c r="G269" s="5"/>
+      <c r="H269" s="6"/>
     </row>
     <row r="270">
       <c r="G270" s="5"/>
+      <c r="H270" s="6"/>
     </row>
     <row r="271">
       <c r="G271" s="5"/>
+      <c r="H271" s="6"/>
     </row>
     <row r="272">
       <c r="G272" s="5"/>
+      <c r="H272" s="6"/>
     </row>
     <row r="273">
       <c r="G273" s="5"/>
+      <c r="H273" s="6"/>
     </row>
     <row r="274">
       <c r="G274" s="5"/>
+      <c r="H274" s="6"/>
     </row>
     <row r="275">
       <c r="G275" s="5"/>
+      <c r="H275" s="6"/>
     </row>
     <row r="276">
       <c r="G276" s="5"/>
+      <c r="H276" s="6"/>
     </row>
     <row r="277">
       <c r="G277" s="5"/>
+      <c r="H277" s="6"/>
     </row>
     <row r="278">
       <c r="G278" s="5"/>
+      <c r="H278" s="6"/>
     </row>
     <row r="279">
       <c r="G279" s="5"/>
+      <c r="H279" s="6"/>
     </row>
     <row r="280">
       <c r="G280" s="5"/>
+      <c r="H280" s="6"/>
     </row>
     <row r="281">
       <c r="G281" s="5"/>
+      <c r="H281" s="6"/>
     </row>
     <row r="282">
       <c r="G282" s="5"/>
+      <c r="H282" s="6"/>
     </row>
     <row r="283">
       <c r="G283" s="5"/>
+      <c r="H283" s="6"/>
     </row>
     <row r="284">
       <c r="G284" s="5"/>
+      <c r="H284" s="6"/>
     </row>
     <row r="285">
       <c r="G285" s="5"/>
+      <c r="H285" s="6"/>
     </row>
     <row r="286">
       <c r="G286" s="5"/>
+      <c r="H286" s="6"/>
     </row>
     <row r="287">
       <c r="G287" s="5"/>
+      <c r="H287" s="6"/>
     </row>
     <row r="288">
       <c r="G288" s="5"/>
+      <c r="H288" s="6"/>
     </row>
     <row r="289">
       <c r="G289" s="5"/>
+      <c r="H289" s="6"/>
     </row>
     <row r="290">
       <c r="G290" s="5"/>
+      <c r="H290" s="6"/>
     </row>
     <row r="291">
       <c r="G291" s="5"/>
+      <c r="H291" s="6"/>
     </row>
     <row r="292">
       <c r="G292" s="5"/>
+      <c r="H292" s="6"/>
     </row>
     <row r="293">
       <c r="G293" s="5"/>
+      <c r="H293" s="6"/>
     </row>
     <row r="294">
       <c r="G294" s="5"/>
+      <c r="H294" s="6"/>
     </row>
     <row r="295">
       <c r="G295" s="5"/>
+      <c r="H295" s="6"/>
     </row>
     <row r="296">
       <c r="G296" s="5"/>
+      <c r="H296" s="6"/>
     </row>
     <row r="297">
       <c r="G297" s="5"/>
+      <c r="H297" s="6"/>
     </row>
     <row r="298">
       <c r="G298" s="5"/>
+      <c r="H298" s="6"/>
     </row>
     <row r="299">
       <c r="G299" s="5"/>
+      <c r="H299" s="6"/>
     </row>
     <row r="300">
       <c r="G300" s="5"/>
+      <c r="H300" s="6"/>
     </row>
     <row r="301">
       <c r="G301" s="5"/>
+      <c r="H301" s="6"/>
     </row>
     <row r="302">
       <c r="G302" s="5"/>
+      <c r="H302" s="6"/>
     </row>
     <row r="303">
       <c r="G303" s="5"/>
+      <c r="H303" s="6"/>
     </row>
     <row r="304">
       <c r="G304" s="5"/>
+      <c r="H304" s="6"/>
     </row>
     <row r="305">
       <c r="G305" s="5"/>
+      <c r="H305" s="6"/>
     </row>
     <row r="306">
       <c r="G306" s="5"/>
+      <c r="H306" s="6"/>
     </row>
     <row r="307">
       <c r="G307" s="5"/>
+      <c r="H307" s="6"/>
     </row>
     <row r="308">
       <c r="G308" s="5"/>
+      <c r="H308" s="6"/>
     </row>
     <row r="309">
       <c r="G309" s="5"/>
+      <c r="H309" s="6"/>
     </row>
     <row r="310">
       <c r="G310" s="5"/>
+      <c r="H310" s="6"/>
     </row>
     <row r="311">
       <c r="G311" s="5"/>
+      <c r="H311" s="6"/>
     </row>
     <row r="312">
       <c r="G312" s="5"/>
+      <c r="H312" s="6"/>
     </row>
     <row r="313">
       <c r="G313" s="5"/>
+      <c r="H313" s="6"/>
     </row>
     <row r="314">
       <c r="G314" s="5"/>
+      <c r="H314" s="6"/>
     </row>
     <row r="315">
       <c r="G315" s="5"/>
+      <c r="H315" s="6"/>
     </row>
     <row r="316">
       <c r="G316" s="5"/>
+      <c r="H316" s="6"/>
     </row>
     <row r="317">
       <c r="G317" s="5"/>
+      <c r="H317" s="6"/>
     </row>
     <row r="318">
       <c r="G318" s="5"/>
+      <c r="H318" s="6"/>
     </row>
     <row r="319">
       <c r="G319" s="5"/>
+      <c r="H319" s="6"/>
     </row>
     <row r="320">
       <c r="G320" s="5"/>
+      <c r="H320" s="6"/>
     </row>
     <row r="321">
       <c r="G321" s="5"/>
+      <c r="H321" s="6"/>
     </row>
     <row r="322">
       <c r="G322" s="5"/>
+      <c r="H322" s="6"/>
     </row>
     <row r="323">
       <c r="G323" s="5"/>
+      <c r="H323" s="6"/>
     </row>
     <row r="324">
       <c r="G324" s="5"/>
+      <c r="H324" s="6"/>
     </row>
     <row r="325">
       <c r="G325" s="5"/>
+      <c r="H325" s="6"/>
     </row>
     <row r="326">
       <c r="G326" s="5"/>
+      <c r="H326" s="6"/>
     </row>
     <row r="327">
       <c r="G327" s="5"/>
+      <c r="H327" s="6"/>
     </row>
     <row r="328">
       <c r="G328" s="5"/>
+      <c r="H328" s="6"/>
     </row>
     <row r="329">
       <c r="G329" s="5"/>
+      <c r="H329" s="6"/>
     </row>
     <row r="330">
       <c r="G330" s="5"/>
+      <c r="H330" s="6"/>
     </row>
     <row r="331">
       <c r="G331" s="5"/>
+      <c r="H331" s="6"/>
     </row>
     <row r="332">
       <c r="G332" s="5"/>
+      <c r="H332" s="6"/>
     </row>
     <row r="333">
       <c r="G333" s="5"/>
+      <c r="H333" s="6"/>
     </row>
     <row r="334">
       <c r="G334" s="5"/>
+      <c r="H334" s="6"/>
     </row>
     <row r="335">
       <c r="G335" s="5"/>
+      <c r="H335" s="6"/>
     </row>
     <row r="336">
       <c r="G336" s="5"/>
+      <c r="H336" s="6"/>
     </row>
     <row r="337">
       <c r="G337" s="5"/>
+      <c r="H337" s="6"/>
     </row>
     <row r="338">
       <c r="G338" s="5"/>
+      <c r="H338" s="6"/>
     </row>
     <row r="339">
       <c r="G339" s="5"/>
+      <c r="H339" s="6"/>
     </row>
     <row r="340">
       <c r="G340" s="5"/>
+      <c r="H340" s="6"/>
     </row>
     <row r="341">
       <c r="G341" s="5"/>
+      <c r="H341" s="6"/>
     </row>
     <row r="342">
       <c r="G342" s="5"/>
+      <c r="H342" s="6"/>
     </row>
     <row r="343">
       <c r="G343" s="5"/>
+      <c r="H343" s="6"/>
     </row>
     <row r="344">
       <c r="G344" s="5"/>
+      <c r="H344" s="6"/>
     </row>
     <row r="345">
       <c r="G345" s="5"/>
+      <c r="H345" s="6"/>
     </row>
     <row r="346">
       <c r="G346" s="5"/>
+      <c r="H346" s="6"/>
     </row>
     <row r="347">
       <c r="G347" s="5"/>
+      <c r="H347" s="6"/>
     </row>
     <row r="348">
       <c r="G348" s="5"/>
+      <c r="H348" s="6"/>
     </row>
     <row r="349">
       <c r="G349" s="5"/>
+      <c r="H349" s="6"/>
     </row>
     <row r="350">
       <c r="G350" s="5"/>
+      <c r="H350" s="6"/>
     </row>
     <row r="351">
       <c r="G351" s="5"/>
+      <c r="H351" s="6"/>
     </row>
     <row r="352">
       <c r="G352" s="5"/>
+      <c r="H352" s="6"/>
     </row>
     <row r="353">
       <c r="G353" s="5"/>
+      <c r="H353" s="6"/>
     </row>
     <row r="354">
       <c r="G354" s="5"/>
+      <c r="H354" s="6"/>
     </row>
     <row r="355">
       <c r="G355" s="5"/>
+      <c r="H355" s="6"/>
     </row>
     <row r="356">
       <c r="G356" s="5"/>
+      <c r="H356" s="6"/>
     </row>
     <row r="357">
       <c r="G357" s="5"/>
+      <c r="H357" s="6"/>
     </row>
     <row r="358">
       <c r="G358" s="5"/>
+      <c r="H358" s="6"/>
     </row>
     <row r="359">
       <c r="G359" s="5"/>
+      <c r="H359" s="6"/>
     </row>
     <row r="360">
       <c r="G360" s="5"/>
+      <c r="H360" s="6"/>
     </row>
     <row r="361">
       <c r="G361" s="5"/>
+      <c r="H361" s="6"/>
     </row>
     <row r="362">
       <c r="G362" s="5"/>
+      <c r="H362" s="6"/>
     </row>
     <row r="363">
       <c r="G363" s="5"/>
+      <c r="H363" s="6"/>
     </row>
     <row r="364">
       <c r="G364" s="5"/>
+      <c r="H364" s="6"/>
     </row>
     <row r="365">
       <c r="G365" s="5"/>
+      <c r="H365" s="6"/>
     </row>
     <row r="366">
       <c r="G366" s="5"/>
+      <c r="H366" s="6"/>
     </row>
     <row r="367">
       <c r="G367" s="5"/>
+      <c r="H367" s="6"/>
     </row>
     <row r="368">
       <c r="G368" s="5"/>
+      <c r="H368" s="6"/>
     </row>
     <row r="369">
       <c r="G369" s="5"/>
+      <c r="H369" s="6"/>
     </row>
     <row r="370">
       <c r="G370" s="5"/>
+      <c r="H370" s="6"/>
     </row>
     <row r="371">
       <c r="G371" s="5"/>
+      <c r="H371" s="6"/>
     </row>
     <row r="372">
       <c r="G372" s="5"/>
+      <c r="H372" s="6"/>
     </row>
     <row r="373">
       <c r="G373" s="5"/>
+      <c r="H373" s="6"/>
     </row>
     <row r="374">
       <c r="G374" s="5"/>
+      <c r="H374" s="6"/>
     </row>
     <row r="375">
       <c r="G375" s="5"/>
+      <c r="H375" s="6"/>
     </row>
     <row r="376">
       <c r="G376" s="5"/>
+      <c r="H376" s="6"/>
     </row>
     <row r="377">
       <c r="G377" s="5"/>
+      <c r="H377" s="6"/>
     </row>
     <row r="378">
       <c r="G378" s="5"/>
+      <c r="H378" s="6"/>
     </row>
     <row r="379">
       <c r="G379" s="5"/>
+      <c r="H379" s="6"/>
     </row>
     <row r="380">
       <c r="G380" s="5"/>
+      <c r="H380" s="6"/>
     </row>
     <row r="381">
       <c r="G381" s="5"/>
+      <c r="H381" s="6"/>
     </row>
     <row r="382">
       <c r="G382" s="5"/>
+      <c r="H382" s="6"/>
     </row>
     <row r="383">
       <c r="G383" s="5"/>
+      <c r="H383" s="6"/>
     </row>
     <row r="384">
       <c r="G384" s="5"/>
+      <c r="H384" s="6"/>
     </row>
     <row r="385">
       <c r="G385" s="5"/>
+      <c r="H385" s="6"/>
     </row>
     <row r="386">
       <c r="G386" s="5"/>
+      <c r="H386" s="6"/>
     </row>
     <row r="387">
       <c r="G387" s="5"/>
+      <c r="H387" s="6"/>
     </row>
     <row r="388">
       <c r="G388" s="5"/>
+      <c r="H388" s="6"/>
     </row>
     <row r="389">
       <c r="G389" s="5"/>
+      <c r="H389" s="6"/>
     </row>
     <row r="390">
       <c r="G390" s="5"/>
+      <c r="H390" s="6"/>
     </row>
     <row r="391">
       <c r="G391" s="5"/>
+      <c r="H391" s="6"/>
     </row>
     <row r="392">
       <c r="G392" s="5"/>
+      <c r="H392" s="6"/>
     </row>
     <row r="393">
       <c r="G393" s="5"/>
+      <c r="H393" s="6"/>
     </row>
     <row r="394">
       <c r="G394" s="5"/>
+      <c r="H394" s="6"/>
     </row>
     <row r="395">
       <c r="G395" s="5"/>
+      <c r="H395" s="6"/>
     </row>
     <row r="396">
       <c r="G396" s="5"/>
+      <c r="H396" s="6"/>
     </row>
     <row r="397">
       <c r="G397" s="5"/>
+      <c r="H397" s="6"/>
     </row>
     <row r="398">
       <c r="G398" s="5"/>
+      <c r="H398" s="6"/>
     </row>
     <row r="399">
       <c r="G399" s="5"/>
+      <c r="H399" s="6"/>
     </row>
     <row r="400">
       <c r="G400" s="5"/>
+      <c r="H400" s="6"/>
     </row>
     <row r="401">
       <c r="G401" s="5"/>
+      <c r="H401" s="6"/>
     </row>
     <row r="402">
       <c r="G402" s="5"/>
+      <c r="H402" s="6"/>
     </row>
     <row r="403">
       <c r="G403" s="5"/>
+      <c r="H403" s="6"/>
     </row>
     <row r="404">
       <c r="G404" s="5"/>
+      <c r="H404" s="6"/>
     </row>
     <row r="405">
       <c r="G405" s="5"/>
+      <c r="H405" s="6"/>
     </row>
     <row r="406">
       <c r="G406" s="5"/>
+      <c r="H406" s="6"/>
     </row>
     <row r="407">
       <c r="G407" s="5"/>
+      <c r="H407" s="6"/>
     </row>
     <row r="408">
       <c r="G408" s="5"/>
+      <c r="H408" s="6"/>
     </row>
     <row r="409">
       <c r="G409" s="5"/>
+      <c r="H409" s="6"/>
     </row>
     <row r="410">
       <c r="G410" s="5"/>
+      <c r="H410" s="6"/>
     </row>
     <row r="411">
       <c r="G411" s="5"/>
+      <c r="H411" s="6"/>
     </row>
     <row r="412">
       <c r="G412" s="5"/>
+      <c r="H412" s="6"/>
     </row>
     <row r="413">
       <c r="G413" s="5"/>
+      <c r="H413" s="6"/>
     </row>
     <row r="414">
       <c r="G414" s="5"/>
+      <c r="H414" s="6"/>
     </row>
     <row r="415">
       <c r="G415" s="5"/>
+      <c r="H415" s="6"/>
     </row>
     <row r="416">
       <c r="G416" s="5"/>
+      <c r="H416" s="6"/>
     </row>
     <row r="417">
       <c r="G417" s="5"/>
+      <c r="H417" s="6"/>
     </row>
     <row r="418">
       <c r="G418" s="5"/>
+      <c r="H418" s="6"/>
     </row>
     <row r="419">
       <c r="G419" s="5"/>
+      <c r="H419" s="6"/>
     </row>
     <row r="420">
       <c r="G420" s="5"/>
+      <c r="H420" s="6"/>
     </row>
     <row r="421">
       <c r="G421" s="5"/>
+      <c r="H421" s="6"/>
     </row>
     <row r="422">
       <c r="G422" s="5"/>
+      <c r="H422" s="6"/>
     </row>
     <row r="423">
       <c r="G423" s="5"/>
+      <c r="H423" s="6"/>
     </row>
     <row r="424">
       <c r="G424" s="5"/>
+      <c r="H424" s="6"/>
     </row>
     <row r="425">
       <c r="G425" s="5"/>
+      <c r="H425" s="6"/>
     </row>
     <row r="426">
       <c r="G426" s="5"/>
+      <c r="H426" s="6"/>
     </row>
     <row r="427">
       <c r="G427" s="5"/>
+      <c r="H427" s="6"/>
     </row>
     <row r="428">
       <c r="G428" s="5"/>
+      <c r="H428" s="6"/>
     </row>
     <row r="429">
       <c r="G429" s="5"/>
+      <c r="H429" s="6"/>
     </row>
     <row r="430">
       <c r="G430" s="5"/>
+      <c r="H430" s="6"/>
     </row>
     <row r="431">
       <c r="G431" s="5"/>
+      <c r="H431" s="6"/>
     </row>
     <row r="432">
       <c r="G432" s="5"/>
+      <c r="H432" s="6"/>
     </row>
     <row r="433">
       <c r="G433" s="5"/>
+      <c r="H433" s="6"/>
     </row>
     <row r="434">
       <c r="G434" s="5"/>
+      <c r="H434" s="6"/>
     </row>
     <row r="435">
       <c r="G435" s="5"/>
+      <c r="H435" s="6"/>
     </row>
     <row r="436">
       <c r="G436" s="5"/>
+      <c r="H436" s="6"/>
     </row>
     <row r="437">
       <c r="G437" s="5"/>
+      <c r="H437" s="6"/>
     </row>
     <row r="438">
       <c r="G438" s="5"/>
+      <c r="H438" s="6"/>
     </row>
     <row r="439">
       <c r="G439" s="5"/>
+      <c r="H439" s="6"/>
     </row>
     <row r="440">
       <c r="G440" s="5"/>
+      <c r="H440" s="6"/>
     </row>
     <row r="441">
       <c r="G441" s="5"/>
+      <c r="H441" s="6"/>
     </row>
     <row r="442">
       <c r="G442" s="5"/>
+      <c r="H442" s="6"/>
     </row>
     <row r="443">
       <c r="G443" s="5"/>
+      <c r="H443" s="6"/>
     </row>
     <row r="444">
       <c r="G444" s="5"/>
+      <c r="H444" s="6"/>
     </row>
     <row r="445">
       <c r="G445" s="5"/>
+      <c r="H445" s="6"/>
     </row>
     <row r="446">
       <c r="G446" s="5"/>
+      <c r="H446" s="6"/>
     </row>
     <row r="447">
       <c r="G447" s="5"/>
+      <c r="H447" s="6"/>
     </row>
     <row r="448">
       <c r="G448" s="5"/>
+      <c r="H448" s="6"/>
     </row>
     <row r="449">
       <c r="G449" s="5"/>
+      <c r="H449" s="6"/>
     </row>
     <row r="450">
       <c r="G450" s="5"/>
+      <c r="H450" s="6"/>
     </row>
     <row r="451">
       <c r="G451" s="5"/>
+      <c r="H451" s="6"/>
     </row>
     <row r="452">
       <c r="G452" s="5"/>
+      <c r="H452" s="6"/>
     </row>
     <row r="453">
       <c r="G453" s="5"/>
+      <c r="H453" s="6"/>
     </row>
     <row r="454">
       <c r="G454" s="5"/>
+      <c r="H454" s="6"/>
     </row>
     <row r="455">
       <c r="G455" s="5"/>
+      <c r="H455" s="6"/>
     </row>
     <row r="456">
       <c r="G456" s="5"/>
+      <c r="H456" s="6"/>
     </row>
     <row r="457">
       <c r="G457" s="5"/>
+      <c r="H457" s="6"/>
     </row>
     <row r="458">
       <c r="G458" s="5"/>
+      <c r="H458" s="6"/>
     </row>
     <row r="459">
       <c r="G459" s="5"/>
+      <c r="H459" s="6"/>
     </row>
     <row r="460">
       <c r="G460" s="5"/>
+      <c r="H460" s="6"/>
     </row>
     <row r="461">
       <c r="G461" s="5"/>
+      <c r="H461" s="6"/>
     </row>
     <row r="462">
       <c r="G462" s="5"/>
+      <c r="H462" s="6"/>
     </row>
     <row r="463">
       <c r="G463" s="5"/>
+      <c r="H463" s="6"/>
     </row>
     <row r="464">
       <c r="G464" s="5"/>
+      <c r="H464" s="6"/>
     </row>
     <row r="465">
       <c r="G465" s="5"/>
+      <c r="H465" s="6"/>
     </row>
     <row r="466">
       <c r="G466" s="5"/>
+      <c r="H466" s="6"/>
     </row>
     <row r="467">
       <c r="G467" s="5"/>
+      <c r="H467" s="6"/>
     </row>
     <row r="468">
       <c r="G468" s="5"/>
+      <c r="H468" s="6"/>
     </row>
     <row r="469">
       <c r="G469" s="5"/>
+      <c r="H469" s="6"/>
     </row>
     <row r="470">
       <c r="G470" s="5"/>
+      <c r="H470" s="6"/>
     </row>
     <row r="471">
       <c r="G471" s="5"/>
+      <c r="H471" s="6"/>
     </row>
     <row r="472">
       <c r="G472" s="5"/>
+      <c r="H472" s="6"/>
     </row>
     <row r="473">
       <c r="G473" s="5"/>
+      <c r="H473" s="6"/>
     </row>
     <row r="474">
       <c r="G474" s="5"/>
+      <c r="H474" s="6"/>
     </row>
     <row r="475">
       <c r="G475" s="5"/>
+      <c r="H475" s="6"/>
     </row>
     <row r="476">
       <c r="G476" s="5"/>
+      <c r="H476" s="6"/>
     </row>
     <row r="477">
       <c r="G477" s="5"/>
+      <c r="H477" s="6"/>
     </row>
     <row r="478">
       <c r="G478" s="5"/>
+      <c r="H478" s="6"/>
     </row>
     <row r="479">
       <c r="G479" s="5"/>
+      <c r="H479" s="6"/>
     </row>
     <row r="480">
       <c r="G480" s="5"/>
+      <c r="H480" s="6"/>
     </row>
     <row r="481">
       <c r="G481" s="5"/>
+      <c r="H481" s="6"/>
     </row>
     <row r="482">
       <c r="G482" s="5"/>
+      <c r="H482" s="6"/>
     </row>
     <row r="483">
       <c r="G483" s="5"/>
+      <c r="H483" s="6"/>
     </row>
     <row r="484">
       <c r="G484" s="5"/>
+      <c r="H484" s="6"/>
     </row>
     <row r="485">
       <c r="G485" s="5"/>
+      <c r="H485" s="6"/>
     </row>
     <row r="486">
       <c r="G486" s="5"/>
+      <c r="H486" s="6"/>
     </row>
     <row r="487">
       <c r="G487" s="5"/>
+      <c r="H487" s="6"/>
     </row>
     <row r="488">
       <c r="G488" s="5"/>
+      <c r="H488" s="6"/>
     </row>
     <row r="489">
       <c r="G489" s="5"/>
+      <c r="H489" s="6"/>
     </row>
     <row r="490">
       <c r="G490" s="5"/>
+      <c r="H490" s="6"/>
     </row>
     <row r="491">
       <c r="G491" s="5"/>
+      <c r="H491" s="6"/>
     </row>
     <row r="492">
       <c r="G492" s="5"/>
+      <c r="H492" s="6"/>
     </row>
     <row r="493">
       <c r="G493" s="5"/>
+      <c r="H493" s="6"/>
     </row>
     <row r="494">
       <c r="G494" s="5"/>
+      <c r="H494" s="6"/>
     </row>
     <row r="495">
       <c r="G495" s="5"/>
+      <c r="H495" s="6"/>
     </row>
     <row r="496">
       <c r="G496" s="5"/>
+      <c r="H496" s="6"/>
     </row>
     <row r="497">
       <c r="G497" s="5"/>
+      <c r="H497" s="6"/>
     </row>
     <row r="498">
       <c r="G498" s="5"/>
+      <c r="H498" s="6"/>
     </row>
     <row r="499">
       <c r="G499" s="5"/>
+      <c r="H499" s="6"/>
     </row>
     <row r="500">
       <c r="G500" s="5"/>
+      <c r="H500" s="6"/>
     </row>
     <row r="501">
       <c r="G501" s="5"/>
+      <c r="H501" s="6"/>
     </row>
     <row r="502">
       <c r="G502" s="5"/>
+      <c r="H502" s="6"/>
     </row>
     <row r="503">
       <c r="G503" s="5"/>
+      <c r="H503" s="6"/>
     </row>
     <row r="504">
       <c r="G504" s="5"/>
+      <c r="H504" s="6"/>
     </row>
     <row r="505">
       <c r="G505" s="5"/>
+      <c r="H505" s="6"/>
     </row>
     <row r="506">
       <c r="G506" s="5"/>
+      <c r="H506" s="6"/>
     </row>
     <row r="507">
       <c r="G507" s="5"/>
+      <c r="H507" s="6"/>
     </row>
     <row r="508">
       <c r="G508" s="5"/>
+      <c r="H508" s="6"/>
     </row>
     <row r="509">
       <c r="G509" s="5"/>
+      <c r="H509" s="6"/>
     </row>
     <row r="510">
       <c r="G510" s="5"/>
+      <c r="H510" s="6"/>
     </row>
     <row r="511">
       <c r="G511" s="5"/>
+      <c r="H511" s="6"/>
     </row>
     <row r="512">
       <c r="G512" s="5"/>
+      <c r="H512" s="6"/>
     </row>
     <row r="513">
       <c r="G513" s="5"/>
+      <c r="H513" s="6"/>
     </row>
     <row r="514">
       <c r="G514" s="5"/>
+      <c r="H514" s="6"/>
     </row>
     <row r="515">
       <c r="G515" s="5"/>
+      <c r="H515" s="6"/>
     </row>
     <row r="516">
       <c r="G516" s="5"/>
+      <c r="H516" s="6"/>
     </row>
     <row r="517">
       <c r="G517" s="5"/>
+      <c r="H517" s="6"/>
     </row>
     <row r="518">
       <c r="G518" s="5"/>
+      <c r="H518" s="6"/>
     </row>
     <row r="519">
       <c r="G519" s="5"/>
+      <c r="H519" s="6"/>
     </row>
     <row r="520">
       <c r="G520" s="5"/>
+      <c r="H520" s="6"/>
     </row>
     <row r="521">
       <c r="G521" s="5"/>
+      <c r="H521" s="6"/>
     </row>
     <row r="522">
       <c r="G522" s="5"/>
+      <c r="H522" s="6"/>
     </row>
     <row r="523">
       <c r="G523" s="5"/>
+      <c r="H523" s="6"/>
     </row>
     <row r="524">
       <c r="G524" s="5"/>
+      <c r="H524" s="6"/>
     </row>
     <row r="525">
       <c r="G525" s="5"/>
+      <c r="H525" s="6"/>
     </row>
     <row r="526">
       <c r="G526" s="5"/>
+      <c r="H526" s="6"/>
     </row>
     <row r="527">
       <c r="G527" s="5"/>
+      <c r="H527" s="6"/>
     </row>
     <row r="528">
       <c r="G528" s="5"/>
+      <c r="H528" s="6"/>
     </row>
     <row r="529">
       <c r="G529" s="5"/>
+      <c r="H529" s="6"/>
     </row>
     <row r="530">
       <c r="G530" s="5"/>
+      <c r="H530" s="6"/>
     </row>
     <row r="531">
       <c r="G531" s="5"/>
+      <c r="H531" s="6"/>
     </row>
     <row r="532">
       <c r="G532" s="5"/>
+      <c r="H532" s="6"/>
     </row>
     <row r="533">
       <c r="G533" s="5"/>
+      <c r="H533" s="6"/>
     </row>
     <row r="534">
       <c r="G534" s="5"/>
+      <c r="H534" s="6"/>
     </row>
     <row r="535">
       <c r="G535" s="5"/>
+      <c r="H535" s="6"/>
     </row>
     <row r="536">
       <c r="G536" s="5"/>
+      <c r="H536" s="6"/>
     </row>
     <row r="537">
       <c r="G537" s="5"/>
+      <c r="H537" s="6"/>
     </row>
     <row r="538">
       <c r="G538" s="5"/>
+      <c r="H538" s="6"/>
     </row>
     <row r="539">
       <c r="G539" s="5"/>
+      <c r="H539" s="6"/>
     </row>
     <row r="540">
       <c r="G540" s="5"/>
+      <c r="H540" s="6"/>
     </row>
     <row r="541">
       <c r="G541" s="5"/>
+      <c r="H541" s="6"/>
     </row>
     <row r="542">
       <c r="G542" s="5"/>
+      <c r="H542" s="6"/>
     </row>
     <row r="543">
       <c r="G543" s="5"/>
+      <c r="H543" s="6"/>
     </row>
     <row r="544">
       <c r="G544" s="5"/>
+      <c r="H544" s="6"/>
     </row>
     <row r="545">
       <c r="G545" s="5"/>
+      <c r="H545" s="6"/>
     </row>
     <row r="546">
       <c r="G546" s="5"/>
+      <c r="H546" s="6"/>
     </row>
     <row r="547">
       <c r="G547" s="5"/>
+      <c r="H547" s="6"/>
     </row>
     <row r="548">
       <c r="G548" s="5"/>
+      <c r="H548" s="6"/>
     </row>
     <row r="549">
       <c r="G549" s="5"/>
+      <c r="H549" s="6"/>
     </row>
     <row r="550">
       <c r="G550" s="5"/>
+      <c r="H550" s="6"/>
     </row>
     <row r="551">
       <c r="G551" s="5"/>
+      <c r="H551" s="6"/>
     </row>
     <row r="552">
       <c r="G552" s="5"/>
+      <c r="H552" s="6"/>
     </row>
     <row r="553">
       <c r="G553" s="5"/>
+      <c r="H553" s="6"/>
     </row>
     <row r="554">
       <c r="G554" s="5"/>
+      <c r="H554" s="6"/>
     </row>
     <row r="555">
       <c r="G555" s="5"/>
+      <c r="H555" s="6"/>
     </row>
     <row r="556">
       <c r="G556" s="5"/>
+      <c r="H556" s="6"/>
     </row>
     <row r="557">
       <c r="G557" s="5"/>
+      <c r="H557" s="6"/>
     </row>
     <row r="558">
       <c r="G558" s="5"/>
+      <c r="H558" s="6"/>
     </row>
     <row r="559">
       <c r="G559" s="5"/>
+      <c r="H559" s="6"/>
     </row>
     <row r="560">
       <c r="G560" s="5"/>
+      <c r="H560" s="6"/>
     </row>
     <row r="561">
       <c r="G561" s="5"/>
+      <c r="H561" s="6"/>
     </row>
     <row r="562">
       <c r="G562" s="5"/>
+      <c r="H562" s="6"/>
     </row>
     <row r="563">
       <c r="G563" s="5"/>
+      <c r="H563" s="6"/>
     </row>
     <row r="564">
       <c r="G564" s="5"/>
+      <c r="H564" s="6"/>
     </row>
     <row r="565">
       <c r="G565" s="5"/>
+      <c r="H565" s="6"/>
     </row>
     <row r="566">
       <c r="G566" s="5"/>
+      <c r="H566" s="6"/>
     </row>
     <row r="567">
       <c r="G567" s="5"/>
+      <c r="H567" s="6"/>
     </row>
     <row r="568">
       <c r="G568" s="5"/>
+      <c r="H568" s="6"/>
     </row>
     <row r="569">
       <c r="G569" s="5"/>
+      <c r="H569" s="6"/>
     </row>
     <row r="570">
       <c r="G570" s="5"/>
+      <c r="H570" s="6"/>
     </row>
     <row r="571">
       <c r="G571" s="5"/>
+      <c r="H571" s="6"/>
     </row>
     <row r="572">
       <c r="G572" s="5"/>
+      <c r="H572" s="6"/>
     </row>
     <row r="573">
       <c r="G573" s="5"/>
+      <c r="H573" s="6"/>
     </row>
     <row r="574">
       <c r="G574" s="5"/>
+      <c r="H574" s="6"/>
     </row>
     <row r="575">
       <c r="G575" s="5"/>
+      <c r="H575" s="6"/>
     </row>
     <row r="576">
       <c r="G576" s="5"/>
+      <c r="H576" s="6"/>
     </row>
     <row r="577">
       <c r="G577" s="5"/>
+      <c r="H577" s="6"/>
     </row>
     <row r="578">
       <c r="G578" s="5"/>
+      <c r="H578" s="6"/>
     </row>
     <row r="579">
       <c r="G579" s="5"/>
+      <c r="H579" s="6"/>
     </row>
     <row r="580">
       <c r="G580" s="5"/>
+      <c r="H580" s="6"/>
     </row>
     <row r="581">
       <c r="G581" s="5"/>
+      <c r="H581" s="6"/>
     </row>
     <row r="582">
       <c r="G582" s="5"/>
+      <c r="H582" s="6"/>
     </row>
     <row r="583">
       <c r="G583" s="5"/>
+      <c r="H583" s="6"/>
     </row>
     <row r="584">
       <c r="G584" s="5"/>
+      <c r="H584" s="6"/>
     </row>
     <row r="585">
       <c r="G585" s="5"/>
+      <c r="H585" s="6"/>
     </row>
     <row r="586">
       <c r="G586" s="5"/>
+      <c r="H586" s="6"/>
     </row>
     <row r="587">
       <c r="G587" s="5"/>
+      <c r="H587" s="6"/>
     </row>
     <row r="588">
       <c r="G588" s="5"/>
+      <c r="H588" s="6"/>
     </row>
     <row r="589">
       <c r="G589" s="5"/>
+      <c r="H589" s="6"/>
     </row>
     <row r="590">
       <c r="G590" s="5"/>
+      <c r="H590" s="6"/>
     </row>
     <row r="591">
       <c r="G591" s="5"/>
+      <c r="H591" s="6"/>
     </row>
     <row r="592">
       <c r="G592" s="5"/>
+      <c r="H592" s="6"/>
     </row>
     <row r="593">
       <c r="G593" s="5"/>
+      <c r="H593" s="6"/>
     </row>
     <row r="594">
       <c r="G594" s="5"/>
+      <c r="H594" s="6"/>
     </row>
     <row r="595">
       <c r="G595" s="5"/>
+      <c r="H595" s="6"/>
     </row>
     <row r="596">
       <c r="G596" s="5"/>
+      <c r="H596" s="6"/>
     </row>
     <row r="597">
       <c r="G597" s="5"/>
+      <c r="H597" s="6"/>
     </row>
     <row r="598">
       <c r="G598" s="5"/>
+      <c r="H598" s="6"/>
     </row>
     <row r="599">
       <c r="G599" s="5"/>
+      <c r="H599" s="6"/>
     </row>
     <row r="600">
       <c r="G600" s="5"/>
+      <c r="H600" s="6"/>
     </row>
     <row r="601">
       <c r="G601" s="5"/>
+      <c r="H601" s="6"/>
     </row>
     <row r="602">
       <c r="G602" s="5"/>
+      <c r="H602" s="6"/>
     </row>
     <row r="603">
       <c r="G603" s="5"/>
+      <c r="H603" s="6"/>
     </row>
     <row r="604">
       <c r="G604" s="5"/>
+      <c r="H604" s="6"/>
     </row>
     <row r="605">
       <c r="G605" s="5"/>
+      <c r="H605" s="6"/>
     </row>
     <row r="606">
       <c r="G606" s="5"/>
+      <c r="H606" s="6"/>
     </row>
     <row r="607">
       <c r="G607" s="5"/>
+      <c r="H607" s="6"/>
     </row>
     <row r="608">
       <c r="G608" s="5"/>
+      <c r="H608" s="6"/>
     </row>
     <row r="609">
       <c r="G609" s="5"/>
+      <c r="H609" s="6"/>
     </row>
     <row r="610">
       <c r="G610" s="5"/>
+      <c r="H610" s="6"/>
     </row>
     <row r="611">
       <c r="G611" s="5"/>
+      <c r="H611" s="6"/>
     </row>
     <row r="612">
       <c r="G612" s="5"/>
+      <c r="H612" s="6"/>
     </row>
     <row r="613">
       <c r="G613" s="5"/>
+      <c r="H613" s="6"/>
     </row>
     <row r="614">
       <c r="G614" s="5"/>
+      <c r="H614" s="6"/>
     </row>
     <row r="615">
       <c r="G615" s="5"/>
+      <c r="H615" s="6"/>
     </row>
     <row r="616">
       <c r="G616" s="5"/>
+      <c r="H616" s="6"/>
     </row>
     <row r="617">
       <c r="G617" s="5"/>
+      <c r="H617" s="6"/>
     </row>
     <row r="618">
       <c r="G618" s="5"/>
+      <c r="H618" s="6"/>
     </row>
     <row r="619">
       <c r="G619" s="5"/>
+      <c r="H619" s="6"/>
     </row>
     <row r="620">
       <c r="G620" s="5"/>
+      <c r="H620" s="6"/>
     </row>
     <row r="621">
       <c r="G621" s="5"/>
+      <c r="H621" s="6"/>
     </row>
     <row r="622">
       <c r="G622" s="5"/>
+      <c r="H622" s="6"/>
     </row>
     <row r="623">
       <c r="G623" s="5"/>
+      <c r="H623" s="6"/>
     </row>
     <row r="624">
       <c r="G624" s="5"/>
+      <c r="H624" s="6"/>
     </row>
     <row r="625">
       <c r="G625" s="5"/>
+      <c r="H625" s="6"/>
     </row>
     <row r="626">
       <c r="G626" s="5"/>
+      <c r="H626" s="6"/>
     </row>
     <row r="627">
       <c r="G627" s="5"/>
+      <c r="H627" s="6"/>
     </row>
     <row r="628">
       <c r="G628" s="5"/>
+      <c r="H628" s="6"/>
     </row>
     <row r="629">
       <c r="G629" s="5"/>
+      <c r="H629" s="6"/>
     </row>
     <row r="630">
       <c r="G630" s="5"/>
+      <c r="H630" s="6"/>
     </row>
     <row r="631">
       <c r="G631" s="5"/>
+      <c r="H631" s="6"/>
     </row>
     <row r="632">
       <c r="G632" s="5"/>
+      <c r="H632" s="6"/>
     </row>
     <row r="633">
       <c r="G633" s="5"/>
+      <c r="H633" s="6"/>
     </row>
     <row r="634">
       <c r="G634" s="5"/>
+      <c r="H634" s="6"/>
     </row>
     <row r="635">
       <c r="G635" s="5"/>
+      <c r="H635" s="6"/>
     </row>
     <row r="636">
       <c r="G636" s="5"/>
+      <c r="H636" s="6"/>
     </row>
     <row r="637">
       <c r="G637" s="5"/>
+      <c r="H637" s="6"/>
     </row>
     <row r="638">
       <c r="G638" s="5"/>
+      <c r="H638" s="6"/>
     </row>
     <row r="639">
       <c r="G639" s="5"/>
+      <c r="H639" s="6"/>
     </row>
     <row r="640">
       <c r="G640" s="5"/>
+      <c r="H640" s="6"/>
     </row>
     <row r="641">
       <c r="G641" s="5"/>
+      <c r="H641" s="6"/>
     </row>
     <row r="642">
       <c r="G642" s="5"/>
+      <c r="H642" s="6"/>
     </row>
     <row r="643">
       <c r="G643" s="5"/>
+      <c r="H643" s="6"/>
     </row>
     <row r="644">
       <c r="G644" s="5"/>
+      <c r="H644" s="6"/>
     </row>
     <row r="645">
       <c r="G645" s="5"/>
+      <c r="H645" s="6"/>
     </row>
     <row r="646">
       <c r="G646" s="5"/>
+      <c r="H646" s="6"/>
     </row>
     <row r="647">
       <c r="G647" s="5"/>
+      <c r="H647" s="6"/>
     </row>
     <row r="648">
       <c r="G648" s="5"/>
+      <c r="H648" s="6"/>
     </row>
     <row r="649">
       <c r="G649" s="5"/>
+      <c r="H649" s="6"/>
     </row>
     <row r="650">
       <c r="G650" s="5"/>
+      <c r="H650" s="6"/>
     </row>
     <row r="651">
       <c r="G651" s="5"/>
+      <c r="H651" s="6"/>
     </row>
     <row r="652">
       <c r="G652" s="5"/>
+      <c r="H652" s="6"/>
     </row>
     <row r="653">
       <c r="G653" s="5"/>
+      <c r="H653" s="6"/>
     </row>
     <row r="654">
       <c r="G654" s="5"/>
+      <c r="H654" s="6"/>
     </row>
     <row r="655">
       <c r="G655" s="5"/>
+      <c r="H655" s="6"/>
     </row>
     <row r="656">
       <c r="G656" s="5"/>
+      <c r="H656" s="6"/>
     </row>
     <row r="657">
       <c r="G657" s="5"/>
+      <c r="H657" s="6"/>
     </row>
     <row r="658">
       <c r="G658" s="5"/>
+      <c r="H658" s="6"/>
     </row>
     <row r="659">
       <c r="G659" s="5"/>
+      <c r="H659" s="6"/>
     </row>
     <row r="660">
       <c r="G660" s="5"/>
+      <c r="H660" s="6"/>
     </row>
     <row r="661">
       <c r="G661" s="5"/>
+      <c r="H661" s="6"/>
     </row>
     <row r="662">
       <c r="G662" s="5"/>
+      <c r="H662" s="6"/>
     </row>
     <row r="663">
       <c r="G663" s="5"/>
+      <c r="H663" s="6"/>
     </row>
     <row r="664">
       <c r="G664" s="5"/>
+      <c r="H664" s="6"/>
     </row>
     <row r="665">
       <c r="G665" s="5"/>
+      <c r="H665" s="6"/>
     </row>
     <row r="666">
       <c r="G666" s="5"/>
+      <c r="H666" s="6"/>
     </row>
     <row r="667">
       <c r="G667" s="5"/>
+      <c r="H667" s="6"/>
     </row>
     <row r="668">
       <c r="G668" s="5"/>
+      <c r="H668" s="6"/>
     </row>
     <row r="669">
       <c r="G669" s="5"/>
+      <c r="H669" s="6"/>
     </row>
     <row r="670">
       <c r="G670" s="5"/>
+      <c r="H670" s="6"/>
     </row>
     <row r="671">
       <c r="G671" s="5"/>
+      <c r="H671" s="6"/>
     </row>
     <row r="672">
       <c r="G672" s="5"/>
+      <c r="H672" s="6"/>
     </row>
     <row r="673">
       <c r="G673" s="5"/>
+      <c r="H673" s="6"/>
     </row>
     <row r="674">
       <c r="G674" s="5"/>
+      <c r="H674" s="6"/>
     </row>
     <row r="675">
       <c r="G675" s="5"/>
+      <c r="H675" s="6"/>
     </row>
     <row r="676">
       <c r="G676" s="5"/>
+      <c r="H676" s="6"/>
     </row>
     <row r="677">
       <c r="G677" s="5"/>
+      <c r="H677" s="6"/>
     </row>
     <row r="678">
       <c r="G678" s="5"/>
+      <c r="H678" s="6"/>
     </row>
     <row r="679">
       <c r="G679" s="5"/>
+      <c r="H679" s="6"/>
     </row>
     <row r="680">
       <c r="G680" s="5"/>
+      <c r="H680" s="6"/>
     </row>
     <row r="681">
       <c r="G681" s="5"/>
+      <c r="H681" s="6"/>
     </row>
     <row r="682">
       <c r="G682" s="5"/>
+      <c r="H682" s="6"/>
     </row>
     <row r="683">
       <c r="G683" s="5"/>
+      <c r="H683" s="6"/>
     </row>
     <row r="684">
       <c r="G684" s="5"/>
+      <c r="H684" s="6"/>
     </row>
     <row r="685">
       <c r="G685" s="5"/>
+      <c r="H685" s="6"/>
     </row>
     <row r="686">
       <c r="G686" s="5"/>
+      <c r="H686" s="6"/>
     </row>
     <row r="687">
       <c r="G687" s="5"/>
+      <c r="H687" s="6"/>
     </row>
     <row r="688">
       <c r="G688" s="5"/>
+      <c r="H688" s="6"/>
     </row>
     <row r="689">
       <c r="G689" s="5"/>
+      <c r="H689" s="6"/>
     </row>
     <row r="690">
       <c r="G690" s="5"/>
+      <c r="H690" s="6"/>
     </row>
     <row r="691">
       <c r="G691" s="5"/>
+      <c r="H691" s="6"/>
     </row>
     <row r="692">
       <c r="G692" s="5"/>
+      <c r="H692" s="6"/>
     </row>
     <row r="693">
       <c r="G693" s="5"/>
+      <c r="H693" s="6"/>
     </row>
     <row r="694">
       <c r="G694" s="5"/>
+      <c r="H694" s="6"/>
     </row>
     <row r="695">
       <c r="G695" s="5"/>
+      <c r="H695" s="6"/>
     </row>
     <row r="696">
       <c r="G696" s="5"/>
+      <c r="H696" s="6"/>
     </row>
     <row r="697">
       <c r="G697" s="5"/>
+      <c r="H697" s="6"/>
     </row>
     <row r="698">
       <c r="G698" s="5"/>
+      <c r="H698" s="6"/>
     </row>
     <row r="699">
       <c r="G699" s="5"/>
+      <c r="H699" s="6"/>
     </row>
     <row r="700">
       <c r="G700" s="5"/>
+      <c r="H700" s="6"/>
     </row>
     <row r="701">
       <c r="G701" s="5"/>
+      <c r="H701" s="6"/>
     </row>
     <row r="702">
       <c r="G702" s="5"/>
+      <c r="H702" s="6"/>
     </row>
     <row r="703">
       <c r="G703" s="5"/>
+      <c r="H703" s="6"/>
     </row>
     <row r="704">
       <c r="G704" s="5"/>
+      <c r="H704" s="6"/>
     </row>
     <row r="705">
       <c r="G705" s="5"/>
+      <c r="H705" s="6"/>
     </row>
     <row r="706">
       <c r="G706" s="5"/>
+      <c r="H706" s="6"/>
     </row>
     <row r="707">
       <c r="G707" s="5"/>
+      <c r="H707" s="6"/>
     </row>
     <row r="708">
       <c r="G708" s="5"/>
+      <c r="H708" s="6"/>
     </row>
     <row r="709">
       <c r="G709" s="5"/>
+      <c r="H709" s="6"/>
     </row>
     <row r="710">
       <c r="G710" s="5"/>
+      <c r="H710" s="6"/>
     </row>
     <row r="711">
       <c r="G711" s="5"/>
+      <c r="H711" s="6"/>
     </row>
     <row r="712">
       <c r="G712" s="5"/>
+      <c r="H712" s="6"/>
     </row>
     <row r="713">
       <c r="G713" s="5"/>
+      <c r="H713" s="6"/>
     </row>
     <row r="714">
       <c r="G714" s="5"/>
+      <c r="H714" s="6"/>
     </row>
     <row r="715">
       <c r="G715" s="5"/>
+      <c r="H715" s="6"/>
     </row>
     <row r="716">
       <c r="G716" s="5"/>
+      <c r="H716" s="6"/>
     </row>
     <row r="717">
       <c r="G717" s="5"/>
+      <c r="H717" s="6"/>
     </row>
     <row r="718">
       <c r="G718" s="5"/>
+      <c r="H718" s="6"/>
     </row>
     <row r="719">
       <c r="G719" s="5"/>
+      <c r="H719" s="6"/>
     </row>
     <row r="720">
       <c r="G720" s="5"/>
+      <c r="H720" s="6"/>
     </row>
     <row r="721">
       <c r="G721" s="5"/>
+      <c r="H721" s="6"/>
     </row>
     <row r="722">
       <c r="G722" s="5"/>
+      <c r="H722" s="6"/>
     </row>
     <row r="723">
       <c r="G723" s="5"/>
+      <c r="H723" s="6"/>
     </row>
     <row r="724">
       <c r="G724" s="5"/>
+      <c r="H724" s="6"/>
     </row>
     <row r="725">
       <c r="G725" s="5"/>
+      <c r="H725" s="6"/>
     </row>
     <row r="726">
       <c r="G726" s="5"/>
+      <c r="H726" s="6"/>
     </row>
     <row r="727">
       <c r="G727" s="5"/>
+      <c r="H727" s="6"/>
     </row>
     <row r="728">
       <c r="G728" s="5"/>
+      <c r="H728" s="6"/>
     </row>
     <row r="729">
       <c r="G729" s="5"/>
+      <c r="H729" s="6"/>
     </row>
     <row r="730">
       <c r="G730" s="5"/>
+      <c r="H730" s="6"/>
     </row>
     <row r="731">
       <c r="G731" s="5"/>
+      <c r="H731" s="6"/>
     </row>
     <row r="732">
       <c r="G732" s="5"/>
+      <c r="H732" s="6"/>
     </row>
     <row r="733">
       <c r="G733" s="5"/>
+      <c r="H733" s="6"/>
     </row>
     <row r="734">
       <c r="G734" s="5"/>
+      <c r="H734" s="6"/>
     </row>
     <row r="735">
       <c r="G735" s="5"/>
+      <c r="H735" s="6"/>
     </row>
     <row r="736">
       <c r="G736" s="5"/>
+      <c r="H736" s="6"/>
     </row>
     <row r="737">
       <c r="G737" s="5"/>
+      <c r="H737" s="6"/>
     </row>
     <row r="738">
       <c r="G738" s="5"/>
+      <c r="H738" s="6"/>
     </row>
     <row r="739">
       <c r="G739" s="5"/>
+      <c r="H739" s="6"/>
     </row>
     <row r="740">
       <c r="G740" s="5"/>
+      <c r="H740" s="6"/>
     </row>
     <row r="741">
       <c r="G741" s="5"/>
+      <c r="H741" s="6"/>
     </row>
     <row r="742">
       <c r="G742" s="5"/>
+      <c r="H742" s="6"/>
     </row>
     <row r="743">
       <c r="G743" s="5"/>
+      <c r="H743" s="6"/>
     </row>
     <row r="744">
       <c r="G744" s="5"/>
+      <c r="H744" s="6"/>
     </row>
     <row r="745">
       <c r="G745" s="5"/>
+      <c r="H745" s="6"/>
     </row>
     <row r="746">
       <c r="G746" s="5"/>
+      <c r="H746" s="6"/>
     </row>
     <row r="747">
       <c r="G747" s="5"/>
+      <c r="H747" s="6"/>
     </row>
     <row r="748">
       <c r="G748" s="5"/>
+      <c r="H748" s="6"/>
     </row>
     <row r="749">
       <c r="G749" s="5"/>
+      <c r="H749" s="6"/>
     </row>
     <row r="750">
       <c r="G750" s="5"/>
+      <c r="H750" s="6"/>
     </row>
     <row r="751">
       <c r="G751" s="5"/>
+      <c r="H751" s="6"/>
     </row>
     <row r="752">
       <c r="G752" s="5"/>
+      <c r="H752" s="6"/>
     </row>
     <row r="753">
       <c r="G753" s="5"/>
+      <c r="H753" s="6"/>
     </row>
     <row r="754">
       <c r="G754" s="5"/>
+      <c r="H754" s="6"/>
     </row>
     <row r="755">
       <c r="G755" s="5"/>
+      <c r="H755" s="6"/>
     </row>
     <row r="756">
       <c r="G756" s="5"/>
+      <c r="H756" s="6"/>
     </row>
     <row r="757">
       <c r="G757" s="5"/>
+      <c r="H757" s="6"/>
     </row>
     <row r="758">
       <c r="G758" s="5"/>
+      <c r="H758" s="6"/>
     </row>
     <row r="759">
       <c r="G759" s="5"/>
+      <c r="H759" s="6"/>
     </row>
     <row r="760">
       <c r="G760" s="5"/>
+      <c r="H760" s="6"/>
     </row>
     <row r="761">
       <c r="G761" s="5"/>
+      <c r="H761" s="6"/>
     </row>
     <row r="762">
       <c r="G762" s="5"/>
+      <c r="H762" s="6"/>
     </row>
     <row r="763">
       <c r="G763" s="5"/>
+      <c r="H763" s="6"/>
     </row>
     <row r="764">
       <c r="G764" s="5"/>
+      <c r="H764" s="6"/>
     </row>
     <row r="765">
       <c r="G765" s="5"/>
+      <c r="H765" s="6"/>
     </row>
     <row r="766">
       <c r="G766" s="5"/>
+      <c r="H766" s="6"/>
     </row>
     <row r="767">
       <c r="G767" s="5"/>
+      <c r="H767" s="6"/>
     </row>
     <row r="768">
       <c r="G768" s="5"/>
+      <c r="H768" s="6"/>
     </row>
     <row r="769">
       <c r="G769" s="5"/>
+      <c r="H769" s="6"/>
     </row>
     <row r="770">
       <c r="G770" s="5"/>
+      <c r="H770" s="6"/>
     </row>
     <row r="771">
       <c r="G771" s="5"/>
+      <c r="H771" s="6"/>
     </row>
     <row r="772">
       <c r="G772" s="5"/>
+      <c r="H772" s="6"/>
     </row>
     <row r="773">
       <c r="G773" s="5"/>
+      <c r="H773" s="6"/>
     </row>
     <row r="774">
       <c r="G774" s="5"/>
+      <c r="H774" s="6"/>
     </row>
     <row r="775">
       <c r="G775" s="5"/>
+      <c r="H775" s="6"/>
     </row>
     <row r="776">
       <c r="G776" s="5"/>
+      <c r="H776" s="6"/>
     </row>
     <row r="777">
       <c r="G777" s="5"/>
+      <c r="H777" s="6"/>
     </row>
     <row r="778">
       <c r="G778" s="5"/>
+      <c r="H778" s="6"/>
     </row>
     <row r="779">
       <c r="G779" s="5"/>
+      <c r="H779" s="6"/>
     </row>
     <row r="780">
       <c r="G780" s="5"/>
+      <c r="H780" s="6"/>
     </row>
     <row r="781">
       <c r="G781" s="5"/>
+      <c r="H781" s="6"/>
     </row>
     <row r="782">
       <c r="G782" s="5"/>
+      <c r="H782" s="6"/>
     </row>
     <row r="783">
       <c r="G783" s="5"/>
+      <c r="H783" s="6"/>
     </row>
     <row r="784">
       <c r="G784" s="5"/>
+      <c r="H784" s="6"/>
     </row>
     <row r="785">
       <c r="G785" s="5"/>
+      <c r="H785" s="6"/>
     </row>
     <row r="786">
       <c r="G786" s="5"/>
+      <c r="H786" s="6"/>
     </row>
     <row r="787">
       <c r="G787" s="5"/>
+      <c r="H787" s="6"/>
     </row>
     <row r="788">
       <c r="G788" s="5"/>
+      <c r="H788" s="6"/>
     </row>
     <row r="789">
       <c r="G789" s="5"/>
+      <c r="H789" s="6"/>
     </row>
     <row r="790">
       <c r="G790" s="5"/>
+      <c r="H790" s="6"/>
     </row>
     <row r="791">
       <c r="G791" s="5"/>
+      <c r="H791" s="6"/>
     </row>
     <row r="792">
       <c r="G792" s="5"/>
+      <c r="H792" s="6"/>
     </row>
     <row r="793">
       <c r="G793" s="5"/>
+      <c r="H793" s="6"/>
     </row>
     <row r="794">
       <c r="G794" s="5"/>
+      <c r="H794" s="6"/>
     </row>
     <row r="795">
       <c r="G795" s="5"/>
+      <c r="H795" s="6"/>
     </row>
     <row r="796">
       <c r="G796" s="5"/>
+      <c r="H796" s="6"/>
     </row>
     <row r="797">
       <c r="G797" s="5"/>
+      <c r="H797" s="6"/>
     </row>
     <row r="798">
       <c r="G798" s="5"/>
+      <c r="H798" s="6"/>
     </row>
     <row r="799">
       <c r="G799" s="5"/>
+      <c r="H799" s="6"/>
     </row>
     <row r="800">
       <c r="G800" s="5"/>
+      <c r="H800" s="6"/>
     </row>
     <row r="801">
       <c r="G801" s="5"/>
+      <c r="H801" s="6"/>
     </row>
     <row r="802">
       <c r="G802" s="5"/>
+      <c r="H802" s="6"/>
     </row>
     <row r="803">
       <c r="G803" s="5"/>
+      <c r="H803" s="6"/>
     </row>
     <row r="804">
       <c r="G804" s="5"/>
+      <c r="H804" s="6"/>
     </row>
     <row r="805">
       <c r="G805" s="5"/>
+      <c r="H805" s="6"/>
     </row>
     <row r="806">
       <c r="G806" s="5"/>
+      <c r="H806" s="6"/>
     </row>
     <row r="807">
       <c r="G807" s="5"/>
+      <c r="H807" s="6"/>
     </row>
     <row r="808">
       <c r="G808" s="5"/>
+      <c r="H808" s="6"/>
     </row>
     <row r="809">
       <c r="G809" s="5"/>
+      <c r="H809" s="6"/>
     </row>
     <row r="810">
       <c r="G810" s="5"/>
+      <c r="H810" s="6"/>
     </row>
     <row r="811">
       <c r="G811" s="5"/>
+      <c r="H811" s="6"/>
     </row>
     <row r="812">
       <c r="G812" s="5"/>
+      <c r="H812" s="6"/>
     </row>
     <row r="813">
       <c r="G813" s="5"/>
+      <c r="H813" s="6"/>
     </row>
     <row r="814">
       <c r="G814" s="5"/>
+      <c r="H814" s="6"/>
     </row>
     <row r="815">
       <c r="G815" s="5"/>
+      <c r="H815" s="6"/>
     </row>
     <row r="816">
       <c r="G816" s="5"/>
+      <c r="H816" s="6"/>
     </row>
     <row r="817">
       <c r="G817" s="5"/>
+      <c r="H817" s="6"/>
     </row>
     <row r="818">
       <c r="G818" s="5"/>
+      <c r="H818" s="6"/>
     </row>
     <row r="819">
       <c r="G819" s="5"/>
+      <c r="H819" s="6"/>
     </row>
     <row r="820">
       <c r="G820" s="5"/>
+      <c r="H820" s="6"/>
     </row>
     <row r="821">
       <c r="G821" s="5"/>
+      <c r="H821" s="6"/>
     </row>
     <row r="822">
       <c r="G822" s="5"/>
+      <c r="H822" s="6"/>
     </row>
     <row r="823">
       <c r="G823" s="5"/>
+      <c r="H823" s="6"/>
     </row>
     <row r="824">
       <c r="G824" s="5"/>
+      <c r="H824" s="6"/>
     </row>
     <row r="825">
       <c r="G825" s="5"/>
+      <c r="H825" s="6"/>
     </row>
     <row r="826">
       <c r="G826" s="5"/>
+      <c r="H826" s="6"/>
     </row>
     <row r="827">
       <c r="G827" s="5"/>
+      <c r="H827" s="6"/>
     </row>
     <row r="828">
       <c r="G828" s="5"/>
+      <c r="H828" s="6"/>
     </row>
     <row r="829">
       <c r="G829" s="5"/>
+      <c r="H829" s="6"/>
     </row>
     <row r="830">
       <c r="G830" s="5"/>
+      <c r="H830" s="6"/>
     </row>
     <row r="831">
       <c r="G831" s="5"/>
+      <c r="H831" s="6"/>
     </row>
     <row r="832">
       <c r="G832" s="5"/>
+      <c r="H832" s="6"/>
     </row>
     <row r="833">
       <c r="G833" s="5"/>
+      <c r="H833" s="6"/>
     </row>
     <row r="834">
       <c r="G834" s="5"/>
+      <c r="H834" s="6"/>
     </row>
     <row r="835">
       <c r="G835" s="5"/>
+      <c r="H835" s="6"/>
     </row>
     <row r="836">
       <c r="G836" s="5"/>
+      <c r="H836" s="6"/>
     </row>
     <row r="837">
       <c r="G837" s="5"/>
+      <c r="H837" s="6"/>
     </row>
     <row r="838">
       <c r="G838" s="5"/>
+      <c r="H838" s="6"/>
     </row>
     <row r="839">
       <c r="G839" s="5"/>
+      <c r="H839" s="6"/>
     </row>
     <row r="840">
       <c r="G840" s="5"/>
+      <c r="H840" s="6"/>
     </row>
     <row r="841">
       <c r="G841" s="5"/>
+      <c r="H841" s="6"/>
     </row>
     <row r="842">
       <c r="G842" s="5"/>
+      <c r="H842" s="6"/>
     </row>
     <row r="843">
       <c r="G843" s="5"/>
+      <c r="H843" s="6"/>
     </row>
     <row r="844">
       <c r="G844" s="5"/>
+      <c r="H844" s="6"/>
     </row>
     <row r="845">
       <c r="G845" s="5"/>
+      <c r="H845" s="6"/>
     </row>
     <row r="846">
       <c r="G846" s="5"/>
+      <c r="H846" s="6"/>
     </row>
     <row r="847">
       <c r="G847" s="5"/>
+      <c r="H847" s="6"/>
     </row>
     <row r="848">
       <c r="G848" s="5"/>
+      <c r="H848" s="6"/>
     </row>
     <row r="849">
       <c r="G849" s="5"/>
+      <c r="H849" s="6"/>
     </row>
     <row r="850">
       <c r="G850" s="5"/>
+      <c r="H850" s="6"/>
     </row>
     <row r="851">
       <c r="G851" s="5"/>
+      <c r="H851" s="6"/>
     </row>
     <row r="852">
       <c r="G852" s="5"/>
+      <c r="H852" s="6"/>
     </row>
     <row r="853">
       <c r="G853" s="5"/>
+      <c r="H853" s="6"/>
     </row>
     <row r="854">
       <c r="G854" s="5"/>
+      <c r="H854" s="6"/>
     </row>
     <row r="855">
       <c r="G855" s="5"/>
+      <c r="H855" s="6"/>
     </row>
     <row r="856">
       <c r="G856" s="5"/>
+      <c r="H856" s="6"/>
     </row>
     <row r="857">
       <c r="G857" s="5"/>
+      <c r="H857" s="6"/>
     </row>
     <row r="858">
       <c r="G858" s="5"/>
+      <c r="H858" s="6"/>
     </row>
     <row r="859">
       <c r="G859" s="5"/>
+      <c r="H859" s="6"/>
     </row>
     <row r="860">
       <c r="G860" s="5"/>
+      <c r="H860" s="6"/>
     </row>
     <row r="861">
       <c r="G861" s="5"/>
+      <c r="H861" s="6"/>
     </row>
     <row r="862">
       <c r="G862" s="5"/>
+      <c r="H862" s="6"/>
     </row>
     <row r="863">
       <c r="G863" s="5"/>
+      <c r="H863" s="6"/>
     </row>
     <row r="864">
       <c r="G864" s="5"/>
+      <c r="H864" s="6"/>
     </row>
     <row r="865">
       <c r="G865" s="5"/>
+      <c r="H865" s="6"/>
     </row>
     <row r="866">
       <c r="G866" s="5"/>
+      <c r="H866" s="6"/>
     </row>
     <row r="867">
       <c r="G867" s="5"/>
+      <c r="H867" s="6"/>
     </row>
     <row r="868">
       <c r="G868" s="5"/>
+      <c r="H868" s="6"/>
     </row>
     <row r="869">
       <c r="G869" s="5"/>
+      <c r="H869" s="6"/>
     </row>
     <row r="870">
       <c r="G870" s="5"/>
+      <c r="H870" s="6"/>
     </row>
     <row r="871">
       <c r="G871" s="5"/>
+      <c r="H871" s="6"/>
     </row>
     <row r="872">
       <c r="G872" s="5"/>
+      <c r="H872" s="6"/>
     </row>
     <row r="873">
       <c r="G873" s="5"/>
+      <c r="H873" s="6"/>
     </row>
     <row r="874">
       <c r="G874" s="5"/>
+      <c r="H874" s="6"/>
     </row>
     <row r="875">
       <c r="G875" s="5"/>
+      <c r="H875" s="6"/>
     </row>
     <row r="876">
       <c r="G876" s="5"/>
+      <c r="H876" s="6"/>
     </row>
     <row r="877">
       <c r="G877" s="5"/>
+      <c r="H877" s="6"/>
     </row>
     <row r="878">
       <c r="G878" s="5"/>
+      <c r="H878" s="6"/>
     </row>
     <row r="879">
       <c r="G879" s="5"/>
+      <c r="H879" s="6"/>
     </row>
     <row r="880">
       <c r="G880" s="5"/>
+      <c r="H880" s="6"/>
     </row>
     <row r="881">
       <c r="G881" s="5"/>
+      <c r="H881" s="6"/>
     </row>
     <row r="882">
       <c r="G882" s="5"/>
+      <c r="H882" s="6"/>
     </row>
     <row r="883">
       <c r="G883" s="5"/>
+      <c r="H883" s="6"/>
     </row>
     <row r="884">
       <c r="G884" s="5"/>
+      <c r="H884" s="6"/>
     </row>
     <row r="885">
       <c r="G885" s="5"/>
+      <c r="H885" s="6"/>
     </row>
     <row r="886">
       <c r="G886" s="5"/>
+      <c r="H886" s="6"/>
     </row>
     <row r="887">
       <c r="G887" s="5"/>
+      <c r="H887" s="6"/>
     </row>
     <row r="888">
       <c r="G888" s="5"/>
+      <c r="H888" s="6"/>
     </row>
     <row r="889">
       <c r="G889" s="5"/>
+      <c r="H889" s="6"/>
     </row>
     <row r="890">
       <c r="G890" s="5"/>
+      <c r="H890" s="6"/>
     </row>
     <row r="891">
       <c r="G891" s="5"/>
+      <c r="H891" s="6"/>
     </row>
     <row r="892">
       <c r="G892" s="5"/>
+      <c r="H892" s="6"/>
     </row>
     <row r="893">
       <c r="G893" s="5"/>
+      <c r="H893" s="6"/>
     </row>
     <row r="894">
       <c r="G894" s="5"/>
+      <c r="H894" s="6"/>
     </row>
     <row r="895">
       <c r="G895" s="5"/>
+      <c r="H895" s="6"/>
     </row>
     <row r="896">
       <c r="G896" s="5"/>
+      <c r="H896" s="6"/>
     </row>
     <row r="897">
       <c r="G897" s="5"/>
+      <c r="H897" s="6"/>
     </row>
     <row r="898">
       <c r="G898" s="5"/>
+      <c r="H898" s="6"/>
     </row>
     <row r="899">
       <c r="G899" s="5"/>
+      <c r="H899" s="6"/>
     </row>
     <row r="900">
       <c r="G900" s="5"/>
+      <c r="H900" s="6"/>
     </row>
     <row r="901">
       <c r="G901" s="5"/>
+      <c r="H901" s="6"/>
     </row>
     <row r="902">
       <c r="G902" s="5"/>
+      <c r="H902" s="6"/>
     </row>
     <row r="903">
       <c r="G903" s="5"/>
+      <c r="H903" s="6"/>
     </row>
     <row r="904">
       <c r="G904" s="5"/>
+      <c r="H904" s="6"/>
     </row>
     <row r="905">
       <c r="G905" s="5"/>
+      <c r="H905" s="6"/>
     </row>
     <row r="906">
       <c r="G906" s="5"/>
+      <c r="H906" s="6"/>
     </row>
     <row r="907">
       <c r="G907" s="5"/>
+      <c r="H907" s="6"/>
     </row>
     <row r="908">
       <c r="G908" s="5"/>
+      <c r="H908" s="6"/>
     </row>
     <row r="909">
       <c r="G909" s="5"/>
+      <c r="H909" s="6"/>
     </row>
     <row r="910">
       <c r="G910" s="5"/>
+      <c r="H910" s="6"/>
     </row>
     <row r="911">
       <c r="G911" s="5"/>
+      <c r="H911" s="6"/>
     </row>
     <row r="912">
       <c r="G912" s="5"/>
+      <c r="H912" s="6"/>
     </row>
     <row r="913">
       <c r="G913" s="5"/>
+      <c r="H913" s="6"/>
     </row>
     <row r="914">
       <c r="G914" s="5"/>
+      <c r="H914" s="6"/>
     </row>
     <row r="915">
       <c r="G915" s="5"/>
+      <c r="H915" s="6"/>
     </row>
     <row r="916">
       <c r="G916" s="5"/>
+      <c r="H916" s="6"/>
     </row>
     <row r="917">
       <c r="G917" s="5"/>
+      <c r="H917" s="6"/>
     </row>
     <row r="918">
       <c r="G918" s="5"/>
+      <c r="H918" s="6"/>
     </row>
     <row r="919">
       <c r="G919" s="5"/>
+      <c r="H919" s="6"/>
     </row>
     <row r="920">
       <c r="G920" s="5"/>
+      <c r="H920" s="6"/>
     </row>
     <row r="921">
       <c r="G921" s="5"/>
+      <c r="H921" s="6"/>
     </row>
     <row r="922">
       <c r="G922" s="5"/>
+      <c r="H922" s="6"/>
     </row>
     <row r="923">
       <c r="G923" s="5"/>
+      <c r="H923" s="6"/>
     </row>
     <row r="924">
       <c r="G924" s="5"/>
+      <c r="H924" s="6"/>
     </row>
     <row r="925">
       <c r="G925" s="5"/>
+      <c r="H925" s="6"/>
     </row>
     <row r="926">
       <c r="G926" s="5"/>
+      <c r="H926" s="6"/>
     </row>
     <row r="927">
       <c r="G927" s="5"/>
+      <c r="H927" s="6"/>
     </row>
     <row r="928">
       <c r="G928" s="5"/>
+      <c r="H928" s="6"/>
     </row>
     <row r="929">
       <c r="G929" s="5"/>
+      <c r="H929" s="6"/>
     </row>
     <row r="930">
       <c r="G930" s="5"/>
+      <c r="H930" s="6"/>
     </row>
     <row r="931">
       <c r="G931" s="5"/>
+      <c r="H931" s="6"/>
     </row>
     <row r="932">
       <c r="G932" s="5"/>
+      <c r="H932" s="6"/>
     </row>
     <row r="933">
       <c r="G933" s="5"/>
+      <c r="H933" s="6"/>
     </row>
     <row r="934">
       <c r="G934" s="5"/>
+      <c r="H934" s="6"/>
     </row>
     <row r="935">
       <c r="G935" s="5"/>
+      <c r="H935" s="6"/>
     </row>
     <row r="936">
       <c r="G936" s="5"/>
+      <c r="H936" s="6"/>
     </row>
     <row r="937">
       <c r="G937" s="5"/>
+      <c r="H937" s="6"/>
     </row>
     <row r="938">
       <c r="G938" s="5"/>
+      <c r="H938" s="6"/>
     </row>
     <row r="939">
       <c r="G939" s="5"/>
+      <c r="H939" s="6"/>
     </row>
     <row r="940">
       <c r="G940" s="5"/>
+      <c r="H940" s="6"/>
     </row>
     <row r="941">
       <c r="G941" s="5"/>
+      <c r="H941" s="6"/>
     </row>
     <row r="942">
       <c r="G942" s="5"/>
+      <c r="H942" s="6"/>
     </row>
     <row r="943">
       <c r="G943" s="5"/>
+      <c r="H943" s="6"/>
     </row>
     <row r="944">
       <c r="G944" s="5"/>
+      <c r="H944" s="6"/>
     </row>
     <row r="945">
       <c r="G945" s="5"/>
+      <c r="H945" s="6"/>
     </row>
     <row r="946">
       <c r="G946" s="5"/>
+      <c r="H946" s="6"/>
     </row>
     <row r="947">
       <c r="G947" s="5"/>
+      <c r="H947" s="6"/>
     </row>
     <row r="948">
       <c r="G948" s="5"/>
+      <c r="H948" s="6"/>
     </row>
     <row r="949">
       <c r="G949" s="5"/>
+      <c r="H949" s="6"/>
     </row>
     <row r="950">
       <c r="G950" s="5"/>
+      <c r="H950" s="6"/>
     </row>
     <row r="951">
       <c r="G951" s="5"/>
+      <c r="H951" s="6"/>
     </row>
     <row r="952">
       <c r="G952" s="5"/>
+      <c r="H952" s="6"/>
     </row>
     <row r="953">
       <c r="G953" s="5"/>
+      <c r="H953" s="6"/>
     </row>
     <row r="954">
       <c r="G954" s="5"/>
+      <c r="H954" s="6"/>
     </row>
     <row r="955">
       <c r="G955" s="5"/>
+      <c r="H955" s="6"/>
     </row>
     <row r="956">
       <c r="G956" s="5"/>
+      <c r="H956" s="6"/>
     </row>
     <row r="957">
       <c r="G957" s="5"/>
+      <c r="H957" s="6"/>
     </row>
     <row r="958">
       <c r="G958" s="5"/>
+      <c r="H958" s="6"/>
     </row>
     <row r="959">
       <c r="G959" s="5"/>
+      <c r="H959" s="6"/>
     </row>
     <row r="960">
       <c r="G960" s="5"/>
+      <c r="H960" s="6"/>
     </row>
     <row r="961">
       <c r="G961" s="5"/>
+      <c r="H961" s="6"/>
     </row>
     <row r="962">
       <c r="G962" s="5"/>
+      <c r="H962" s="6"/>
     </row>
     <row r="963">
       <c r="G963" s="5"/>
+      <c r="H963" s="6"/>
     </row>
     <row r="964">
       <c r="G964" s="5"/>
+      <c r="H964" s="6"/>
     </row>
     <row r="965">
       <c r="G965" s="5"/>
+      <c r="H965" s="6"/>
     </row>
     <row r="966">
       <c r="G966" s="5"/>
+      <c r="H966" s="6"/>
     </row>
     <row r="967">
       <c r="G967" s="5"/>
+      <c r="H967" s="6"/>
     </row>
     <row r="968">
       <c r="G968" s="5"/>
+      <c r="H968" s="6"/>
     </row>
     <row r="969">
       <c r="G969" s="5"/>
+      <c r="H969" s="6"/>
     </row>
     <row r="970">
       <c r="G970" s="5"/>
+      <c r="H970" s="6"/>
     </row>
     <row r="971">
       <c r="G971" s="5"/>
+      <c r="H971" s="6"/>
     </row>
     <row r="972">
       <c r="G972" s="5"/>
+      <c r="H972" s="6"/>
     </row>
     <row r="973">
       <c r="G973" s="5"/>
+      <c r="H973" s="6"/>
     </row>
     <row r="974">
       <c r="G974" s="5"/>
+      <c r="H974" s="6"/>
     </row>
     <row r="975">
       <c r="G975" s="5"/>
+      <c r="H975" s="6"/>
     </row>
     <row r="976">
       <c r="G976" s="5"/>
+      <c r="H976" s="6"/>
     </row>
     <row r="977">
       <c r="G977" s="5"/>
+      <c r="H977" s="6"/>
     </row>
     <row r="978">
       <c r="G978" s="5"/>
+      <c r="H978" s="6"/>
     </row>
     <row r="979">
       <c r="G979" s="5"/>
+      <c r="H979" s="6"/>
     </row>
     <row r="980">
       <c r="G980" s="5"/>
+      <c r="H980" s="6"/>
     </row>
     <row r="981">
       <c r="G981" s="5"/>
+      <c r="H981" s="6"/>
     </row>
     <row r="982">
       <c r="G982" s="5"/>
+      <c r="H982" s="6"/>
     </row>
     <row r="983">
       <c r="G983" s="5"/>
+      <c r="H983" s="6"/>
     </row>
     <row r="984">
       <c r="G984" s="5"/>
+      <c r="H984" s="6"/>
     </row>
     <row r="985">
       <c r="G985" s="5"/>
+      <c r="H985" s="6"/>
     </row>
     <row r="986">
       <c r="G986" s="5"/>
+      <c r="H986" s="6"/>
     </row>
     <row r="987">
       <c r="G987" s="5"/>
+      <c r="H987" s="6"/>
     </row>
     <row r="988">
       <c r="G988" s="5"/>
+      <c r="H988" s="6"/>
     </row>
     <row r="989">
       <c r="G989" s="5"/>
+      <c r="H989" s="6"/>
     </row>
     <row r="990">
       <c r="G990" s="5"/>
+      <c r="H990" s="6"/>
     </row>
     <row r="991">
       <c r="G991" s="5"/>
+      <c r="H991" s="6"/>
     </row>
     <row r="992">
       <c r="G992" s="5"/>
+      <c r="H992" s="6"/>
     </row>
     <row r="993">
       <c r="G993" s="5"/>
+      <c r="H993" s="6"/>
     </row>
     <row r="994">
       <c r="G994" s="5"/>
+      <c r="H994" s="6"/>
     </row>
     <row r="995">
       <c r="G995" s="5"/>
+      <c r="H995" s="6"/>
     </row>
     <row r="996">
       <c r="G996" s="5"/>
+      <c r="H996" s="6"/>
     </row>
     <row r="997">
       <c r="G997" s="5"/>
+      <c r="H997" s="6"/>
     </row>
     <row r="998">
       <c r="G998" s="5"/>
+      <c r="H998" s="6"/>
     </row>
     <row r="999">
       <c r="G999" s="5"/>
+      <c r="H999" s="6"/>
     </row>
     <row r="1000">
       <c r="G1000" s="5"/>
+      <c r="H1000" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -7768,6 +8927,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="18.75"/>
     <col customWidth="1" min="7" max="7" width="32.63"/>
+    <col customWidth="1" min="8" max="8" width="21.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7781,24 +8941,27 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1">
         <v>10.0</v>
@@ -7807,21 +8970,24 @@
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1">
         <v>10.0</v>
@@ -7830,21 +8996,24 @@
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>125</v>
+        <v>140</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
@@ -7853,21 +9022,24 @@
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>127</v>
+        <v>143</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C5" s="1">
         <v>10.0</v>
@@ -7876,21 +9048,24 @@
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -7899,21 +9074,24 @@
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>131</v>
+        <v>148</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C7" s="1">
         <v>3.0</v>
@@ -7922,44 +9100,50 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>134</v>
+        <v>152</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="C8" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C9" s="1">
         <v>3.0</v>
@@ -7968,41 +9152,44 @@
         <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>138</v>
+        <v>151</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C10" s="1">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C11" s="1">
         <v>3.0</v>
@@ -8011,21 +9198,24 @@
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>141</v>
+        <v>160</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -8034,21 +9224,27 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>143</v>
+        <v>163</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C13" s="1">
         <v>3.0</v>
@@ -8057,21 +9253,24 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>145</v>
+        <v>166</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C14" s="1">
         <v>3.0</v>
@@ -8080,21 +9279,24 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C15" s="1">
         <v>3.0</v>
@@ -8103,21 +9305,24 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>149</v>
+        <v>172</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C16" s="1">
         <v>3.0</v>
@@ -8126,21 +9331,24 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>151</v>
+        <v>175</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C17" s="1">
         <v>1.0</v>
@@ -8149,21 +9357,22 @@
         <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="H17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C18" s="1">
         <v>1.0</v>
@@ -8172,21 +9381,24 @@
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>156</v>
+        <v>181</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C19" s="1">
         <v>1.0</v>
@@ -8195,44 +9407,42 @@
         <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>160</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C21" s="1">
         <v>1.0</v>
@@ -8241,13 +9451,16 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>162</v>
+        <v>187</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="22">
@@ -8255,18 +9468,22 @@
     </row>
     <row r="23">
       <c r="G23" s="5"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24">
       <c r="G24" s="5"/>
+      <c r="J24" s="4"/>
     </row>
     <row r="25">
       <c r="G25" s="5"/>
     </row>
     <row r="26">
       <c r="G26" s="5"/>
+      <c r="J26" s="4"/>
     </row>
     <row r="27">
       <c r="G27" s="5"/>
+      <c r="J27" s="4"/>
     </row>
     <row r="28">
       <c r="G28" s="5"/>
@@ -11213,19 +12430,21 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -11234,15 +12453,18 @@
         <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>166</v>
+        <v>192</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
@@ -11251,15 +12473,15 @@
         <v>34</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
@@ -11268,15 +12490,18 @@
         <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>170</v>
+        <v>197</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
@@ -11285,15 +12510,18 @@
         <v>34</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>172</v>
+        <v>200</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C6" s="1">
         <v>1.0</v>
@@ -11302,7 +12530,7 @@
         <v>34</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
@@ -14313,7 +15541,7 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>56</v>
@@ -14321,10 +15549,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -14333,15 +15561,15 @@
         <v>28.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
@@ -14350,15 +15578,15 @@
         <v>56.0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
@@ -14367,7 +15595,7 @@
         <v>84.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -14381,52 +15609,63 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -283,7 +283,7 @@
   </si>
   <si>
     <t>When Scored:&lt;/br&gt;
-Gain 1 Reclaims</t>
+Gain 1 Retains</t>
   </si>
   <si>
     <t>Common Blue 1</t>
@@ -612,7 +612,7 @@
     <t>Black 1</t>
   </si>
   <si>
-    <t>black_deck</t>
+    <t>trial_deck</t>
   </si>
   <si>
     <t xml:space="preserve">Add X / 2 (rounded down) temporary Black balls to the Combola at the start of the Trial. </t>
@@ -654,7 +654,7 @@
     <t>judgement_deck</t>
   </si>
   <si>
-    <t>You only have one Key</t>
+    <t>Lose one Key.</t>
   </si>
   <si>
     <t>Judgement 2</t>
@@ -4816,7 +4816,7 @@
         <v>83</v>
       </c>
       <c r="C17" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
@@ -15558,7 +15558,7 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>28.0</v>
+        <v>56.0</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>205</v>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -9,8 +9,7 @@
     <sheet state="visible" name="Stamps" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="Trials" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="Judgement" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Aims" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="Ideas" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Ideas" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="187">
   <si>
     <t>Discards</t>
   </si>
@@ -200,43 +199,59 @@
     <t>lane_deck</t>
   </si>
   <si>
-    <t xml:space="preserve">All balls in this Lane are Retained after this Lane has Scored. </t>
+    <t xml:space="preserve">Move all balls in this Lane to the Combola after it has Scored. </t>
   </si>
   <si>
     <t>Lane 2</t>
   </si>
   <si>
-    <t xml:space="preserve">You may discard 3 Colored balls to Discard one Black ball from this Lane when this Lane is Scored. </t>
+    <t xml:space="preserve">Reduce Lane size by 1. 
+Score the last ball in the Lane twice when this Lane is Scored. </t>
   </si>
   <si>
     <t>Lane 3</t>
   </si>
   <si>
-    <t>You may move one ball from this Lane to an open Lane after this Lane has Scored.</t>
-  </si>
-  <si>
-    <t>1?</t>
+    <t xml:space="preserve">Increase Lane size by 3. </t>
   </si>
   <si>
     <t>Lane 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Black balls scores points equal to the damage they dealt when this Lane is Scored. </t>
-  </si>
-  <si>
-    <t>2?</t>
+    <t xml:space="preserve">Draw one ball from this Lane whenever it Explodes. </t>
   </si>
   <si>
     <t>Lane 5</t>
   </si>
   <si>
-    <t xml:space="preserve">You may draw a Discarded ball when this Lane is about to get Scored. </t>
+    <t xml:space="preserve">Gain 1 Point whenever you place a ball in the other Lane while this Lane is full. </t>
+  </si>
+  <si>
+    <t>Too powerful</t>
   </si>
   <si>
     <t>Lane 6</t>
   </si>
   <si>
-    <t xml:space="preserve">The last ball in this Lane is Scored twice. </t>
+    <t xml:space="preserve">Balls of the majority color in this Lane are Shielded. </t>
+  </si>
+  <si>
+    <t>Lane 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Destroy the balls of the majority color when this Lane Explodes. </t>
+  </si>
+  <si>
+    <t>Lane 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw a ball whenever a ball is Destroyed in this Lane. </t>
+  </si>
+  <si>
+    <t>Lane 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 1 Power whenever a ball is Destroyed in this Lane. </t>
   </si>
   <si>
     <t>Rarity</t>
@@ -266,178 +281,71 @@
     <t>Black</t>
   </si>
   <si>
-    <t>Common Yellow 1</t>
-  </si>
-  <si>
     <t>ball_deck</t>
   </si>
   <si>
-    <t xml:space="preserve">When Scored:&lt;/br&gt;
+    <t xml:space="preserve">&lt;b&gt;When Scored:&lt;/b&gt;&lt;/br&gt;
 Gain 1 Yellow if Yellow is the majority Color in this Lane. </t>
   </si>
   <si>
-    <t>- 1 / 3</t>
-  </si>
-  <si>
-    <t>Common Yellow 2</t>
-  </si>
-  <si>
-    <t>When Scored:&lt;/br&gt;
+    <t>&lt;b&gt;When Scored:&lt;/b&gt;&lt;/br&gt;
 Gain 1 Retains</t>
   </si>
   <si>
-    <t>Common Blue 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Hit:&lt;/br&gt;
-Gain 1 Shield if the ball was Black. </t>
-  </si>
-  <si>
-    <t>0.75 * 0.5</t>
-  </si>
-  <si>
-    <t>Common Blue 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
+    <t>&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
+Draw a ball.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 1 Power whenever this Collides with a Blue ball. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
 Draw a random Discarded ball.  </t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Common Green 1</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When Scored:&lt;/br&gt;
-Gain 1 Green if adjacent to two different colors. </t>
-  </si>
-  <si>
-    <t>1.0 * 0.5</t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Hit:&lt;/br&gt;
-Gain 1 Bounces. </t>
-  </si>
-  <si>
-    <t>1.5 - 3.0</t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
+    <t>Shielded</t>
+  </si>
+  <si>
+    <t>Gain 1 Bounces whenever this Collides with a Black ball.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
 Gain 1 Yellow for each Yellow ball in the Draw area. </t>
   </si>
   <si>
-    <t>1.0 - 3.0</t>
-  </si>
-  <si>
-    <t>Uncommon Yellow 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
+    <t xml:space="preserve">&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
 Reveal a ball. Draw it and repeat this effect if it was Yellow. </t>
   </si>
   <si>
-    <t>Uncommon Yellow 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw this ball when it is Retained or Redeemed. </t>
-  </si>
-  <si>
-    <t>Uncommon Blue 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain 1 Blue whenever this hits or is hit by a Blue ball. </t>
-  </si>
-  <si>
-    <t>2 * x</t>
-  </si>
-  <si>
-    <t>Uncommon Blue 2</t>
-  </si>
-  <si>
-    <t>When Placed:&lt;/br&gt;
-Gain 1 Redeem. You may Discard a colored ball from this Lane to get 1 additional Redeem.</t>
-  </si>
-  <si>
-    <t>Uncommon Blue 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redeem this ball at the start of a Trial. </t>
-  </si>
-  <si>
-    <t>Uncommon Blue 4</t>
-  </si>
-  <si>
-    <t>On Hit:&lt;/br&gt;
-If the hit ball matches the majority color in this Lane, Redeem it. If the hit ball is Black and Black is the majority color in this Lane, Discard the hit ball and this ball instead.</t>
-  </si>
-  <si>
-    <t>2.0 if black is majority. Need exhausted?</t>
-  </si>
-  <si>
-    <t>Uncommon Green 1</t>
-  </si>
-  <si>
-    <t>On Hit:&lt;/br&gt;
-Score the hit ball.</t>
-  </si>
-  <si>
-    <t>1.0 - ?</t>
-  </si>
-  <si>
-    <t>Uncommon Green 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Hit:&lt;/br&gt;
-Gain 1 Bounces if the ball was Yellow.&lt;/br&gt;
-Gain 1 Redeems if the ball was Blue.&lt;/br&gt;
-Gain both if it was Green. </t>
-  </si>
-  <si>
-    <t>Rare Yellow 1</t>
+    <t xml:space="preserve">Score any ball this Collides with. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 4 Gold when this is bought. </t>
   </si>
   <si>
     <t xml:space="preserve">When Placed:&lt;/br&gt;
 Score all balls in this Lane if there are fewer balls in this Lane than the other Lane. </t>
   </si>
   <si>
-    <t>Rare Yellow 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When Scored:&lt;/br&gt;
-Gain 1 Green for each ball of the majority color in this Lane. </t>
-  </si>
-  <si>
-    <t>Rare Blue 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When a ball is Redeemed you may Draw it and place it in this Lane instead. </t>
-  </si>
-  <si>
-    <t>Rare Blue 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When Scored:&lt;/br&gt;
-Gain 3 Blue. </t>
-  </si>
-  <si>
-    <t>Rare Green 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw:&lt;/br&gt;
-Discard a Black ball from a Lane if you have 5 or less Health. </t>
-  </si>
-  <si>
-    <t>2.0</t>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Brittle 2</t>
+  </si>
+  <si>
+    <t>Destroy any ball this lands on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjacent balls are Shielded. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw this ball when it is Retained or Redeemed. </t>
+  </si>
+  <si>
+    <t>Gain 1 point whenever this collides with a Blue ball.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redeem this ball at the start of a Trial. </t>
   </si>
   <si>
     <t>Common Stamp 1</t>
@@ -467,9 +375,6 @@
     <t>Common Stamp 3</t>
   </si>
   <si>
-    <t>Gain X Shield</t>
-  </si>
-  <si>
     <t>Common Stamp 4</t>
   </si>
   <si>
@@ -479,31 +384,21 @@
     <t>x=1 --&gt; 1 but then weaker?</t>
   </si>
   <si>
-    <t>Common Stamp 5</t>
-  </si>
-  <si>
-    <t>Gain X Retains&lt;/br&gt;
-Gain X Shield</t>
+    <t>Uncommon Stamp 1</t>
+  </si>
+  <si>
+    <t>3+X</t>
+  </si>
+  <si>
+    <t>Gain X Bounces</t>
   </si>
   <si>
     <t>1.5 / x</t>
   </si>
   <si>
-    <t>Uncommon Stamp 1</t>
-  </si>
-  <si>
-    <t>3+X</t>
-  </si>
-  <si>
-    <t>Gain X Bounces</t>
-  </si>
-  <si>
     <t>Uncommon Stamp 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 3X Yellow if you have a Lane with at least that many balls. </t>
-  </si>
-  <si>
     <t>Uncommon Stamp 3</t>
   </si>
   <si>
@@ -537,9 +432,6 @@
     <t>Uncommon Stamp 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Score all balls in a Lane with no more than 2X balls. </t>
-  </si>
-  <si>
     <t>50%: 2 / x</t>
   </si>
   <si>
@@ -582,30 +474,36 @@
     <t>Rare Stamp 2</t>
   </si>
   <si>
+    <t>2.4 / x</t>
+  </si>
+  <si>
+    <t>Rare Stamp 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain X Keys and lose X Health. </t>
+  </si>
+  <si>
+    <t>Rare Stamp 4</t>
+  </si>
+  <si>
+    <t>Rare Stamp 5</t>
+  </si>
+  <si>
+    <t>Discard X Black balls from the Combola.</t>
+  </si>
+  <si>
+    <t>Can be game breaking</t>
+  </si>
+  <si>
+    <t>Move all Destroyed balls to the Combola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield a ball. </t>
+  </si>
+  <si>
     <t>Gain X Gold</t>
   </si>
   <si>
-    <t>2.4 / x</t>
-  </si>
-  <si>
-    <t>Rare Stamp 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain X Keys and lose X Health. </t>
-  </si>
-  <si>
-    <t>Rare Stamp 4</t>
-  </si>
-  <si>
-    <t>Rare Stamp 5</t>
-  </si>
-  <si>
-    <t>Discard X Black balls from the Combola.</t>
-  </si>
-  <si>
-    <t>Can be game breaking</t>
-  </si>
-  <si>
     <t>Strength</t>
   </si>
   <si>
@@ -615,37 +513,22 @@
     <t>trial_deck</t>
   </si>
   <si>
-    <t xml:space="preserve">Add X / 2 (rounded down) temporary Black balls to the Combola at the start of the Trial. </t>
-  </si>
-  <si>
-    <t>1.5*x</t>
-  </si>
-  <si>
     <t>Black 2</t>
   </si>
   <si>
-    <t>Discard X colored balls at the start of the Trial.</t>
-  </si>
-  <si>
     <t>Black 3</t>
   </si>
   <si>
-    <t>Exhaust one of your highest level Stamps at the start of this game.</t>
-  </si>
-  <si>
-    <t>3?</t>
+    <t xml:space="preserve">Lose [Level] Power. </t>
   </si>
   <si>
     <t>Black 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Black balls are Retained. </t>
+    <t xml:space="preserve">Black balls are moved to the Combola after they are Scored. </t>
   </si>
   <si>
     <t>Black 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw a Black ball and gain 1 Shield whenever you open a Lane. </t>
   </si>
   <si>
     <t>Judgement 1</t>
@@ -673,21 +556,15 @@
     <t>Stars</t>
   </si>
   <si>
-    <t xml:space="preserve">Score when 3 are in same Lane. Additional points for adjacent Stars. Stars exlode when scored. </t>
+    <t xml:space="preserve">Two starts in the Same Lane provides 1 Point before they both are destroyed. </t>
   </si>
   <si>
     <t>Freeze</t>
   </si>
   <si>
-    <t xml:space="preserve">Frozen balls are not discarded when Scored. Freeze effect is removed after scoring. </t>
-  </si>
-  <si>
     <t>Burn</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 1 point each round. Discard the ball after 3 rounds. </t>
-  </si>
-  <si>
     <t>Rock?</t>
   </si>
   <si>
@@ -700,7 +577,16 @@
     <t>Explode:</t>
   </si>
   <si>
-    <t xml:space="preserve">Discard the next ball when Scored. </t>
+    <t>Shielded:</t>
+  </si>
+  <si>
+    <t>Can't be destroyed and Brittle isn't reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brittle X: </t>
+  </si>
+  <si>
+    <t>Destroyed after X collisions</t>
   </si>
 </sst>
 </file>
@@ -746,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -764,13 +650,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -808,10 +687,6 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1287,7 +1162,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="23.0"/>
+    <col customWidth="1" min="4" max="4" width="31.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1320,9 +1195,6 @@
       <c r="D2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="1">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -1351,13 +1223,10 @@
       <c r="D4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>59</v>
@@ -1366,32 +1235,29 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C6" s="1">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>59</v>
@@ -1400,35 +1266,50 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="5"/>
+      <c r="B8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="9">
-      <c r="D9" s="5"/>
+      <c r="A9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="10">
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11">
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12">
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14">
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="5"/>
+      <c r="A10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="16">
       <c r="D16" s="5"/>
@@ -4398,7 +4279,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.38"/>
-    <col customWidth="1" min="7" max="7" width="34.25"/>
+    <col customWidth="1" min="8" max="8" width="34.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4412,97 +4293,93 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="6"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C4" s="1">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1">
         <v>10.0</v>
@@ -4511,24 +4388,21 @@
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F5" s="1">
         <v>2.0</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>85</v>
+      <c r="G5" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -4537,48 +4411,40 @@
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F6" s="1">
         <v>2.0</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1">
         <v>2.0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C8" s="1">
         <v>10.0</v>
@@ -4587,25 +4453,21 @@
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1">
         <v>2.0</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="4"/>
+      <c r="G8" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1">
         <v>10.0</v>
@@ -4614,52 +4476,46 @@
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F9" s="1">
         <v>2.0</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>97</v>
+      <c r="G9" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F10" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>100</v>
+        <v>2.0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="J10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1">
         <v>3.0</v>
@@ -4668,25 +4524,19 @@
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1">
         <v>4.0</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>103</v>
+      <c r="H11" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -4695,23 +4545,19 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F12" s="1">
         <v>4.0</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="J12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C13" s="1">
         <v>3.0</v>
@@ -4720,23 +4566,19 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F13" s="1">
         <v>4.0</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C14" s="1">
         <v>3.0</v>
@@ -4745,25 +4587,16 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" s="1">
         <v>4.0</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="J14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="B15" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C15" s="1">
         <v>3.0</v>
@@ -4772,23 +4605,16 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="6"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C16" s="1">
         <v>3.0</v>
@@ -4797,77 +4623,54 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F16" s="1">
         <v>4.0</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="4"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="B17" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F17" s="1">
         <v>4.0</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>117</v>
-      </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="B18" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C18" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F18" s="1">
         <v>4.0</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="H18" s="4"/>
       <c r="J18" s="4"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="B19" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C19" s="1">
         <v>3.0</v>
@@ -4875,48 +4678,44 @@
       <c r="D19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F19" s="1">
         <v>4.0</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="6"/>
+      <c r="G19" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="J19" s="4"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="1">
         <v>1.0</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J20" s="4"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="B21" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C21" s="1">
         <v>1.0</v>
@@ -4925,22 +4724,18 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F21" s="1">
         <v>8.0</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="B22" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1">
         <v>1.0</v>
@@ -4949,22 +4744,16 @@
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C23" s="1">
         <v>1.0</v>
@@ -4973,22 +4762,16 @@
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F23" s="1">
         <v>8.0</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="B24" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1">
         <v>1.0</v>
@@ -4997,3921 +4780,3033 @@
         <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F24" s="1">
         <v>8.0</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="25">
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
+      <c r="B25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H25" s="4"/>
     </row>
     <row r="26">
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27">
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28">
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29">
-      <c r="G29" s="5"/>
-      <c r="H29" s="6"/>
+      <c r="C29" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
+      <c r="C30" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="31">
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
+      <c r="C31" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="32">
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
+      <c r="E32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="33">
-      <c r="G33" s="5"/>
-      <c r="H33" s="6"/>
+      <c r="F33" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="34">
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
+      <c r="F34" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H34" s="4"/>
     </row>
     <row r="35">
-      <c r="G35" s="5"/>
-      <c r="H35" s="6"/>
+      <c r="H35" s="4" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="36">
-      <c r="G36" s="5"/>
-      <c r="H36" s="6"/>
+      <c r="H36" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="37">
-      <c r="G37" s="5"/>
-      <c r="H37" s="6"/>
+      <c r="H37" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="38">
-      <c r="G38" s="5"/>
-      <c r="H38" s="6"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39">
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40">
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
+      <c r="H40" s="5"/>
     </row>
     <row r="41">
-      <c r="G41" s="5"/>
-      <c r="H41" s="6"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42">
-      <c r="G42" s="5"/>
-      <c r="H42" s="6"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43">
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44">
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45">
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
+      <c r="H45" s="5"/>
     </row>
     <row r="46">
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
+      <c r="H46" s="5"/>
     </row>
     <row r="47">
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
+      <c r="H47" s="5"/>
     </row>
     <row r="48">
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
+      <c r="H48" s="5"/>
     </row>
     <row r="49">
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
+      <c r="H49" s="5"/>
     </row>
     <row r="50">
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51">
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
+      <c r="H51" s="5"/>
     </row>
     <row r="52">
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
+      <c r="H52" s="5"/>
     </row>
     <row r="53">
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
+      <c r="H53" s="5"/>
     </row>
     <row r="54">
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
+      <c r="H54" s="5"/>
     </row>
     <row r="55">
-      <c r="G55" s="5"/>
-      <c r="H55" s="6"/>
+      <c r="H55" s="5"/>
     </row>
     <row r="56">
-      <c r="G56" s="5"/>
-      <c r="H56" s="6"/>
+      <c r="H56" s="5"/>
     </row>
     <row r="57">
-      <c r="G57" s="5"/>
-      <c r="H57" s="6"/>
+      <c r="H57" s="5"/>
     </row>
     <row r="58">
-      <c r="G58" s="5"/>
-      <c r="H58" s="6"/>
+      <c r="H58" s="5"/>
     </row>
     <row r="59">
-      <c r="G59" s="5"/>
-      <c r="H59" s="6"/>
+      <c r="H59" s="5"/>
     </row>
     <row r="60">
-      <c r="G60" s="5"/>
-      <c r="H60" s="6"/>
+      <c r="H60" s="5"/>
     </row>
     <row r="61">
-      <c r="G61" s="5"/>
-      <c r="H61" s="6"/>
+      <c r="H61" s="5"/>
     </row>
     <row r="62">
-      <c r="G62" s="5"/>
-      <c r="H62" s="6"/>
+      <c r="H62" s="5"/>
     </row>
     <row r="63">
-      <c r="G63" s="5"/>
-      <c r="H63" s="6"/>
+      <c r="H63" s="5"/>
     </row>
     <row r="64">
-      <c r="G64" s="5"/>
-      <c r="H64" s="6"/>
+      <c r="H64" s="5"/>
     </row>
     <row r="65">
-      <c r="G65" s="5"/>
-      <c r="H65" s="6"/>
+      <c r="H65" s="5"/>
     </row>
     <row r="66">
-      <c r="G66" s="5"/>
-      <c r="H66" s="6"/>
+      <c r="H66" s="5"/>
     </row>
     <row r="67">
-      <c r="G67" s="5"/>
-      <c r="H67" s="6"/>
+      <c r="H67" s="5"/>
     </row>
     <row r="68">
-      <c r="G68" s="5"/>
-      <c r="H68" s="6"/>
+      <c r="H68" s="5"/>
     </row>
     <row r="69">
-      <c r="G69" s="5"/>
-      <c r="H69" s="6"/>
+      <c r="H69" s="5"/>
     </row>
     <row r="70">
-      <c r="G70" s="5"/>
-      <c r="H70" s="6"/>
+      <c r="H70" s="5"/>
     </row>
     <row r="71">
-      <c r="G71" s="5"/>
-      <c r="H71" s="6"/>
+      <c r="H71" s="5"/>
     </row>
     <row r="72">
-      <c r="G72" s="5"/>
-      <c r="H72" s="6"/>
+      <c r="H72" s="5"/>
     </row>
     <row r="73">
-      <c r="G73" s="5"/>
-      <c r="H73" s="6"/>
+      <c r="H73" s="5"/>
     </row>
     <row r="74">
-      <c r="G74" s="5"/>
-      <c r="H74" s="6"/>
+      <c r="H74" s="5"/>
     </row>
     <row r="75">
-      <c r="G75" s="5"/>
-      <c r="H75" s="6"/>
+      <c r="H75" s="5"/>
     </row>
     <row r="76">
-      <c r="G76" s="5"/>
-      <c r="H76" s="6"/>
+      <c r="H76" s="5"/>
     </row>
     <row r="77">
-      <c r="G77" s="5"/>
-      <c r="H77" s="6"/>
+      <c r="H77" s="5"/>
     </row>
     <row r="78">
-      <c r="G78" s="5"/>
-      <c r="H78" s="6"/>
+      <c r="H78" s="5"/>
     </row>
     <row r="79">
-      <c r="G79" s="5"/>
-      <c r="H79" s="6"/>
+      <c r="H79" s="5"/>
     </row>
     <row r="80">
-      <c r="G80" s="5"/>
-      <c r="H80" s="6"/>
+      <c r="H80" s="5"/>
     </row>
     <row r="81">
-      <c r="G81" s="5"/>
-      <c r="H81" s="6"/>
+      <c r="H81" s="5"/>
     </row>
     <row r="82">
-      <c r="G82" s="5"/>
-      <c r="H82" s="6"/>
+      <c r="H82" s="5"/>
     </row>
     <row r="83">
-      <c r="G83" s="5"/>
-      <c r="H83" s="6"/>
+      <c r="H83" s="5"/>
     </row>
     <row r="84">
-      <c r="G84" s="5"/>
-      <c r="H84" s="6"/>
+      <c r="H84" s="5"/>
     </row>
     <row r="85">
-      <c r="G85" s="5"/>
-      <c r="H85" s="6"/>
+      <c r="H85" s="5"/>
     </row>
     <row r="86">
-      <c r="G86" s="5"/>
-      <c r="H86" s="6"/>
+      <c r="H86" s="5"/>
     </row>
     <row r="87">
-      <c r="G87" s="5"/>
-      <c r="H87" s="6"/>
+      <c r="H87" s="5"/>
     </row>
     <row r="88">
-      <c r="G88" s="5"/>
-      <c r="H88" s="6"/>
+      <c r="H88" s="5"/>
     </row>
     <row r="89">
-      <c r="G89" s="5"/>
-      <c r="H89" s="6"/>
+      <c r="H89" s="5"/>
     </row>
     <row r="90">
-      <c r="G90" s="5"/>
-      <c r="H90" s="6"/>
+      <c r="H90" s="5"/>
     </row>
     <row r="91">
-      <c r="G91" s="5"/>
-      <c r="H91" s="6"/>
+      <c r="H91" s="5"/>
     </row>
     <row r="92">
-      <c r="G92" s="5"/>
-      <c r="H92" s="6"/>
+      <c r="H92" s="5"/>
     </row>
     <row r="93">
-      <c r="G93" s="5"/>
-      <c r="H93" s="6"/>
+      <c r="H93" s="5"/>
     </row>
     <row r="94">
-      <c r="G94" s="5"/>
-      <c r="H94" s="6"/>
+      <c r="H94" s="5"/>
     </row>
     <row r="95">
-      <c r="G95" s="5"/>
-      <c r="H95" s="6"/>
+      <c r="H95" s="5"/>
     </row>
     <row r="96">
-      <c r="G96" s="5"/>
-      <c r="H96" s="6"/>
+      <c r="H96" s="5"/>
     </row>
     <row r="97">
-      <c r="G97" s="5"/>
-      <c r="H97" s="6"/>
+      <c r="H97" s="5"/>
     </row>
     <row r="98">
-      <c r="G98" s="5"/>
-      <c r="H98" s="6"/>
+      <c r="H98" s="5"/>
     </row>
     <row r="99">
-      <c r="G99" s="5"/>
-      <c r="H99" s="6"/>
+      <c r="H99" s="5"/>
     </row>
     <row r="100">
-      <c r="G100" s="5"/>
-      <c r="H100" s="6"/>
+      <c r="H100" s="5"/>
     </row>
     <row r="101">
-      <c r="G101" s="5"/>
-      <c r="H101" s="6"/>
+      <c r="H101" s="5"/>
     </row>
     <row r="102">
-      <c r="G102" s="5"/>
-      <c r="H102" s="6"/>
+      <c r="H102" s="5"/>
     </row>
     <row r="103">
-      <c r="G103" s="5"/>
-      <c r="H103" s="6"/>
+      <c r="H103" s="5"/>
     </row>
     <row r="104">
-      <c r="G104" s="5"/>
-      <c r="H104" s="6"/>
+      <c r="H104" s="5"/>
     </row>
     <row r="105">
-      <c r="G105" s="5"/>
-      <c r="H105" s="6"/>
+      <c r="H105" s="5"/>
     </row>
     <row r="106">
-      <c r="G106" s="5"/>
-      <c r="H106" s="6"/>
+      <c r="H106" s="5"/>
     </row>
     <row r="107">
-      <c r="G107" s="5"/>
-      <c r="H107" s="6"/>
+      <c r="H107" s="5"/>
     </row>
     <row r="108">
-      <c r="G108" s="5"/>
-      <c r="H108" s="6"/>
+      <c r="H108" s="5"/>
     </row>
     <row r="109">
-      <c r="G109" s="5"/>
-      <c r="H109" s="6"/>
+      <c r="H109" s="5"/>
     </row>
     <row r="110">
-      <c r="G110" s="5"/>
-      <c r="H110" s="6"/>
+      <c r="H110" s="5"/>
     </row>
     <row r="111">
-      <c r="G111" s="5"/>
-      <c r="H111" s="6"/>
+      <c r="H111" s="5"/>
     </row>
     <row r="112">
-      <c r="G112" s="5"/>
-      <c r="H112" s="6"/>
+      <c r="H112" s="5"/>
     </row>
     <row r="113">
-      <c r="G113" s="5"/>
-      <c r="H113" s="6"/>
+      <c r="H113" s="5"/>
     </row>
     <row r="114">
-      <c r="G114" s="5"/>
-      <c r="H114" s="6"/>
+      <c r="H114" s="5"/>
     </row>
     <row r="115">
-      <c r="G115" s="5"/>
-      <c r="H115" s="6"/>
+      <c r="H115" s="5"/>
     </row>
     <row r="116">
-      <c r="G116" s="5"/>
-      <c r="H116" s="6"/>
+      <c r="H116" s="5"/>
     </row>
     <row r="117">
-      <c r="G117" s="5"/>
-      <c r="H117" s="6"/>
+      <c r="H117" s="5"/>
     </row>
     <row r="118">
-      <c r="G118" s="5"/>
-      <c r="H118" s="6"/>
+      <c r="H118" s="5"/>
     </row>
     <row r="119">
-      <c r="G119" s="5"/>
-      <c r="H119" s="6"/>
+      <c r="H119" s="5"/>
     </row>
     <row r="120">
-      <c r="G120" s="5"/>
-      <c r="H120" s="6"/>
+      <c r="H120" s="5"/>
     </row>
     <row r="121">
-      <c r="G121" s="5"/>
-      <c r="H121" s="6"/>
+      <c r="H121" s="5"/>
     </row>
     <row r="122">
-      <c r="G122" s="5"/>
-      <c r="H122" s="6"/>
+      <c r="H122" s="5"/>
     </row>
     <row r="123">
-      <c r="G123" s="5"/>
-      <c r="H123" s="6"/>
+      <c r="H123" s="5"/>
     </row>
     <row r="124">
-      <c r="G124" s="5"/>
-      <c r="H124" s="6"/>
+      <c r="H124" s="5"/>
     </row>
     <row r="125">
-      <c r="G125" s="5"/>
-      <c r="H125" s="6"/>
+      <c r="H125" s="5"/>
     </row>
     <row r="126">
-      <c r="G126" s="5"/>
-      <c r="H126" s="6"/>
+      <c r="H126" s="5"/>
     </row>
     <row r="127">
-      <c r="G127" s="5"/>
-      <c r="H127" s="6"/>
+      <c r="H127" s="5"/>
     </row>
     <row r="128">
-      <c r="G128" s="5"/>
-      <c r="H128" s="6"/>
+      <c r="H128" s="5"/>
     </row>
     <row r="129">
-      <c r="G129" s="5"/>
-      <c r="H129" s="6"/>
+      <c r="H129" s="5"/>
     </row>
     <row r="130">
-      <c r="G130" s="5"/>
-      <c r="H130" s="6"/>
+      <c r="H130" s="5"/>
     </row>
     <row r="131">
-      <c r="G131" s="5"/>
-      <c r="H131" s="6"/>
+      <c r="H131" s="5"/>
     </row>
     <row r="132">
-      <c r="G132" s="5"/>
-      <c r="H132" s="6"/>
+      <c r="H132" s="5"/>
     </row>
     <row r="133">
-      <c r="G133" s="5"/>
-      <c r="H133" s="6"/>
+      <c r="H133" s="5"/>
     </row>
     <row r="134">
-      <c r="G134" s="5"/>
-      <c r="H134" s="6"/>
+      <c r="H134" s="5"/>
     </row>
     <row r="135">
-      <c r="G135" s="5"/>
-      <c r="H135" s="6"/>
+      <c r="H135" s="5"/>
     </row>
     <row r="136">
-      <c r="G136" s="5"/>
-      <c r="H136" s="6"/>
+      <c r="H136" s="5"/>
     </row>
     <row r="137">
-      <c r="G137" s="5"/>
-      <c r="H137" s="6"/>
+      <c r="H137" s="5"/>
     </row>
     <row r="138">
-      <c r="G138" s="5"/>
-      <c r="H138" s="6"/>
+      <c r="H138" s="5"/>
     </row>
     <row r="139">
-      <c r="G139" s="5"/>
-      <c r="H139" s="6"/>
+      <c r="H139" s="5"/>
     </row>
     <row r="140">
-      <c r="G140" s="5"/>
-      <c r="H140" s="6"/>
+      <c r="H140" s="5"/>
     </row>
     <row r="141">
-      <c r="G141" s="5"/>
-      <c r="H141" s="6"/>
+      <c r="H141" s="5"/>
     </row>
     <row r="142">
-      <c r="G142" s="5"/>
-      <c r="H142" s="6"/>
+      <c r="H142" s="5"/>
     </row>
     <row r="143">
-      <c r="G143" s="5"/>
-      <c r="H143" s="6"/>
+      <c r="H143" s="5"/>
     </row>
     <row r="144">
-      <c r="G144" s="5"/>
-      <c r="H144" s="6"/>
+      <c r="H144" s="5"/>
     </row>
     <row r="145">
-      <c r="G145" s="5"/>
-      <c r="H145" s="6"/>
+      <c r="H145" s="5"/>
     </row>
     <row r="146">
-      <c r="G146" s="5"/>
-      <c r="H146" s="6"/>
+      <c r="H146" s="5"/>
     </row>
     <row r="147">
-      <c r="G147" s="5"/>
-      <c r="H147" s="6"/>
+      <c r="H147" s="5"/>
     </row>
     <row r="148">
-      <c r="G148" s="5"/>
-      <c r="H148" s="6"/>
+      <c r="H148" s="5"/>
     </row>
     <row r="149">
-      <c r="G149" s="5"/>
-      <c r="H149" s="6"/>
+      <c r="H149" s="5"/>
     </row>
     <row r="150">
-      <c r="G150" s="5"/>
-      <c r="H150" s="6"/>
+      <c r="H150" s="5"/>
     </row>
     <row r="151">
-      <c r="G151" s="5"/>
-      <c r="H151" s="6"/>
+      <c r="H151" s="5"/>
     </row>
     <row r="152">
-      <c r="G152" s="5"/>
-      <c r="H152" s="6"/>
+      <c r="H152" s="5"/>
     </row>
     <row r="153">
-      <c r="G153" s="5"/>
-      <c r="H153" s="6"/>
+      <c r="H153" s="5"/>
     </row>
     <row r="154">
-      <c r="G154" s="5"/>
-      <c r="H154" s="6"/>
+      <c r="H154" s="5"/>
     </row>
     <row r="155">
-      <c r="G155" s="5"/>
-      <c r="H155" s="6"/>
+      <c r="H155" s="5"/>
     </row>
     <row r="156">
-      <c r="G156" s="5"/>
-      <c r="H156" s="6"/>
+      <c r="H156" s="5"/>
     </row>
     <row r="157">
-      <c r="G157" s="5"/>
-      <c r="H157" s="6"/>
+      <c r="H157" s="5"/>
     </row>
     <row r="158">
-      <c r="G158" s="5"/>
-      <c r="H158" s="6"/>
+      <c r="H158" s="5"/>
     </row>
     <row r="159">
-      <c r="G159" s="5"/>
-      <c r="H159" s="6"/>
+      <c r="H159" s="5"/>
     </row>
     <row r="160">
-      <c r="G160" s="5"/>
-      <c r="H160" s="6"/>
+      <c r="H160" s="5"/>
     </row>
     <row r="161">
-      <c r="G161" s="5"/>
-      <c r="H161" s="6"/>
+      <c r="H161" s="5"/>
     </row>
     <row r="162">
-      <c r="G162" s="5"/>
-      <c r="H162" s="6"/>
+      <c r="H162" s="5"/>
     </row>
     <row r="163">
-      <c r="G163" s="5"/>
-      <c r="H163" s="6"/>
+      <c r="H163" s="5"/>
     </row>
     <row r="164">
-      <c r="G164" s="5"/>
-      <c r="H164" s="6"/>
+      <c r="H164" s="5"/>
     </row>
     <row r="165">
-      <c r="G165" s="5"/>
-      <c r="H165" s="6"/>
+      <c r="H165" s="5"/>
     </row>
     <row r="166">
-      <c r="G166" s="5"/>
-      <c r="H166" s="6"/>
+      <c r="H166" s="5"/>
     </row>
     <row r="167">
-      <c r="G167" s="5"/>
-      <c r="H167" s="6"/>
+      <c r="H167" s="5"/>
     </row>
     <row r="168">
-      <c r="G168" s="5"/>
-      <c r="H168" s="6"/>
+      <c r="H168" s="5"/>
     </row>
     <row r="169">
-      <c r="G169" s="5"/>
-      <c r="H169" s="6"/>
+      <c r="H169" s="5"/>
     </row>
     <row r="170">
-      <c r="G170" s="5"/>
-      <c r="H170" s="6"/>
+      <c r="H170" s="5"/>
     </row>
     <row r="171">
-      <c r="G171" s="5"/>
-      <c r="H171" s="6"/>
+      <c r="H171" s="5"/>
     </row>
     <row r="172">
-      <c r="G172" s="5"/>
-      <c r="H172" s="6"/>
+      <c r="H172" s="5"/>
     </row>
     <row r="173">
-      <c r="G173" s="5"/>
-      <c r="H173" s="6"/>
+      <c r="H173" s="5"/>
     </row>
     <row r="174">
-      <c r="G174" s="5"/>
-      <c r="H174" s="6"/>
+      <c r="H174" s="5"/>
     </row>
     <row r="175">
-      <c r="G175" s="5"/>
-      <c r="H175" s="6"/>
+      <c r="H175" s="5"/>
     </row>
     <row r="176">
-      <c r="G176" s="5"/>
-      <c r="H176" s="6"/>
+      <c r="H176" s="5"/>
     </row>
     <row r="177">
-      <c r="G177" s="5"/>
-      <c r="H177" s="6"/>
+      <c r="H177" s="5"/>
     </row>
     <row r="178">
-      <c r="G178" s="5"/>
-      <c r="H178" s="6"/>
+      <c r="H178" s="5"/>
     </row>
     <row r="179">
-      <c r="G179" s="5"/>
-      <c r="H179" s="6"/>
+      <c r="H179" s="5"/>
     </row>
     <row r="180">
-      <c r="G180" s="5"/>
-      <c r="H180" s="6"/>
+      <c r="H180" s="5"/>
     </row>
     <row r="181">
-      <c r="G181" s="5"/>
-      <c r="H181" s="6"/>
+      <c r="H181" s="5"/>
     </row>
     <row r="182">
-      <c r="G182" s="5"/>
-      <c r="H182" s="6"/>
+      <c r="H182" s="5"/>
     </row>
     <row r="183">
-      <c r="G183" s="5"/>
-      <c r="H183" s="6"/>
+      <c r="H183" s="5"/>
     </row>
     <row r="184">
-      <c r="G184" s="5"/>
-      <c r="H184" s="6"/>
+      <c r="H184" s="5"/>
     </row>
     <row r="185">
-      <c r="G185" s="5"/>
-      <c r="H185" s="6"/>
+      <c r="H185" s="5"/>
     </row>
     <row r="186">
-      <c r="G186" s="5"/>
-      <c r="H186" s="6"/>
+      <c r="H186" s="5"/>
     </row>
     <row r="187">
-      <c r="G187" s="5"/>
-      <c r="H187" s="6"/>
+      <c r="H187" s="5"/>
     </row>
     <row r="188">
-      <c r="G188" s="5"/>
-      <c r="H188" s="6"/>
+      <c r="H188" s="5"/>
     </row>
     <row r="189">
-      <c r="G189" s="5"/>
-      <c r="H189" s="6"/>
+      <c r="H189" s="5"/>
     </row>
     <row r="190">
-      <c r="G190" s="5"/>
-      <c r="H190" s="6"/>
+      <c r="H190" s="5"/>
     </row>
     <row r="191">
-      <c r="G191" s="5"/>
-      <c r="H191" s="6"/>
+      <c r="H191" s="5"/>
     </row>
     <row r="192">
-      <c r="G192" s="5"/>
-      <c r="H192" s="6"/>
+      <c r="H192" s="5"/>
     </row>
     <row r="193">
-      <c r="G193" s="5"/>
-      <c r="H193" s="6"/>
+      <c r="H193" s="5"/>
     </row>
     <row r="194">
-      <c r="G194" s="5"/>
-      <c r="H194" s="6"/>
+      <c r="H194" s="5"/>
     </row>
     <row r="195">
-      <c r="G195" s="5"/>
-      <c r="H195" s="6"/>
+      <c r="H195" s="5"/>
     </row>
     <row r="196">
-      <c r="G196" s="5"/>
-      <c r="H196" s="6"/>
+      <c r="H196" s="5"/>
     </row>
     <row r="197">
-      <c r="G197" s="5"/>
-      <c r="H197" s="6"/>
+      <c r="H197" s="5"/>
     </row>
     <row r="198">
-      <c r="G198" s="5"/>
-      <c r="H198" s="6"/>
+      <c r="H198" s="5"/>
     </row>
     <row r="199">
-      <c r="G199" s="5"/>
-      <c r="H199" s="6"/>
+      <c r="H199" s="5"/>
     </row>
     <row r="200">
-      <c r="G200" s="5"/>
-      <c r="H200" s="6"/>
+      <c r="H200" s="5"/>
     </row>
     <row r="201">
-      <c r="G201" s="5"/>
-      <c r="H201" s="6"/>
+      <c r="H201" s="5"/>
     </row>
     <row r="202">
-      <c r="G202" s="5"/>
-      <c r="H202" s="6"/>
+      <c r="H202" s="5"/>
     </row>
     <row r="203">
-      <c r="G203" s="5"/>
-      <c r="H203" s="6"/>
+      <c r="H203" s="5"/>
     </row>
     <row r="204">
-      <c r="G204" s="5"/>
-      <c r="H204" s="6"/>
+      <c r="H204" s="5"/>
     </row>
     <row r="205">
-      <c r="G205" s="5"/>
-      <c r="H205" s="6"/>
+      <c r="H205" s="5"/>
     </row>
     <row r="206">
-      <c r="G206" s="5"/>
-      <c r="H206" s="6"/>
+      <c r="H206" s="5"/>
     </row>
     <row r="207">
-      <c r="G207" s="5"/>
-      <c r="H207" s="6"/>
+      <c r="H207" s="5"/>
     </row>
     <row r="208">
-      <c r="G208" s="5"/>
-      <c r="H208" s="6"/>
+      <c r="H208" s="5"/>
     </row>
     <row r="209">
-      <c r="G209" s="5"/>
-      <c r="H209" s="6"/>
+      <c r="H209" s="5"/>
     </row>
     <row r="210">
-      <c r="G210" s="5"/>
-      <c r="H210" s="6"/>
+      <c r="H210" s="5"/>
     </row>
     <row r="211">
-      <c r="G211" s="5"/>
-      <c r="H211" s="6"/>
+      <c r="H211" s="5"/>
     </row>
     <row r="212">
-      <c r="G212" s="5"/>
-      <c r="H212" s="6"/>
+      <c r="H212" s="5"/>
     </row>
     <row r="213">
-      <c r="G213" s="5"/>
-      <c r="H213" s="6"/>
+      <c r="H213" s="5"/>
     </row>
     <row r="214">
-      <c r="G214" s="5"/>
-      <c r="H214" s="6"/>
+      <c r="H214" s="5"/>
     </row>
     <row r="215">
-      <c r="G215" s="5"/>
-      <c r="H215" s="6"/>
+      <c r="H215" s="5"/>
     </row>
     <row r="216">
-      <c r="G216" s="5"/>
-      <c r="H216" s="6"/>
+      <c r="H216" s="5"/>
     </row>
     <row r="217">
-      <c r="G217" s="5"/>
-      <c r="H217" s="6"/>
+      <c r="H217" s="5"/>
     </row>
     <row r="218">
-      <c r="G218" s="5"/>
-      <c r="H218" s="6"/>
+      <c r="H218" s="5"/>
     </row>
     <row r="219">
-      <c r="G219" s="5"/>
-      <c r="H219" s="6"/>
+      <c r="H219" s="5"/>
     </row>
     <row r="220">
-      <c r="G220" s="5"/>
-      <c r="H220" s="6"/>
+      <c r="H220" s="5"/>
     </row>
     <row r="221">
-      <c r="G221" s="5"/>
-      <c r="H221" s="6"/>
+      <c r="H221" s="5"/>
     </row>
     <row r="222">
-      <c r="G222" s="5"/>
-      <c r="H222" s="6"/>
+      <c r="H222" s="5"/>
     </row>
     <row r="223">
-      <c r="G223" s="5"/>
-      <c r="H223" s="6"/>
+      <c r="H223" s="5"/>
     </row>
     <row r="224">
-      <c r="G224" s="5"/>
-      <c r="H224" s="6"/>
+      <c r="H224" s="5"/>
     </row>
     <row r="225">
-      <c r="G225" s="5"/>
-      <c r="H225" s="6"/>
+      <c r="H225" s="5"/>
     </row>
     <row r="226">
-      <c r="G226" s="5"/>
-      <c r="H226" s="6"/>
+      <c r="H226" s="5"/>
     </row>
     <row r="227">
-      <c r="G227" s="5"/>
-      <c r="H227" s="6"/>
+      <c r="H227" s="5"/>
     </row>
     <row r="228">
-      <c r="G228" s="5"/>
-      <c r="H228" s="6"/>
+      <c r="H228" s="5"/>
     </row>
     <row r="229">
-      <c r="G229" s="5"/>
-      <c r="H229" s="6"/>
+      <c r="H229" s="5"/>
     </row>
     <row r="230">
-      <c r="G230" s="5"/>
-      <c r="H230" s="6"/>
+      <c r="H230" s="5"/>
     </row>
     <row r="231">
-      <c r="G231" s="5"/>
-      <c r="H231" s="6"/>
+      <c r="H231" s="5"/>
     </row>
     <row r="232">
-      <c r="G232" s="5"/>
-      <c r="H232" s="6"/>
+      <c r="H232" s="5"/>
     </row>
     <row r="233">
-      <c r="G233" s="5"/>
-      <c r="H233" s="6"/>
+      <c r="H233" s="5"/>
     </row>
     <row r="234">
-      <c r="G234" s="5"/>
-      <c r="H234" s="6"/>
+      <c r="H234" s="5"/>
     </row>
     <row r="235">
-      <c r="G235" s="5"/>
-      <c r="H235" s="6"/>
+      <c r="H235" s="5"/>
     </row>
     <row r="236">
-      <c r="G236" s="5"/>
-      <c r="H236" s="6"/>
+      <c r="H236" s="5"/>
     </row>
     <row r="237">
-      <c r="G237" s="5"/>
-      <c r="H237" s="6"/>
+      <c r="H237" s="5"/>
     </row>
     <row r="238">
-      <c r="G238" s="5"/>
-      <c r="H238" s="6"/>
+      <c r="H238" s="5"/>
     </row>
     <row r="239">
-      <c r="G239" s="5"/>
-      <c r="H239" s="6"/>
+      <c r="H239" s="5"/>
     </row>
     <row r="240">
-      <c r="G240" s="5"/>
-      <c r="H240" s="6"/>
+      <c r="H240" s="5"/>
     </row>
     <row r="241">
-      <c r="G241" s="5"/>
-      <c r="H241" s="6"/>
+      <c r="H241" s="5"/>
     </row>
     <row r="242">
-      <c r="G242" s="5"/>
-      <c r="H242" s="6"/>
+      <c r="H242" s="5"/>
     </row>
     <row r="243">
-      <c r="G243" s="5"/>
-      <c r="H243" s="6"/>
+      <c r="H243" s="5"/>
     </row>
     <row r="244">
-      <c r="G244" s="5"/>
-      <c r="H244" s="6"/>
+      <c r="H244" s="5"/>
     </row>
     <row r="245">
-      <c r="G245" s="5"/>
-      <c r="H245" s="6"/>
+      <c r="H245" s="5"/>
     </row>
     <row r="246">
-      <c r="G246" s="5"/>
-      <c r="H246" s="6"/>
+      <c r="H246" s="5"/>
     </row>
     <row r="247">
-      <c r="G247" s="5"/>
-      <c r="H247" s="6"/>
+      <c r="H247" s="5"/>
     </row>
     <row r="248">
-      <c r="G248" s="5"/>
-      <c r="H248" s="6"/>
+      <c r="H248" s="5"/>
     </row>
     <row r="249">
-      <c r="G249" s="5"/>
-      <c r="H249" s="6"/>
+      <c r="H249" s="5"/>
     </row>
     <row r="250">
-      <c r="G250" s="5"/>
-      <c r="H250" s="6"/>
+      <c r="H250" s="5"/>
     </row>
     <row r="251">
-      <c r="G251" s="5"/>
-      <c r="H251" s="6"/>
+      <c r="H251" s="5"/>
     </row>
     <row r="252">
-      <c r="G252" s="5"/>
-      <c r="H252" s="6"/>
+      <c r="H252" s="5"/>
     </row>
     <row r="253">
-      <c r="G253" s="5"/>
-      <c r="H253" s="6"/>
+      <c r="H253" s="5"/>
     </row>
     <row r="254">
-      <c r="G254" s="5"/>
-      <c r="H254" s="6"/>
+      <c r="H254" s="5"/>
     </row>
     <row r="255">
-      <c r="G255" s="5"/>
-      <c r="H255" s="6"/>
+      <c r="H255" s="5"/>
     </row>
     <row r="256">
-      <c r="G256" s="5"/>
-      <c r="H256" s="6"/>
+      <c r="H256" s="5"/>
     </row>
     <row r="257">
-      <c r="G257" s="5"/>
-      <c r="H257" s="6"/>
+      <c r="H257" s="5"/>
     </row>
     <row r="258">
-      <c r="G258" s="5"/>
-      <c r="H258" s="6"/>
+      <c r="H258" s="5"/>
     </row>
     <row r="259">
-      <c r="G259" s="5"/>
-      <c r="H259" s="6"/>
+      <c r="H259" s="5"/>
     </row>
     <row r="260">
-      <c r="G260" s="5"/>
-      <c r="H260" s="6"/>
+      <c r="H260" s="5"/>
     </row>
     <row r="261">
-      <c r="G261" s="5"/>
-      <c r="H261" s="6"/>
+      <c r="H261" s="5"/>
     </row>
     <row r="262">
-      <c r="G262" s="5"/>
-      <c r="H262" s="6"/>
+      <c r="H262" s="5"/>
     </row>
     <row r="263">
-      <c r="G263" s="5"/>
-      <c r="H263" s="6"/>
+      <c r="H263" s="5"/>
     </row>
     <row r="264">
-      <c r="G264" s="5"/>
-      <c r="H264" s="6"/>
+      <c r="H264" s="5"/>
     </row>
     <row r="265">
-      <c r="G265" s="5"/>
-      <c r="H265" s="6"/>
+      <c r="H265" s="5"/>
     </row>
     <row r="266">
-      <c r="G266" s="5"/>
-      <c r="H266" s="6"/>
+      <c r="H266" s="5"/>
     </row>
     <row r="267">
-      <c r="G267" s="5"/>
-      <c r="H267" s="6"/>
+      <c r="H267" s="5"/>
     </row>
     <row r="268">
-      <c r="G268" s="5"/>
-      <c r="H268" s="6"/>
+      <c r="H268" s="5"/>
     </row>
     <row r="269">
-      <c r="G269" s="5"/>
-      <c r="H269" s="6"/>
+      <c r="H269" s="5"/>
     </row>
     <row r="270">
-      <c r="G270" s="5"/>
-      <c r="H270" s="6"/>
+      <c r="H270" s="5"/>
     </row>
     <row r="271">
-      <c r="G271" s="5"/>
-      <c r="H271" s="6"/>
+      <c r="H271" s="5"/>
     </row>
     <row r="272">
-      <c r="G272" s="5"/>
-      <c r="H272" s="6"/>
+      <c r="H272" s="5"/>
     </row>
     <row r="273">
-      <c r="G273" s="5"/>
-      <c r="H273" s="6"/>
+      <c r="H273" s="5"/>
     </row>
     <row r="274">
-      <c r="G274" s="5"/>
-      <c r="H274" s="6"/>
+      <c r="H274" s="5"/>
     </row>
     <row r="275">
-      <c r="G275" s="5"/>
-      <c r="H275" s="6"/>
+      <c r="H275" s="5"/>
     </row>
     <row r="276">
-      <c r="G276" s="5"/>
-      <c r="H276" s="6"/>
+      <c r="H276" s="5"/>
     </row>
     <row r="277">
-      <c r="G277" s="5"/>
-      <c r="H277" s="6"/>
+      <c r="H277" s="5"/>
     </row>
     <row r="278">
-      <c r="G278" s="5"/>
-      <c r="H278" s="6"/>
+      <c r="H278" s="5"/>
     </row>
     <row r="279">
-      <c r="G279" s="5"/>
-      <c r="H279" s="6"/>
+      <c r="H279" s="5"/>
     </row>
     <row r="280">
-      <c r="G280" s="5"/>
-      <c r="H280" s="6"/>
+      <c r="H280" s="5"/>
     </row>
     <row r="281">
-      <c r="G281" s="5"/>
-      <c r="H281" s="6"/>
+      <c r="H281" s="5"/>
     </row>
     <row r="282">
-      <c r="G282" s="5"/>
-      <c r="H282" s="6"/>
+      <c r="H282" s="5"/>
     </row>
     <row r="283">
-      <c r="G283" s="5"/>
-      <c r="H283" s="6"/>
+      <c r="H283" s="5"/>
     </row>
     <row r="284">
-      <c r="G284" s="5"/>
-      <c r="H284" s="6"/>
+      <c r="H284" s="5"/>
     </row>
     <row r="285">
-      <c r="G285" s="5"/>
-      <c r="H285" s="6"/>
+      <c r="H285" s="5"/>
     </row>
     <row r="286">
-      <c r="G286" s="5"/>
-      <c r="H286" s="6"/>
+      <c r="H286" s="5"/>
     </row>
     <row r="287">
-      <c r="G287" s="5"/>
-      <c r="H287" s="6"/>
+      <c r="H287" s="5"/>
     </row>
     <row r="288">
-      <c r="G288" s="5"/>
-      <c r="H288" s="6"/>
+      <c r="H288" s="5"/>
     </row>
     <row r="289">
-      <c r="G289" s="5"/>
-      <c r="H289" s="6"/>
+      <c r="H289" s="5"/>
     </row>
     <row r="290">
-      <c r="G290" s="5"/>
-      <c r="H290" s="6"/>
+      <c r="H290" s="5"/>
     </row>
     <row r="291">
-      <c r="G291" s="5"/>
-      <c r="H291" s="6"/>
+      <c r="H291" s="5"/>
     </row>
     <row r="292">
-      <c r="G292" s="5"/>
-      <c r="H292" s="6"/>
+      <c r="H292" s="5"/>
     </row>
     <row r="293">
-      <c r="G293" s="5"/>
-      <c r="H293" s="6"/>
+      <c r="H293" s="5"/>
     </row>
     <row r="294">
-      <c r="G294" s="5"/>
-      <c r="H294" s="6"/>
+      <c r="H294" s="5"/>
     </row>
     <row r="295">
-      <c r="G295" s="5"/>
-      <c r="H295" s="6"/>
+      <c r="H295" s="5"/>
     </row>
     <row r="296">
-      <c r="G296" s="5"/>
-      <c r="H296" s="6"/>
+      <c r="H296" s="5"/>
     </row>
     <row r="297">
-      <c r="G297" s="5"/>
-      <c r="H297" s="6"/>
+      <c r="H297" s="5"/>
     </row>
     <row r="298">
-      <c r="G298" s="5"/>
-      <c r="H298" s="6"/>
+      <c r="H298" s="5"/>
     </row>
     <row r="299">
-      <c r="G299" s="5"/>
-      <c r="H299" s="6"/>
+      <c r="H299" s="5"/>
     </row>
     <row r="300">
-      <c r="G300" s="5"/>
-      <c r="H300" s="6"/>
+      <c r="H300" s="5"/>
     </row>
     <row r="301">
-      <c r="G301" s="5"/>
-      <c r="H301" s="6"/>
+      <c r="H301" s="5"/>
     </row>
     <row r="302">
-      <c r="G302" s="5"/>
-      <c r="H302" s="6"/>
+      <c r="H302" s="5"/>
     </row>
     <row r="303">
-      <c r="G303" s="5"/>
-      <c r="H303" s="6"/>
+      <c r="H303" s="5"/>
     </row>
     <row r="304">
-      <c r="G304" s="5"/>
-      <c r="H304" s="6"/>
+      <c r="H304" s="5"/>
     </row>
     <row r="305">
-      <c r="G305" s="5"/>
-      <c r="H305" s="6"/>
+      <c r="H305" s="5"/>
     </row>
     <row r="306">
-      <c r="G306" s="5"/>
-      <c r="H306" s="6"/>
+      <c r="H306" s="5"/>
     </row>
     <row r="307">
-      <c r="G307" s="5"/>
-      <c r="H307" s="6"/>
+      <c r="H307" s="5"/>
     </row>
     <row r="308">
-      <c r="G308" s="5"/>
-      <c r="H308" s="6"/>
+      <c r="H308" s="5"/>
     </row>
     <row r="309">
-      <c r="G309" s="5"/>
-      <c r="H309" s="6"/>
+      <c r="H309" s="5"/>
     </row>
     <row r="310">
-      <c r="G310" s="5"/>
-      <c r="H310" s="6"/>
+      <c r="H310" s="5"/>
     </row>
     <row r="311">
-      <c r="G311" s="5"/>
-      <c r="H311" s="6"/>
+      <c r="H311" s="5"/>
     </row>
     <row r="312">
-      <c r="G312" s="5"/>
-      <c r="H312" s="6"/>
+      <c r="H312" s="5"/>
     </row>
     <row r="313">
-      <c r="G313" s="5"/>
-      <c r="H313" s="6"/>
+      <c r="H313" s="5"/>
     </row>
     <row r="314">
-      <c r="G314" s="5"/>
-      <c r="H314" s="6"/>
+      <c r="H314" s="5"/>
     </row>
     <row r="315">
-      <c r="G315" s="5"/>
-      <c r="H315" s="6"/>
+      <c r="H315" s="5"/>
     </row>
     <row r="316">
-      <c r="G316" s="5"/>
-      <c r="H316" s="6"/>
+      <c r="H316" s="5"/>
     </row>
     <row r="317">
-      <c r="G317" s="5"/>
-      <c r="H317" s="6"/>
+      <c r="H317" s="5"/>
     </row>
     <row r="318">
-      <c r="G318" s="5"/>
-      <c r="H318" s="6"/>
+      <c r="H318" s="5"/>
     </row>
     <row r="319">
-      <c r="G319" s="5"/>
-      <c r="H319" s="6"/>
+      <c r="H319" s="5"/>
     </row>
     <row r="320">
-      <c r="G320" s="5"/>
-      <c r="H320" s="6"/>
+      <c r="H320" s="5"/>
     </row>
     <row r="321">
-      <c r="G321" s="5"/>
-      <c r="H321" s="6"/>
+      <c r="H321" s="5"/>
     </row>
     <row r="322">
-      <c r="G322" s="5"/>
-      <c r="H322" s="6"/>
+      <c r="H322" s="5"/>
     </row>
     <row r="323">
-      <c r="G323" s="5"/>
-      <c r="H323" s="6"/>
+      <c r="H323" s="5"/>
     </row>
     <row r="324">
-      <c r="G324" s="5"/>
-      <c r="H324" s="6"/>
+      <c r="H324" s="5"/>
     </row>
     <row r="325">
-      <c r="G325" s="5"/>
-      <c r="H325" s="6"/>
+      <c r="H325" s="5"/>
     </row>
     <row r="326">
-      <c r="G326" s="5"/>
-      <c r="H326" s="6"/>
+      <c r="H326" s="5"/>
     </row>
     <row r="327">
-      <c r="G327" s="5"/>
-      <c r="H327" s="6"/>
+      <c r="H327" s="5"/>
     </row>
     <row r="328">
-      <c r="G328" s="5"/>
-      <c r="H328" s="6"/>
+      <c r="H328" s="5"/>
     </row>
     <row r="329">
-      <c r="G329" s="5"/>
-      <c r="H329" s="6"/>
+      <c r="H329" s="5"/>
     </row>
     <row r="330">
-      <c r="G330" s="5"/>
-      <c r="H330" s="6"/>
+      <c r="H330" s="5"/>
     </row>
     <row r="331">
-      <c r="G331" s="5"/>
-      <c r="H331" s="6"/>
+      <c r="H331" s="5"/>
     </row>
     <row r="332">
-      <c r="G332" s="5"/>
-      <c r="H332" s="6"/>
+      <c r="H332" s="5"/>
     </row>
     <row r="333">
-      <c r="G333" s="5"/>
-      <c r="H333" s="6"/>
+      <c r="H333" s="5"/>
     </row>
     <row r="334">
-      <c r="G334" s="5"/>
-      <c r="H334" s="6"/>
+      <c r="H334" s="5"/>
     </row>
     <row r="335">
-      <c r="G335" s="5"/>
-      <c r="H335" s="6"/>
+      <c r="H335" s="5"/>
     </row>
     <row r="336">
-      <c r="G336" s="5"/>
-      <c r="H336" s="6"/>
+      <c r="H336" s="5"/>
     </row>
     <row r="337">
-      <c r="G337" s="5"/>
-      <c r="H337" s="6"/>
+      <c r="H337" s="5"/>
     </row>
     <row r="338">
-      <c r="G338" s="5"/>
-      <c r="H338" s="6"/>
+      <c r="H338" s="5"/>
     </row>
     <row r="339">
-      <c r="G339" s="5"/>
-      <c r="H339" s="6"/>
+      <c r="H339" s="5"/>
     </row>
     <row r="340">
-      <c r="G340" s="5"/>
-      <c r="H340" s="6"/>
+      <c r="H340" s="5"/>
     </row>
     <row r="341">
-      <c r="G341" s="5"/>
-      <c r="H341" s="6"/>
+      <c r="H341" s="5"/>
     </row>
     <row r="342">
-      <c r="G342" s="5"/>
-      <c r="H342" s="6"/>
+      <c r="H342" s="5"/>
     </row>
     <row r="343">
-      <c r="G343" s="5"/>
-      <c r="H343" s="6"/>
+      <c r="H343" s="5"/>
     </row>
     <row r="344">
-      <c r="G344" s="5"/>
-      <c r="H344" s="6"/>
+      <c r="H344" s="5"/>
     </row>
     <row r="345">
-      <c r="G345" s="5"/>
-      <c r="H345" s="6"/>
+      <c r="H345" s="5"/>
     </row>
     <row r="346">
-      <c r="G346" s="5"/>
-      <c r="H346" s="6"/>
+      <c r="H346" s="5"/>
     </row>
     <row r="347">
-      <c r="G347" s="5"/>
-      <c r="H347" s="6"/>
+      <c r="H347" s="5"/>
     </row>
     <row r="348">
-      <c r="G348" s="5"/>
-      <c r="H348" s="6"/>
+      <c r="H348" s="5"/>
     </row>
     <row r="349">
-      <c r="G349" s="5"/>
-      <c r="H349" s="6"/>
+      <c r="H349" s="5"/>
     </row>
     <row r="350">
-      <c r="G350" s="5"/>
-      <c r="H350" s="6"/>
+      <c r="H350" s="5"/>
     </row>
     <row r="351">
-      <c r="G351" s="5"/>
-      <c r="H351" s="6"/>
+      <c r="H351" s="5"/>
     </row>
     <row r="352">
-      <c r="G352" s="5"/>
-      <c r="H352" s="6"/>
+      <c r="H352" s="5"/>
     </row>
     <row r="353">
-      <c r="G353" s="5"/>
-      <c r="H353" s="6"/>
+      <c r="H353" s="5"/>
     </row>
     <row r="354">
-      <c r="G354" s="5"/>
-      <c r="H354" s="6"/>
+      <c r="H354" s="5"/>
     </row>
     <row r="355">
-      <c r="G355" s="5"/>
-      <c r="H355" s="6"/>
+      <c r="H355" s="5"/>
     </row>
     <row r="356">
-      <c r="G356" s="5"/>
-      <c r="H356" s="6"/>
+      <c r="H356" s="5"/>
     </row>
     <row r="357">
-      <c r="G357" s="5"/>
-      <c r="H357" s="6"/>
+      <c r="H357" s="5"/>
     </row>
     <row r="358">
-      <c r="G358" s="5"/>
-      <c r="H358" s="6"/>
+      <c r="H358" s="5"/>
     </row>
     <row r="359">
-      <c r="G359" s="5"/>
-      <c r="H359" s="6"/>
+      <c r="H359" s="5"/>
     </row>
     <row r="360">
-      <c r="G360" s="5"/>
-      <c r="H360" s="6"/>
+      <c r="H360" s="5"/>
     </row>
     <row r="361">
-      <c r="G361" s="5"/>
-      <c r="H361" s="6"/>
+      <c r="H361" s="5"/>
     </row>
     <row r="362">
-      <c r="G362" s="5"/>
-      <c r="H362" s="6"/>
+      <c r="H362" s="5"/>
     </row>
     <row r="363">
-      <c r="G363" s="5"/>
-      <c r="H363" s="6"/>
+      <c r="H363" s="5"/>
     </row>
     <row r="364">
-      <c r="G364" s="5"/>
-      <c r="H364" s="6"/>
+      <c r="H364" s="5"/>
     </row>
     <row r="365">
-      <c r="G365" s="5"/>
-      <c r="H365" s="6"/>
+      <c r="H365" s="5"/>
     </row>
     <row r="366">
-      <c r="G366" s="5"/>
-      <c r="H366" s="6"/>
+      <c r="H366" s="5"/>
     </row>
     <row r="367">
-      <c r="G367" s="5"/>
-      <c r="H367" s="6"/>
+      <c r="H367" s="5"/>
     </row>
     <row r="368">
-      <c r="G368" s="5"/>
-      <c r="H368" s="6"/>
+      <c r="H368" s="5"/>
     </row>
     <row r="369">
-      <c r="G369" s="5"/>
-      <c r="H369" s="6"/>
+      <c r="H369" s="5"/>
     </row>
     <row r="370">
-      <c r="G370" s="5"/>
-      <c r="H370" s="6"/>
+      <c r="H370" s="5"/>
     </row>
     <row r="371">
-      <c r="G371" s="5"/>
-      <c r="H371" s="6"/>
+      <c r="H371" s="5"/>
     </row>
     <row r="372">
-      <c r="G372" s="5"/>
-      <c r="H372" s="6"/>
+      <c r="H372" s="5"/>
     </row>
     <row r="373">
-      <c r="G373" s="5"/>
-      <c r="H373" s="6"/>
+      <c r="H373" s="5"/>
     </row>
     <row r="374">
-      <c r="G374" s="5"/>
-      <c r="H374" s="6"/>
+      <c r="H374" s="5"/>
     </row>
     <row r="375">
-      <c r="G375" s="5"/>
-      <c r="H375" s="6"/>
+      <c r="H375" s="5"/>
     </row>
     <row r="376">
-      <c r="G376" s="5"/>
-      <c r="H376" s="6"/>
+      <c r="H376" s="5"/>
     </row>
     <row r="377">
-      <c r="G377" s="5"/>
-      <c r="H377" s="6"/>
+      <c r="H377" s="5"/>
     </row>
     <row r="378">
-      <c r="G378" s="5"/>
-      <c r="H378" s="6"/>
+      <c r="H378" s="5"/>
     </row>
     <row r="379">
-      <c r="G379" s="5"/>
-      <c r="H379" s="6"/>
+      <c r="H379" s="5"/>
     </row>
     <row r="380">
-      <c r="G380" s="5"/>
-      <c r="H380" s="6"/>
+      <c r="H380" s="5"/>
     </row>
     <row r="381">
-      <c r="G381" s="5"/>
-      <c r="H381" s="6"/>
+      <c r="H381" s="5"/>
     </row>
     <row r="382">
-      <c r="G382" s="5"/>
-      <c r="H382" s="6"/>
+      <c r="H382" s="5"/>
     </row>
     <row r="383">
-      <c r="G383" s="5"/>
-      <c r="H383" s="6"/>
+      <c r="H383" s="5"/>
     </row>
     <row r="384">
-      <c r="G384" s="5"/>
-      <c r="H384" s="6"/>
+      <c r="H384" s="5"/>
     </row>
     <row r="385">
-      <c r="G385" s="5"/>
-      <c r="H385" s="6"/>
+      <c r="H385" s="5"/>
     </row>
     <row r="386">
-      <c r="G386" s="5"/>
-      <c r="H386" s="6"/>
+      <c r="H386" s="5"/>
     </row>
     <row r="387">
-      <c r="G387" s="5"/>
-      <c r="H387" s="6"/>
+      <c r="H387" s="5"/>
     </row>
     <row r="388">
-      <c r="G388" s="5"/>
-      <c r="H388" s="6"/>
+      <c r="H388" s="5"/>
     </row>
     <row r="389">
-      <c r="G389" s="5"/>
-      <c r="H389" s="6"/>
+      <c r="H389" s="5"/>
     </row>
     <row r="390">
-      <c r="G390" s="5"/>
-      <c r="H390" s="6"/>
+      <c r="H390" s="5"/>
     </row>
     <row r="391">
-      <c r="G391" s="5"/>
-      <c r="H391" s="6"/>
+      <c r="H391" s="5"/>
     </row>
     <row r="392">
-      <c r="G392" s="5"/>
-      <c r="H392" s="6"/>
+      <c r="H392" s="5"/>
     </row>
     <row r="393">
-      <c r="G393" s="5"/>
-      <c r="H393" s="6"/>
+      <c r="H393" s="5"/>
     </row>
     <row r="394">
-      <c r="G394" s="5"/>
-      <c r="H394" s="6"/>
+      <c r="H394" s="5"/>
     </row>
     <row r="395">
-      <c r="G395" s="5"/>
-      <c r="H395" s="6"/>
+      <c r="H395" s="5"/>
     </row>
     <row r="396">
-      <c r="G396" s="5"/>
-      <c r="H396" s="6"/>
+      <c r="H396" s="5"/>
     </row>
     <row r="397">
-      <c r="G397" s="5"/>
-      <c r="H397" s="6"/>
+      <c r="H397" s="5"/>
     </row>
     <row r="398">
-      <c r="G398" s="5"/>
-      <c r="H398" s="6"/>
+      <c r="H398" s="5"/>
     </row>
     <row r="399">
-      <c r="G399" s="5"/>
-      <c r="H399" s="6"/>
+      <c r="H399" s="5"/>
     </row>
     <row r="400">
-      <c r="G400" s="5"/>
-      <c r="H400" s="6"/>
+      <c r="H400" s="5"/>
     </row>
     <row r="401">
-      <c r="G401" s="5"/>
-      <c r="H401" s="6"/>
+      <c r="H401" s="5"/>
     </row>
     <row r="402">
-      <c r="G402" s="5"/>
-      <c r="H402" s="6"/>
+      <c r="H402" s="5"/>
     </row>
     <row r="403">
-      <c r="G403" s="5"/>
-      <c r="H403" s="6"/>
+      <c r="H403" s="5"/>
     </row>
     <row r="404">
-      <c r="G404" s="5"/>
-      <c r="H404" s="6"/>
+      <c r="H404" s="5"/>
     </row>
     <row r="405">
-      <c r="G405" s="5"/>
-      <c r="H405" s="6"/>
+      <c r="H405" s="5"/>
     </row>
     <row r="406">
-      <c r="G406" s="5"/>
-      <c r="H406" s="6"/>
+      <c r="H406" s="5"/>
     </row>
     <row r="407">
-      <c r="G407" s="5"/>
-      <c r="H407" s="6"/>
+      <c r="H407" s="5"/>
     </row>
     <row r="408">
-      <c r="G408" s="5"/>
-      <c r="H408" s="6"/>
+      <c r="H408" s="5"/>
     </row>
     <row r="409">
-      <c r="G409" s="5"/>
-      <c r="H409" s="6"/>
+      <c r="H409" s="5"/>
     </row>
     <row r="410">
-      <c r="G410" s="5"/>
-      <c r="H410" s="6"/>
+      <c r="H410" s="5"/>
     </row>
     <row r="411">
-      <c r="G411" s="5"/>
-      <c r="H411" s="6"/>
+      <c r="H411" s="5"/>
     </row>
     <row r="412">
-      <c r="G412" s="5"/>
-      <c r="H412" s="6"/>
+      <c r="H412" s="5"/>
     </row>
     <row r="413">
-      <c r="G413" s="5"/>
-      <c r="H413" s="6"/>
+      <c r="H413" s="5"/>
     </row>
     <row r="414">
-      <c r="G414" s="5"/>
-      <c r="H414" s="6"/>
+      <c r="H414" s="5"/>
     </row>
     <row r="415">
-      <c r="G415" s="5"/>
-      <c r="H415" s="6"/>
+      <c r="H415" s="5"/>
     </row>
     <row r="416">
-      <c r="G416" s="5"/>
-      <c r="H416" s="6"/>
+      <c r="H416" s="5"/>
     </row>
     <row r="417">
-      <c r="G417" s="5"/>
-      <c r="H417" s="6"/>
+      <c r="H417" s="5"/>
     </row>
     <row r="418">
-      <c r="G418" s="5"/>
-      <c r="H418" s="6"/>
+      <c r="H418" s="5"/>
     </row>
     <row r="419">
-      <c r="G419" s="5"/>
-      <c r="H419" s="6"/>
+      <c r="H419" s="5"/>
     </row>
     <row r="420">
-      <c r="G420" s="5"/>
-      <c r="H420" s="6"/>
+      <c r="H420" s="5"/>
     </row>
     <row r="421">
-      <c r="G421" s="5"/>
-      <c r="H421" s="6"/>
+      <c r="H421" s="5"/>
     </row>
     <row r="422">
-      <c r="G422" s="5"/>
-      <c r="H422" s="6"/>
+      <c r="H422" s="5"/>
     </row>
     <row r="423">
-      <c r="G423" s="5"/>
-      <c r="H423" s="6"/>
+      <c r="H423" s="5"/>
     </row>
     <row r="424">
-      <c r="G424" s="5"/>
-      <c r="H424" s="6"/>
+      <c r="H424" s="5"/>
     </row>
     <row r="425">
-      <c r="G425" s="5"/>
-      <c r="H425" s="6"/>
+      <c r="H425" s="5"/>
     </row>
     <row r="426">
-      <c r="G426" s="5"/>
-      <c r="H426" s="6"/>
+      <c r="H426" s="5"/>
     </row>
     <row r="427">
-      <c r="G427" s="5"/>
-      <c r="H427" s="6"/>
+      <c r="H427" s="5"/>
     </row>
     <row r="428">
-      <c r="G428" s="5"/>
-      <c r="H428" s="6"/>
+      <c r="H428" s="5"/>
     </row>
     <row r="429">
-      <c r="G429" s="5"/>
-      <c r="H429" s="6"/>
+      <c r="H429" s="5"/>
     </row>
     <row r="430">
-      <c r="G430" s="5"/>
-      <c r="H430" s="6"/>
+      <c r="H430" s="5"/>
     </row>
     <row r="431">
-      <c r="G431" s="5"/>
-      <c r="H431" s="6"/>
+      <c r="H431" s="5"/>
     </row>
     <row r="432">
-      <c r="G432" s="5"/>
-      <c r="H432" s="6"/>
+      <c r="H432" s="5"/>
     </row>
     <row r="433">
-      <c r="G433" s="5"/>
-      <c r="H433" s="6"/>
+      <c r="H433" s="5"/>
     </row>
     <row r="434">
-      <c r="G434" s="5"/>
-      <c r="H434" s="6"/>
+      <c r="H434" s="5"/>
     </row>
     <row r="435">
-      <c r="G435" s="5"/>
-      <c r="H435" s="6"/>
+      <c r="H435" s="5"/>
     </row>
     <row r="436">
-      <c r="G436" s="5"/>
-      <c r="H436" s="6"/>
+      <c r="H436" s="5"/>
     </row>
     <row r="437">
-      <c r="G437" s="5"/>
-      <c r="H437" s="6"/>
+      <c r="H437" s="5"/>
     </row>
     <row r="438">
-      <c r="G438" s="5"/>
-      <c r="H438" s="6"/>
+      <c r="H438" s="5"/>
     </row>
     <row r="439">
-      <c r="G439" s="5"/>
-      <c r="H439" s="6"/>
+      <c r="H439" s="5"/>
     </row>
     <row r="440">
-      <c r="G440" s="5"/>
-      <c r="H440" s="6"/>
+      <c r="H440" s="5"/>
     </row>
     <row r="441">
-      <c r="G441" s="5"/>
-      <c r="H441" s="6"/>
+      <c r="H441" s="5"/>
     </row>
     <row r="442">
-      <c r="G442" s="5"/>
-      <c r="H442" s="6"/>
+      <c r="H442" s="5"/>
     </row>
     <row r="443">
-      <c r="G443" s="5"/>
-      <c r="H443" s="6"/>
+      <c r="H443" s="5"/>
     </row>
     <row r="444">
-      <c r="G444" s="5"/>
-      <c r="H444" s="6"/>
+      <c r="H444" s="5"/>
     </row>
     <row r="445">
-      <c r="G445" s="5"/>
-      <c r="H445" s="6"/>
+      <c r="H445" s="5"/>
     </row>
     <row r="446">
-      <c r="G446" s="5"/>
-      <c r="H446" s="6"/>
+      <c r="H446" s="5"/>
     </row>
     <row r="447">
-      <c r="G447" s="5"/>
-      <c r="H447" s="6"/>
+      <c r="H447" s="5"/>
     </row>
     <row r="448">
-      <c r="G448" s="5"/>
-      <c r="H448" s="6"/>
+      <c r="H448" s="5"/>
     </row>
     <row r="449">
-      <c r="G449" s="5"/>
-      <c r="H449" s="6"/>
+      <c r="H449" s="5"/>
     </row>
     <row r="450">
-      <c r="G450" s="5"/>
-      <c r="H450" s="6"/>
+      <c r="H450" s="5"/>
     </row>
     <row r="451">
-      <c r="G451" s="5"/>
-      <c r="H451" s="6"/>
+      <c r="H451" s="5"/>
     </row>
     <row r="452">
-      <c r="G452" s="5"/>
-      <c r="H452" s="6"/>
+      <c r="H452" s="5"/>
     </row>
     <row r="453">
-      <c r="G453" s="5"/>
-      <c r="H453" s="6"/>
+      <c r="H453" s="5"/>
     </row>
     <row r="454">
-      <c r="G454" s="5"/>
-      <c r="H454" s="6"/>
+      <c r="H454" s="5"/>
     </row>
     <row r="455">
-      <c r="G455" s="5"/>
-      <c r="H455" s="6"/>
+      <c r="H455" s="5"/>
     </row>
     <row r="456">
-      <c r="G456" s="5"/>
-      <c r="H456" s="6"/>
+      <c r="H456" s="5"/>
     </row>
     <row r="457">
-      <c r="G457" s="5"/>
-      <c r="H457" s="6"/>
+      <c r="H457" s="5"/>
     </row>
     <row r="458">
-      <c r="G458" s="5"/>
-      <c r="H458" s="6"/>
+      <c r="H458" s="5"/>
     </row>
     <row r="459">
-      <c r="G459" s="5"/>
-      <c r="H459" s="6"/>
+      <c r="H459" s="5"/>
     </row>
     <row r="460">
-      <c r="G460" s="5"/>
-      <c r="H460" s="6"/>
+      <c r="H460" s="5"/>
     </row>
     <row r="461">
-      <c r="G461" s="5"/>
-      <c r="H461" s="6"/>
+      <c r="H461" s="5"/>
     </row>
     <row r="462">
-      <c r="G462" s="5"/>
-      <c r="H462" s="6"/>
+      <c r="H462" s="5"/>
     </row>
     <row r="463">
-      <c r="G463" s="5"/>
-      <c r="H463" s="6"/>
+      <c r="H463" s="5"/>
     </row>
     <row r="464">
-      <c r="G464" s="5"/>
-      <c r="H464" s="6"/>
+      <c r="H464" s="5"/>
     </row>
     <row r="465">
-      <c r="G465" s="5"/>
-      <c r="H465" s="6"/>
+      <c r="H465" s="5"/>
     </row>
     <row r="466">
-      <c r="G466" s="5"/>
-      <c r="H466" s="6"/>
+      <c r="H466" s="5"/>
     </row>
     <row r="467">
-      <c r="G467" s="5"/>
-      <c r="H467" s="6"/>
+      <c r="H467" s="5"/>
     </row>
     <row r="468">
-      <c r="G468" s="5"/>
-      <c r="H468" s="6"/>
+      <c r="H468" s="5"/>
     </row>
     <row r="469">
-      <c r="G469" s="5"/>
-      <c r="H469" s="6"/>
+      <c r="H469" s="5"/>
     </row>
     <row r="470">
-      <c r="G470" s="5"/>
-      <c r="H470" s="6"/>
+      <c r="H470" s="5"/>
     </row>
     <row r="471">
-      <c r="G471" s="5"/>
-      <c r="H471" s="6"/>
+      <c r="H471" s="5"/>
     </row>
     <row r="472">
-      <c r="G472" s="5"/>
-      <c r="H472" s="6"/>
+      <c r="H472" s="5"/>
     </row>
     <row r="473">
-      <c r="G473" s="5"/>
-      <c r="H473" s="6"/>
+      <c r="H473" s="5"/>
     </row>
     <row r="474">
-      <c r="G474" s="5"/>
-      <c r="H474" s="6"/>
+      <c r="H474" s="5"/>
     </row>
     <row r="475">
-      <c r="G475" s="5"/>
-      <c r="H475" s="6"/>
+      <c r="H475" s="5"/>
     </row>
     <row r="476">
-      <c r="G476" s="5"/>
-      <c r="H476" s="6"/>
+      <c r="H476" s="5"/>
     </row>
     <row r="477">
-      <c r="G477" s="5"/>
-      <c r="H477" s="6"/>
+      <c r="H477" s="5"/>
     </row>
     <row r="478">
-      <c r="G478" s="5"/>
-      <c r="H478" s="6"/>
+      <c r="H478" s="5"/>
     </row>
     <row r="479">
-      <c r="G479" s="5"/>
-      <c r="H479" s="6"/>
+      <c r="H479" s="5"/>
     </row>
     <row r="480">
-      <c r="G480" s="5"/>
-      <c r="H480" s="6"/>
+      <c r="H480" s="5"/>
     </row>
     <row r="481">
-      <c r="G481" s="5"/>
-      <c r="H481" s="6"/>
+      <c r="H481" s="5"/>
     </row>
     <row r="482">
-      <c r="G482" s="5"/>
-      <c r="H482" s="6"/>
+      <c r="H482" s="5"/>
     </row>
     <row r="483">
-      <c r="G483" s="5"/>
-      <c r="H483" s="6"/>
+      <c r="H483" s="5"/>
     </row>
     <row r="484">
-      <c r="G484" s="5"/>
-      <c r="H484" s="6"/>
+      <c r="H484" s="5"/>
     </row>
     <row r="485">
-      <c r="G485" s="5"/>
-      <c r="H485" s="6"/>
+      <c r="H485" s="5"/>
     </row>
     <row r="486">
-      <c r="G486" s="5"/>
-      <c r="H486" s="6"/>
+      <c r="H486" s="5"/>
     </row>
     <row r="487">
-      <c r="G487" s="5"/>
-      <c r="H487" s="6"/>
+      <c r="H487" s="5"/>
     </row>
     <row r="488">
-      <c r="G488" s="5"/>
-      <c r="H488" s="6"/>
+      <c r="H488" s="5"/>
     </row>
     <row r="489">
-      <c r="G489" s="5"/>
-      <c r="H489" s="6"/>
+      <c r="H489" s="5"/>
     </row>
     <row r="490">
-      <c r="G490" s="5"/>
-      <c r="H490" s="6"/>
+      <c r="H490" s="5"/>
     </row>
     <row r="491">
-      <c r="G491" s="5"/>
-      <c r="H491" s="6"/>
+      <c r="H491" s="5"/>
     </row>
     <row r="492">
-      <c r="G492" s="5"/>
-      <c r="H492" s="6"/>
+      <c r="H492" s="5"/>
     </row>
     <row r="493">
-      <c r="G493" s="5"/>
-      <c r="H493" s="6"/>
+      <c r="H493" s="5"/>
     </row>
     <row r="494">
-      <c r="G494" s="5"/>
-      <c r="H494" s="6"/>
+      <c r="H494" s="5"/>
     </row>
     <row r="495">
-      <c r="G495" s="5"/>
-      <c r="H495" s="6"/>
+      <c r="H495" s="5"/>
     </row>
     <row r="496">
-      <c r="G496" s="5"/>
-      <c r="H496" s="6"/>
+      <c r="H496" s="5"/>
     </row>
     <row r="497">
-      <c r="G497" s="5"/>
-      <c r="H497" s="6"/>
+      <c r="H497" s="5"/>
     </row>
     <row r="498">
-      <c r="G498" s="5"/>
-      <c r="H498" s="6"/>
+      <c r="H498" s="5"/>
     </row>
     <row r="499">
-      <c r="G499" s="5"/>
-      <c r="H499" s="6"/>
+      <c r="H499" s="5"/>
     </row>
     <row r="500">
-      <c r="G500" s="5"/>
-      <c r="H500" s="6"/>
+      <c r="H500" s="5"/>
     </row>
     <row r="501">
-      <c r="G501" s="5"/>
-      <c r="H501" s="6"/>
+      <c r="H501" s="5"/>
     </row>
     <row r="502">
-      <c r="G502" s="5"/>
-      <c r="H502" s="6"/>
+      <c r="H502" s="5"/>
     </row>
     <row r="503">
-      <c r="G503" s="5"/>
-      <c r="H503" s="6"/>
+      <c r="H503" s="5"/>
     </row>
     <row r="504">
-      <c r="G504" s="5"/>
-      <c r="H504" s="6"/>
+      <c r="H504" s="5"/>
     </row>
     <row r="505">
-      <c r="G505" s="5"/>
-      <c r="H505" s="6"/>
+      <c r="H505" s="5"/>
     </row>
     <row r="506">
-      <c r="G506" s="5"/>
-      <c r="H506" s="6"/>
+      <c r="H506" s="5"/>
     </row>
     <row r="507">
-      <c r="G507" s="5"/>
-      <c r="H507" s="6"/>
+      <c r="H507" s="5"/>
     </row>
     <row r="508">
-      <c r="G508" s="5"/>
-      <c r="H508" s="6"/>
+      <c r="H508" s="5"/>
     </row>
     <row r="509">
-      <c r="G509" s="5"/>
-      <c r="H509" s="6"/>
+      <c r="H509" s="5"/>
     </row>
     <row r="510">
-      <c r="G510" s="5"/>
-      <c r="H510" s="6"/>
+      <c r="H510" s="5"/>
     </row>
     <row r="511">
-      <c r="G511" s="5"/>
-      <c r="H511" s="6"/>
+      <c r="H511" s="5"/>
     </row>
     <row r="512">
-      <c r="G512" s="5"/>
-      <c r="H512" s="6"/>
+      <c r="H512" s="5"/>
     </row>
     <row r="513">
-      <c r="G513" s="5"/>
-      <c r="H513" s="6"/>
+      <c r="H513" s="5"/>
     </row>
     <row r="514">
-      <c r="G514" s="5"/>
-      <c r="H514" s="6"/>
+      <c r="H514" s="5"/>
     </row>
     <row r="515">
-      <c r="G515" s="5"/>
-      <c r="H515" s="6"/>
+      <c r="H515" s="5"/>
     </row>
     <row r="516">
-      <c r="G516" s="5"/>
-      <c r="H516" s="6"/>
+      <c r="H516" s="5"/>
     </row>
     <row r="517">
-      <c r="G517" s="5"/>
-      <c r="H517" s="6"/>
+      <c r="H517" s="5"/>
     </row>
     <row r="518">
-      <c r="G518" s="5"/>
-      <c r="H518" s="6"/>
+      <c r="H518" s="5"/>
     </row>
     <row r="519">
-      <c r="G519" s="5"/>
-      <c r="H519" s="6"/>
+      <c r="H519" s="5"/>
     </row>
     <row r="520">
-      <c r="G520" s="5"/>
-      <c r="H520" s="6"/>
+      <c r="H520" s="5"/>
     </row>
     <row r="521">
-      <c r="G521" s="5"/>
-      <c r="H521" s="6"/>
+      <c r="H521" s="5"/>
     </row>
     <row r="522">
-      <c r="G522" s="5"/>
-      <c r="H522" s="6"/>
+      <c r="H522" s="5"/>
     </row>
     <row r="523">
-      <c r="G523" s="5"/>
-      <c r="H523" s="6"/>
+      <c r="H523" s="5"/>
     </row>
     <row r="524">
-      <c r="G524" s="5"/>
-      <c r="H524" s="6"/>
+      <c r="H524" s="5"/>
     </row>
     <row r="525">
-      <c r="G525" s="5"/>
-      <c r="H525" s="6"/>
+      <c r="H525" s="5"/>
     </row>
     <row r="526">
-      <c r="G526" s="5"/>
-      <c r="H526" s="6"/>
+      <c r="H526" s="5"/>
     </row>
     <row r="527">
-      <c r="G527" s="5"/>
-      <c r="H527" s="6"/>
+      <c r="H527" s="5"/>
     </row>
     <row r="528">
-      <c r="G528" s="5"/>
-      <c r="H528" s="6"/>
+      <c r="H528" s="5"/>
     </row>
     <row r="529">
-      <c r="G529" s="5"/>
-      <c r="H529" s="6"/>
+      <c r="H529" s="5"/>
     </row>
     <row r="530">
-      <c r="G530" s="5"/>
-      <c r="H530" s="6"/>
+      <c r="H530" s="5"/>
     </row>
     <row r="531">
-      <c r="G531" s="5"/>
-      <c r="H531" s="6"/>
+      <c r="H531" s="5"/>
     </row>
     <row r="532">
-      <c r="G532" s="5"/>
-      <c r="H532" s="6"/>
+      <c r="H532" s="5"/>
     </row>
     <row r="533">
-      <c r="G533" s="5"/>
-      <c r="H533" s="6"/>
+      <c r="H533" s="5"/>
     </row>
     <row r="534">
-      <c r="G534" s="5"/>
-      <c r="H534" s="6"/>
+      <c r="H534" s="5"/>
     </row>
     <row r="535">
-      <c r="G535" s="5"/>
-      <c r="H535" s="6"/>
+      <c r="H535" s="5"/>
     </row>
     <row r="536">
-      <c r="G536" s="5"/>
-      <c r="H536" s="6"/>
+      <c r="H536" s="5"/>
     </row>
     <row r="537">
-      <c r="G537" s="5"/>
-      <c r="H537" s="6"/>
+      <c r="H537" s="5"/>
     </row>
     <row r="538">
-      <c r="G538" s="5"/>
-      <c r="H538" s="6"/>
+      <c r="H538" s="5"/>
     </row>
     <row r="539">
-      <c r="G539" s="5"/>
-      <c r="H539" s="6"/>
+      <c r="H539" s="5"/>
     </row>
     <row r="540">
-      <c r="G540" s="5"/>
-      <c r="H540" s="6"/>
+      <c r="H540" s="5"/>
     </row>
     <row r="541">
-      <c r="G541" s="5"/>
-      <c r="H541" s="6"/>
+      <c r="H541" s="5"/>
     </row>
     <row r="542">
-      <c r="G542" s="5"/>
-      <c r="H542" s="6"/>
+      <c r="H542" s="5"/>
     </row>
     <row r="543">
-      <c r="G543" s="5"/>
-      <c r="H543" s="6"/>
+      <c r="H543" s="5"/>
     </row>
     <row r="544">
-      <c r="G544" s="5"/>
-      <c r="H544" s="6"/>
+      <c r="H544" s="5"/>
     </row>
     <row r="545">
-      <c r="G545" s="5"/>
-      <c r="H545" s="6"/>
+      <c r="H545" s="5"/>
     </row>
     <row r="546">
-      <c r="G546" s="5"/>
-      <c r="H546" s="6"/>
+      <c r="H546" s="5"/>
     </row>
     <row r="547">
-      <c r="G547" s="5"/>
-      <c r="H547" s="6"/>
+      <c r="H547" s="5"/>
     </row>
     <row r="548">
-      <c r="G548" s="5"/>
-      <c r="H548" s="6"/>
+      <c r="H548" s="5"/>
     </row>
     <row r="549">
-      <c r="G549" s="5"/>
-      <c r="H549" s="6"/>
+      <c r="H549" s="5"/>
     </row>
     <row r="550">
-      <c r="G550" s="5"/>
-      <c r="H550" s="6"/>
+      <c r="H550" s="5"/>
     </row>
     <row r="551">
-      <c r="G551" s="5"/>
-      <c r="H551" s="6"/>
+      <c r="H551" s="5"/>
     </row>
     <row r="552">
-      <c r="G552" s="5"/>
-      <c r="H552" s="6"/>
+      <c r="H552" s="5"/>
     </row>
     <row r="553">
-      <c r="G553" s="5"/>
-      <c r="H553" s="6"/>
+      <c r="H553" s="5"/>
     </row>
     <row r="554">
-      <c r="G554" s="5"/>
-      <c r="H554" s="6"/>
+      <c r="H554" s="5"/>
     </row>
     <row r="555">
-      <c r="G555" s="5"/>
-      <c r="H555" s="6"/>
+      <c r="H555" s="5"/>
     </row>
     <row r="556">
-      <c r="G556" s="5"/>
-      <c r="H556" s="6"/>
+      <c r="H556" s="5"/>
     </row>
     <row r="557">
-      <c r="G557" s="5"/>
-      <c r="H557" s="6"/>
+      <c r="H557" s="5"/>
     </row>
     <row r="558">
-      <c r="G558" s="5"/>
-      <c r="H558" s="6"/>
+      <c r="H558" s="5"/>
     </row>
     <row r="559">
-      <c r="G559" s="5"/>
-      <c r="H559" s="6"/>
+      <c r="H559" s="5"/>
     </row>
     <row r="560">
-      <c r="G560" s="5"/>
-      <c r="H560" s="6"/>
+      <c r="H560" s="5"/>
     </row>
     <row r="561">
-      <c r="G561" s="5"/>
-      <c r="H561" s="6"/>
+      <c r="H561" s="5"/>
     </row>
     <row r="562">
-      <c r="G562" s="5"/>
-      <c r="H562" s="6"/>
+      <c r="H562" s="5"/>
     </row>
     <row r="563">
-      <c r="G563" s="5"/>
-      <c r="H563" s="6"/>
+      <c r="H563" s="5"/>
     </row>
     <row r="564">
-      <c r="G564" s="5"/>
-      <c r="H564" s="6"/>
+      <c r="H564" s="5"/>
     </row>
     <row r="565">
-      <c r="G565" s="5"/>
-      <c r="H565" s="6"/>
+      <c r="H565" s="5"/>
     </row>
     <row r="566">
-      <c r="G566" s="5"/>
-      <c r="H566" s="6"/>
+      <c r="H566" s="5"/>
     </row>
     <row r="567">
-      <c r="G567" s="5"/>
-      <c r="H567" s="6"/>
+      <c r="H567" s="5"/>
     </row>
     <row r="568">
-      <c r="G568" s="5"/>
-      <c r="H568" s="6"/>
+      <c r="H568" s="5"/>
     </row>
     <row r="569">
-      <c r="G569" s="5"/>
-      <c r="H569" s="6"/>
+      <c r="H569" s="5"/>
     </row>
     <row r="570">
-      <c r="G570" s="5"/>
-      <c r="H570" s="6"/>
+      <c r="H570" s="5"/>
     </row>
     <row r="571">
-      <c r="G571" s="5"/>
-      <c r="H571" s="6"/>
+      <c r="H571" s="5"/>
     </row>
     <row r="572">
-      <c r="G572" s="5"/>
-      <c r="H572" s="6"/>
+      <c r="H572" s="5"/>
     </row>
     <row r="573">
-      <c r="G573" s="5"/>
-      <c r="H573" s="6"/>
+      <c r="H573" s="5"/>
     </row>
     <row r="574">
-      <c r="G574" s="5"/>
-      <c r="H574" s="6"/>
+      <c r="H574" s="5"/>
     </row>
     <row r="575">
-      <c r="G575" s="5"/>
-      <c r="H575" s="6"/>
+      <c r="H575" s="5"/>
     </row>
     <row r="576">
-      <c r="G576" s="5"/>
-      <c r="H576" s="6"/>
+      <c r="H576" s="5"/>
     </row>
     <row r="577">
-      <c r="G577" s="5"/>
-      <c r="H577" s="6"/>
+      <c r="H577" s="5"/>
     </row>
     <row r="578">
-      <c r="G578" s="5"/>
-      <c r="H578" s="6"/>
+      <c r="H578" s="5"/>
     </row>
     <row r="579">
-      <c r="G579" s="5"/>
-      <c r="H579" s="6"/>
+      <c r="H579" s="5"/>
     </row>
     <row r="580">
-      <c r="G580" s="5"/>
-      <c r="H580" s="6"/>
+      <c r="H580" s="5"/>
     </row>
     <row r="581">
-      <c r="G581" s="5"/>
-      <c r="H581" s="6"/>
+      <c r="H581" s="5"/>
     </row>
     <row r="582">
-      <c r="G582" s="5"/>
-      <c r="H582" s="6"/>
+      <c r="H582" s="5"/>
     </row>
     <row r="583">
-      <c r="G583" s="5"/>
-      <c r="H583" s="6"/>
+      <c r="H583" s="5"/>
     </row>
     <row r="584">
-      <c r="G584" s="5"/>
-      <c r="H584" s="6"/>
+      <c r="H584" s="5"/>
     </row>
     <row r="585">
-      <c r="G585" s="5"/>
-      <c r="H585" s="6"/>
+      <c r="H585" s="5"/>
     </row>
     <row r="586">
-      <c r="G586" s="5"/>
-      <c r="H586" s="6"/>
+      <c r="H586" s="5"/>
     </row>
     <row r="587">
-      <c r="G587" s="5"/>
-      <c r="H587" s="6"/>
+      <c r="H587" s="5"/>
     </row>
     <row r="588">
-      <c r="G588" s="5"/>
-      <c r="H588" s="6"/>
+      <c r="H588" s="5"/>
     </row>
     <row r="589">
-      <c r="G589" s="5"/>
-      <c r="H589" s="6"/>
+      <c r="H589" s="5"/>
     </row>
     <row r="590">
-      <c r="G590" s="5"/>
-      <c r="H590" s="6"/>
+      <c r="H590" s="5"/>
     </row>
     <row r="591">
-      <c r="G591" s="5"/>
-      <c r="H591" s="6"/>
+      <c r="H591" s="5"/>
     </row>
     <row r="592">
-      <c r="G592" s="5"/>
-      <c r="H592" s="6"/>
+      <c r="H592" s="5"/>
     </row>
     <row r="593">
-      <c r="G593" s="5"/>
-      <c r="H593" s="6"/>
+      <c r="H593" s="5"/>
     </row>
     <row r="594">
-      <c r="G594" s="5"/>
-      <c r="H594" s="6"/>
+      <c r="H594" s="5"/>
     </row>
     <row r="595">
-      <c r="G595" s="5"/>
-      <c r="H595" s="6"/>
+      <c r="H595" s="5"/>
     </row>
     <row r="596">
-      <c r="G596" s="5"/>
-      <c r="H596" s="6"/>
+      <c r="H596" s="5"/>
     </row>
     <row r="597">
-      <c r="G597" s="5"/>
-      <c r="H597" s="6"/>
+      <c r="H597" s="5"/>
     </row>
     <row r="598">
-      <c r="G598" s="5"/>
-      <c r="H598" s="6"/>
+      <c r="H598" s="5"/>
     </row>
     <row r="599">
-      <c r="G599" s="5"/>
-      <c r="H599" s="6"/>
+      <c r="H599" s="5"/>
     </row>
     <row r="600">
-      <c r="G600" s="5"/>
-      <c r="H600" s="6"/>
+      <c r="H600" s="5"/>
     </row>
     <row r="601">
-      <c r="G601" s="5"/>
-      <c r="H601" s="6"/>
+      <c r="H601" s="5"/>
     </row>
     <row r="602">
-      <c r="G602" s="5"/>
-      <c r="H602" s="6"/>
+      <c r="H602" s="5"/>
     </row>
     <row r="603">
-      <c r="G603" s="5"/>
-      <c r="H603" s="6"/>
+      <c r="H603" s="5"/>
     </row>
     <row r="604">
-      <c r="G604" s="5"/>
-      <c r="H604" s="6"/>
+      <c r="H604" s="5"/>
     </row>
     <row r="605">
-      <c r="G605" s="5"/>
-      <c r="H605" s="6"/>
+      <c r="H605" s="5"/>
     </row>
     <row r="606">
-      <c r="G606" s="5"/>
-      <c r="H606" s="6"/>
+      <c r="H606" s="5"/>
     </row>
     <row r="607">
-      <c r="G607" s="5"/>
-      <c r="H607" s="6"/>
+      <c r="H607" s="5"/>
     </row>
     <row r="608">
-      <c r="G608" s="5"/>
-      <c r="H608" s="6"/>
+      <c r="H608" s="5"/>
     </row>
     <row r="609">
-      <c r="G609" s="5"/>
-      <c r="H609" s="6"/>
+      <c r="H609" s="5"/>
     </row>
     <row r="610">
-      <c r="G610" s="5"/>
-      <c r="H610" s="6"/>
+      <c r="H610" s="5"/>
     </row>
     <row r="611">
-      <c r="G611" s="5"/>
-      <c r="H611" s="6"/>
+      <c r="H611" s="5"/>
     </row>
     <row r="612">
-      <c r="G612" s="5"/>
-      <c r="H612" s="6"/>
+      <c r="H612" s="5"/>
     </row>
     <row r="613">
-      <c r="G613" s="5"/>
-      <c r="H613" s="6"/>
+      <c r="H613" s="5"/>
     </row>
     <row r="614">
-      <c r="G614" s="5"/>
-      <c r="H614" s="6"/>
+      <c r="H614" s="5"/>
     </row>
     <row r="615">
-      <c r="G615" s="5"/>
-      <c r="H615" s="6"/>
+      <c r="H615" s="5"/>
     </row>
     <row r="616">
-      <c r="G616" s="5"/>
-      <c r="H616" s="6"/>
+      <c r="H616" s="5"/>
     </row>
     <row r="617">
-      <c r="G617" s="5"/>
-      <c r="H617" s="6"/>
+      <c r="H617" s="5"/>
     </row>
     <row r="618">
-      <c r="G618" s="5"/>
-      <c r="H618" s="6"/>
+      <c r="H618" s="5"/>
     </row>
     <row r="619">
-      <c r="G619" s="5"/>
-      <c r="H619" s="6"/>
+      <c r="H619" s="5"/>
     </row>
     <row r="620">
-      <c r="G620" s="5"/>
-      <c r="H620" s="6"/>
+      <c r="H620" s="5"/>
     </row>
     <row r="621">
-      <c r="G621" s="5"/>
-      <c r="H621" s="6"/>
+      <c r="H621" s="5"/>
     </row>
     <row r="622">
-      <c r="G622" s="5"/>
-      <c r="H622" s="6"/>
+      <c r="H622" s="5"/>
     </row>
     <row r="623">
-      <c r="G623" s="5"/>
-      <c r="H623" s="6"/>
+      <c r="H623" s="5"/>
     </row>
     <row r="624">
-      <c r="G624" s="5"/>
-      <c r="H624" s="6"/>
+      <c r="H624" s="5"/>
     </row>
     <row r="625">
-      <c r="G625" s="5"/>
-      <c r="H625" s="6"/>
+      <c r="H625" s="5"/>
     </row>
     <row r="626">
-      <c r="G626" s="5"/>
-      <c r="H626" s="6"/>
+      <c r="H626" s="5"/>
     </row>
     <row r="627">
-      <c r="G627" s="5"/>
-      <c r="H627" s="6"/>
+      <c r="H627" s="5"/>
     </row>
     <row r="628">
-      <c r="G628" s="5"/>
-      <c r="H628" s="6"/>
+      <c r="H628" s="5"/>
     </row>
     <row r="629">
-      <c r="G629" s="5"/>
-      <c r="H629" s="6"/>
+      <c r="H629" s="5"/>
     </row>
     <row r="630">
-      <c r="G630" s="5"/>
-      <c r="H630" s="6"/>
+      <c r="H630" s="5"/>
     </row>
     <row r="631">
-      <c r="G631" s="5"/>
-      <c r="H631" s="6"/>
+      <c r="H631" s="5"/>
     </row>
     <row r="632">
-      <c r="G632" s="5"/>
-      <c r="H632" s="6"/>
+      <c r="H632" s="5"/>
     </row>
     <row r="633">
-      <c r="G633" s="5"/>
-      <c r="H633" s="6"/>
+      <c r="H633" s="5"/>
     </row>
     <row r="634">
-      <c r="G634" s="5"/>
-      <c r="H634" s="6"/>
+      <c r="H634" s="5"/>
     </row>
     <row r="635">
-      <c r="G635" s="5"/>
-      <c r="H635" s="6"/>
+      <c r="H635" s="5"/>
     </row>
     <row r="636">
-      <c r="G636" s="5"/>
-      <c r="H636" s="6"/>
+      <c r="H636" s="5"/>
     </row>
     <row r="637">
-      <c r="G637" s="5"/>
-      <c r="H637" s="6"/>
+      <c r="H637" s="5"/>
     </row>
     <row r="638">
-      <c r="G638" s="5"/>
-      <c r="H638" s="6"/>
+      <c r="H638" s="5"/>
     </row>
     <row r="639">
-      <c r="G639" s="5"/>
-      <c r="H639" s="6"/>
+      <c r="H639" s="5"/>
     </row>
     <row r="640">
-      <c r="G640" s="5"/>
-      <c r="H640" s="6"/>
+      <c r="H640" s="5"/>
     </row>
     <row r="641">
-      <c r="G641" s="5"/>
-      <c r="H641" s="6"/>
+      <c r="H641" s="5"/>
     </row>
     <row r="642">
-      <c r="G642" s="5"/>
-      <c r="H642" s="6"/>
+      <c r="H642" s="5"/>
     </row>
     <row r="643">
-      <c r="G643" s="5"/>
-      <c r="H643" s="6"/>
+      <c r="H643" s="5"/>
     </row>
     <row r="644">
-      <c r="G644" s="5"/>
-      <c r="H644" s="6"/>
+      <c r="H644" s="5"/>
     </row>
     <row r="645">
-      <c r="G645" s="5"/>
-      <c r="H645" s="6"/>
+      <c r="H645" s="5"/>
     </row>
     <row r="646">
-      <c r="G646" s="5"/>
-      <c r="H646" s="6"/>
+      <c r="H646" s="5"/>
     </row>
     <row r="647">
-      <c r="G647" s="5"/>
-      <c r="H647" s="6"/>
+      <c r="H647" s="5"/>
     </row>
     <row r="648">
-      <c r="G648" s="5"/>
-      <c r="H648" s="6"/>
+      <c r="H648" s="5"/>
     </row>
     <row r="649">
-      <c r="G649" s="5"/>
-      <c r="H649" s="6"/>
+      <c r="H649" s="5"/>
     </row>
     <row r="650">
-      <c r="G650" s="5"/>
-      <c r="H650" s="6"/>
+      <c r="H650" s="5"/>
     </row>
     <row r="651">
-      <c r="G651" s="5"/>
-      <c r="H651" s="6"/>
+      <c r="H651" s="5"/>
     </row>
     <row r="652">
-      <c r="G652" s="5"/>
-      <c r="H652" s="6"/>
+      <c r="H652" s="5"/>
     </row>
     <row r="653">
-      <c r="G653" s="5"/>
-      <c r="H653" s="6"/>
+      <c r="H653" s="5"/>
     </row>
     <row r="654">
-      <c r="G654" s="5"/>
-      <c r="H654" s="6"/>
+      <c r="H654" s="5"/>
     </row>
     <row r="655">
-      <c r="G655" s="5"/>
-      <c r="H655" s="6"/>
+      <c r="H655" s="5"/>
     </row>
     <row r="656">
-      <c r="G656" s="5"/>
-      <c r="H656" s="6"/>
+      <c r="H656" s="5"/>
     </row>
     <row r="657">
-      <c r="G657" s="5"/>
-      <c r="H657" s="6"/>
+      <c r="H657" s="5"/>
     </row>
     <row r="658">
-      <c r="G658" s="5"/>
-      <c r="H658" s="6"/>
+      <c r="H658" s="5"/>
     </row>
     <row r="659">
-      <c r="G659" s="5"/>
-      <c r="H659" s="6"/>
+      <c r="H659" s="5"/>
     </row>
     <row r="660">
-      <c r="G660" s="5"/>
-      <c r="H660" s="6"/>
+      <c r="H660" s="5"/>
     </row>
     <row r="661">
-      <c r="G661" s="5"/>
-      <c r="H661" s="6"/>
+      <c r="H661" s="5"/>
     </row>
     <row r="662">
-      <c r="G662" s="5"/>
-      <c r="H662" s="6"/>
+      <c r="H662" s="5"/>
     </row>
     <row r="663">
-      <c r="G663" s="5"/>
-      <c r="H663" s="6"/>
+      <c r="H663" s="5"/>
     </row>
     <row r="664">
-      <c r="G664" s="5"/>
-      <c r="H664" s="6"/>
+      <c r="H664" s="5"/>
     </row>
     <row r="665">
-      <c r="G665" s="5"/>
-      <c r="H665" s="6"/>
+      <c r="H665" s="5"/>
     </row>
     <row r="666">
-      <c r="G666" s="5"/>
-      <c r="H666" s="6"/>
+      <c r="H666" s="5"/>
     </row>
     <row r="667">
-      <c r="G667" s="5"/>
-      <c r="H667" s="6"/>
+      <c r="H667" s="5"/>
     </row>
     <row r="668">
-      <c r="G668" s="5"/>
-      <c r="H668" s="6"/>
+      <c r="H668" s="5"/>
     </row>
     <row r="669">
-      <c r="G669" s="5"/>
-      <c r="H669" s="6"/>
+      <c r="H669" s="5"/>
     </row>
     <row r="670">
-      <c r="G670" s="5"/>
-      <c r="H670" s="6"/>
+      <c r="H670" s="5"/>
     </row>
     <row r="671">
-      <c r="G671" s="5"/>
-      <c r="H671" s="6"/>
+      <c r="H671" s="5"/>
     </row>
     <row r="672">
-      <c r="G672" s="5"/>
-      <c r="H672" s="6"/>
+      <c r="H672" s="5"/>
     </row>
     <row r="673">
-      <c r="G673" s="5"/>
-      <c r="H673" s="6"/>
+      <c r="H673" s="5"/>
     </row>
     <row r="674">
-      <c r="G674" s="5"/>
-      <c r="H674" s="6"/>
+      <c r="H674" s="5"/>
     </row>
     <row r="675">
-      <c r="G675" s="5"/>
-      <c r="H675" s="6"/>
+      <c r="H675" s="5"/>
     </row>
     <row r="676">
-      <c r="G676" s="5"/>
-      <c r="H676" s="6"/>
+      <c r="H676" s="5"/>
     </row>
     <row r="677">
-      <c r="G677" s="5"/>
-      <c r="H677" s="6"/>
+      <c r="H677" s="5"/>
     </row>
     <row r="678">
-      <c r="G678" s="5"/>
-      <c r="H678" s="6"/>
+      <c r="H678" s="5"/>
     </row>
     <row r="679">
-      <c r="G679" s="5"/>
-      <c r="H679" s="6"/>
+      <c r="H679" s="5"/>
     </row>
     <row r="680">
-      <c r="G680" s="5"/>
-      <c r="H680" s="6"/>
+      <c r="H680" s="5"/>
     </row>
     <row r="681">
-      <c r="G681" s="5"/>
-      <c r="H681" s="6"/>
+      <c r="H681" s="5"/>
     </row>
     <row r="682">
-      <c r="G682" s="5"/>
-      <c r="H682" s="6"/>
+      <c r="H682" s="5"/>
     </row>
     <row r="683">
-      <c r="G683" s="5"/>
-      <c r="H683" s="6"/>
+      <c r="H683" s="5"/>
     </row>
     <row r="684">
-      <c r="G684" s="5"/>
-      <c r="H684" s="6"/>
+      <c r="H684" s="5"/>
     </row>
     <row r="685">
-      <c r="G685" s="5"/>
-      <c r="H685" s="6"/>
+      <c r="H685" s="5"/>
     </row>
     <row r="686">
-      <c r="G686" s="5"/>
-      <c r="H686" s="6"/>
+      <c r="H686" s="5"/>
     </row>
     <row r="687">
-      <c r="G687" s="5"/>
-      <c r="H687" s="6"/>
+      <c r="H687" s="5"/>
     </row>
     <row r="688">
-      <c r="G688" s="5"/>
-      <c r="H688" s="6"/>
+      <c r="H688" s="5"/>
     </row>
     <row r="689">
-      <c r="G689" s="5"/>
-      <c r="H689" s="6"/>
+      <c r="H689" s="5"/>
     </row>
     <row r="690">
-      <c r="G690" s="5"/>
-      <c r="H690" s="6"/>
+      <c r="H690" s="5"/>
     </row>
     <row r="691">
-      <c r="G691" s="5"/>
-      <c r="H691" s="6"/>
+      <c r="H691" s="5"/>
     </row>
     <row r="692">
-      <c r="G692" s="5"/>
-      <c r="H692" s="6"/>
+      <c r="H692" s="5"/>
     </row>
     <row r="693">
-      <c r="G693" s="5"/>
-      <c r="H693" s="6"/>
+      <c r="H693" s="5"/>
     </row>
     <row r="694">
-      <c r="G694" s="5"/>
-      <c r="H694" s="6"/>
+      <c r="H694" s="5"/>
     </row>
     <row r="695">
-      <c r="G695" s="5"/>
-      <c r="H695" s="6"/>
+      <c r="H695" s="5"/>
     </row>
     <row r="696">
-      <c r="G696" s="5"/>
-      <c r="H696" s="6"/>
+      <c r="H696" s="5"/>
     </row>
     <row r="697">
-      <c r="G697" s="5"/>
-      <c r="H697" s="6"/>
+      <c r="H697" s="5"/>
     </row>
     <row r="698">
-      <c r="G698" s="5"/>
-      <c r="H698" s="6"/>
+      <c r="H698" s="5"/>
     </row>
     <row r="699">
-      <c r="G699" s="5"/>
-      <c r="H699" s="6"/>
+      <c r="H699" s="5"/>
     </row>
     <row r="700">
-      <c r="G700" s="5"/>
-      <c r="H700" s="6"/>
+      <c r="H700" s="5"/>
     </row>
     <row r="701">
-      <c r="G701" s="5"/>
-      <c r="H701" s="6"/>
+      <c r="H701" s="5"/>
     </row>
     <row r="702">
-      <c r="G702" s="5"/>
-      <c r="H702" s="6"/>
+      <c r="H702" s="5"/>
     </row>
     <row r="703">
-      <c r="G703" s="5"/>
-      <c r="H703" s="6"/>
+      <c r="H703" s="5"/>
     </row>
     <row r="704">
-      <c r="G704" s="5"/>
-      <c r="H704" s="6"/>
+      <c r="H704" s="5"/>
     </row>
     <row r="705">
-      <c r="G705" s="5"/>
-      <c r="H705" s="6"/>
+      <c r="H705" s="5"/>
     </row>
     <row r="706">
-      <c r="G706" s="5"/>
-      <c r="H706" s="6"/>
+      <c r="H706" s="5"/>
     </row>
     <row r="707">
-      <c r="G707" s="5"/>
-      <c r="H707" s="6"/>
+      <c r="H707" s="5"/>
     </row>
     <row r="708">
-      <c r="G708" s="5"/>
-      <c r="H708" s="6"/>
+      <c r="H708" s="5"/>
     </row>
     <row r="709">
-      <c r="G709" s="5"/>
-      <c r="H709" s="6"/>
+      <c r="H709" s="5"/>
     </row>
     <row r="710">
-      <c r="G710" s="5"/>
-      <c r="H710" s="6"/>
+      <c r="H710" s="5"/>
     </row>
     <row r="711">
-      <c r="G711" s="5"/>
-      <c r="H711" s="6"/>
+      <c r="H711" s="5"/>
     </row>
     <row r="712">
-      <c r="G712" s="5"/>
-      <c r="H712" s="6"/>
+      <c r="H712" s="5"/>
     </row>
     <row r="713">
-      <c r="G713" s="5"/>
-      <c r="H713" s="6"/>
+      <c r="H713" s="5"/>
     </row>
     <row r="714">
-      <c r="G714" s="5"/>
-      <c r="H714" s="6"/>
+      <c r="H714" s="5"/>
     </row>
     <row r="715">
-      <c r="G715" s="5"/>
-      <c r="H715" s="6"/>
+      <c r="H715" s="5"/>
     </row>
     <row r="716">
-      <c r="G716" s="5"/>
-      <c r="H716" s="6"/>
+      <c r="H716" s="5"/>
     </row>
     <row r="717">
-      <c r="G717" s="5"/>
-      <c r="H717" s="6"/>
+      <c r="H717" s="5"/>
     </row>
     <row r="718">
-      <c r="G718" s="5"/>
-      <c r="H718" s="6"/>
+      <c r="H718" s="5"/>
     </row>
     <row r="719">
-      <c r="G719" s="5"/>
-      <c r="H719" s="6"/>
+      <c r="H719" s="5"/>
     </row>
     <row r="720">
-      <c r="G720" s="5"/>
-      <c r="H720" s="6"/>
+      <c r="H720" s="5"/>
     </row>
     <row r="721">
-      <c r="G721" s="5"/>
-      <c r="H721" s="6"/>
+      <c r="H721" s="5"/>
     </row>
     <row r="722">
-      <c r="G722" s="5"/>
-      <c r="H722" s="6"/>
+      <c r="H722" s="5"/>
     </row>
     <row r="723">
-      <c r="G723" s="5"/>
-      <c r="H723" s="6"/>
+      <c r="H723" s="5"/>
     </row>
     <row r="724">
-      <c r="G724" s="5"/>
-      <c r="H724" s="6"/>
+      <c r="H724" s="5"/>
     </row>
     <row r="725">
-      <c r="G725" s="5"/>
-      <c r="H725" s="6"/>
+      <c r="H725" s="5"/>
     </row>
     <row r="726">
-      <c r="G726" s="5"/>
-      <c r="H726" s="6"/>
+      <c r="H726" s="5"/>
     </row>
     <row r="727">
-      <c r="G727" s="5"/>
-      <c r="H727" s="6"/>
+      <c r="H727" s="5"/>
     </row>
     <row r="728">
-      <c r="G728" s="5"/>
-      <c r="H728" s="6"/>
+      <c r="H728" s="5"/>
     </row>
     <row r="729">
-      <c r="G729" s="5"/>
-      <c r="H729" s="6"/>
+      <c r="H729" s="5"/>
     </row>
     <row r="730">
-      <c r="G730" s="5"/>
-      <c r="H730" s="6"/>
+      <c r="H730" s="5"/>
     </row>
     <row r="731">
-      <c r="G731" s="5"/>
-      <c r="H731" s="6"/>
+      <c r="H731" s="5"/>
     </row>
     <row r="732">
-      <c r="G732" s="5"/>
-      <c r="H732" s="6"/>
+      <c r="H732" s="5"/>
     </row>
     <row r="733">
-      <c r="G733" s="5"/>
-      <c r="H733" s="6"/>
+      <c r="H733" s="5"/>
     </row>
     <row r="734">
-      <c r="G734" s="5"/>
-      <c r="H734" s="6"/>
+      <c r="H734" s="5"/>
     </row>
     <row r="735">
-      <c r="G735" s="5"/>
-      <c r="H735" s="6"/>
+      <c r="H735" s="5"/>
     </row>
     <row r="736">
-      <c r="G736" s="5"/>
-      <c r="H736" s="6"/>
+      <c r="H736" s="5"/>
     </row>
     <row r="737">
-      <c r="G737" s="5"/>
-      <c r="H737" s="6"/>
+      <c r="H737" s="5"/>
     </row>
     <row r="738">
-      <c r="G738" s="5"/>
-      <c r="H738" s="6"/>
+      <c r="H738" s="5"/>
     </row>
     <row r="739">
-      <c r="G739" s="5"/>
-      <c r="H739" s="6"/>
+      <c r="H739" s="5"/>
     </row>
     <row r="740">
-      <c r="G740" s="5"/>
-      <c r="H740" s="6"/>
+      <c r="H740" s="5"/>
     </row>
     <row r="741">
-      <c r="G741" s="5"/>
-      <c r="H741" s="6"/>
+      <c r="H741" s="5"/>
     </row>
     <row r="742">
-      <c r="G742" s="5"/>
-      <c r="H742" s="6"/>
+      <c r="H742" s="5"/>
     </row>
     <row r="743">
-      <c r="G743" s="5"/>
-      <c r="H743" s="6"/>
+      <c r="H743" s="5"/>
     </row>
     <row r="744">
-      <c r="G744" s="5"/>
-      <c r="H744" s="6"/>
+      <c r="H744" s="5"/>
     </row>
     <row r="745">
-      <c r="G745" s="5"/>
-      <c r="H745" s="6"/>
+      <c r="H745" s="5"/>
     </row>
     <row r="746">
-      <c r="G746" s="5"/>
-      <c r="H746" s="6"/>
+      <c r="H746" s="5"/>
     </row>
     <row r="747">
-      <c r="G747" s="5"/>
-      <c r="H747" s="6"/>
+      <c r="H747" s="5"/>
     </row>
     <row r="748">
-      <c r="G748" s="5"/>
-      <c r="H748" s="6"/>
+      <c r="H748" s="5"/>
     </row>
     <row r="749">
-      <c r="G749" s="5"/>
-      <c r="H749" s="6"/>
+      <c r="H749" s="5"/>
     </row>
     <row r="750">
-      <c r="G750" s="5"/>
-      <c r="H750" s="6"/>
+      <c r="H750" s="5"/>
     </row>
     <row r="751">
-      <c r="G751" s="5"/>
-      <c r="H751" s="6"/>
+      <c r="H751" s="5"/>
     </row>
     <row r="752">
-      <c r="G752" s="5"/>
-      <c r="H752" s="6"/>
+      <c r="H752" s="5"/>
     </row>
     <row r="753">
-      <c r="G753" s="5"/>
-      <c r="H753" s="6"/>
+      <c r="H753" s="5"/>
     </row>
     <row r="754">
-      <c r="G754" s="5"/>
-      <c r="H754" s="6"/>
+      <c r="H754" s="5"/>
     </row>
     <row r="755">
-      <c r="G755" s="5"/>
-      <c r="H755" s="6"/>
+      <c r="H755" s="5"/>
     </row>
     <row r="756">
-      <c r="G756" s="5"/>
-      <c r="H756" s="6"/>
+      <c r="H756" s="5"/>
     </row>
     <row r="757">
-      <c r="G757" s="5"/>
-      <c r="H757" s="6"/>
+      <c r="H757" s="5"/>
     </row>
     <row r="758">
-      <c r="G758" s="5"/>
-      <c r="H758" s="6"/>
+      <c r="H758" s="5"/>
     </row>
     <row r="759">
-      <c r="G759" s="5"/>
-      <c r="H759" s="6"/>
+      <c r="H759" s="5"/>
     </row>
     <row r="760">
-      <c r="G760" s="5"/>
-      <c r="H760" s="6"/>
+      <c r="H760" s="5"/>
     </row>
     <row r="761">
-      <c r="G761" s="5"/>
-      <c r="H761" s="6"/>
+      <c r="H761" s="5"/>
     </row>
     <row r="762">
-      <c r="G762" s="5"/>
-      <c r="H762" s="6"/>
+      <c r="H762" s="5"/>
     </row>
     <row r="763">
-      <c r="G763" s="5"/>
-      <c r="H763" s="6"/>
+      <c r="H763" s="5"/>
     </row>
     <row r="764">
-      <c r="G764" s="5"/>
-      <c r="H764" s="6"/>
+      <c r="H764" s="5"/>
     </row>
     <row r="765">
-      <c r="G765" s="5"/>
-      <c r="H765" s="6"/>
+      <c r="H765" s="5"/>
     </row>
     <row r="766">
-      <c r="G766" s="5"/>
-      <c r="H766" s="6"/>
+      <c r="H766" s="5"/>
     </row>
     <row r="767">
-      <c r="G767" s="5"/>
-      <c r="H767" s="6"/>
+      <c r="H767" s="5"/>
     </row>
     <row r="768">
-      <c r="G768" s="5"/>
-      <c r="H768" s="6"/>
+      <c r="H768" s="5"/>
     </row>
     <row r="769">
-      <c r="G769" s="5"/>
-      <c r="H769" s="6"/>
+      <c r="H769" s="5"/>
     </row>
     <row r="770">
-      <c r="G770" s="5"/>
-      <c r="H770" s="6"/>
+      <c r="H770" s="5"/>
     </row>
     <row r="771">
-      <c r="G771" s="5"/>
-      <c r="H771" s="6"/>
+      <c r="H771" s="5"/>
     </row>
     <row r="772">
-      <c r="G772" s="5"/>
-      <c r="H772" s="6"/>
+      <c r="H772" s="5"/>
     </row>
     <row r="773">
-      <c r="G773" s="5"/>
-      <c r="H773" s="6"/>
+      <c r="H773" s="5"/>
     </row>
     <row r="774">
-      <c r="G774" s="5"/>
-      <c r="H774" s="6"/>
+      <c r="H774" s="5"/>
     </row>
     <row r="775">
-      <c r="G775" s="5"/>
-      <c r="H775" s="6"/>
+      <c r="H775" s="5"/>
     </row>
     <row r="776">
-      <c r="G776" s="5"/>
-      <c r="H776" s="6"/>
+      <c r="H776" s="5"/>
     </row>
     <row r="777">
-      <c r="G777" s="5"/>
-      <c r="H777" s="6"/>
+      <c r="H777" s="5"/>
     </row>
     <row r="778">
-      <c r="G778" s="5"/>
-      <c r="H778" s="6"/>
+      <c r="H778" s="5"/>
     </row>
     <row r="779">
-      <c r="G779" s="5"/>
-      <c r="H779" s="6"/>
+      <c r="H779" s="5"/>
     </row>
     <row r="780">
-      <c r="G780" s="5"/>
-      <c r="H780" s="6"/>
+      <c r="H780" s="5"/>
     </row>
     <row r="781">
-      <c r="G781" s="5"/>
-      <c r="H781" s="6"/>
+      <c r="H781" s="5"/>
     </row>
     <row r="782">
-      <c r="G782" s="5"/>
-      <c r="H782" s="6"/>
+      <c r="H782" s="5"/>
     </row>
     <row r="783">
-      <c r="G783" s="5"/>
-      <c r="H783" s="6"/>
+      <c r="H783" s="5"/>
     </row>
     <row r="784">
-      <c r="G784" s="5"/>
-      <c r="H784" s="6"/>
+      <c r="H784" s="5"/>
     </row>
     <row r="785">
-      <c r="G785" s="5"/>
-      <c r="H785" s="6"/>
+      <c r="H785" s="5"/>
     </row>
     <row r="786">
-      <c r="G786" s="5"/>
-      <c r="H786" s="6"/>
+      <c r="H786" s="5"/>
     </row>
     <row r="787">
-      <c r="G787" s="5"/>
-      <c r="H787" s="6"/>
+      <c r="H787" s="5"/>
     </row>
     <row r="788">
-      <c r="G788" s="5"/>
-      <c r="H788" s="6"/>
+      <c r="H788" s="5"/>
     </row>
     <row r="789">
-      <c r="G789" s="5"/>
-      <c r="H789" s="6"/>
+      <c r="H789" s="5"/>
     </row>
     <row r="790">
-      <c r="G790" s="5"/>
-      <c r="H790" s="6"/>
+      <c r="H790" s="5"/>
     </row>
     <row r="791">
-      <c r="G791" s="5"/>
-      <c r="H791" s="6"/>
+      <c r="H791" s="5"/>
     </row>
     <row r="792">
-      <c r="G792" s="5"/>
-      <c r="H792" s="6"/>
+      <c r="H792" s="5"/>
     </row>
     <row r="793">
-      <c r="G793" s="5"/>
-      <c r="H793" s="6"/>
+      <c r="H793" s="5"/>
     </row>
     <row r="794">
-      <c r="G794" s="5"/>
-      <c r="H794" s="6"/>
+      <c r="H794" s="5"/>
     </row>
     <row r="795">
-      <c r="G795" s="5"/>
-      <c r="H795" s="6"/>
+      <c r="H795" s="5"/>
     </row>
     <row r="796">
-      <c r="G796" s="5"/>
-      <c r="H796" s="6"/>
+      <c r="H796" s="5"/>
     </row>
     <row r="797">
-      <c r="G797" s="5"/>
-      <c r="H797" s="6"/>
+      <c r="H797" s="5"/>
     </row>
     <row r="798">
-      <c r="G798" s="5"/>
-      <c r="H798" s="6"/>
+      <c r="H798" s="5"/>
     </row>
     <row r="799">
-      <c r="G799" s="5"/>
-      <c r="H799" s="6"/>
+      <c r="H799" s="5"/>
     </row>
     <row r="800">
-      <c r="G800" s="5"/>
-      <c r="H800" s="6"/>
+      <c r="H800" s="5"/>
     </row>
     <row r="801">
-      <c r="G801" s="5"/>
-      <c r="H801" s="6"/>
+      <c r="H801" s="5"/>
     </row>
     <row r="802">
-      <c r="G802" s="5"/>
-      <c r="H802" s="6"/>
+      <c r="H802" s="5"/>
     </row>
     <row r="803">
-      <c r="G803" s="5"/>
-      <c r="H803" s="6"/>
+      <c r="H803" s="5"/>
     </row>
     <row r="804">
-      <c r="G804" s="5"/>
-      <c r="H804" s="6"/>
+      <c r="H804" s="5"/>
     </row>
     <row r="805">
-      <c r="G805" s="5"/>
-      <c r="H805" s="6"/>
+      <c r="H805" s="5"/>
     </row>
     <row r="806">
-      <c r="G806" s="5"/>
-      <c r="H806" s="6"/>
+      <c r="H806" s="5"/>
     </row>
     <row r="807">
-      <c r="G807" s="5"/>
-      <c r="H807" s="6"/>
+      <c r="H807" s="5"/>
     </row>
     <row r="808">
-      <c r="G808" s="5"/>
-      <c r="H808" s="6"/>
+      <c r="H808" s="5"/>
     </row>
     <row r="809">
-      <c r="G809" s="5"/>
-      <c r="H809" s="6"/>
+      <c r="H809" s="5"/>
     </row>
     <row r="810">
-      <c r="G810" s="5"/>
-      <c r="H810" s="6"/>
+      <c r="H810" s="5"/>
     </row>
     <row r="811">
-      <c r="G811" s="5"/>
-      <c r="H811" s="6"/>
+      <c r="H811" s="5"/>
     </row>
     <row r="812">
-      <c r="G812" s="5"/>
-      <c r="H812" s="6"/>
+      <c r="H812" s="5"/>
     </row>
     <row r="813">
-      <c r="G813" s="5"/>
-      <c r="H813" s="6"/>
+      <c r="H813" s="5"/>
     </row>
     <row r="814">
-      <c r="G814" s="5"/>
-      <c r="H814" s="6"/>
+      <c r="H814" s="5"/>
     </row>
     <row r="815">
-      <c r="G815" s="5"/>
-      <c r="H815" s="6"/>
+      <c r="H815" s="5"/>
     </row>
     <row r="816">
-      <c r="G816" s="5"/>
-      <c r="H816" s="6"/>
+      <c r="H816" s="5"/>
     </row>
     <row r="817">
-      <c r="G817" s="5"/>
-      <c r="H817" s="6"/>
+      <c r="H817" s="5"/>
     </row>
     <row r="818">
-      <c r="G818" s="5"/>
-      <c r="H818" s="6"/>
+      <c r="H818" s="5"/>
     </row>
     <row r="819">
-      <c r="G819" s="5"/>
-      <c r="H819" s="6"/>
+      <c r="H819" s="5"/>
     </row>
     <row r="820">
-      <c r="G820" s="5"/>
-      <c r="H820" s="6"/>
+      <c r="H820" s="5"/>
     </row>
     <row r="821">
-      <c r="G821" s="5"/>
-      <c r="H821" s="6"/>
+      <c r="H821" s="5"/>
     </row>
     <row r="822">
-      <c r="G822" s="5"/>
-      <c r="H822" s="6"/>
+      <c r="H822" s="5"/>
     </row>
     <row r="823">
-      <c r="G823" s="5"/>
-      <c r="H823" s="6"/>
+      <c r="H823" s="5"/>
     </row>
     <row r="824">
-      <c r="G824" s="5"/>
-      <c r="H824" s="6"/>
+      <c r="H824" s="5"/>
     </row>
     <row r="825">
-      <c r="G825" s="5"/>
-      <c r="H825" s="6"/>
+      <c r="H825" s="5"/>
     </row>
     <row r="826">
-      <c r="G826" s="5"/>
-      <c r="H826" s="6"/>
+      <c r="H826" s="5"/>
     </row>
     <row r="827">
-      <c r="G827" s="5"/>
-      <c r="H827" s="6"/>
+      <c r="H827" s="5"/>
     </row>
     <row r="828">
-      <c r="G828" s="5"/>
-      <c r="H828" s="6"/>
+      <c r="H828" s="5"/>
     </row>
     <row r="829">
-      <c r="G829" s="5"/>
-      <c r="H829" s="6"/>
+      <c r="H829" s="5"/>
     </row>
     <row r="830">
-      <c r="G830" s="5"/>
-      <c r="H830" s="6"/>
+      <c r="H830" s="5"/>
     </row>
     <row r="831">
-      <c r="G831" s="5"/>
-      <c r="H831" s="6"/>
+      <c r="H831" s="5"/>
     </row>
     <row r="832">
-      <c r="G832" s="5"/>
-      <c r="H832" s="6"/>
+      <c r="H832" s="5"/>
     </row>
     <row r="833">
-      <c r="G833" s="5"/>
-      <c r="H833" s="6"/>
+      <c r="H833" s="5"/>
     </row>
     <row r="834">
-      <c r="G834" s="5"/>
-      <c r="H834" s="6"/>
+      <c r="H834" s="5"/>
     </row>
     <row r="835">
-      <c r="G835" s="5"/>
-      <c r="H835" s="6"/>
+      <c r="H835" s="5"/>
     </row>
     <row r="836">
-      <c r="G836" s="5"/>
-      <c r="H836" s="6"/>
+      <c r="H836" s="5"/>
     </row>
     <row r="837">
-      <c r="G837" s="5"/>
-      <c r="H837" s="6"/>
+      <c r="H837" s="5"/>
     </row>
     <row r="838">
-      <c r="G838" s="5"/>
-      <c r="H838" s="6"/>
+      <c r="H838" s="5"/>
     </row>
     <row r="839">
-      <c r="G839" s="5"/>
-      <c r="H839" s="6"/>
+      <c r="H839" s="5"/>
     </row>
     <row r="840">
-      <c r="G840" s="5"/>
-      <c r="H840" s="6"/>
+      <c r="H840" s="5"/>
     </row>
     <row r="841">
-      <c r="G841" s="5"/>
-      <c r="H841" s="6"/>
+      <c r="H841" s="5"/>
     </row>
     <row r="842">
-      <c r="G842" s="5"/>
-      <c r="H842" s="6"/>
+      <c r="H842" s="5"/>
     </row>
     <row r="843">
-      <c r="G843" s="5"/>
-      <c r="H843" s="6"/>
+      <c r="H843" s="5"/>
     </row>
     <row r="844">
-      <c r="G844" s="5"/>
-      <c r="H844" s="6"/>
+      <c r="H844" s="5"/>
     </row>
     <row r="845">
-      <c r="G845" s="5"/>
-      <c r="H845" s="6"/>
+      <c r="H845" s="5"/>
     </row>
     <row r="846">
-      <c r="G846" s="5"/>
-      <c r="H846" s="6"/>
+      <c r="H846" s="5"/>
     </row>
     <row r="847">
-      <c r="G847" s="5"/>
-      <c r="H847" s="6"/>
+      <c r="H847" s="5"/>
     </row>
     <row r="848">
-      <c r="G848" s="5"/>
-      <c r="H848" s="6"/>
+      <c r="H848" s="5"/>
     </row>
     <row r="849">
-      <c r="G849" s="5"/>
-      <c r="H849" s="6"/>
+      <c r="H849" s="5"/>
     </row>
     <row r="850">
-      <c r="G850" s="5"/>
-      <c r="H850" s="6"/>
+      <c r="H850" s="5"/>
     </row>
     <row r="851">
-      <c r="G851" s="5"/>
-      <c r="H851" s="6"/>
+      <c r="H851" s="5"/>
     </row>
     <row r="852">
-      <c r="G852" s="5"/>
-      <c r="H852" s="6"/>
+      <c r="H852" s="5"/>
     </row>
     <row r="853">
-      <c r="G853" s="5"/>
-      <c r="H853" s="6"/>
+      <c r="H853" s="5"/>
     </row>
     <row r="854">
-      <c r="G854" s="5"/>
-      <c r="H854" s="6"/>
+      <c r="H854" s="5"/>
     </row>
     <row r="855">
-      <c r="G855" s="5"/>
-      <c r="H855" s="6"/>
+      <c r="H855" s="5"/>
     </row>
     <row r="856">
-      <c r="G856" s="5"/>
-      <c r="H856" s="6"/>
+      <c r="H856" s="5"/>
     </row>
     <row r="857">
-      <c r="G857" s="5"/>
-      <c r="H857" s="6"/>
+      <c r="H857" s="5"/>
     </row>
     <row r="858">
-      <c r="G858" s="5"/>
-      <c r="H858" s="6"/>
+      <c r="H858" s="5"/>
     </row>
     <row r="859">
-      <c r="G859" s="5"/>
-      <c r="H859" s="6"/>
+      <c r="H859" s="5"/>
     </row>
     <row r="860">
-      <c r="G860" s="5"/>
-      <c r="H860" s="6"/>
+      <c r="H860" s="5"/>
     </row>
     <row r="861">
-      <c r="G861" s="5"/>
-      <c r="H861" s="6"/>
+      <c r="H861" s="5"/>
     </row>
     <row r="862">
-      <c r="G862" s="5"/>
-      <c r="H862" s="6"/>
+      <c r="H862" s="5"/>
     </row>
     <row r="863">
-      <c r="G863" s="5"/>
-      <c r="H863" s="6"/>
+      <c r="H863" s="5"/>
     </row>
     <row r="864">
-      <c r="G864" s="5"/>
-      <c r="H864" s="6"/>
+      <c r="H864" s="5"/>
     </row>
     <row r="865">
-      <c r="G865" s="5"/>
-      <c r="H865" s="6"/>
+      <c r="H865" s="5"/>
     </row>
     <row r="866">
-      <c r="G866" s="5"/>
-      <c r="H866" s="6"/>
+      <c r="H866" s="5"/>
     </row>
     <row r="867">
-      <c r="G867" s="5"/>
-      <c r="H867" s="6"/>
+      <c r="H867" s="5"/>
     </row>
     <row r="868">
-      <c r="G868" s="5"/>
-      <c r="H868" s="6"/>
+      <c r="H868" s="5"/>
     </row>
     <row r="869">
-      <c r="G869" s="5"/>
-      <c r="H869" s="6"/>
+      <c r="H869" s="5"/>
     </row>
     <row r="870">
-      <c r="G870" s="5"/>
-      <c r="H870" s="6"/>
+      <c r="H870" s="5"/>
     </row>
     <row r="871">
-      <c r="G871" s="5"/>
-      <c r="H871" s="6"/>
+      <c r="H871" s="5"/>
     </row>
     <row r="872">
-      <c r="G872" s="5"/>
-      <c r="H872" s="6"/>
+      <c r="H872" s="5"/>
     </row>
     <row r="873">
-      <c r="G873" s="5"/>
-      <c r="H873" s="6"/>
+      <c r="H873" s="5"/>
     </row>
     <row r="874">
-      <c r="G874" s="5"/>
-      <c r="H874" s="6"/>
+      <c r="H874" s="5"/>
     </row>
     <row r="875">
-      <c r="G875" s="5"/>
-      <c r="H875" s="6"/>
+      <c r="H875" s="5"/>
     </row>
     <row r="876">
-      <c r="G876" s="5"/>
-      <c r="H876" s="6"/>
+      <c r="H876" s="5"/>
     </row>
     <row r="877">
-      <c r="G877" s="5"/>
-      <c r="H877" s="6"/>
+      <c r="H877" s="5"/>
     </row>
     <row r="878">
-      <c r="G878" s="5"/>
-      <c r="H878" s="6"/>
+      <c r="H878" s="5"/>
     </row>
     <row r="879">
-      <c r="G879" s="5"/>
-      <c r="H879" s="6"/>
+      <c r="H879" s="5"/>
     </row>
     <row r="880">
-      <c r="G880" s="5"/>
-      <c r="H880" s="6"/>
+      <c r="H880" s="5"/>
     </row>
     <row r="881">
-      <c r="G881" s="5"/>
-      <c r="H881" s="6"/>
+      <c r="H881" s="5"/>
     </row>
     <row r="882">
-      <c r="G882" s="5"/>
-      <c r="H882" s="6"/>
+      <c r="H882" s="5"/>
     </row>
     <row r="883">
-      <c r="G883" s="5"/>
-      <c r="H883" s="6"/>
+      <c r="H883" s="5"/>
     </row>
     <row r="884">
-      <c r="G884" s="5"/>
-      <c r="H884" s="6"/>
+      <c r="H884" s="5"/>
     </row>
     <row r="885">
-      <c r="G885" s="5"/>
-      <c r="H885" s="6"/>
+      <c r="H885" s="5"/>
     </row>
     <row r="886">
-      <c r="G886" s="5"/>
-      <c r="H886" s="6"/>
+      <c r="H886" s="5"/>
     </row>
     <row r="887">
-      <c r="G887" s="5"/>
-      <c r="H887" s="6"/>
+      <c r="H887" s="5"/>
     </row>
     <row r="888">
-      <c r="G888" s="5"/>
-      <c r="H888" s="6"/>
+      <c r="H888" s="5"/>
     </row>
     <row r="889">
-      <c r="G889" s="5"/>
-      <c r="H889" s="6"/>
+      <c r="H889" s="5"/>
     </row>
     <row r="890">
-      <c r="G890" s="5"/>
-      <c r="H890" s="6"/>
+      <c r="H890" s="5"/>
     </row>
     <row r="891">
-      <c r="G891" s="5"/>
-      <c r="H891" s="6"/>
+      <c r="H891" s="5"/>
     </row>
     <row r="892">
-      <c r="G892" s="5"/>
-      <c r="H892" s="6"/>
+      <c r="H892" s="5"/>
     </row>
     <row r="893">
-      <c r="G893" s="5"/>
-      <c r="H893" s="6"/>
+      <c r="H893" s="5"/>
     </row>
     <row r="894">
-      <c r="G894" s="5"/>
-      <c r="H894" s="6"/>
+      <c r="H894" s="5"/>
     </row>
     <row r="895">
-      <c r="G895" s="5"/>
-      <c r="H895" s="6"/>
+      <c r="H895" s="5"/>
     </row>
     <row r="896">
-      <c r="G896" s="5"/>
-      <c r="H896" s="6"/>
+      <c r="H896" s="5"/>
     </row>
     <row r="897">
-      <c r="G897" s="5"/>
-      <c r="H897" s="6"/>
+      <c r="H897" s="5"/>
     </row>
     <row r="898">
-      <c r="G898" s="5"/>
-      <c r="H898" s="6"/>
+      <c r="H898" s="5"/>
     </row>
     <row r="899">
-      <c r="G899" s="5"/>
-      <c r="H899" s="6"/>
+      <c r="H899" s="5"/>
     </row>
     <row r="900">
-      <c r="G900" s="5"/>
-      <c r="H900" s="6"/>
+      <c r="H900" s="5"/>
     </row>
     <row r="901">
-      <c r="G901" s="5"/>
-      <c r="H901" s="6"/>
+      <c r="H901" s="5"/>
     </row>
     <row r="902">
-      <c r="G902" s="5"/>
-      <c r="H902" s="6"/>
+      <c r="H902" s="5"/>
     </row>
     <row r="903">
-      <c r="G903" s="5"/>
-      <c r="H903" s="6"/>
+      <c r="H903" s="5"/>
     </row>
     <row r="904">
-      <c r="G904" s="5"/>
-      <c r="H904" s="6"/>
+      <c r="H904" s="5"/>
     </row>
     <row r="905">
-      <c r="G905" s="5"/>
-      <c r="H905" s="6"/>
+      <c r="H905" s="5"/>
     </row>
     <row r="906">
-      <c r="G906" s="5"/>
-      <c r="H906" s="6"/>
+      <c r="H906" s="5"/>
     </row>
     <row r="907">
-      <c r="G907" s="5"/>
-      <c r="H907" s="6"/>
+      <c r="H907" s="5"/>
     </row>
     <row r="908">
-      <c r="G908" s="5"/>
-      <c r="H908" s="6"/>
+      <c r="H908" s="5"/>
     </row>
     <row r="909">
-      <c r="G909" s="5"/>
-      <c r="H909" s="6"/>
+      <c r="H909" s="5"/>
     </row>
     <row r="910">
-      <c r="G910" s="5"/>
-      <c r="H910" s="6"/>
+      <c r="H910" s="5"/>
     </row>
     <row r="911">
-      <c r="G911" s="5"/>
-      <c r="H911" s="6"/>
+      <c r="H911" s="5"/>
     </row>
     <row r="912">
-      <c r="G912" s="5"/>
-      <c r="H912" s="6"/>
+      <c r="H912" s="5"/>
     </row>
     <row r="913">
-      <c r="G913" s="5"/>
-      <c r="H913" s="6"/>
+      <c r="H913" s="5"/>
     </row>
     <row r="914">
-      <c r="G914" s="5"/>
-      <c r="H914" s="6"/>
+      <c r="H914" s="5"/>
     </row>
     <row r="915">
-      <c r="G915" s="5"/>
-      <c r="H915" s="6"/>
+      <c r="H915" s="5"/>
     </row>
     <row r="916">
-      <c r="G916" s="5"/>
-      <c r="H916" s="6"/>
+      <c r="H916" s="5"/>
     </row>
     <row r="917">
-      <c r="G917" s="5"/>
-      <c r="H917" s="6"/>
+      <c r="H917" s="5"/>
     </row>
     <row r="918">
-      <c r="G918" s="5"/>
-      <c r="H918" s="6"/>
+      <c r="H918" s="5"/>
     </row>
     <row r="919">
-      <c r="G919" s="5"/>
-      <c r="H919" s="6"/>
+      <c r="H919" s="5"/>
     </row>
     <row r="920">
-      <c r="G920" s="5"/>
-      <c r="H920" s="6"/>
+      <c r="H920" s="5"/>
     </row>
     <row r="921">
-      <c r="G921" s="5"/>
-      <c r="H921" s="6"/>
+      <c r="H921" s="5"/>
     </row>
     <row r="922">
-      <c r="G922" s="5"/>
-      <c r="H922" s="6"/>
+      <c r="H922" s="5"/>
     </row>
     <row r="923">
-      <c r="G923" s="5"/>
-      <c r="H923" s="6"/>
+      <c r="H923" s="5"/>
     </row>
     <row r="924">
-      <c r="G924" s="5"/>
-      <c r="H924" s="6"/>
+      <c r="H924" s="5"/>
     </row>
     <row r="925">
-      <c r="G925" s="5"/>
-      <c r="H925" s="6"/>
+      <c r="H925" s="5"/>
     </row>
     <row r="926">
-      <c r="G926" s="5"/>
-      <c r="H926" s="6"/>
+      <c r="H926" s="5"/>
     </row>
     <row r="927">
-      <c r="G927" s="5"/>
-      <c r="H927" s="6"/>
+      <c r="H927" s="5"/>
     </row>
     <row r="928">
-      <c r="G928" s="5"/>
-      <c r="H928" s="6"/>
+      <c r="H928" s="5"/>
     </row>
     <row r="929">
-      <c r="G929" s="5"/>
-      <c r="H929" s="6"/>
+      <c r="H929" s="5"/>
     </row>
     <row r="930">
-      <c r="G930" s="5"/>
-      <c r="H930" s="6"/>
+      <c r="H930" s="5"/>
     </row>
     <row r="931">
-      <c r="G931" s="5"/>
-      <c r="H931" s="6"/>
+      <c r="H931" s="5"/>
     </row>
     <row r="932">
-      <c r="G932" s="5"/>
-      <c r="H932" s="6"/>
+      <c r="H932" s="5"/>
     </row>
     <row r="933">
-      <c r="G933" s="5"/>
-      <c r="H933" s="6"/>
+      <c r="H933" s="5"/>
     </row>
     <row r="934">
-      <c r="G934" s="5"/>
-      <c r="H934" s="6"/>
+      <c r="H934" s="5"/>
     </row>
     <row r="935">
-      <c r="G935" s="5"/>
-      <c r="H935" s="6"/>
+      <c r="H935" s="5"/>
     </row>
     <row r="936">
-      <c r="G936" s="5"/>
-      <c r="H936" s="6"/>
+      <c r="H936" s="5"/>
     </row>
     <row r="937">
-      <c r="G937" s="5"/>
-      <c r="H937" s="6"/>
+      <c r="H937" s="5"/>
     </row>
     <row r="938">
-      <c r="G938" s="5"/>
-      <c r="H938" s="6"/>
+      <c r="H938" s="5"/>
     </row>
     <row r="939">
-      <c r="G939" s="5"/>
-      <c r="H939" s="6"/>
+      <c r="H939" s="5"/>
     </row>
     <row r="940">
-      <c r="G940" s="5"/>
-      <c r="H940" s="6"/>
+      <c r="H940" s="5"/>
     </row>
     <row r="941">
-      <c r="G941" s="5"/>
-      <c r="H941" s="6"/>
+      <c r="H941" s="5"/>
     </row>
     <row r="942">
-      <c r="G942" s="5"/>
-      <c r="H942" s="6"/>
+      <c r="H942" s="5"/>
     </row>
     <row r="943">
-      <c r="G943" s="5"/>
-      <c r="H943" s="6"/>
+      <c r="H943" s="5"/>
     </row>
     <row r="944">
-      <c r="G944" s="5"/>
-      <c r="H944" s="6"/>
+      <c r="H944" s="5"/>
     </row>
     <row r="945">
-      <c r="G945" s="5"/>
-      <c r="H945" s="6"/>
+      <c r="H945" s="5"/>
     </row>
     <row r="946">
-      <c r="G946" s="5"/>
-      <c r="H946" s="6"/>
+      <c r="H946" s="5"/>
     </row>
     <row r="947">
-      <c r="G947" s="5"/>
-      <c r="H947" s="6"/>
+      <c r="H947" s="5"/>
     </row>
     <row r="948">
-      <c r="G948" s="5"/>
-      <c r="H948" s="6"/>
+      <c r="H948" s="5"/>
     </row>
     <row r="949">
-      <c r="G949" s="5"/>
-      <c r="H949" s="6"/>
+      <c r="H949" s="5"/>
     </row>
     <row r="950">
-      <c r="G950" s="5"/>
-      <c r="H950" s="6"/>
+      <c r="H950" s="5"/>
     </row>
     <row r="951">
-      <c r="G951" s="5"/>
-      <c r="H951" s="6"/>
+      <c r="H951" s="5"/>
     </row>
     <row r="952">
-      <c r="G952" s="5"/>
-      <c r="H952" s="6"/>
+      <c r="H952" s="5"/>
     </row>
     <row r="953">
-      <c r="G953" s="5"/>
-      <c r="H953" s="6"/>
+      <c r="H953" s="5"/>
     </row>
     <row r="954">
-      <c r="G954" s="5"/>
-      <c r="H954" s="6"/>
+      <c r="H954" s="5"/>
     </row>
     <row r="955">
-      <c r="G955" s="5"/>
-      <c r="H955" s="6"/>
+      <c r="H955" s="5"/>
     </row>
     <row r="956">
-      <c r="G956" s="5"/>
-      <c r="H956" s="6"/>
+      <c r="H956" s="5"/>
     </row>
     <row r="957">
-      <c r="G957" s="5"/>
-      <c r="H957" s="6"/>
+      <c r="H957" s="5"/>
     </row>
     <row r="958">
-      <c r="G958" s="5"/>
-      <c r="H958" s="6"/>
+      <c r="H958" s="5"/>
     </row>
     <row r="959">
-      <c r="G959" s="5"/>
-      <c r="H959" s="6"/>
+      <c r="H959" s="5"/>
     </row>
     <row r="960">
-      <c r="G960" s="5"/>
-      <c r="H960" s="6"/>
+      <c r="H960" s="5"/>
     </row>
     <row r="961">
-      <c r="G961" s="5"/>
-      <c r="H961" s="6"/>
+      <c r="H961" s="5"/>
     </row>
     <row r="962">
-      <c r="G962" s="5"/>
-      <c r="H962" s="6"/>
+      <c r="H962" s="5"/>
     </row>
     <row r="963">
-      <c r="G963" s="5"/>
-      <c r="H963" s="6"/>
+      <c r="H963" s="5"/>
     </row>
     <row r="964">
-      <c r="G964" s="5"/>
-      <c r="H964" s="6"/>
+      <c r="H964" s="5"/>
     </row>
     <row r="965">
-      <c r="G965" s="5"/>
-      <c r="H965" s="6"/>
+      <c r="H965" s="5"/>
     </row>
     <row r="966">
-      <c r="G966" s="5"/>
-      <c r="H966" s="6"/>
+      <c r="H966" s="5"/>
     </row>
     <row r="967">
-      <c r="G967" s="5"/>
-      <c r="H967" s="6"/>
+      <c r="H967" s="5"/>
     </row>
     <row r="968">
-      <c r="G968" s="5"/>
-      <c r="H968" s="6"/>
+      <c r="H968" s="5"/>
     </row>
     <row r="969">
-      <c r="G969" s="5"/>
-      <c r="H969" s="6"/>
+      <c r="H969" s="5"/>
     </row>
     <row r="970">
-      <c r="G970" s="5"/>
-      <c r="H970" s="6"/>
+      <c r="H970" s="5"/>
     </row>
     <row r="971">
-      <c r="G971" s="5"/>
-      <c r="H971" s="6"/>
+      <c r="H971" s="5"/>
     </row>
     <row r="972">
-      <c r="G972" s="5"/>
-      <c r="H972" s="6"/>
+      <c r="H972" s="5"/>
     </row>
     <row r="973">
-      <c r="G973" s="5"/>
-      <c r="H973" s="6"/>
+      <c r="H973" s="5"/>
     </row>
     <row r="974">
-      <c r="G974" s="5"/>
-      <c r="H974" s="6"/>
+      <c r="H974" s="5"/>
     </row>
     <row r="975">
-      <c r="G975" s="5"/>
-      <c r="H975" s="6"/>
+      <c r="H975" s="5"/>
     </row>
     <row r="976">
-      <c r="G976" s="5"/>
-      <c r="H976" s="6"/>
+      <c r="H976" s="5"/>
     </row>
     <row r="977">
-      <c r="G977" s="5"/>
-      <c r="H977" s="6"/>
+      <c r="H977" s="5"/>
     </row>
     <row r="978">
-      <c r="G978" s="5"/>
-      <c r="H978" s="6"/>
+      <c r="H978" s="5"/>
     </row>
     <row r="979">
-      <c r="G979" s="5"/>
-      <c r="H979" s="6"/>
+      <c r="H979" s="5"/>
     </row>
     <row r="980">
-      <c r="G980" s="5"/>
-      <c r="H980" s="6"/>
+      <c r="H980" s="5"/>
     </row>
     <row r="981">
-      <c r="G981" s="5"/>
-      <c r="H981" s="6"/>
+      <c r="H981" s="5"/>
     </row>
     <row r="982">
-      <c r="G982" s="5"/>
-      <c r="H982" s="6"/>
+      <c r="H982" s="5"/>
     </row>
     <row r="983">
-      <c r="G983" s="5"/>
-      <c r="H983" s="6"/>
+      <c r="H983" s="5"/>
     </row>
     <row r="984">
-      <c r="G984" s="5"/>
-      <c r="H984" s="6"/>
+      <c r="H984" s="5"/>
     </row>
     <row r="985">
-      <c r="G985" s="5"/>
-      <c r="H985" s="6"/>
+      <c r="H985" s="5"/>
     </row>
     <row r="986">
-      <c r="G986" s="5"/>
-      <c r="H986" s="6"/>
+      <c r="H986" s="5"/>
     </row>
     <row r="987">
-      <c r="G987" s="5"/>
-      <c r="H987" s="6"/>
+      <c r="H987" s="5"/>
     </row>
     <row r="988">
-      <c r="G988" s="5"/>
-      <c r="H988" s="6"/>
+      <c r="H988" s="5"/>
     </row>
     <row r="989">
-      <c r="G989" s="5"/>
-      <c r="H989" s="6"/>
+      <c r="H989" s="5"/>
     </row>
     <row r="990">
-      <c r="G990" s="5"/>
-      <c r="H990" s="6"/>
+      <c r="H990" s="5"/>
     </row>
     <row r="991">
-      <c r="G991" s="5"/>
-      <c r="H991" s="6"/>
+      <c r="H991" s="5"/>
     </row>
     <row r="992">
-      <c r="G992" s="5"/>
-      <c r="H992" s="6"/>
+      <c r="H992" s="5"/>
     </row>
     <row r="993">
-      <c r="G993" s="5"/>
-      <c r="H993" s="6"/>
+      <c r="H993" s="5"/>
     </row>
     <row r="994">
-      <c r="G994" s="5"/>
-      <c r="H994" s="6"/>
+      <c r="H994" s="5"/>
     </row>
     <row r="995">
-      <c r="G995" s="5"/>
-      <c r="H995" s="6"/>
+      <c r="H995" s="5"/>
     </row>
     <row r="996">
-      <c r="G996" s="5"/>
-      <c r="H996" s="6"/>
+      <c r="H996" s="5"/>
     </row>
     <row r="997">
-      <c r="G997" s="5"/>
-      <c r="H997" s="6"/>
+      <c r="H997" s="5"/>
     </row>
     <row r="998">
-      <c r="G998" s="5"/>
-      <c r="H998" s="6"/>
+      <c r="H998" s="5"/>
     </row>
     <row r="999">
-      <c r="G999" s="5"/>
-      <c r="H999" s="6"/>
+      <c r="H999" s="5"/>
     </row>
     <row r="1000">
-      <c r="G1000" s="5"/>
-      <c r="H1000" s="6"/>
+      <c r="H1000" s="5"/>
+    </row>
+    <row r="1001">
+      <c r="H1001" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -8941,13 +7836,13 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>56</v>
@@ -8958,10 +7853,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1">
         <v>10.0</v>
@@ -8970,24 +7865,24 @@
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C3" s="1">
         <v>10.0</v>
@@ -8996,24 +7891,24 @@
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
@@ -9022,24 +7917,22 @@
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>143</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C5" s="1">
         <v>10.0</v>
@@ -9048,50 +7941,27 @@
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C7" s="1">
         <v>3.0</v>
@@ -9100,24 +7970,24 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C8" s="1">
         <v>0.0</v>
@@ -9126,24 +7996,22 @@
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>154</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G8" s="6"/>
       <c r="H8" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C9" s="1">
         <v>3.0</v>
@@ -9152,21 +8020,21 @@
         <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C10" s="1">
         <v>3.0</v>
@@ -9175,21 +8043,21 @@
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1">
         <v>3.0</v>
@@ -9198,24 +8066,24 @@
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -9224,27 +8092,27 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C13" s="1">
         <v>3.0</v>
@@ -9253,24 +8121,22 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>166</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G13" s="4"/>
       <c r="H13" s="1" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C14" s="1">
         <v>3.0</v>
@@ -9279,24 +8145,24 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1">
         <v>3.0</v>
@@ -9305,24 +8171,24 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C16" s="1">
         <v>3.0</v>
@@ -9331,24 +8197,24 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C17" s="1">
         <v>1.0</v>
@@ -9357,22 +8223,22 @@
         <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C18" s="1">
         <v>1.0</v>
@@ -9381,24 +8247,21 @@
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C19" s="1">
         <v>1.0</v>
@@ -9407,21 +8270,21 @@
         <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C20" s="1">
         <v>0.0</v>
@@ -9430,19 +8293,19 @@
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G20" s="9"/>
+        <v>146</v>
+      </c>
+      <c r="G20" s="6"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C21" s="1">
         <v>1.0</v>
@@ -9451,16 +8314,16 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
@@ -9471,18 +8334,24 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24">
-      <c r="G24" s="5"/>
+      <c r="G24" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="J24" s="4"/>
     </row>
     <row r="25">
-      <c r="G25" s="5"/>
+      <c r="G25" s="4" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="26">
-      <c r="G26" s="5"/>
+      <c r="G26" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="J26" s="4"/>
     </row>
     <row r="27">
-      <c r="G27" s="5"/>
+      <c r="G27" s="4"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28">
@@ -12430,7 +11299,7 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>56</v>
@@ -12441,10 +11310,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -12452,19 +11321,14 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>193</v>
-      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
@@ -12472,16 +11336,14 @@
       <c r="D3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>195</v>
-      </c>
+      <c r="E3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
@@ -12490,18 +11352,15 @@
         <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
@@ -12510,18 +11369,15 @@
         <v>34</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3.0</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C6" s="1">
         <v>1.0</v>
@@ -12529,9 +11385,7 @@
       <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>202</v>
-      </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7">
       <c r="E7" s="5"/>
@@ -15541,7 +14395,7 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>56</v>
@@ -15549,10 +14403,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -15561,15 +14415,15 @@
         <v>56.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
@@ -15578,15 +14432,15 @@
         <v>56.0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
@@ -15595,7 +14449,7 @@
         <v>84.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -15609,63 +14463,62 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="17.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>220</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="215">
   <si>
     <t>Discards</t>
   </si>
@@ -587,9 +587,6 @@
     <t xml:space="preserve">Draw all Destroyed balls. </t>
   </si>
   <si>
-    <t>Strength</t>
-  </si>
-  <si>
     <t>Black 1</t>
   </si>
   <si>
@@ -616,6 +613,9 @@
   </si>
   <si>
     <t>Black 5</t>
+  </si>
+  <si>
+    <t>Strength</t>
   </si>
   <si>
     <t>Judgement 1</t>
@@ -7503,8 +7503,9 @@
       <c r="E2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>95</v>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1">
+        <v>1.0</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>95</v>
@@ -7526,8 +7527,9 @@
       <c r="E3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>95</v>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>1.0</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>95</v>
@@ -7549,8 +7551,9 @@
       <c r="E4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>95</v>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>1.0</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>95</v>
@@ -11107,6 +11110,12 @@
       <c r="E2" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>143</v>
       </c>
@@ -11127,6 +11136,12 @@
       <c r="E3" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="H3" s="1" t="s">
         <v>145</v>
       </c>
@@ -11147,6 +11162,12 @@
       <c r="E4" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>147</v>
       </c>
@@ -11167,6 +11188,12 @@
       <c r="E5" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="H5" s="1" t="s">
         <v>149</v>
       </c>
@@ -11186,6 +11213,12 @@
       </c>
       <c r="E6" s="1" t="s">
         <v>96</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>151</v>
@@ -15500,7 +15533,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="33.75"/>
+    <col customWidth="1" min="4" max="4" width="33.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15513,3078 +15546,3060 @@
       <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>189</v>
+      <c r="D2" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C3" s="1">
         <v>0.0</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>192</v>
+      <c r="D4" s="4" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>194</v>
+      <c r="D5" s="4" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C6" s="1">
         <v>0.0</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7">
-      <c r="E7" s="5"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8">
-      <c r="E8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9">
-      <c r="E9" s="5"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10">
-      <c r="E10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11">
-      <c r="E11" s="5"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12">
-      <c r="E12" s="5"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13">
-      <c r="E13" s="5"/>
+      <c r="D13" s="5"/>
     </row>
     <row r="14">
-      <c r="E14" s="5"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15">
-      <c r="E15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16">
-      <c r="E16" s="5"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17">
-      <c r="E17" s="5"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18">
-      <c r="E18" s="5"/>
+      <c r="D18" s="5"/>
     </row>
     <row r="19">
-      <c r="E19" s="5"/>
+      <c r="D19" s="5"/>
     </row>
     <row r="20">
-      <c r="E20" s="5"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="21">
-      <c r="E21" s="5"/>
+      <c r="D21" s="5"/>
     </row>
     <row r="22">
-      <c r="E22" s="5"/>
+      <c r="D22" s="5"/>
     </row>
     <row r="23">
-      <c r="E23" s="5"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24">
-      <c r="E24" s="5"/>
+      <c r="D24" s="5"/>
     </row>
     <row r="25">
-      <c r="E25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26">
-      <c r="E26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27">
-      <c r="E27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28">
-      <c r="E28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29">
-      <c r="E29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30">
-      <c r="E30" s="5"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31">
-      <c r="E31" s="5"/>
+      <c r="D31" s="5"/>
     </row>
     <row r="32">
-      <c r="E32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
     <row r="33">
-      <c r="E33" s="5"/>
+      <c r="D33" s="5"/>
     </row>
     <row r="34">
-      <c r="E34" s="5"/>
+      <c r="D34" s="5"/>
     </row>
     <row r="35">
-      <c r="E35" s="5"/>
+      <c r="D35" s="5"/>
     </row>
     <row r="36">
-      <c r="E36" s="5"/>
+      <c r="D36" s="5"/>
     </row>
     <row r="37">
-      <c r="E37" s="5"/>
+      <c r="D37" s="5"/>
     </row>
     <row r="38">
-      <c r="E38" s="5"/>
+      <c r="D38" s="5"/>
     </row>
     <row r="39">
-      <c r="E39" s="5"/>
+      <c r="D39" s="5"/>
     </row>
     <row r="40">
-      <c r="E40" s="5"/>
+      <c r="D40" s="5"/>
     </row>
     <row r="41">
-      <c r="E41" s="5"/>
+      <c r="D41" s="5"/>
     </row>
     <row r="42">
-      <c r="E42" s="5"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43">
-      <c r="E43" s="5"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44">
-      <c r="E44" s="5"/>
+      <c r="D44" s="5"/>
     </row>
     <row r="45">
-      <c r="E45" s="5"/>
+      <c r="D45" s="5"/>
     </row>
     <row r="46">
-      <c r="E46" s="5"/>
+      <c r="D46" s="5"/>
     </row>
     <row r="47">
-      <c r="E47" s="5"/>
+      <c r="D47" s="5"/>
     </row>
     <row r="48">
-      <c r="E48" s="5"/>
+      <c r="D48" s="5"/>
     </row>
     <row r="49">
-      <c r="E49" s="5"/>
+      <c r="D49" s="5"/>
     </row>
     <row r="50">
-      <c r="E50" s="5"/>
+      <c r="D50" s="5"/>
     </row>
     <row r="51">
-      <c r="E51" s="5"/>
+      <c r="D51" s="5"/>
     </row>
     <row r="52">
-      <c r="E52" s="5"/>
+      <c r="D52" s="5"/>
     </row>
     <row r="53">
-      <c r="E53" s="5"/>
+      <c r="D53" s="5"/>
     </row>
     <row r="54">
-      <c r="E54" s="5"/>
+      <c r="D54" s="5"/>
     </row>
     <row r="55">
-      <c r="E55" s="5"/>
+      <c r="D55" s="5"/>
     </row>
     <row r="56">
-      <c r="E56" s="5"/>
+      <c r="D56" s="5"/>
     </row>
     <row r="57">
-      <c r="E57" s="5"/>
+      <c r="D57" s="5"/>
     </row>
     <row r="58">
-      <c r="E58" s="5"/>
+      <c r="D58" s="5"/>
     </row>
     <row r="59">
-      <c r="E59" s="5"/>
+      <c r="D59" s="5"/>
     </row>
     <row r="60">
-      <c r="E60" s="5"/>
+      <c r="D60" s="5"/>
     </row>
     <row r="61">
-      <c r="E61" s="5"/>
+      <c r="D61" s="5"/>
     </row>
     <row r="62">
-      <c r="E62" s="5"/>
+      <c r="D62" s="5"/>
     </row>
     <row r="63">
-      <c r="E63" s="5"/>
+      <c r="D63" s="5"/>
     </row>
     <row r="64">
-      <c r="E64" s="5"/>
+      <c r="D64" s="5"/>
     </row>
     <row r="65">
-      <c r="E65" s="5"/>
+      <c r="D65" s="5"/>
     </row>
     <row r="66">
-      <c r="E66" s="5"/>
+      <c r="D66" s="5"/>
     </row>
     <row r="67">
-      <c r="E67" s="5"/>
+      <c r="D67" s="5"/>
     </row>
     <row r="68">
-      <c r="E68" s="5"/>
+      <c r="D68" s="5"/>
     </row>
     <row r="69">
-      <c r="E69" s="5"/>
+      <c r="D69" s="5"/>
     </row>
     <row r="70">
-      <c r="E70" s="5"/>
+      <c r="D70" s="5"/>
     </row>
     <row r="71">
-      <c r="E71" s="5"/>
+      <c r="D71" s="5"/>
     </row>
     <row r="72">
-      <c r="E72" s="5"/>
+      <c r="D72" s="5"/>
     </row>
     <row r="73">
-      <c r="E73" s="5"/>
+      <c r="D73" s="5"/>
     </row>
     <row r="74">
-      <c r="E74" s="5"/>
+      <c r="D74" s="5"/>
     </row>
     <row r="75">
-      <c r="E75" s="5"/>
+      <c r="D75" s="5"/>
     </row>
     <row r="76">
-      <c r="E76" s="5"/>
+      <c r="D76" s="5"/>
     </row>
     <row r="77">
-      <c r="E77" s="5"/>
+      <c r="D77" s="5"/>
     </row>
     <row r="78">
-      <c r="E78" s="5"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79">
-      <c r="E79" s="5"/>
+      <c r="D79" s="5"/>
     </row>
     <row r="80">
-      <c r="E80" s="5"/>
+      <c r="D80" s="5"/>
     </row>
     <row r="81">
-      <c r="E81" s="5"/>
+      <c r="D81" s="5"/>
     </row>
     <row r="82">
-      <c r="E82" s="5"/>
+      <c r="D82" s="5"/>
     </row>
     <row r="83">
-      <c r="E83" s="5"/>
+      <c r="D83" s="5"/>
     </row>
     <row r="84">
-      <c r="E84" s="5"/>
+      <c r="D84" s="5"/>
     </row>
     <row r="85">
-      <c r="E85" s="5"/>
+      <c r="D85" s="5"/>
     </row>
     <row r="86">
-      <c r="E86" s="5"/>
+      <c r="D86" s="5"/>
     </row>
     <row r="87">
-      <c r="E87" s="5"/>
+      <c r="D87" s="5"/>
     </row>
     <row r="88">
-      <c r="E88" s="5"/>
+      <c r="D88" s="5"/>
     </row>
     <row r="89">
-      <c r="E89" s="5"/>
+      <c r="D89" s="5"/>
     </row>
     <row r="90">
-      <c r="E90" s="5"/>
+      <c r="D90" s="5"/>
     </row>
     <row r="91">
-      <c r="E91" s="5"/>
+      <c r="D91" s="5"/>
     </row>
     <row r="92">
-      <c r="E92" s="5"/>
+      <c r="D92" s="5"/>
     </row>
     <row r="93">
-      <c r="E93" s="5"/>
+      <c r="D93" s="5"/>
     </row>
     <row r="94">
-      <c r="E94" s="5"/>
+      <c r="D94" s="5"/>
     </row>
     <row r="95">
-      <c r="E95" s="5"/>
+      <c r="D95" s="5"/>
     </row>
     <row r="96">
-      <c r="E96" s="5"/>
+      <c r="D96" s="5"/>
     </row>
     <row r="97">
-      <c r="E97" s="5"/>
+      <c r="D97" s="5"/>
     </row>
     <row r="98">
-      <c r="E98" s="5"/>
+      <c r="D98" s="5"/>
     </row>
     <row r="99">
-      <c r="E99" s="5"/>
+      <c r="D99" s="5"/>
     </row>
     <row r="100">
-      <c r="E100" s="5"/>
+      <c r="D100" s="5"/>
     </row>
     <row r="101">
-      <c r="E101" s="5"/>
+      <c r="D101" s="5"/>
     </row>
     <row r="102">
-      <c r="E102" s="5"/>
+      <c r="D102" s="5"/>
     </row>
     <row r="103">
-      <c r="E103" s="5"/>
+      <c r="D103" s="5"/>
     </row>
     <row r="104">
-      <c r="E104" s="5"/>
+      <c r="D104" s="5"/>
     </row>
     <row r="105">
-      <c r="E105" s="5"/>
+      <c r="D105" s="5"/>
     </row>
     <row r="106">
-      <c r="E106" s="5"/>
+      <c r="D106" s="5"/>
     </row>
     <row r="107">
-      <c r="E107" s="5"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108">
-      <c r="E108" s="5"/>
+      <c r="D108" s="5"/>
     </row>
     <row r="109">
-      <c r="E109" s="5"/>
+      <c r="D109" s="5"/>
     </row>
     <row r="110">
-      <c r="E110" s="5"/>
+      <c r="D110" s="5"/>
     </row>
     <row r="111">
-      <c r="E111" s="5"/>
+      <c r="D111" s="5"/>
     </row>
     <row r="112">
-      <c r="E112" s="5"/>
+      <c r="D112" s="5"/>
     </row>
     <row r="113">
-      <c r="E113" s="5"/>
+      <c r="D113" s="5"/>
     </row>
     <row r="114">
-      <c r="E114" s="5"/>
+      <c r="D114" s="5"/>
     </row>
     <row r="115">
-      <c r="E115" s="5"/>
+      <c r="D115" s="5"/>
     </row>
     <row r="116">
-      <c r="E116" s="5"/>
+      <c r="D116" s="5"/>
     </row>
     <row r="117">
-      <c r="E117" s="5"/>
+      <c r="D117" s="5"/>
     </row>
     <row r="118">
-      <c r="E118" s="5"/>
+      <c r="D118" s="5"/>
     </row>
     <row r="119">
-      <c r="E119" s="5"/>
+      <c r="D119" s="5"/>
     </row>
     <row r="120">
-      <c r="E120" s="5"/>
+      <c r="D120" s="5"/>
     </row>
     <row r="121">
-      <c r="E121" s="5"/>
+      <c r="D121" s="5"/>
     </row>
     <row r="122">
-      <c r="E122" s="5"/>
+      <c r="D122" s="5"/>
     </row>
     <row r="123">
-      <c r="E123" s="5"/>
+      <c r="D123" s="5"/>
     </row>
     <row r="124">
-      <c r="E124" s="5"/>
+      <c r="D124" s="5"/>
     </row>
     <row r="125">
-      <c r="E125" s="5"/>
+      <c r="D125" s="5"/>
     </row>
     <row r="126">
-      <c r="E126" s="5"/>
+      <c r="D126" s="5"/>
     </row>
     <row r="127">
-      <c r="E127" s="5"/>
+      <c r="D127" s="5"/>
     </row>
     <row r="128">
-      <c r="E128" s="5"/>
+      <c r="D128" s="5"/>
     </row>
     <row r="129">
-      <c r="E129" s="5"/>
+      <c r="D129" s="5"/>
     </row>
     <row r="130">
-      <c r="E130" s="5"/>
+      <c r="D130" s="5"/>
     </row>
     <row r="131">
-      <c r="E131" s="5"/>
+      <c r="D131" s="5"/>
     </row>
     <row r="132">
-      <c r="E132" s="5"/>
+      <c r="D132" s="5"/>
     </row>
     <row r="133">
-      <c r="E133" s="5"/>
+      <c r="D133" s="5"/>
     </row>
     <row r="134">
-      <c r="E134" s="5"/>
+      <c r="D134" s="5"/>
     </row>
     <row r="135">
-      <c r="E135" s="5"/>
+      <c r="D135" s="5"/>
     </row>
     <row r="136">
-      <c r="E136" s="5"/>
+      <c r="D136" s="5"/>
     </row>
     <row r="137">
-      <c r="E137" s="5"/>
+      <c r="D137" s="5"/>
     </row>
     <row r="138">
-      <c r="E138" s="5"/>
+      <c r="D138" s="5"/>
     </row>
     <row r="139">
-      <c r="E139" s="5"/>
+      <c r="D139" s="5"/>
     </row>
     <row r="140">
-      <c r="E140" s="5"/>
+      <c r="D140" s="5"/>
     </row>
     <row r="141">
-      <c r="E141" s="5"/>
+      <c r="D141" s="5"/>
     </row>
     <row r="142">
-      <c r="E142" s="5"/>
+      <c r="D142" s="5"/>
     </row>
     <row r="143">
-      <c r="E143" s="5"/>
+      <c r="D143" s="5"/>
     </row>
     <row r="144">
-      <c r="E144" s="5"/>
+      <c r="D144" s="5"/>
     </row>
     <row r="145">
-      <c r="E145" s="5"/>
+      <c r="D145" s="5"/>
     </row>
     <row r="146">
-      <c r="E146" s="5"/>
+      <c r="D146" s="5"/>
     </row>
     <row r="147">
-      <c r="E147" s="5"/>
+      <c r="D147" s="5"/>
     </row>
     <row r="148">
-      <c r="E148" s="5"/>
+      <c r="D148" s="5"/>
     </row>
     <row r="149">
-      <c r="E149" s="5"/>
+      <c r="D149" s="5"/>
     </row>
     <row r="150">
-      <c r="E150" s="5"/>
+      <c r="D150" s="5"/>
     </row>
     <row r="151">
-      <c r="E151" s="5"/>
+      <c r="D151" s="5"/>
     </row>
     <row r="152">
-      <c r="E152" s="5"/>
+      <c r="D152" s="5"/>
     </row>
     <row r="153">
-      <c r="E153" s="5"/>
+      <c r="D153" s="5"/>
     </row>
     <row r="154">
-      <c r="E154" s="5"/>
+      <c r="D154" s="5"/>
     </row>
     <row r="155">
-      <c r="E155" s="5"/>
+      <c r="D155" s="5"/>
     </row>
     <row r="156">
-      <c r="E156" s="5"/>
+      <c r="D156" s="5"/>
     </row>
     <row r="157">
-      <c r="E157" s="5"/>
+      <c r="D157" s="5"/>
     </row>
     <row r="158">
-      <c r="E158" s="5"/>
+      <c r="D158" s="5"/>
     </row>
     <row r="159">
-      <c r="E159" s="5"/>
+      <c r="D159" s="5"/>
     </row>
     <row r="160">
-      <c r="E160" s="5"/>
+      <c r="D160" s="5"/>
     </row>
     <row r="161">
-      <c r="E161" s="5"/>
+      <c r="D161" s="5"/>
     </row>
     <row r="162">
-      <c r="E162" s="5"/>
+      <c r="D162" s="5"/>
     </row>
     <row r="163">
-      <c r="E163" s="5"/>
+      <c r="D163" s="5"/>
     </row>
     <row r="164">
-      <c r="E164" s="5"/>
+      <c r="D164" s="5"/>
     </row>
     <row r="165">
-      <c r="E165" s="5"/>
+      <c r="D165" s="5"/>
     </row>
     <row r="166">
-      <c r="E166" s="5"/>
+      <c r="D166" s="5"/>
     </row>
     <row r="167">
-      <c r="E167" s="5"/>
+      <c r="D167" s="5"/>
     </row>
     <row r="168">
-      <c r="E168" s="5"/>
+      <c r="D168" s="5"/>
     </row>
     <row r="169">
-      <c r="E169" s="5"/>
+      <c r="D169" s="5"/>
     </row>
     <row r="170">
-      <c r="E170" s="5"/>
+      <c r="D170" s="5"/>
     </row>
     <row r="171">
-      <c r="E171" s="5"/>
+      <c r="D171" s="5"/>
     </row>
     <row r="172">
-      <c r="E172" s="5"/>
+      <c r="D172" s="5"/>
     </row>
     <row r="173">
-      <c r="E173" s="5"/>
+      <c r="D173" s="5"/>
     </row>
     <row r="174">
-      <c r="E174" s="5"/>
+      <c r="D174" s="5"/>
     </row>
     <row r="175">
-      <c r="E175" s="5"/>
+      <c r="D175" s="5"/>
     </row>
     <row r="176">
-      <c r="E176" s="5"/>
+      <c r="D176" s="5"/>
     </row>
     <row r="177">
-      <c r="E177" s="5"/>
+      <c r="D177" s="5"/>
     </row>
     <row r="178">
-      <c r="E178" s="5"/>
+      <c r="D178" s="5"/>
     </row>
     <row r="179">
-      <c r="E179" s="5"/>
+      <c r="D179" s="5"/>
     </row>
     <row r="180">
-      <c r="E180" s="5"/>
+      <c r="D180" s="5"/>
     </row>
     <row r="181">
-      <c r="E181" s="5"/>
+      <c r="D181" s="5"/>
     </row>
     <row r="182">
-      <c r="E182" s="5"/>
+      <c r="D182" s="5"/>
     </row>
     <row r="183">
-      <c r="E183" s="5"/>
+      <c r="D183" s="5"/>
     </row>
     <row r="184">
-      <c r="E184" s="5"/>
+      <c r="D184" s="5"/>
     </row>
     <row r="185">
-      <c r="E185" s="5"/>
+      <c r="D185" s="5"/>
     </row>
     <row r="186">
-      <c r="E186" s="5"/>
+      <c r="D186" s="5"/>
     </row>
     <row r="187">
-      <c r="E187" s="5"/>
+      <c r="D187" s="5"/>
     </row>
     <row r="188">
-      <c r="E188" s="5"/>
+      <c r="D188" s="5"/>
     </row>
     <row r="189">
-      <c r="E189" s="5"/>
+      <c r="D189" s="5"/>
     </row>
     <row r="190">
-      <c r="E190" s="5"/>
+      <c r="D190" s="5"/>
     </row>
     <row r="191">
-      <c r="E191" s="5"/>
+      <c r="D191" s="5"/>
     </row>
     <row r="192">
-      <c r="E192" s="5"/>
+      <c r="D192" s="5"/>
     </row>
     <row r="193">
-      <c r="E193" s="5"/>
+      <c r="D193" s="5"/>
     </row>
     <row r="194">
-      <c r="E194" s="5"/>
+      <c r="D194" s="5"/>
     </row>
     <row r="195">
-      <c r="E195" s="5"/>
+      <c r="D195" s="5"/>
     </row>
     <row r="196">
-      <c r="E196" s="5"/>
+      <c r="D196" s="5"/>
     </row>
     <row r="197">
-      <c r="E197" s="5"/>
+      <c r="D197" s="5"/>
     </row>
     <row r="198">
-      <c r="E198" s="5"/>
+      <c r="D198" s="5"/>
     </row>
     <row r="199">
-      <c r="E199" s="5"/>
+      <c r="D199" s="5"/>
     </row>
     <row r="200">
-      <c r="E200" s="5"/>
+      <c r="D200" s="5"/>
     </row>
     <row r="201">
-      <c r="E201" s="5"/>
+      <c r="D201" s="5"/>
     </row>
     <row r="202">
-      <c r="E202" s="5"/>
+      <c r="D202" s="5"/>
     </row>
     <row r="203">
-      <c r="E203" s="5"/>
+      <c r="D203" s="5"/>
     </row>
     <row r="204">
-      <c r="E204" s="5"/>
+      <c r="D204" s="5"/>
     </row>
     <row r="205">
-      <c r="E205" s="5"/>
+      <c r="D205" s="5"/>
     </row>
     <row r="206">
-      <c r="E206" s="5"/>
+      <c r="D206" s="5"/>
     </row>
     <row r="207">
-      <c r="E207" s="5"/>
+      <c r="D207" s="5"/>
     </row>
     <row r="208">
-      <c r="E208" s="5"/>
+      <c r="D208" s="5"/>
     </row>
     <row r="209">
-      <c r="E209" s="5"/>
+      <c r="D209" s="5"/>
     </row>
     <row r="210">
-      <c r="E210" s="5"/>
+      <c r="D210" s="5"/>
     </row>
     <row r="211">
-      <c r="E211" s="5"/>
+      <c r="D211" s="5"/>
     </row>
     <row r="212">
-      <c r="E212" s="5"/>
+      <c r="D212" s="5"/>
     </row>
     <row r="213">
-      <c r="E213" s="5"/>
+      <c r="D213" s="5"/>
     </row>
     <row r="214">
-      <c r="E214" s="5"/>
+      <c r="D214" s="5"/>
     </row>
     <row r="215">
-      <c r="E215" s="5"/>
+      <c r="D215" s="5"/>
     </row>
     <row r="216">
-      <c r="E216" s="5"/>
+      <c r="D216" s="5"/>
     </row>
     <row r="217">
-      <c r="E217" s="5"/>
+      <c r="D217" s="5"/>
     </row>
     <row r="218">
-      <c r="E218" s="5"/>
+      <c r="D218" s="5"/>
     </row>
     <row r="219">
-      <c r="E219" s="5"/>
+      <c r="D219" s="5"/>
     </row>
     <row r="220">
-      <c r="E220" s="5"/>
+      <c r="D220" s="5"/>
     </row>
     <row r="221">
-      <c r="E221" s="5"/>
+      <c r="D221" s="5"/>
     </row>
     <row r="222">
-      <c r="E222" s="5"/>
+      <c r="D222" s="5"/>
     </row>
     <row r="223">
-      <c r="E223" s="5"/>
+      <c r="D223" s="5"/>
     </row>
     <row r="224">
-      <c r="E224" s="5"/>
+      <c r="D224" s="5"/>
     </row>
     <row r="225">
-      <c r="E225" s="5"/>
+      <c r="D225" s="5"/>
     </row>
     <row r="226">
-      <c r="E226" s="5"/>
+      <c r="D226" s="5"/>
     </row>
     <row r="227">
-      <c r="E227" s="5"/>
+      <c r="D227" s="5"/>
     </row>
     <row r="228">
-      <c r="E228" s="5"/>
+      <c r="D228" s="5"/>
     </row>
     <row r="229">
-      <c r="E229" s="5"/>
+      <c r="D229" s="5"/>
     </row>
     <row r="230">
-      <c r="E230" s="5"/>
+      <c r="D230" s="5"/>
     </row>
     <row r="231">
-      <c r="E231" s="5"/>
+      <c r="D231" s="5"/>
     </row>
     <row r="232">
-      <c r="E232" s="5"/>
+      <c r="D232" s="5"/>
     </row>
     <row r="233">
-      <c r="E233" s="5"/>
+      <c r="D233" s="5"/>
     </row>
     <row r="234">
-      <c r="E234" s="5"/>
+      <c r="D234" s="5"/>
     </row>
     <row r="235">
-      <c r="E235" s="5"/>
+      <c r="D235" s="5"/>
     </row>
     <row r="236">
-      <c r="E236" s="5"/>
+      <c r="D236" s="5"/>
     </row>
     <row r="237">
-      <c r="E237" s="5"/>
+      <c r="D237" s="5"/>
     </row>
     <row r="238">
-      <c r="E238" s="5"/>
+      <c r="D238" s="5"/>
     </row>
     <row r="239">
-      <c r="E239" s="5"/>
+      <c r="D239" s="5"/>
     </row>
     <row r="240">
-      <c r="E240" s="5"/>
+      <c r="D240" s="5"/>
     </row>
     <row r="241">
-      <c r="E241" s="5"/>
+      <c r="D241" s="5"/>
     </row>
     <row r="242">
-      <c r="E242" s="5"/>
+      <c r="D242" s="5"/>
     </row>
     <row r="243">
-      <c r="E243" s="5"/>
+      <c r="D243" s="5"/>
     </row>
     <row r="244">
-      <c r="E244" s="5"/>
+      <c r="D244" s="5"/>
     </row>
     <row r="245">
-      <c r="E245" s="5"/>
+      <c r="D245" s="5"/>
     </row>
     <row r="246">
-      <c r="E246" s="5"/>
+      <c r="D246" s="5"/>
     </row>
     <row r="247">
-      <c r="E247" s="5"/>
+      <c r="D247" s="5"/>
     </row>
     <row r="248">
-      <c r="E248" s="5"/>
+      <c r="D248" s="5"/>
     </row>
     <row r="249">
-      <c r="E249" s="5"/>
+      <c r="D249" s="5"/>
     </row>
     <row r="250">
-      <c r="E250" s="5"/>
+      <c r="D250" s="5"/>
     </row>
     <row r="251">
-      <c r="E251" s="5"/>
+      <c r="D251" s="5"/>
     </row>
     <row r="252">
-      <c r="E252" s="5"/>
+      <c r="D252" s="5"/>
     </row>
     <row r="253">
-      <c r="E253" s="5"/>
+      <c r="D253" s="5"/>
     </row>
     <row r="254">
-      <c r="E254" s="5"/>
+      <c r="D254" s="5"/>
     </row>
     <row r="255">
-      <c r="E255" s="5"/>
+      <c r="D255" s="5"/>
     </row>
     <row r="256">
-      <c r="E256" s="5"/>
+      <c r="D256" s="5"/>
     </row>
     <row r="257">
-      <c r="E257" s="5"/>
+      <c r="D257" s="5"/>
     </row>
     <row r="258">
-      <c r="E258" s="5"/>
+      <c r="D258" s="5"/>
     </row>
     <row r="259">
-      <c r="E259" s="5"/>
+      <c r="D259" s="5"/>
     </row>
     <row r="260">
-      <c r="E260" s="5"/>
+      <c r="D260" s="5"/>
     </row>
     <row r="261">
-      <c r="E261" s="5"/>
+      <c r="D261" s="5"/>
     </row>
     <row r="262">
-      <c r="E262" s="5"/>
+      <c r="D262" s="5"/>
     </row>
     <row r="263">
-      <c r="E263" s="5"/>
+      <c r="D263" s="5"/>
     </row>
     <row r="264">
-      <c r="E264" s="5"/>
+      <c r="D264" s="5"/>
     </row>
     <row r="265">
-      <c r="E265" s="5"/>
+      <c r="D265" s="5"/>
     </row>
     <row r="266">
-      <c r="E266" s="5"/>
+      <c r="D266" s="5"/>
     </row>
     <row r="267">
-      <c r="E267" s="5"/>
+      <c r="D267" s="5"/>
     </row>
     <row r="268">
-      <c r="E268" s="5"/>
+      <c r="D268" s="5"/>
     </row>
     <row r="269">
-      <c r="E269" s="5"/>
+      <c r="D269" s="5"/>
     </row>
     <row r="270">
-      <c r="E270" s="5"/>
+      <c r="D270" s="5"/>
     </row>
     <row r="271">
-      <c r="E271" s="5"/>
+      <c r="D271" s="5"/>
     </row>
     <row r="272">
-      <c r="E272" s="5"/>
+      <c r="D272" s="5"/>
     </row>
     <row r="273">
-      <c r="E273" s="5"/>
+      <c r="D273" s="5"/>
     </row>
     <row r="274">
-      <c r="E274" s="5"/>
+      <c r="D274" s="5"/>
     </row>
     <row r="275">
-      <c r="E275" s="5"/>
+      <c r="D275" s="5"/>
     </row>
     <row r="276">
-      <c r="E276" s="5"/>
+      <c r="D276" s="5"/>
     </row>
     <row r="277">
-      <c r="E277" s="5"/>
+      <c r="D277" s="5"/>
     </row>
     <row r="278">
-      <c r="E278" s="5"/>
+      <c r="D278" s="5"/>
     </row>
     <row r="279">
-      <c r="E279" s="5"/>
+      <c r="D279" s="5"/>
     </row>
     <row r="280">
-      <c r="E280" s="5"/>
+      <c r="D280" s="5"/>
     </row>
     <row r="281">
-      <c r="E281" s="5"/>
+      <c r="D281" s="5"/>
     </row>
     <row r="282">
-      <c r="E282" s="5"/>
+      <c r="D282" s="5"/>
     </row>
     <row r="283">
-      <c r="E283" s="5"/>
+      <c r="D283" s="5"/>
     </row>
     <row r="284">
-      <c r="E284" s="5"/>
+      <c r="D284" s="5"/>
     </row>
     <row r="285">
-      <c r="E285" s="5"/>
+      <c r="D285" s="5"/>
     </row>
     <row r="286">
-      <c r="E286" s="5"/>
+      <c r="D286" s="5"/>
     </row>
     <row r="287">
-      <c r="E287" s="5"/>
+      <c r="D287" s="5"/>
     </row>
     <row r="288">
-      <c r="E288" s="5"/>
+      <c r="D288" s="5"/>
     </row>
     <row r="289">
-      <c r="E289" s="5"/>
+      <c r="D289" s="5"/>
     </row>
     <row r="290">
-      <c r="E290" s="5"/>
+      <c r="D290" s="5"/>
     </row>
     <row r="291">
-      <c r="E291" s="5"/>
+      <c r="D291" s="5"/>
     </row>
     <row r="292">
-      <c r="E292" s="5"/>
+      <c r="D292" s="5"/>
     </row>
     <row r="293">
-      <c r="E293" s="5"/>
+      <c r="D293" s="5"/>
     </row>
     <row r="294">
-      <c r="E294" s="5"/>
+      <c r="D294" s="5"/>
     </row>
     <row r="295">
-      <c r="E295" s="5"/>
+      <c r="D295" s="5"/>
     </row>
     <row r="296">
-      <c r="E296" s="5"/>
+      <c r="D296" s="5"/>
     </row>
     <row r="297">
-      <c r="E297" s="5"/>
+      <c r="D297" s="5"/>
     </row>
     <row r="298">
-      <c r="E298" s="5"/>
+      <c r="D298" s="5"/>
     </row>
     <row r="299">
-      <c r="E299" s="5"/>
+      <c r="D299" s="5"/>
     </row>
     <row r="300">
-      <c r="E300" s="5"/>
+      <c r="D300" s="5"/>
     </row>
     <row r="301">
-      <c r="E301" s="5"/>
+      <c r="D301" s="5"/>
     </row>
     <row r="302">
-      <c r="E302" s="5"/>
+      <c r="D302" s="5"/>
     </row>
     <row r="303">
-      <c r="E303" s="5"/>
+      <c r="D303" s="5"/>
     </row>
     <row r="304">
-      <c r="E304" s="5"/>
+      <c r="D304" s="5"/>
     </row>
     <row r="305">
-      <c r="E305" s="5"/>
+      <c r="D305" s="5"/>
     </row>
     <row r="306">
-      <c r="E306" s="5"/>
+      <c r="D306" s="5"/>
     </row>
     <row r="307">
-      <c r="E307" s="5"/>
+      <c r="D307" s="5"/>
     </row>
     <row r="308">
-      <c r="E308" s="5"/>
+      <c r="D308" s="5"/>
     </row>
     <row r="309">
-      <c r="E309" s="5"/>
+      <c r="D309" s="5"/>
     </row>
     <row r="310">
-      <c r="E310" s="5"/>
+      <c r="D310" s="5"/>
     </row>
     <row r="311">
-      <c r="E311" s="5"/>
+      <c r="D311" s="5"/>
     </row>
     <row r="312">
-      <c r="E312" s="5"/>
+      <c r="D312" s="5"/>
     </row>
     <row r="313">
-      <c r="E313" s="5"/>
+      <c r="D313" s="5"/>
     </row>
     <row r="314">
-      <c r="E314" s="5"/>
+      <c r="D314" s="5"/>
     </row>
     <row r="315">
-      <c r="E315" s="5"/>
+      <c r="D315" s="5"/>
     </row>
     <row r="316">
-      <c r="E316" s="5"/>
+      <c r="D316" s="5"/>
     </row>
     <row r="317">
-      <c r="E317" s="5"/>
+      <c r="D317" s="5"/>
     </row>
     <row r="318">
-      <c r="E318" s="5"/>
+      <c r="D318" s="5"/>
     </row>
     <row r="319">
-      <c r="E319" s="5"/>
+      <c r="D319" s="5"/>
     </row>
     <row r="320">
-      <c r="E320" s="5"/>
+      <c r="D320" s="5"/>
     </row>
     <row r="321">
-      <c r="E321" s="5"/>
+      <c r="D321" s="5"/>
     </row>
     <row r="322">
-      <c r="E322" s="5"/>
+      <c r="D322" s="5"/>
     </row>
     <row r="323">
-      <c r="E323" s="5"/>
+      <c r="D323" s="5"/>
     </row>
     <row r="324">
-      <c r="E324" s="5"/>
+      <c r="D324" s="5"/>
     </row>
     <row r="325">
-      <c r="E325" s="5"/>
+      <c r="D325" s="5"/>
     </row>
     <row r="326">
-      <c r="E326" s="5"/>
+      <c r="D326" s="5"/>
     </row>
     <row r="327">
-      <c r="E327" s="5"/>
+      <c r="D327" s="5"/>
     </row>
     <row r="328">
-      <c r="E328" s="5"/>
+      <c r="D328" s="5"/>
     </row>
     <row r="329">
-      <c r="E329" s="5"/>
+      <c r="D329" s="5"/>
     </row>
     <row r="330">
-      <c r="E330" s="5"/>
+      <c r="D330" s="5"/>
     </row>
     <row r="331">
-      <c r="E331" s="5"/>
+      <c r="D331" s="5"/>
     </row>
     <row r="332">
-      <c r="E332" s="5"/>
+      <c r="D332" s="5"/>
     </row>
     <row r="333">
-      <c r="E333" s="5"/>
+      <c r="D333" s="5"/>
     </row>
     <row r="334">
-      <c r="E334" s="5"/>
+      <c r="D334" s="5"/>
     </row>
     <row r="335">
-      <c r="E335" s="5"/>
+      <c r="D335" s="5"/>
     </row>
     <row r="336">
-      <c r="E336" s="5"/>
+      <c r="D336" s="5"/>
     </row>
     <row r="337">
-      <c r="E337" s="5"/>
+      <c r="D337" s="5"/>
     </row>
     <row r="338">
-      <c r="E338" s="5"/>
+      <c r="D338" s="5"/>
     </row>
     <row r="339">
-      <c r="E339" s="5"/>
+      <c r="D339" s="5"/>
     </row>
     <row r="340">
-      <c r="E340" s="5"/>
+      <c r="D340" s="5"/>
     </row>
     <row r="341">
-      <c r="E341" s="5"/>
+      <c r="D341" s="5"/>
     </row>
     <row r="342">
-      <c r="E342" s="5"/>
+      <c r="D342" s="5"/>
     </row>
     <row r="343">
-      <c r="E343" s="5"/>
+      <c r="D343" s="5"/>
     </row>
     <row r="344">
-      <c r="E344" s="5"/>
+      <c r="D344" s="5"/>
     </row>
     <row r="345">
-      <c r="E345" s="5"/>
+      <c r="D345" s="5"/>
     </row>
     <row r="346">
-      <c r="E346" s="5"/>
+      <c r="D346" s="5"/>
     </row>
     <row r="347">
-      <c r="E347" s="5"/>
+      <c r="D347" s="5"/>
     </row>
     <row r="348">
-      <c r="E348" s="5"/>
+      <c r="D348" s="5"/>
     </row>
     <row r="349">
-      <c r="E349" s="5"/>
+      <c r="D349" s="5"/>
     </row>
     <row r="350">
-      <c r="E350" s="5"/>
+      <c r="D350" s="5"/>
     </row>
     <row r="351">
-      <c r="E351" s="5"/>
+      <c r="D351" s="5"/>
     </row>
     <row r="352">
-      <c r="E352" s="5"/>
+      <c r="D352" s="5"/>
     </row>
     <row r="353">
-      <c r="E353" s="5"/>
+      <c r="D353" s="5"/>
     </row>
     <row r="354">
-      <c r="E354" s="5"/>
+      <c r="D354" s="5"/>
     </row>
     <row r="355">
-      <c r="E355" s="5"/>
+      <c r="D355" s="5"/>
     </row>
     <row r="356">
-      <c r="E356" s="5"/>
+      <c r="D356" s="5"/>
     </row>
     <row r="357">
-      <c r="E357" s="5"/>
+      <c r="D357" s="5"/>
     </row>
     <row r="358">
-      <c r="E358" s="5"/>
+      <c r="D358" s="5"/>
     </row>
     <row r="359">
-      <c r="E359" s="5"/>
+      <c r="D359" s="5"/>
     </row>
     <row r="360">
-      <c r="E360" s="5"/>
+      <c r="D360" s="5"/>
     </row>
     <row r="361">
-      <c r="E361" s="5"/>
+      <c r="D361" s="5"/>
     </row>
     <row r="362">
-      <c r="E362" s="5"/>
+      <c r="D362" s="5"/>
     </row>
     <row r="363">
-      <c r="E363" s="5"/>
+      <c r="D363" s="5"/>
     </row>
     <row r="364">
-      <c r="E364" s="5"/>
+      <c r="D364" s="5"/>
     </row>
     <row r="365">
-      <c r="E365" s="5"/>
+      <c r="D365" s="5"/>
     </row>
     <row r="366">
-      <c r="E366" s="5"/>
+      <c r="D366" s="5"/>
     </row>
     <row r="367">
-      <c r="E367" s="5"/>
+      <c r="D367" s="5"/>
     </row>
     <row r="368">
-      <c r="E368" s="5"/>
+      <c r="D368" s="5"/>
     </row>
     <row r="369">
-      <c r="E369" s="5"/>
+      <c r="D369" s="5"/>
     </row>
     <row r="370">
-      <c r="E370" s="5"/>
+      <c r="D370" s="5"/>
     </row>
     <row r="371">
-      <c r="E371" s="5"/>
+      <c r="D371" s="5"/>
     </row>
     <row r="372">
-      <c r="E372" s="5"/>
+      <c r="D372" s="5"/>
     </row>
     <row r="373">
-      <c r="E373" s="5"/>
+      <c r="D373" s="5"/>
     </row>
     <row r="374">
-      <c r="E374" s="5"/>
+      <c r="D374" s="5"/>
     </row>
     <row r="375">
-      <c r="E375" s="5"/>
+      <c r="D375" s="5"/>
     </row>
     <row r="376">
-      <c r="E376" s="5"/>
+      <c r="D376" s="5"/>
     </row>
     <row r="377">
-      <c r="E377" s="5"/>
+      <c r="D377" s="5"/>
     </row>
     <row r="378">
-      <c r="E378" s="5"/>
+      <c r="D378" s="5"/>
     </row>
     <row r="379">
-      <c r="E379" s="5"/>
+      <c r="D379" s="5"/>
     </row>
     <row r="380">
-      <c r="E380" s="5"/>
+      <c r="D380" s="5"/>
     </row>
     <row r="381">
-      <c r="E381" s="5"/>
+      <c r="D381" s="5"/>
     </row>
     <row r="382">
-      <c r="E382" s="5"/>
+      <c r="D382" s="5"/>
     </row>
     <row r="383">
-      <c r="E383" s="5"/>
+      <c r="D383" s="5"/>
     </row>
     <row r="384">
-      <c r="E384" s="5"/>
+      <c r="D384" s="5"/>
     </row>
     <row r="385">
-      <c r="E385" s="5"/>
+      <c r="D385" s="5"/>
     </row>
     <row r="386">
-      <c r="E386" s="5"/>
+      <c r="D386" s="5"/>
     </row>
     <row r="387">
-      <c r="E387" s="5"/>
+      <c r="D387" s="5"/>
     </row>
     <row r="388">
-      <c r="E388" s="5"/>
+      <c r="D388" s="5"/>
     </row>
     <row r="389">
-      <c r="E389" s="5"/>
+      <c r="D389" s="5"/>
     </row>
     <row r="390">
-      <c r="E390" s="5"/>
+      <c r="D390" s="5"/>
     </row>
     <row r="391">
-      <c r="E391" s="5"/>
+      <c r="D391" s="5"/>
     </row>
     <row r="392">
-      <c r="E392" s="5"/>
+      <c r="D392" s="5"/>
     </row>
     <row r="393">
-      <c r="E393" s="5"/>
+      <c r="D393" s="5"/>
     </row>
     <row r="394">
-      <c r="E394" s="5"/>
+      <c r="D394" s="5"/>
     </row>
     <row r="395">
-      <c r="E395" s="5"/>
+      <c r="D395" s="5"/>
     </row>
     <row r="396">
-      <c r="E396" s="5"/>
+      <c r="D396" s="5"/>
     </row>
     <row r="397">
-      <c r="E397" s="5"/>
+      <c r="D397" s="5"/>
     </row>
     <row r="398">
-      <c r="E398" s="5"/>
+      <c r="D398" s="5"/>
     </row>
     <row r="399">
-      <c r="E399" s="5"/>
+      <c r="D399" s="5"/>
     </row>
     <row r="400">
-      <c r="E400" s="5"/>
+      <c r="D400" s="5"/>
     </row>
     <row r="401">
-      <c r="E401" s="5"/>
+      <c r="D401" s="5"/>
     </row>
     <row r="402">
-      <c r="E402" s="5"/>
+      <c r="D402" s="5"/>
     </row>
     <row r="403">
-      <c r="E403" s="5"/>
+      <c r="D403" s="5"/>
     </row>
     <row r="404">
-      <c r="E404" s="5"/>
+      <c r="D404" s="5"/>
     </row>
     <row r="405">
-      <c r="E405" s="5"/>
+      <c r="D405" s="5"/>
     </row>
     <row r="406">
-      <c r="E406" s="5"/>
+      <c r="D406" s="5"/>
     </row>
     <row r="407">
-      <c r="E407" s="5"/>
+      <c r="D407" s="5"/>
     </row>
     <row r="408">
-      <c r="E408" s="5"/>
+      <c r="D408" s="5"/>
     </row>
     <row r="409">
-      <c r="E409" s="5"/>
+      <c r="D409" s="5"/>
     </row>
     <row r="410">
-      <c r="E410" s="5"/>
+      <c r="D410" s="5"/>
     </row>
     <row r="411">
-      <c r="E411" s="5"/>
+      <c r="D411" s="5"/>
     </row>
     <row r="412">
-      <c r="E412" s="5"/>
+      <c r="D412" s="5"/>
     </row>
     <row r="413">
-      <c r="E413" s="5"/>
+      <c r="D413" s="5"/>
     </row>
     <row r="414">
-      <c r="E414" s="5"/>
+      <c r="D414" s="5"/>
     </row>
     <row r="415">
-      <c r="E415" s="5"/>
+      <c r="D415" s="5"/>
     </row>
     <row r="416">
-      <c r="E416" s="5"/>
+      <c r="D416" s="5"/>
     </row>
     <row r="417">
-      <c r="E417" s="5"/>
+      <c r="D417" s="5"/>
     </row>
     <row r="418">
-      <c r="E418" s="5"/>
+      <c r="D418" s="5"/>
     </row>
     <row r="419">
-      <c r="E419" s="5"/>
+      <c r="D419" s="5"/>
     </row>
     <row r="420">
-      <c r="E420" s="5"/>
+      <c r="D420" s="5"/>
     </row>
     <row r="421">
-      <c r="E421" s="5"/>
+      <c r="D421" s="5"/>
     </row>
     <row r="422">
-      <c r="E422" s="5"/>
+      <c r="D422" s="5"/>
     </row>
     <row r="423">
-      <c r="E423" s="5"/>
+      <c r="D423" s="5"/>
     </row>
     <row r="424">
-      <c r="E424" s="5"/>
+      <c r="D424" s="5"/>
     </row>
     <row r="425">
-      <c r="E425" s="5"/>
+      <c r="D425" s="5"/>
     </row>
     <row r="426">
-      <c r="E426" s="5"/>
+      <c r="D426" s="5"/>
     </row>
     <row r="427">
-      <c r="E427" s="5"/>
+      <c r="D427" s="5"/>
     </row>
     <row r="428">
-      <c r="E428" s="5"/>
+      <c r="D428" s="5"/>
     </row>
     <row r="429">
-      <c r="E429" s="5"/>
+      <c r="D429" s="5"/>
     </row>
     <row r="430">
-      <c r="E430" s="5"/>
+      <c r="D430" s="5"/>
     </row>
     <row r="431">
-      <c r="E431" s="5"/>
+      <c r="D431" s="5"/>
     </row>
     <row r="432">
-      <c r="E432" s="5"/>
+      <c r="D432" s="5"/>
     </row>
     <row r="433">
-      <c r="E433" s="5"/>
+      <c r="D433" s="5"/>
     </row>
     <row r="434">
-      <c r="E434" s="5"/>
+      <c r="D434" s="5"/>
     </row>
     <row r="435">
-      <c r="E435" s="5"/>
+      <c r="D435" s="5"/>
     </row>
     <row r="436">
-      <c r="E436" s="5"/>
+      <c r="D436" s="5"/>
     </row>
     <row r="437">
-      <c r="E437" s="5"/>
+      <c r="D437" s="5"/>
     </row>
     <row r="438">
-      <c r="E438" s="5"/>
+      <c r="D438" s="5"/>
     </row>
     <row r="439">
-      <c r="E439" s="5"/>
+      <c r="D439" s="5"/>
     </row>
     <row r="440">
-      <c r="E440" s="5"/>
+      <c r="D440" s="5"/>
     </row>
     <row r="441">
-      <c r="E441" s="5"/>
+      <c r="D441" s="5"/>
     </row>
     <row r="442">
-      <c r="E442" s="5"/>
+      <c r="D442" s="5"/>
     </row>
     <row r="443">
-      <c r="E443" s="5"/>
+      <c r="D443" s="5"/>
     </row>
     <row r="444">
-      <c r="E444" s="5"/>
+      <c r="D444" s="5"/>
     </row>
     <row r="445">
-      <c r="E445" s="5"/>
+      <c r="D445" s="5"/>
     </row>
     <row r="446">
-      <c r="E446" s="5"/>
+      <c r="D446" s="5"/>
     </row>
     <row r="447">
-      <c r="E447" s="5"/>
+      <c r="D447" s="5"/>
     </row>
     <row r="448">
-      <c r="E448" s="5"/>
+      <c r="D448" s="5"/>
     </row>
     <row r="449">
-      <c r="E449" s="5"/>
+      <c r="D449" s="5"/>
     </row>
     <row r="450">
-      <c r="E450" s="5"/>
+      <c r="D450" s="5"/>
     </row>
     <row r="451">
-      <c r="E451" s="5"/>
+      <c r="D451" s="5"/>
     </row>
     <row r="452">
-      <c r="E452" s="5"/>
+      <c r="D452" s="5"/>
     </row>
     <row r="453">
-      <c r="E453" s="5"/>
+      <c r="D453" s="5"/>
     </row>
     <row r="454">
-      <c r="E454" s="5"/>
+      <c r="D454" s="5"/>
     </row>
     <row r="455">
-      <c r="E455" s="5"/>
+      <c r="D455" s="5"/>
     </row>
     <row r="456">
-      <c r="E456" s="5"/>
+      <c r="D456" s="5"/>
     </row>
     <row r="457">
-      <c r="E457" s="5"/>
+      <c r="D457" s="5"/>
     </row>
     <row r="458">
-      <c r="E458" s="5"/>
+      <c r="D458" s="5"/>
     </row>
     <row r="459">
-      <c r="E459" s="5"/>
+      <c r="D459" s="5"/>
     </row>
     <row r="460">
-      <c r="E460" s="5"/>
+      <c r="D460" s="5"/>
     </row>
     <row r="461">
-      <c r="E461" s="5"/>
+      <c r="D461" s="5"/>
     </row>
     <row r="462">
-      <c r="E462" s="5"/>
+      <c r="D462" s="5"/>
     </row>
     <row r="463">
-      <c r="E463" s="5"/>
+      <c r="D463" s="5"/>
     </row>
     <row r="464">
-      <c r="E464" s="5"/>
+      <c r="D464" s="5"/>
     </row>
     <row r="465">
-      <c r="E465" s="5"/>
+      <c r="D465" s="5"/>
     </row>
     <row r="466">
-      <c r="E466" s="5"/>
+      <c r="D466" s="5"/>
     </row>
     <row r="467">
-      <c r="E467" s="5"/>
+      <c r="D467" s="5"/>
     </row>
     <row r="468">
-      <c r="E468" s="5"/>
+      <c r="D468" s="5"/>
     </row>
     <row r="469">
-      <c r="E469" s="5"/>
+      <c r="D469" s="5"/>
     </row>
     <row r="470">
-      <c r="E470" s="5"/>
+      <c r="D470" s="5"/>
     </row>
     <row r="471">
-      <c r="E471" s="5"/>
+      <c r="D471" s="5"/>
     </row>
     <row r="472">
-      <c r="E472" s="5"/>
+      <c r="D472" s="5"/>
     </row>
     <row r="473">
-      <c r="E473" s="5"/>
+      <c r="D473" s="5"/>
     </row>
     <row r="474">
-      <c r="E474" s="5"/>
+      <c r="D474" s="5"/>
     </row>
     <row r="475">
-      <c r="E475" s="5"/>
+      <c r="D475" s="5"/>
     </row>
     <row r="476">
-      <c r="E476" s="5"/>
+      <c r="D476" s="5"/>
     </row>
     <row r="477">
-      <c r="E477" s="5"/>
+      <c r="D477" s="5"/>
     </row>
     <row r="478">
-      <c r="E478" s="5"/>
+      <c r="D478" s="5"/>
     </row>
     <row r="479">
-      <c r="E479" s="5"/>
+      <c r="D479" s="5"/>
     </row>
     <row r="480">
-      <c r="E480" s="5"/>
+      <c r="D480" s="5"/>
     </row>
     <row r="481">
-      <c r="E481" s="5"/>
+      <c r="D481" s="5"/>
     </row>
     <row r="482">
-      <c r="E482" s="5"/>
+      <c r="D482" s="5"/>
     </row>
     <row r="483">
-      <c r="E483" s="5"/>
+      <c r="D483" s="5"/>
     </row>
     <row r="484">
-      <c r="E484" s="5"/>
+      <c r="D484" s="5"/>
     </row>
     <row r="485">
-      <c r="E485" s="5"/>
+      <c r="D485" s="5"/>
     </row>
     <row r="486">
-      <c r="E486" s="5"/>
+      <c r="D486" s="5"/>
     </row>
     <row r="487">
-      <c r="E487" s="5"/>
+      <c r="D487" s="5"/>
     </row>
     <row r="488">
-      <c r="E488" s="5"/>
+      <c r="D488" s="5"/>
     </row>
     <row r="489">
-      <c r="E489" s="5"/>
+      <c r="D489" s="5"/>
     </row>
     <row r="490">
-      <c r="E490" s="5"/>
+      <c r="D490" s="5"/>
     </row>
     <row r="491">
-      <c r="E491" s="5"/>
+      <c r="D491" s="5"/>
     </row>
     <row r="492">
-      <c r="E492" s="5"/>
+      <c r="D492" s="5"/>
     </row>
     <row r="493">
-      <c r="E493" s="5"/>
+      <c r="D493" s="5"/>
     </row>
     <row r="494">
-      <c r="E494" s="5"/>
+      <c r="D494" s="5"/>
     </row>
     <row r="495">
-      <c r="E495" s="5"/>
+      <c r="D495" s="5"/>
     </row>
     <row r="496">
-      <c r="E496" s="5"/>
+      <c r="D496" s="5"/>
     </row>
     <row r="497">
-      <c r="E497" s="5"/>
+      <c r="D497" s="5"/>
     </row>
     <row r="498">
-      <c r="E498" s="5"/>
+      <c r="D498" s="5"/>
     </row>
     <row r="499">
-      <c r="E499" s="5"/>
+      <c r="D499" s="5"/>
     </row>
     <row r="500">
-      <c r="E500" s="5"/>
+      <c r="D500" s="5"/>
     </row>
     <row r="501">
-      <c r="E501" s="5"/>
+      <c r="D501" s="5"/>
     </row>
     <row r="502">
-      <c r="E502" s="5"/>
+      <c r="D502" s="5"/>
     </row>
     <row r="503">
-      <c r="E503" s="5"/>
+      <c r="D503" s="5"/>
     </row>
     <row r="504">
-      <c r="E504" s="5"/>
+      <c r="D504" s="5"/>
     </row>
     <row r="505">
-      <c r="E505" s="5"/>
+      <c r="D505" s="5"/>
     </row>
     <row r="506">
-      <c r="E506" s="5"/>
+      <c r="D506" s="5"/>
     </row>
     <row r="507">
-      <c r="E507" s="5"/>
+      <c r="D507" s="5"/>
     </row>
     <row r="508">
-      <c r="E508" s="5"/>
+      <c r="D508" s="5"/>
     </row>
     <row r="509">
-      <c r="E509" s="5"/>
+      <c r="D509" s="5"/>
     </row>
     <row r="510">
-      <c r="E510" s="5"/>
+      <c r="D510" s="5"/>
     </row>
     <row r="511">
-      <c r="E511" s="5"/>
+      <c r="D511" s="5"/>
     </row>
     <row r="512">
-      <c r="E512" s="5"/>
+      <c r="D512" s="5"/>
     </row>
     <row r="513">
-      <c r="E513" s="5"/>
+      <c r="D513" s="5"/>
     </row>
     <row r="514">
-      <c r="E514" s="5"/>
+      <c r="D514" s="5"/>
     </row>
     <row r="515">
-      <c r="E515" s="5"/>
+      <c r="D515" s="5"/>
     </row>
     <row r="516">
-      <c r="E516" s="5"/>
+      <c r="D516" s="5"/>
     </row>
     <row r="517">
-      <c r="E517" s="5"/>
+      <c r="D517" s="5"/>
     </row>
     <row r="518">
-      <c r="E518" s="5"/>
+      <c r="D518" s="5"/>
     </row>
     <row r="519">
-      <c r="E519" s="5"/>
+      <c r="D519" s="5"/>
     </row>
     <row r="520">
-      <c r="E520" s="5"/>
+      <c r="D520" s="5"/>
     </row>
     <row r="521">
-      <c r="E521" s="5"/>
+      <c r="D521" s="5"/>
     </row>
     <row r="522">
-      <c r="E522" s="5"/>
+      <c r="D522" s="5"/>
     </row>
     <row r="523">
-      <c r="E523" s="5"/>
+      <c r="D523" s="5"/>
     </row>
     <row r="524">
-      <c r="E524" s="5"/>
+      <c r="D524" s="5"/>
     </row>
     <row r="525">
-      <c r="E525" s="5"/>
+      <c r="D525" s="5"/>
     </row>
     <row r="526">
-      <c r="E526" s="5"/>
+      <c r="D526" s="5"/>
     </row>
     <row r="527">
-      <c r="E527" s="5"/>
+      <c r="D527" s="5"/>
     </row>
     <row r="528">
-      <c r="E528" s="5"/>
+      <c r="D528" s="5"/>
     </row>
     <row r="529">
-      <c r="E529" s="5"/>
+      <c r="D529" s="5"/>
     </row>
     <row r="530">
-      <c r="E530" s="5"/>
+      <c r="D530" s="5"/>
     </row>
     <row r="531">
-      <c r="E531" s="5"/>
+      <c r="D531" s="5"/>
     </row>
     <row r="532">
-      <c r="E532" s="5"/>
+      <c r="D532" s="5"/>
     </row>
     <row r="533">
-      <c r="E533" s="5"/>
+      <c r="D533" s="5"/>
     </row>
     <row r="534">
-      <c r="E534" s="5"/>
+      <c r="D534" s="5"/>
     </row>
     <row r="535">
-      <c r="E535" s="5"/>
+      <c r="D535" s="5"/>
     </row>
     <row r="536">
-      <c r="E536" s="5"/>
+      <c r="D536" s="5"/>
     </row>
     <row r="537">
-      <c r="E537" s="5"/>
+      <c r="D537" s="5"/>
     </row>
     <row r="538">
-      <c r="E538" s="5"/>
+      <c r="D538" s="5"/>
     </row>
     <row r="539">
-      <c r="E539" s="5"/>
+      <c r="D539" s="5"/>
     </row>
     <row r="540">
-      <c r="E540" s="5"/>
+      <c r="D540" s="5"/>
     </row>
     <row r="541">
-      <c r="E541" s="5"/>
+      <c r="D541" s="5"/>
     </row>
     <row r="542">
-      <c r="E542" s="5"/>
+      <c r="D542" s="5"/>
     </row>
     <row r="543">
-      <c r="E543" s="5"/>
+      <c r="D543" s="5"/>
     </row>
     <row r="544">
-      <c r="E544" s="5"/>
+      <c r="D544" s="5"/>
     </row>
     <row r="545">
-      <c r="E545" s="5"/>
+      <c r="D545" s="5"/>
     </row>
     <row r="546">
-      <c r="E546" s="5"/>
+      <c r="D546" s="5"/>
     </row>
     <row r="547">
-      <c r="E547" s="5"/>
+      <c r="D547" s="5"/>
     </row>
     <row r="548">
-      <c r="E548" s="5"/>
+      <c r="D548" s="5"/>
     </row>
     <row r="549">
-      <c r="E549" s="5"/>
+      <c r="D549" s="5"/>
     </row>
     <row r="550">
-      <c r="E550" s="5"/>
+      <c r="D550" s="5"/>
     </row>
     <row r="551">
-      <c r="E551" s="5"/>
+      <c r="D551" s="5"/>
     </row>
     <row r="552">
-      <c r="E552" s="5"/>
+      <c r="D552" s="5"/>
     </row>
     <row r="553">
-      <c r="E553" s="5"/>
+      <c r="D553" s="5"/>
     </row>
     <row r="554">
-      <c r="E554" s="5"/>
+      <c r="D554" s="5"/>
     </row>
     <row r="555">
-      <c r="E555" s="5"/>
+      <c r="D555" s="5"/>
     </row>
     <row r="556">
-      <c r="E556" s="5"/>
+      <c r="D556" s="5"/>
     </row>
     <row r="557">
-      <c r="E557" s="5"/>
+      <c r="D557" s="5"/>
     </row>
     <row r="558">
-      <c r="E558" s="5"/>
+      <c r="D558" s="5"/>
     </row>
     <row r="559">
-      <c r="E559" s="5"/>
+      <c r="D559" s="5"/>
     </row>
     <row r="560">
-      <c r="E560" s="5"/>
+      <c r="D560" s="5"/>
     </row>
     <row r="561">
-      <c r="E561" s="5"/>
+      <c r="D561" s="5"/>
     </row>
     <row r="562">
-      <c r="E562" s="5"/>
+      <c r="D562" s="5"/>
     </row>
     <row r="563">
-      <c r="E563" s="5"/>
+      <c r="D563" s="5"/>
     </row>
     <row r="564">
-      <c r="E564" s="5"/>
+      <c r="D564" s="5"/>
     </row>
     <row r="565">
-      <c r="E565" s="5"/>
+      <c r="D565" s="5"/>
     </row>
     <row r="566">
-      <c r="E566" s="5"/>
+      <c r="D566" s="5"/>
     </row>
     <row r="567">
-      <c r="E567" s="5"/>
+      <c r="D567" s="5"/>
     </row>
     <row r="568">
-      <c r="E568" s="5"/>
+      <c r="D568" s="5"/>
     </row>
     <row r="569">
-      <c r="E569" s="5"/>
+      <c r="D569" s="5"/>
     </row>
     <row r="570">
-      <c r="E570" s="5"/>
+      <c r="D570" s="5"/>
     </row>
     <row r="571">
-      <c r="E571" s="5"/>
+      <c r="D571" s="5"/>
     </row>
     <row r="572">
-      <c r="E572" s="5"/>
+      <c r="D572" s="5"/>
     </row>
     <row r="573">
-      <c r="E573" s="5"/>
+      <c r="D573" s="5"/>
     </row>
     <row r="574">
-      <c r="E574" s="5"/>
+      <c r="D574" s="5"/>
     </row>
     <row r="575">
-      <c r="E575" s="5"/>
+      <c r="D575" s="5"/>
     </row>
     <row r="576">
-      <c r="E576" s="5"/>
+      <c r="D576" s="5"/>
     </row>
     <row r="577">
-      <c r="E577" s="5"/>
+      <c r="D577" s="5"/>
     </row>
     <row r="578">
-      <c r="E578" s="5"/>
+      <c r="D578" s="5"/>
     </row>
     <row r="579">
-      <c r="E579" s="5"/>
+      <c r="D579" s="5"/>
     </row>
     <row r="580">
-      <c r="E580" s="5"/>
+      <c r="D580" s="5"/>
     </row>
     <row r="581">
-      <c r="E581" s="5"/>
+      <c r="D581" s="5"/>
     </row>
     <row r="582">
-      <c r="E582" s="5"/>
+      <c r="D582" s="5"/>
     </row>
     <row r="583">
-      <c r="E583" s="5"/>
+      <c r="D583" s="5"/>
     </row>
     <row r="584">
-      <c r="E584" s="5"/>
+      <c r="D584" s="5"/>
     </row>
     <row r="585">
-      <c r="E585" s="5"/>
+      <c r="D585" s="5"/>
     </row>
     <row r="586">
-      <c r="E586" s="5"/>
+      <c r="D586" s="5"/>
     </row>
     <row r="587">
-      <c r="E587" s="5"/>
+      <c r="D587" s="5"/>
     </row>
     <row r="588">
-      <c r="E588" s="5"/>
+      <c r="D588" s="5"/>
     </row>
     <row r="589">
-      <c r="E589" s="5"/>
+      <c r="D589" s="5"/>
     </row>
     <row r="590">
-      <c r="E590" s="5"/>
+      <c r="D590" s="5"/>
     </row>
     <row r="591">
-      <c r="E591" s="5"/>
+      <c r="D591" s="5"/>
     </row>
     <row r="592">
-      <c r="E592" s="5"/>
+      <c r="D592" s="5"/>
     </row>
     <row r="593">
-      <c r="E593" s="5"/>
+      <c r="D593" s="5"/>
     </row>
     <row r="594">
-      <c r="E594" s="5"/>
+      <c r="D594" s="5"/>
     </row>
     <row r="595">
-      <c r="E595" s="5"/>
+      <c r="D595" s="5"/>
     </row>
     <row r="596">
-      <c r="E596" s="5"/>
+      <c r="D596" s="5"/>
     </row>
     <row r="597">
-      <c r="E597" s="5"/>
+      <c r="D597" s="5"/>
     </row>
     <row r="598">
-      <c r="E598" s="5"/>
+      <c r="D598" s="5"/>
     </row>
     <row r="599">
-      <c r="E599" s="5"/>
+      <c r="D599" s="5"/>
     </row>
     <row r="600">
-      <c r="E600" s="5"/>
+      <c r="D600" s="5"/>
     </row>
     <row r="601">
-      <c r="E601" s="5"/>
+      <c r="D601" s="5"/>
     </row>
     <row r="602">
-      <c r="E602" s="5"/>
+      <c r="D602" s="5"/>
     </row>
     <row r="603">
-      <c r="E603" s="5"/>
+      <c r="D603" s="5"/>
     </row>
     <row r="604">
-      <c r="E604" s="5"/>
+      <c r="D604" s="5"/>
     </row>
     <row r="605">
-      <c r="E605" s="5"/>
+      <c r="D605" s="5"/>
     </row>
     <row r="606">
-      <c r="E606" s="5"/>
+      <c r="D606" s="5"/>
     </row>
     <row r="607">
-      <c r="E607" s="5"/>
+      <c r="D607" s="5"/>
     </row>
     <row r="608">
-      <c r="E608" s="5"/>
+      <c r="D608" s="5"/>
     </row>
     <row r="609">
-      <c r="E609" s="5"/>
+      <c r="D609" s="5"/>
     </row>
     <row r="610">
-      <c r="E610" s="5"/>
+      <c r="D610" s="5"/>
     </row>
     <row r="611">
-      <c r="E611" s="5"/>
+      <c r="D611" s="5"/>
     </row>
     <row r="612">
-      <c r="E612" s="5"/>
+      <c r="D612" s="5"/>
     </row>
     <row r="613">
-      <c r="E613" s="5"/>
+      <c r="D613" s="5"/>
     </row>
     <row r="614">
-      <c r="E614" s="5"/>
+      <c r="D614" s="5"/>
     </row>
     <row r="615">
-      <c r="E615" s="5"/>
+      <c r="D615" s="5"/>
     </row>
     <row r="616">
-      <c r="E616" s="5"/>
+      <c r="D616" s="5"/>
     </row>
     <row r="617">
-      <c r="E617" s="5"/>
+      <c r="D617" s="5"/>
     </row>
     <row r="618">
-      <c r="E618" s="5"/>
+      <c r="D618" s="5"/>
     </row>
     <row r="619">
-      <c r="E619" s="5"/>
+      <c r="D619" s="5"/>
     </row>
     <row r="620">
-      <c r="E620" s="5"/>
+      <c r="D620" s="5"/>
     </row>
     <row r="621">
-      <c r="E621" s="5"/>
+      <c r="D621" s="5"/>
     </row>
     <row r="622">
-      <c r="E622" s="5"/>
+      <c r="D622" s="5"/>
     </row>
     <row r="623">
-      <c r="E623" s="5"/>
+      <c r="D623" s="5"/>
     </row>
     <row r="624">
-      <c r="E624" s="5"/>
+      <c r="D624" s="5"/>
     </row>
     <row r="625">
-      <c r="E625" s="5"/>
+      <c r="D625" s="5"/>
     </row>
     <row r="626">
-      <c r="E626" s="5"/>
+      <c r="D626" s="5"/>
     </row>
     <row r="627">
-      <c r="E627" s="5"/>
+      <c r="D627" s="5"/>
     </row>
     <row r="628">
-      <c r="E628" s="5"/>
+      <c r="D628" s="5"/>
     </row>
     <row r="629">
-      <c r="E629" s="5"/>
+      <c r="D629" s="5"/>
     </row>
     <row r="630">
-      <c r="E630" s="5"/>
+      <c r="D630" s="5"/>
     </row>
     <row r="631">
-      <c r="E631" s="5"/>
+      <c r="D631" s="5"/>
     </row>
     <row r="632">
-      <c r="E632" s="5"/>
+      <c r="D632" s="5"/>
     </row>
     <row r="633">
-      <c r="E633" s="5"/>
+      <c r="D633" s="5"/>
     </row>
     <row r="634">
-      <c r="E634" s="5"/>
+      <c r="D634" s="5"/>
     </row>
     <row r="635">
-      <c r="E635" s="5"/>
+      <c r="D635" s="5"/>
     </row>
     <row r="636">
-      <c r="E636" s="5"/>
+      <c r="D636" s="5"/>
     </row>
     <row r="637">
-      <c r="E637" s="5"/>
+      <c r="D637" s="5"/>
     </row>
     <row r="638">
-      <c r="E638" s="5"/>
+      <c r="D638" s="5"/>
     </row>
     <row r="639">
-      <c r="E639" s="5"/>
+      <c r="D639" s="5"/>
     </row>
     <row r="640">
-      <c r="E640" s="5"/>
+      <c r="D640" s="5"/>
     </row>
     <row r="641">
-      <c r="E641" s="5"/>
+      <c r="D641" s="5"/>
     </row>
     <row r="642">
-      <c r="E642" s="5"/>
+      <c r="D642" s="5"/>
     </row>
     <row r="643">
-      <c r="E643" s="5"/>
+      <c r="D643" s="5"/>
     </row>
     <row r="644">
-      <c r="E644" s="5"/>
+      <c r="D644" s="5"/>
     </row>
     <row r="645">
-      <c r="E645" s="5"/>
+      <c r="D645" s="5"/>
     </row>
     <row r="646">
-      <c r="E646" s="5"/>
+      <c r="D646" s="5"/>
     </row>
     <row r="647">
-      <c r="E647" s="5"/>
+      <c r="D647" s="5"/>
     </row>
     <row r="648">
-      <c r="E648" s="5"/>
+      <c r="D648" s="5"/>
     </row>
     <row r="649">
-      <c r="E649" s="5"/>
+      <c r="D649" s="5"/>
     </row>
     <row r="650">
-      <c r="E650" s="5"/>
+      <c r="D650" s="5"/>
     </row>
     <row r="651">
-      <c r="E651" s="5"/>
+      <c r="D651" s="5"/>
     </row>
     <row r="652">
-      <c r="E652" s="5"/>
+      <c r="D652" s="5"/>
     </row>
     <row r="653">
-      <c r="E653" s="5"/>
+      <c r="D653" s="5"/>
     </row>
     <row r="654">
-      <c r="E654" s="5"/>
+      <c r="D654" s="5"/>
     </row>
     <row r="655">
-      <c r="E655" s="5"/>
+      <c r="D655" s="5"/>
     </row>
     <row r="656">
-      <c r="E656" s="5"/>
+      <c r="D656" s="5"/>
     </row>
     <row r="657">
-      <c r="E657" s="5"/>
+      <c r="D657" s="5"/>
     </row>
     <row r="658">
-      <c r="E658" s="5"/>
+      <c r="D658" s="5"/>
     </row>
     <row r="659">
-      <c r="E659" s="5"/>
+      <c r="D659" s="5"/>
     </row>
     <row r="660">
-      <c r="E660" s="5"/>
+      <c r="D660" s="5"/>
     </row>
     <row r="661">
-      <c r="E661" s="5"/>
+      <c r="D661" s="5"/>
     </row>
     <row r="662">
-      <c r="E662" s="5"/>
+      <c r="D662" s="5"/>
     </row>
     <row r="663">
-      <c r="E663" s="5"/>
+      <c r="D663" s="5"/>
     </row>
     <row r="664">
-      <c r="E664" s="5"/>
+      <c r="D664" s="5"/>
     </row>
     <row r="665">
-      <c r="E665" s="5"/>
+      <c r="D665" s="5"/>
     </row>
     <row r="666">
-      <c r="E666" s="5"/>
+      <c r="D666" s="5"/>
     </row>
     <row r="667">
-      <c r="E667" s="5"/>
+      <c r="D667" s="5"/>
     </row>
     <row r="668">
-      <c r="E668" s="5"/>
+      <c r="D668" s="5"/>
     </row>
     <row r="669">
-      <c r="E669" s="5"/>
+      <c r="D669" s="5"/>
     </row>
     <row r="670">
-      <c r="E670" s="5"/>
+      <c r="D670" s="5"/>
     </row>
     <row r="671">
-      <c r="E671" s="5"/>
+      <c r="D671" s="5"/>
     </row>
     <row r="672">
-      <c r="E672" s="5"/>
+      <c r="D672" s="5"/>
     </row>
     <row r="673">
-      <c r="E673" s="5"/>
+      <c r="D673" s="5"/>
     </row>
     <row r="674">
-      <c r="E674" s="5"/>
+      <c r="D674" s="5"/>
     </row>
     <row r="675">
-      <c r="E675" s="5"/>
+      <c r="D675" s="5"/>
     </row>
     <row r="676">
-      <c r="E676" s="5"/>
+      <c r="D676" s="5"/>
     </row>
     <row r="677">
-      <c r="E677" s="5"/>
+      <c r="D677" s="5"/>
     </row>
     <row r="678">
-      <c r="E678" s="5"/>
+      <c r="D678" s="5"/>
     </row>
     <row r="679">
-      <c r="E679" s="5"/>
+      <c r="D679" s="5"/>
     </row>
     <row r="680">
-      <c r="E680" s="5"/>
+      <c r="D680" s="5"/>
     </row>
     <row r="681">
-      <c r="E681" s="5"/>
+      <c r="D681" s="5"/>
     </row>
     <row r="682">
-      <c r="E682" s="5"/>
+      <c r="D682" s="5"/>
     </row>
     <row r="683">
-      <c r="E683" s="5"/>
+      <c r="D683" s="5"/>
     </row>
     <row r="684">
-      <c r="E684" s="5"/>
+      <c r="D684" s="5"/>
     </row>
     <row r="685">
-      <c r="E685" s="5"/>
+      <c r="D685" s="5"/>
     </row>
     <row r="686">
-      <c r="E686" s="5"/>
+      <c r="D686" s="5"/>
     </row>
     <row r="687">
-      <c r="E687" s="5"/>
+      <c r="D687" s="5"/>
     </row>
     <row r="688">
-      <c r="E688" s="5"/>
+      <c r="D688" s="5"/>
     </row>
     <row r="689">
-      <c r="E689" s="5"/>
+      <c r="D689" s="5"/>
     </row>
     <row r="690">
-      <c r="E690" s="5"/>
+      <c r="D690" s="5"/>
     </row>
     <row r="691">
-      <c r="E691" s="5"/>
+      <c r="D691" s="5"/>
     </row>
     <row r="692">
-      <c r="E692" s="5"/>
+      <c r="D692" s="5"/>
     </row>
     <row r="693">
-      <c r="E693" s="5"/>
+      <c r="D693" s="5"/>
     </row>
     <row r="694">
-      <c r="E694" s="5"/>
+      <c r="D694" s="5"/>
     </row>
     <row r="695">
-      <c r="E695" s="5"/>
+      <c r="D695" s="5"/>
     </row>
     <row r="696">
-      <c r="E696" s="5"/>
+      <c r="D696" s="5"/>
     </row>
     <row r="697">
-      <c r="E697" s="5"/>
+      <c r="D697" s="5"/>
     </row>
     <row r="698">
-      <c r="E698" s="5"/>
+      <c r="D698" s="5"/>
     </row>
     <row r="699">
-      <c r="E699" s="5"/>
+      <c r="D699" s="5"/>
     </row>
     <row r="700">
-      <c r="E700" s="5"/>
+      <c r="D700" s="5"/>
     </row>
     <row r="701">
-      <c r="E701" s="5"/>
+      <c r="D701" s="5"/>
     </row>
     <row r="702">
-      <c r="E702" s="5"/>
+      <c r="D702" s="5"/>
     </row>
     <row r="703">
-      <c r="E703" s="5"/>
+      <c r="D703" s="5"/>
     </row>
     <row r="704">
-      <c r="E704" s="5"/>
+      <c r="D704" s="5"/>
     </row>
     <row r="705">
-      <c r="E705" s="5"/>
+      <c r="D705" s="5"/>
     </row>
     <row r="706">
-      <c r="E706" s="5"/>
+      <c r="D706" s="5"/>
     </row>
     <row r="707">
-      <c r="E707" s="5"/>
+      <c r="D707" s="5"/>
     </row>
     <row r="708">
-      <c r="E708" s="5"/>
+      <c r="D708" s="5"/>
     </row>
     <row r="709">
-      <c r="E709" s="5"/>
+      <c r="D709" s="5"/>
     </row>
     <row r="710">
-      <c r="E710" s="5"/>
+      <c r="D710" s="5"/>
     </row>
     <row r="711">
-      <c r="E711" s="5"/>
+      <c r="D711" s="5"/>
     </row>
     <row r="712">
-      <c r="E712" s="5"/>
+      <c r="D712" s="5"/>
     </row>
     <row r="713">
-      <c r="E713" s="5"/>
+      <c r="D713" s="5"/>
     </row>
     <row r="714">
-      <c r="E714" s="5"/>
+      <c r="D714" s="5"/>
     </row>
     <row r="715">
-      <c r="E715" s="5"/>
+      <c r="D715" s="5"/>
     </row>
     <row r="716">
-      <c r="E716" s="5"/>
+      <c r="D716" s="5"/>
     </row>
     <row r="717">
-      <c r="E717" s="5"/>
+      <c r="D717" s="5"/>
     </row>
     <row r="718">
-      <c r="E718" s="5"/>
+      <c r="D718" s="5"/>
     </row>
     <row r="719">
-      <c r="E719" s="5"/>
+      <c r="D719" s="5"/>
     </row>
     <row r="720">
-      <c r="E720" s="5"/>
+      <c r="D720" s="5"/>
     </row>
     <row r="721">
-      <c r="E721" s="5"/>
+      <c r="D721" s="5"/>
     </row>
     <row r="722">
-      <c r="E722" s="5"/>
+      <c r="D722" s="5"/>
     </row>
     <row r="723">
-      <c r="E723" s="5"/>
+      <c r="D723" s="5"/>
     </row>
     <row r="724">
-      <c r="E724" s="5"/>
+      <c r="D724" s="5"/>
     </row>
     <row r="725">
-      <c r="E725" s="5"/>
+      <c r="D725" s="5"/>
     </row>
     <row r="726">
-      <c r="E726" s="5"/>
+      <c r="D726" s="5"/>
     </row>
     <row r="727">
-      <c r="E727" s="5"/>
+      <c r="D727" s="5"/>
     </row>
     <row r="728">
-      <c r="E728" s="5"/>
+      <c r="D728" s="5"/>
     </row>
     <row r="729">
-      <c r="E729" s="5"/>
+      <c r="D729" s="5"/>
     </row>
     <row r="730">
-      <c r="E730" s="5"/>
+      <c r="D730" s="5"/>
     </row>
     <row r="731">
-      <c r="E731" s="5"/>
+      <c r="D731" s="5"/>
     </row>
     <row r="732">
-      <c r="E732" s="5"/>
+      <c r="D732" s="5"/>
     </row>
     <row r="733">
-      <c r="E733" s="5"/>
+      <c r="D733" s="5"/>
     </row>
     <row r="734">
-      <c r="E734" s="5"/>
+      <c r="D734" s="5"/>
     </row>
     <row r="735">
-      <c r="E735" s="5"/>
+      <c r="D735" s="5"/>
     </row>
     <row r="736">
-      <c r="E736" s="5"/>
+      <c r="D736" s="5"/>
     </row>
     <row r="737">
-      <c r="E737" s="5"/>
+      <c r="D737" s="5"/>
     </row>
     <row r="738">
-      <c r="E738" s="5"/>
+      <c r="D738" s="5"/>
     </row>
     <row r="739">
-      <c r="E739" s="5"/>
+      <c r="D739" s="5"/>
     </row>
     <row r="740">
-      <c r="E740" s="5"/>
+      <c r="D740" s="5"/>
     </row>
     <row r="741">
-      <c r="E741" s="5"/>
+      <c r="D741" s="5"/>
     </row>
     <row r="742">
-      <c r="E742" s="5"/>
+      <c r="D742" s="5"/>
     </row>
     <row r="743">
-      <c r="E743" s="5"/>
+      <c r="D743" s="5"/>
     </row>
     <row r="744">
-      <c r="E744" s="5"/>
+      <c r="D744" s="5"/>
     </row>
     <row r="745">
-      <c r="E745" s="5"/>
+      <c r="D745" s="5"/>
     </row>
     <row r="746">
-      <c r="E746" s="5"/>
+      <c r="D746" s="5"/>
     </row>
     <row r="747">
-      <c r="E747" s="5"/>
+      <c r="D747" s="5"/>
     </row>
     <row r="748">
-      <c r="E748" s="5"/>
+      <c r="D748" s="5"/>
     </row>
     <row r="749">
-      <c r="E749" s="5"/>
+      <c r="D749" s="5"/>
     </row>
     <row r="750">
-      <c r="E750" s="5"/>
+      <c r="D750" s="5"/>
     </row>
     <row r="751">
-      <c r="E751" s="5"/>
+      <c r="D751" s="5"/>
     </row>
     <row r="752">
-      <c r="E752" s="5"/>
+      <c r="D752" s="5"/>
     </row>
     <row r="753">
-      <c r="E753" s="5"/>
+      <c r="D753" s="5"/>
     </row>
     <row r="754">
-      <c r="E754" s="5"/>
+      <c r="D754" s="5"/>
     </row>
     <row r="755">
-      <c r="E755" s="5"/>
+      <c r="D755" s="5"/>
     </row>
     <row r="756">
-      <c r="E756" s="5"/>
+      <c r="D756" s="5"/>
     </row>
     <row r="757">
-      <c r="E757" s="5"/>
+      <c r="D757" s="5"/>
     </row>
     <row r="758">
-      <c r="E758" s="5"/>
+      <c r="D758" s="5"/>
     </row>
     <row r="759">
-      <c r="E759" s="5"/>
+      <c r="D759" s="5"/>
     </row>
     <row r="760">
-      <c r="E760" s="5"/>
+      <c r="D760" s="5"/>
     </row>
     <row r="761">
-      <c r="E761" s="5"/>
+      <c r="D761" s="5"/>
     </row>
     <row r="762">
-      <c r="E762" s="5"/>
+      <c r="D762" s="5"/>
     </row>
     <row r="763">
-      <c r="E763" s="5"/>
+      <c r="D763" s="5"/>
     </row>
     <row r="764">
-      <c r="E764" s="5"/>
+      <c r="D764" s="5"/>
     </row>
     <row r="765">
-      <c r="E765" s="5"/>
+      <c r="D765" s="5"/>
     </row>
     <row r="766">
-      <c r="E766" s="5"/>
+      <c r="D766" s="5"/>
     </row>
     <row r="767">
-      <c r="E767" s="5"/>
+      <c r="D767" s="5"/>
     </row>
     <row r="768">
-      <c r="E768" s="5"/>
+      <c r="D768" s="5"/>
     </row>
     <row r="769">
-      <c r="E769" s="5"/>
+      <c r="D769" s="5"/>
     </row>
     <row r="770">
-      <c r="E770" s="5"/>
+      <c r="D770" s="5"/>
     </row>
     <row r="771">
-      <c r="E771" s="5"/>
+      <c r="D771" s="5"/>
     </row>
     <row r="772">
-      <c r="E772" s="5"/>
+      <c r="D772" s="5"/>
     </row>
     <row r="773">
-      <c r="E773" s="5"/>
+      <c r="D773" s="5"/>
     </row>
     <row r="774">
-      <c r="E774" s="5"/>
+      <c r="D774" s="5"/>
     </row>
     <row r="775">
-      <c r="E775" s="5"/>
+      <c r="D775" s="5"/>
     </row>
     <row r="776">
-      <c r="E776" s="5"/>
+      <c r="D776" s="5"/>
     </row>
     <row r="777">
-      <c r="E777" s="5"/>
+      <c r="D777" s="5"/>
     </row>
     <row r="778">
-      <c r="E778" s="5"/>
+      <c r="D778" s="5"/>
     </row>
     <row r="779">
-      <c r="E779" s="5"/>
+      <c r="D779" s="5"/>
     </row>
     <row r="780">
-      <c r="E780" s="5"/>
+      <c r="D780" s="5"/>
     </row>
     <row r="781">
-      <c r="E781" s="5"/>
+      <c r="D781" s="5"/>
     </row>
     <row r="782">
-      <c r="E782" s="5"/>
+      <c r="D782" s="5"/>
     </row>
     <row r="783">
-      <c r="E783" s="5"/>
+      <c r="D783" s="5"/>
     </row>
     <row r="784">
-      <c r="E784" s="5"/>
+      <c r="D784" s="5"/>
     </row>
     <row r="785">
-      <c r="E785" s="5"/>
+      <c r="D785" s="5"/>
     </row>
     <row r="786">
-      <c r="E786" s="5"/>
+      <c r="D786" s="5"/>
     </row>
     <row r="787">
-      <c r="E787" s="5"/>
+      <c r="D787" s="5"/>
     </row>
     <row r="788">
-      <c r="E788" s="5"/>
+      <c r="D788" s="5"/>
     </row>
     <row r="789">
-      <c r="E789" s="5"/>
+      <c r="D789" s="5"/>
     </row>
     <row r="790">
-      <c r="E790" s="5"/>
+      <c r="D790" s="5"/>
     </row>
     <row r="791">
-      <c r="E791" s="5"/>
+      <c r="D791" s="5"/>
     </row>
     <row r="792">
-      <c r="E792" s="5"/>
+      <c r="D792" s="5"/>
     </row>
     <row r="793">
-      <c r="E793" s="5"/>
+      <c r="D793" s="5"/>
     </row>
     <row r="794">
-      <c r="E794" s="5"/>
+      <c r="D794" s="5"/>
     </row>
     <row r="795">
-      <c r="E795" s="5"/>
+      <c r="D795" s="5"/>
     </row>
     <row r="796">
-      <c r="E796" s="5"/>
+      <c r="D796" s="5"/>
     </row>
     <row r="797">
-      <c r="E797" s="5"/>
+      <c r="D797" s="5"/>
     </row>
     <row r="798">
-      <c r="E798" s="5"/>
+      <c r="D798" s="5"/>
     </row>
     <row r="799">
-      <c r="E799" s="5"/>
+      <c r="D799" s="5"/>
     </row>
     <row r="800">
-      <c r="E800" s="5"/>
+      <c r="D800" s="5"/>
     </row>
     <row r="801">
-      <c r="E801" s="5"/>
+      <c r="D801" s="5"/>
     </row>
     <row r="802">
-      <c r="E802" s="5"/>
+      <c r="D802" s="5"/>
     </row>
     <row r="803">
-      <c r="E803" s="5"/>
+      <c r="D803" s="5"/>
     </row>
     <row r="804">
-      <c r="E804" s="5"/>
+      <c r="D804" s="5"/>
     </row>
     <row r="805">
-      <c r="E805" s="5"/>
+      <c r="D805" s="5"/>
     </row>
     <row r="806">
-      <c r="E806" s="5"/>
+      <c r="D806" s="5"/>
     </row>
     <row r="807">
-      <c r="E807" s="5"/>
+      <c r="D807" s="5"/>
     </row>
     <row r="808">
-      <c r="E808" s="5"/>
+      <c r="D808" s="5"/>
     </row>
     <row r="809">
-      <c r="E809" s="5"/>
+      <c r="D809" s="5"/>
     </row>
     <row r="810">
-      <c r="E810" s="5"/>
+      <c r="D810" s="5"/>
     </row>
     <row r="811">
-      <c r="E811" s="5"/>
+      <c r="D811" s="5"/>
     </row>
     <row r="812">
-      <c r="E812" s="5"/>
+      <c r="D812" s="5"/>
     </row>
     <row r="813">
-      <c r="E813" s="5"/>
+      <c r="D813" s="5"/>
     </row>
     <row r="814">
-      <c r="E814" s="5"/>
+      <c r="D814" s="5"/>
     </row>
     <row r="815">
-      <c r="E815" s="5"/>
+      <c r="D815" s="5"/>
     </row>
     <row r="816">
-      <c r="E816" s="5"/>
+      <c r="D816" s="5"/>
     </row>
     <row r="817">
-      <c r="E817" s="5"/>
+      <c r="D817" s="5"/>
     </row>
     <row r="818">
-      <c r="E818" s="5"/>
+      <c r="D818" s="5"/>
     </row>
     <row r="819">
-      <c r="E819" s="5"/>
+      <c r="D819" s="5"/>
     </row>
     <row r="820">
-      <c r="E820" s="5"/>
+      <c r="D820" s="5"/>
     </row>
     <row r="821">
-      <c r="E821" s="5"/>
+      <c r="D821" s="5"/>
     </row>
     <row r="822">
-      <c r="E822" s="5"/>
+      <c r="D822" s="5"/>
     </row>
     <row r="823">
-      <c r="E823" s="5"/>
+      <c r="D823" s="5"/>
     </row>
     <row r="824">
-      <c r="E824" s="5"/>
+      <c r="D824" s="5"/>
     </row>
     <row r="825">
-      <c r="E825" s="5"/>
+      <c r="D825" s="5"/>
     </row>
     <row r="826">
-      <c r="E826" s="5"/>
+      <c r="D826" s="5"/>
     </row>
     <row r="827">
-      <c r="E827" s="5"/>
+      <c r="D827" s="5"/>
     </row>
     <row r="828">
-      <c r="E828" s="5"/>
+      <c r="D828" s="5"/>
     </row>
     <row r="829">
-      <c r="E829" s="5"/>
+      <c r="D829" s="5"/>
     </row>
     <row r="830">
-      <c r="E830" s="5"/>
+      <c r="D830" s="5"/>
     </row>
     <row r="831">
-      <c r="E831" s="5"/>
+      <c r="D831" s="5"/>
     </row>
     <row r="832">
-      <c r="E832" s="5"/>
+      <c r="D832" s="5"/>
     </row>
     <row r="833">
-      <c r="E833" s="5"/>
+      <c r="D833" s="5"/>
     </row>
     <row r="834">
-      <c r="E834" s="5"/>
+      <c r="D834" s="5"/>
     </row>
     <row r="835">
-      <c r="E835" s="5"/>
+      <c r="D835" s="5"/>
     </row>
     <row r="836">
-      <c r="E836" s="5"/>
+      <c r="D836" s="5"/>
     </row>
     <row r="837">
-      <c r="E837" s="5"/>
+      <c r="D837" s="5"/>
     </row>
     <row r="838">
-      <c r="E838" s="5"/>
+      <c r="D838" s="5"/>
     </row>
     <row r="839">
-      <c r="E839" s="5"/>
+      <c r="D839" s="5"/>
     </row>
     <row r="840">
-      <c r="E840" s="5"/>
+      <c r="D840" s="5"/>
     </row>
     <row r="841">
-      <c r="E841" s="5"/>
+      <c r="D841" s="5"/>
     </row>
     <row r="842">
-      <c r="E842" s="5"/>
+      <c r="D842" s="5"/>
     </row>
     <row r="843">
-      <c r="E843" s="5"/>
+      <c r="D843" s="5"/>
     </row>
     <row r="844">
-      <c r="E844" s="5"/>
+      <c r="D844" s="5"/>
     </row>
     <row r="845">
-      <c r="E845" s="5"/>
+      <c r="D845" s="5"/>
     </row>
     <row r="846">
-      <c r="E846" s="5"/>
+      <c r="D846" s="5"/>
     </row>
     <row r="847">
-      <c r="E847" s="5"/>
+      <c r="D847" s="5"/>
     </row>
     <row r="848">
-      <c r="E848" s="5"/>
+      <c r="D848" s="5"/>
     </row>
     <row r="849">
-      <c r="E849" s="5"/>
+      <c r="D849" s="5"/>
     </row>
     <row r="850">
-      <c r="E850" s="5"/>
+      <c r="D850" s="5"/>
     </row>
     <row r="851">
-      <c r="E851" s="5"/>
+      <c r="D851" s="5"/>
     </row>
     <row r="852">
-      <c r="E852" s="5"/>
+      <c r="D852" s="5"/>
     </row>
     <row r="853">
-      <c r="E853" s="5"/>
+      <c r="D853" s="5"/>
     </row>
     <row r="854">
-      <c r="E854" s="5"/>
+      <c r="D854" s="5"/>
     </row>
     <row r="855">
-      <c r="E855" s="5"/>
+      <c r="D855" s="5"/>
     </row>
     <row r="856">
-      <c r="E856" s="5"/>
+      <c r="D856" s="5"/>
     </row>
     <row r="857">
-      <c r="E857" s="5"/>
+      <c r="D857" s="5"/>
     </row>
     <row r="858">
-      <c r="E858" s="5"/>
+      <c r="D858" s="5"/>
     </row>
     <row r="859">
-      <c r="E859" s="5"/>
+      <c r="D859" s="5"/>
     </row>
     <row r="860">
-      <c r="E860" s="5"/>
+      <c r="D860" s="5"/>
     </row>
     <row r="861">
-      <c r="E861" s="5"/>
+      <c r="D861" s="5"/>
     </row>
     <row r="862">
-      <c r="E862" s="5"/>
+      <c r="D862" s="5"/>
     </row>
     <row r="863">
-      <c r="E863" s="5"/>
+      <c r="D863" s="5"/>
     </row>
     <row r="864">
-      <c r="E864" s="5"/>
+      <c r="D864" s="5"/>
     </row>
     <row r="865">
-      <c r="E865" s="5"/>
+      <c r="D865" s="5"/>
     </row>
     <row r="866">
-      <c r="E866" s="5"/>
+      <c r="D866" s="5"/>
     </row>
     <row r="867">
-      <c r="E867" s="5"/>
+      <c r="D867" s="5"/>
     </row>
     <row r="868">
-      <c r="E868" s="5"/>
+      <c r="D868" s="5"/>
     </row>
     <row r="869">
-      <c r="E869" s="5"/>
+      <c r="D869" s="5"/>
     </row>
     <row r="870">
-      <c r="E870" s="5"/>
+      <c r="D870" s="5"/>
     </row>
     <row r="871">
-      <c r="E871" s="5"/>
+      <c r="D871" s="5"/>
     </row>
     <row r="872">
-      <c r="E872" s="5"/>
+      <c r="D872" s="5"/>
     </row>
     <row r="873">
-      <c r="E873" s="5"/>
+      <c r="D873" s="5"/>
     </row>
     <row r="874">
-      <c r="E874" s="5"/>
+      <c r="D874" s="5"/>
     </row>
     <row r="875">
-      <c r="E875" s="5"/>
+      <c r="D875" s="5"/>
     </row>
     <row r="876">
-      <c r="E876" s="5"/>
+      <c r="D876" s="5"/>
     </row>
     <row r="877">
-      <c r="E877" s="5"/>
+      <c r="D877" s="5"/>
     </row>
     <row r="878">
-      <c r="E878" s="5"/>
+      <c r="D878" s="5"/>
     </row>
     <row r="879">
-      <c r="E879" s="5"/>
+      <c r="D879" s="5"/>
     </row>
     <row r="880">
-      <c r="E880" s="5"/>
+      <c r="D880" s="5"/>
     </row>
     <row r="881">
-      <c r="E881" s="5"/>
+      <c r="D881" s="5"/>
     </row>
     <row r="882">
-      <c r="E882" s="5"/>
+      <c r="D882" s="5"/>
     </row>
     <row r="883">
-      <c r="E883" s="5"/>
+      <c r="D883" s="5"/>
     </row>
     <row r="884">
-      <c r="E884" s="5"/>
+      <c r="D884" s="5"/>
     </row>
     <row r="885">
-      <c r="E885" s="5"/>
+      <c r="D885" s="5"/>
     </row>
     <row r="886">
-      <c r="E886" s="5"/>
+      <c r="D886" s="5"/>
     </row>
     <row r="887">
-      <c r="E887" s="5"/>
+      <c r="D887" s="5"/>
     </row>
     <row r="888">
-      <c r="E888" s="5"/>
+      <c r="D888" s="5"/>
     </row>
     <row r="889">
-      <c r="E889" s="5"/>
+      <c r="D889" s="5"/>
     </row>
     <row r="890">
-      <c r="E890" s="5"/>
+      <c r="D890" s="5"/>
     </row>
     <row r="891">
-      <c r="E891" s="5"/>
+      <c r="D891" s="5"/>
     </row>
     <row r="892">
-      <c r="E892" s="5"/>
+      <c r="D892" s="5"/>
     </row>
     <row r="893">
-      <c r="E893" s="5"/>
+      <c r="D893" s="5"/>
     </row>
     <row r="894">
-      <c r="E894" s="5"/>
+      <c r="D894" s="5"/>
     </row>
     <row r="895">
-      <c r="E895" s="5"/>
+      <c r="D895" s="5"/>
     </row>
     <row r="896">
-      <c r="E896" s="5"/>
+      <c r="D896" s="5"/>
     </row>
     <row r="897">
-      <c r="E897" s="5"/>
+      <c r="D897" s="5"/>
     </row>
     <row r="898">
-      <c r="E898" s="5"/>
+      <c r="D898" s="5"/>
     </row>
     <row r="899">
-      <c r="E899" s="5"/>
+      <c r="D899" s="5"/>
     </row>
     <row r="900">
-      <c r="E900" s="5"/>
+      <c r="D900" s="5"/>
     </row>
     <row r="901">
-      <c r="E901" s="5"/>
+      <c r="D901" s="5"/>
     </row>
     <row r="902">
-      <c r="E902" s="5"/>
+      <c r="D902" s="5"/>
     </row>
     <row r="903">
-      <c r="E903" s="5"/>
+      <c r="D903" s="5"/>
     </row>
     <row r="904">
-      <c r="E904" s="5"/>
+      <c r="D904" s="5"/>
     </row>
     <row r="905">
-      <c r="E905" s="5"/>
+      <c r="D905" s="5"/>
     </row>
     <row r="906">
-      <c r="E906" s="5"/>
+      <c r="D906" s="5"/>
     </row>
     <row r="907">
-      <c r="E907" s="5"/>
+      <c r="D907" s="5"/>
     </row>
     <row r="908">
-      <c r="E908" s="5"/>
+      <c r="D908" s="5"/>
     </row>
     <row r="909">
-      <c r="E909" s="5"/>
+      <c r="D909" s="5"/>
     </row>
     <row r="910">
-      <c r="E910" s="5"/>
+      <c r="D910" s="5"/>
     </row>
     <row r="911">
-      <c r="E911" s="5"/>
+      <c r="D911" s="5"/>
     </row>
     <row r="912">
-      <c r="E912" s="5"/>
+      <c r="D912" s="5"/>
     </row>
     <row r="913">
-      <c r="E913" s="5"/>
+      <c r="D913" s="5"/>
     </row>
     <row r="914">
-      <c r="E914" s="5"/>
+      <c r="D914" s="5"/>
     </row>
     <row r="915">
-      <c r="E915" s="5"/>
+      <c r="D915" s="5"/>
     </row>
     <row r="916">
-      <c r="E916" s="5"/>
+      <c r="D916" s="5"/>
     </row>
     <row r="917">
-      <c r="E917" s="5"/>
+      <c r="D917" s="5"/>
     </row>
     <row r="918">
-      <c r="E918" s="5"/>
+      <c r="D918" s="5"/>
     </row>
     <row r="919">
-      <c r="E919" s="5"/>
+      <c r="D919" s="5"/>
     </row>
     <row r="920">
-      <c r="E920" s="5"/>
+      <c r="D920" s="5"/>
     </row>
     <row r="921">
-      <c r="E921" s="5"/>
+      <c r="D921" s="5"/>
     </row>
     <row r="922">
-      <c r="E922" s="5"/>
+      <c r="D922" s="5"/>
     </row>
     <row r="923">
-      <c r="E923" s="5"/>
+      <c r="D923" s="5"/>
     </row>
     <row r="924">
-      <c r="E924" s="5"/>
+      <c r="D924" s="5"/>
     </row>
     <row r="925">
-      <c r="E925" s="5"/>
+      <c r="D925" s="5"/>
     </row>
     <row r="926">
-      <c r="E926" s="5"/>
+      <c r="D926" s="5"/>
     </row>
     <row r="927">
-      <c r="E927" s="5"/>
+      <c r="D927" s="5"/>
     </row>
     <row r="928">
-      <c r="E928" s="5"/>
+      <c r="D928" s="5"/>
     </row>
     <row r="929">
-      <c r="E929" s="5"/>
+      <c r="D929" s="5"/>
     </row>
     <row r="930">
-      <c r="E930" s="5"/>
+      <c r="D930" s="5"/>
     </row>
     <row r="931">
-      <c r="E931" s="5"/>
+      <c r="D931" s="5"/>
     </row>
     <row r="932">
-      <c r="E932" s="5"/>
+      <c r="D932" s="5"/>
     </row>
     <row r="933">
-      <c r="E933" s="5"/>
+      <c r="D933" s="5"/>
     </row>
     <row r="934">
-      <c r="E934" s="5"/>
+      <c r="D934" s="5"/>
     </row>
     <row r="935">
-      <c r="E935" s="5"/>
+      <c r="D935" s="5"/>
     </row>
     <row r="936">
-      <c r="E936" s="5"/>
+      <c r="D936" s="5"/>
     </row>
     <row r="937">
-      <c r="E937" s="5"/>
+      <c r="D937" s="5"/>
     </row>
     <row r="938">
-      <c r="E938" s="5"/>
+      <c r="D938" s="5"/>
     </row>
     <row r="939">
-      <c r="E939" s="5"/>
+      <c r="D939" s="5"/>
     </row>
     <row r="940">
-      <c r="E940" s="5"/>
+      <c r="D940" s="5"/>
     </row>
     <row r="941">
-      <c r="E941" s="5"/>
+      <c r="D941" s="5"/>
     </row>
     <row r="942">
-      <c r="E942" s="5"/>
+      <c r="D942" s="5"/>
     </row>
     <row r="943">
-      <c r="E943" s="5"/>
+      <c r="D943" s="5"/>
     </row>
     <row r="944">
-      <c r="E944" s="5"/>
+      <c r="D944" s="5"/>
     </row>
     <row r="945">
-      <c r="E945" s="5"/>
+      <c r="D945" s="5"/>
     </row>
     <row r="946">
-      <c r="E946" s="5"/>
+      <c r="D946" s="5"/>
     </row>
     <row r="947">
-      <c r="E947" s="5"/>
+      <c r="D947" s="5"/>
     </row>
     <row r="948">
-      <c r="E948" s="5"/>
+      <c r="D948" s="5"/>
     </row>
     <row r="949">
-      <c r="E949" s="5"/>
+      <c r="D949" s="5"/>
     </row>
     <row r="950">
-      <c r="E950" s="5"/>
+      <c r="D950" s="5"/>
     </row>
     <row r="951">
-      <c r="E951" s="5"/>
+      <c r="D951" s="5"/>
     </row>
     <row r="952">
-      <c r="E952" s="5"/>
+      <c r="D952" s="5"/>
     </row>
     <row r="953">
-      <c r="E953" s="5"/>
+      <c r="D953" s="5"/>
     </row>
     <row r="954">
-      <c r="E954" s="5"/>
+      <c r="D954" s="5"/>
     </row>
     <row r="955">
-      <c r="E955" s="5"/>
+      <c r="D955" s="5"/>
     </row>
     <row r="956">
-      <c r="E956" s="5"/>
+      <c r="D956" s="5"/>
     </row>
     <row r="957">
-      <c r="E957" s="5"/>
+      <c r="D957" s="5"/>
     </row>
     <row r="958">
-      <c r="E958" s="5"/>
+      <c r="D958" s="5"/>
     </row>
     <row r="959">
-      <c r="E959" s="5"/>
+      <c r="D959" s="5"/>
     </row>
     <row r="960">
-      <c r="E960" s="5"/>
+      <c r="D960" s="5"/>
     </row>
     <row r="961">
-      <c r="E961" s="5"/>
+      <c r="D961" s="5"/>
     </row>
     <row r="962">
-      <c r="E962" s="5"/>
+      <c r="D962" s="5"/>
     </row>
     <row r="963">
-      <c r="E963" s="5"/>
+      <c r="D963" s="5"/>
     </row>
     <row r="964">
-      <c r="E964" s="5"/>
+      <c r="D964" s="5"/>
     </row>
     <row r="965">
-      <c r="E965" s="5"/>
+      <c r="D965" s="5"/>
     </row>
     <row r="966">
-      <c r="E966" s="5"/>
+      <c r="D966" s="5"/>
     </row>
     <row r="967">
-      <c r="E967" s="5"/>
+      <c r="D967" s="5"/>
     </row>
     <row r="968">
-      <c r="E968" s="5"/>
+      <c r="D968" s="5"/>
     </row>
     <row r="969">
-      <c r="E969" s="5"/>
+      <c r="D969" s="5"/>
     </row>
     <row r="970">
-      <c r="E970" s="5"/>
+      <c r="D970" s="5"/>
     </row>
     <row r="971">
-      <c r="E971" s="5"/>
+      <c r="D971" s="5"/>
     </row>
     <row r="972">
-      <c r="E972" s="5"/>
+      <c r="D972" s="5"/>
     </row>
     <row r="973">
-      <c r="E973" s="5"/>
+      <c r="D973" s="5"/>
     </row>
     <row r="974">
-      <c r="E974" s="5"/>
+      <c r="D974" s="5"/>
     </row>
     <row r="975">
-      <c r="E975" s="5"/>
+      <c r="D975" s="5"/>
     </row>
     <row r="976">
-      <c r="E976" s="5"/>
+      <c r="D976" s="5"/>
     </row>
     <row r="977">
-      <c r="E977" s="5"/>
+      <c r="D977" s="5"/>
     </row>
     <row r="978">
-      <c r="E978" s="5"/>
+      <c r="D978" s="5"/>
     </row>
     <row r="979">
-      <c r="E979" s="5"/>
+      <c r="D979" s="5"/>
     </row>
     <row r="980">
-      <c r="E980" s="5"/>
+      <c r="D980" s="5"/>
     </row>
     <row r="981">
-      <c r="E981" s="5"/>
+      <c r="D981" s="5"/>
     </row>
     <row r="982">
-      <c r="E982" s="5"/>
+      <c r="D982" s="5"/>
     </row>
     <row r="983">
-      <c r="E983" s="5"/>
+      <c r="D983" s="5"/>
     </row>
     <row r="984">
-      <c r="E984" s="5"/>
+      <c r="D984" s="5"/>
     </row>
     <row r="985">
-      <c r="E985" s="5"/>
+      <c r="D985" s="5"/>
     </row>
     <row r="986">
-      <c r="E986" s="5"/>
+      <c r="D986" s="5"/>
     </row>
     <row r="987">
-      <c r="E987" s="5"/>
+      <c r="D987" s="5"/>
     </row>
     <row r="988">
-      <c r="E988" s="5"/>
+      <c r="D988" s="5"/>
     </row>
     <row r="989">
-      <c r="E989" s="5"/>
+      <c r="D989" s="5"/>
     </row>
     <row r="990">
-      <c r="E990" s="5"/>
+      <c r="D990" s="5"/>
     </row>
     <row r="991">
-      <c r="E991" s="5"/>
+      <c r="D991" s="5"/>
     </row>
     <row r="992">
-      <c r="E992" s="5"/>
+      <c r="D992" s="5"/>
     </row>
     <row r="993">
-      <c r="E993" s="5"/>
+      <c r="D993" s="5"/>
     </row>
     <row r="994">
-      <c r="E994" s="5"/>
+      <c r="D994" s="5"/>
     </row>
     <row r="995">
-      <c r="E995" s="5"/>
+      <c r="D995" s="5"/>
     </row>
     <row r="996">
-      <c r="E996" s="5"/>
+      <c r="D996" s="5"/>
     </row>
     <row r="997">
-      <c r="E997" s="5"/>
+      <c r="D997" s="5"/>
     </row>
     <row r="998">
-      <c r="E998" s="5"/>
+      <c r="D998" s="5"/>
     </row>
     <row r="999">
-      <c r="E999" s="5"/>
+      <c r="D999" s="5"/>
     </row>
     <row r="1000">
-      <c r="E1000" s="5"/>
+      <c r="D1000" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -18612,7 +18627,7 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>56</v>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="225">
   <si>
     <t>Discards</t>
   </si>
@@ -203,6 +203,9 @@
     <t>Gain 1 point for each pair of balls of different colors in a lane when it is scored.</t>
   </si>
   <si>
+    <t>Max 2</t>
+  </si>
+  <si>
     <t>Combola 2</t>
   </si>
   <si>
@@ -212,7 +215,7 @@
     <t>Combola 3</t>
   </si>
   <si>
-    <t>Gain 2 points if blue is the majority color in the discard when you score a lane.</t>
+    <t>Gain 1 points for every two balls that match in color between the Lanes.</t>
   </si>
   <si>
     <t>Combola 4</t>
@@ -221,10 +224,16 @@
     <t xml:space="preserve">Gain 1 point if the first and last ball in a lane is of the same color when it is scored. </t>
   </si>
   <si>
+    <t>Max 1</t>
+  </si>
+  <si>
     <t>Combola 5</t>
   </si>
   <si>
     <t>When a lane is scored, gain 1 point for each ball that is adjacent to two balls of colors different from its own.</t>
+  </si>
+  <si>
+    <t>Max 3</t>
   </si>
   <si>
     <t>Lane 1</t>
@@ -493,25 +502,25 @@
     <t>1 - 2 - 4</t>
   </si>
   <si>
-    <t>Gain 1 Retains</t>
+    <t>Gain 2 Retains</t>
   </si>
   <si>
     <t>Stamp 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Add 1 temporary Yellow ball to the Combola. </t>
+    <t xml:space="preserve">Add 2 temporary Yellow balls to the Combola. </t>
   </si>
   <si>
     <t>Stamp 3</t>
   </si>
   <si>
-    <t>Gain 1 Channels</t>
+    <t>Gain 2 Channels</t>
   </si>
   <si>
     <t>Stamp 4</t>
   </si>
   <si>
-    <t>Draw 1 ball</t>
+    <t>Gain 1 Bounces</t>
   </si>
   <si>
     <t>Stamp 5</t>
@@ -520,160 +529,182 @@
     <t>7 - 11</t>
   </si>
   <si>
+    <t xml:space="preserve">Play when a Lane explodes. The Lane does not close but balls are still destroyed as normal. </t>
+  </si>
+  <si>
+    <t>Stamp 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 4 balls and increase the size of one Lane by 2. </t>
+  </si>
+  <si>
+    <t>Stamp 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 3 random Blue balls from the Discard. </t>
+  </si>
+  <si>
+    <t>Stamp 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score a Lane. The Lane then Explodes. </t>
+  </si>
+  <si>
+    <t>Stamp 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard 4 non-black balls from the Combola to gain 1 Key. </t>
+  </si>
+  <si>
+    <t>Stamp 10</t>
+  </si>
+  <si>
+    <t>Gain 3 Health</t>
+  </si>
+  <si>
+    <t>Stamp 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy half of all balls (rounded up) in a Lane. Then Score that Lane. </t>
+  </si>
+  <si>
+    <t>Stamp 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play as a copy of a Stamp of Level 4 or lower five times. </t>
+  </si>
+  <si>
+    <t>Stamp 13</t>
+  </si>
+  <si>
+    <t>Gain 2 Gold</t>
+  </si>
+  <si>
+    <t>Stamp 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score all balls in the Lane with the fewest number of balls. </t>
+  </si>
+  <si>
+    <t>Stamp 15</t>
+  </si>
+  <si>
+    <t>Gain 1 Key and lose 1 Health</t>
+  </si>
+  <si>
+    <t>Stamp 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw all Destroyed balls. </t>
+  </si>
+  <si>
+    <t>Black 1</t>
+  </si>
+  <si>
+    <t>trial_deck</t>
+  </si>
+  <si>
+    <t>Gain 1 Key.&lt;/br&gt;&lt;/br&gt;
+Add 1 Black ball to the Combola per Level.</t>
+  </si>
+  <si>
+    <t>Black 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase Lane size by 1.&lt;/br&gt;&lt;/br&gt;
+Increase Damage Taken by 1 for each Level. </t>
+  </si>
+  <si>
+    <t>Black 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lose 1 Power per Level. </t>
+  </si>
+  <si>
+    <t>Black 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black balls are moved to the Combola after they are Scored. </t>
+  </si>
+  <si>
+    <t>Black 5</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>Judgement 1</t>
+  </si>
+  <si>
+    <t>judgement_deck</t>
+  </si>
+  <si>
+    <t>Lose one Key.</t>
+  </si>
+  <si>
+    <t>Judgement 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup:&lt;/br&gt;
+Discard half of all balls in the Combola. Return any discarded Black balls. </t>
+  </si>
+  <si>
+    <t>Judgement 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have an additional Key. </t>
+  </si>
+  <si>
+    <t>Stars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two starts in the Same Lane provides 1 Point before they both are destroyed. </t>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>Rock?</t>
+  </si>
+  <si>
+    <t>Magnetic?</t>
+  </si>
+  <si>
+    <t>Ghost?</t>
+  </si>
+  <si>
+    <t>Explode:</t>
+  </si>
+  <si>
+    <t>Shielded:</t>
+  </si>
+  <si>
+    <t>Can't be destroyed and Brittle isn't reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brittle X: </t>
+  </si>
+  <si>
+    <t>Destroyed after X collisions</t>
+  </si>
+  <si>
+    <t>Stamps</t>
+  </si>
+  <si>
+    <t>Draw a Discarded ball of your choice.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Destroy all balls except 1 in a Lane. </t>
-  </si>
-  <si>
-    <t>Stamp 6</t>
-  </si>
-  <si>
-    <t>Gain 3 Bounces</t>
-  </si>
-  <si>
-    <t>Stamp 7</t>
   </si>
   <si>
     <t xml:space="preserve">Draw 3 balls.&lt;/br&gt;&lt;/br&gt;
 You may Destroy all balls in the Draw area. </t>
   </si>
   <si>
-    <t>Stamp 8</t>
-  </si>
-  <si>
-    <t>Stamp 9</t>
-  </si>
-  <si>
-    <t>Draw a Discarded ball of your choice.</t>
-  </si>
-  <si>
-    <t>Stamp 10</t>
-  </si>
-  <si>
-    <t>Gain 2 Health</t>
-  </si>
-  <si>
-    <t>Stamp 11</t>
-  </si>
-  <si>
     <t xml:space="preserve">Draw 3 random Discarded balls. </t>
-  </si>
-  <si>
-    <t>Stamp 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play as a copy of a Stamp of Level 4 or lower five times. </t>
-  </si>
-  <si>
-    <t>Stamp 13</t>
-  </si>
-  <si>
-    <t>Gain 3 Gold</t>
-  </si>
-  <si>
-    <t>Stamp 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score all balls in the Lane with the fewest number of balls. </t>
-  </si>
-  <si>
-    <t>Stamp 15</t>
-  </si>
-  <si>
-    <t>Gain 1 Key and lose 1 Health</t>
-  </si>
-  <si>
-    <t>Stamp 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw all Destroyed balls. </t>
-  </si>
-  <si>
-    <t>Black 1</t>
-  </si>
-  <si>
-    <t>trial_deck</t>
-  </si>
-  <si>
-    <t>Gain 1 Key.&lt;/br&gt;&lt;/br&gt;
-Add 1 Black ball to the Combola per Level.</t>
-  </si>
-  <si>
-    <t>Black 2</t>
-  </si>
-  <si>
-    <t>Black 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lose 1 Power per Level. </t>
-  </si>
-  <si>
-    <t>Black 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black balls are moved to the Combola after they are Scored. </t>
-  </si>
-  <si>
-    <t>Black 5</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
-    <t>Judgement 1</t>
-  </si>
-  <si>
-    <t>judgement_deck</t>
-  </si>
-  <si>
-    <t>Lose one Key.</t>
-  </si>
-  <si>
-    <t>Judgement 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setup:&lt;/br&gt;
-Discard half of all balls in the Combola. Return any discarded Black balls. </t>
-  </si>
-  <si>
-    <t>Judgement 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You have an additional Key. </t>
-  </si>
-  <si>
-    <t>Stars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two starts in the Same Lane provides 1 Point before they both are destroyed. </t>
-  </si>
-  <si>
-    <t>Freeze</t>
-  </si>
-  <si>
-    <t>Burn</t>
-  </si>
-  <si>
-    <t>Rock?</t>
-  </si>
-  <si>
-    <t>Magnetic?</t>
-  </si>
-  <si>
-    <t>Ghost?</t>
-  </si>
-  <si>
-    <t>Explode:</t>
-  </si>
-  <si>
-    <t>Shielded:</t>
-  </si>
-  <si>
-    <t>Can't be destroyed and Brittle isn't reduced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brittle X: </t>
-  </si>
-  <si>
-    <t>Destroyed after X collisions</t>
   </si>
 </sst>
 </file>
@@ -1290,10 +1321,13 @@
       <c r="D2" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>59</v>
@@ -1302,12 +1336,15 @@
         <v>1.0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>59</v>
@@ -1316,12 +1353,15 @@
         <v>1.0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>59</v>
@@ -1330,12 +1370,15 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>59</v>
@@ -1344,7 +1387,10 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -4363,131 +4409,131 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1">
         <v>0.0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1">
         <v>1.0</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1">
         <v>1.0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1">
         <v>1.0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1">
         <v>1.0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -7472,13 +7518,13 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>57</v>
@@ -7489,82 +7535,82 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C2" s="1">
         <v>6.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
         <v>1.0</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C3" s="1">
         <v>6.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
         <v>1.0</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1">
         <v>5.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
         <v>1.0</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="1">
         <v>8.0</v>
@@ -7573,7 +7619,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1">
         <v>2.0</v>
@@ -7582,7 +7628,7 @@
         <v>1.0</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I5" s="1">
         <v>1.0</v>
@@ -7590,10 +7636,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C6" s="1">
         <v>8.0</v>
@@ -7602,7 +7648,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1">
         <v>2.0</v>
@@ -7611,7 +7657,7 @@
         <v>1.0</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I6" s="1">
         <v>0.5</v>
@@ -7619,10 +7665,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1">
         <v>8.0</v>
@@ -7631,7 +7677,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1">
         <v>2.0</v>
@@ -7640,18 +7686,18 @@
         <v>1.0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1">
         <v>8.0</v>
@@ -7660,7 +7706,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1">
         <v>2.0</v>
@@ -7669,7 +7715,7 @@
         <v>1.0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I8" s="1">
         <v>0.5</v>
@@ -7677,10 +7723,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1">
         <v>8.0</v>
@@ -7689,7 +7735,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1">
         <v>2.0</v>
@@ -7698,19 +7744,19 @@
         <v>1.0</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1">
         <v>8.0</v>
@@ -7719,7 +7765,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F10" s="1">
         <v>2.0</v>
@@ -7728,7 +7774,7 @@
         <v>1.0</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I10" s="1">
         <v>0.5</v>
@@ -7737,10 +7783,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1">
         <v>8.0</v>
@@ -7749,7 +7795,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F11" s="1">
         <v>2.0</v>
@@ -7758,19 +7804,19 @@
         <v>1.0</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -7779,7 +7825,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F12" s="1">
         <v>4.0</v>
@@ -7788,16 +7834,16 @@
         <v>1.0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C13" s="1">
         <v>3.0</v>
@@ -7806,7 +7852,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1">
         <v>4.0</v>
@@ -7815,16 +7861,16 @@
         <v>1.0</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1">
         <v>3.0</v>
@@ -7833,7 +7879,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F14" s="1">
         <v>4.0</v>
@@ -7842,16 +7888,16 @@
         <v>1.0</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1">
         <v>3.0</v>
@@ -7860,7 +7906,7 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
@@ -7869,16 +7915,16 @@
         <v>1.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1">
         <v>3.0</v>
@@ -7887,7 +7933,7 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1">
         <v>4.0</v>
@@ -7896,16 +7942,16 @@
         <v>3.0</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C17" s="1">
         <v>3.0</v>
@@ -7914,7 +7960,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1">
         <v>4.0</v>
@@ -7923,16 +7969,16 @@
         <v>1.0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C18" s="1">
         <v>3.0</v>
@@ -7941,7 +7987,7 @@
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1">
         <v>4.0</v>
@@ -7950,16 +7996,16 @@
         <v>1.0</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C19" s="1">
         <v>3.0</v>
@@ -7968,7 +8014,7 @@
         <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1">
         <v>4.0</v>
@@ -7977,16 +8023,16 @@
         <v>1.0</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C20" s="1">
         <v>3.0</v>
@@ -7995,7 +8041,7 @@
         <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1">
         <v>0.0</v>
@@ -8004,16 +8050,16 @@
         <v>1.0</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C21" s="1">
         <v>0.0</v>
@@ -8022,7 +8068,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1">
         <v>8.0</v>
@@ -8031,15 +8077,15 @@
         <v>1.0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C22" s="1">
         <v>0.0</v>
@@ -8048,7 +8094,7 @@
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
@@ -8057,10 +8103,10 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1">
         <v>1.0</v>
@@ -8069,7 +8115,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F23" s="1">
         <v>8.0</v>
@@ -8078,15 +8124,15 @@
         <v>4.0</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C24" s="1">
         <v>0.0</v>
@@ -8095,7 +8141,7 @@
         <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1">
         <v>8.0</v>
@@ -8107,10 +8153,10 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C25" s="1">
         <v>1.0</v>
@@ -8119,7 +8165,7 @@
         <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F25" s="1">
         <v>8.0</v>
@@ -8128,7 +8174,7 @@
         <v>6.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
@@ -11076,16 +11122,16 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>56</v>
@@ -11096,140 +11142,140 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C6" s="1">
         <v>1.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C7" s="1">
         <v>8.0</v>
@@ -11238,24 +11284,24 @@
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1">
         <v>2.0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C8" s="1">
         <v>8.0</v>
@@ -11264,24 +11310,24 @@
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1">
         <v>2.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1">
         <v>8.0</v>
@@ -11290,24 +11336,24 @@
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1">
         <v>2.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C10" s="1">
         <v>8.0</v>
@@ -11316,24 +11362,24 @@
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F10" s="1">
         <v>2.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -11342,24 +11388,24 @@
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F11" s="1">
         <v>4.0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -11368,24 +11414,24 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1">
         <v>4.0</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H12" s="1" t="s">
         <v>166</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -11394,48 +11440,50 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1">
         <v>4.0</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C14" s="1">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1">
         <v>4.0</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H14" s="4"/>
+        <v>166</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -11444,24 +11492,24 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -11470,24 +11518,24 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1">
         <v>4.0</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C17" s="1">
         <v>2.0</v>
@@ -11496,24 +11544,24 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1">
         <v>4.0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C18" s="1">
         <v>2.0</v>
@@ -11522,24 +11570,24 @@
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1">
         <v>4.0</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C19" s="1">
         <v>1.0</v>
@@ -11548,7 +11596,7 @@
         <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -11557,16 +11605,16 @@
         <v>16.0</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C20" s="1">
         <v>1.0</v>
@@ -11575,7 +11623,7 @@
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F20" s="1">
         <v>8.0</v>
@@ -11584,16 +11632,16 @@
         <v>16.0</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C21" s="1">
         <v>1.0</v>
@@ -11602,7 +11650,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F21" s="1">
         <v>8.0</v>
@@ -11611,15 +11659,15 @@
         <v>16.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C22" s="1">
         <v>1.0</v>
@@ -11628,7 +11676,7 @@
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
@@ -11637,7 +11685,7 @@
         <v>16.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K22" s="4"/>
     </row>
@@ -15555,64 +15603,66 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="4"/>
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C5" s="1">
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C6" s="1">
         <v>0.0</v>
@@ -18627,7 +18677,7 @@
         <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>56</v>
@@ -18635,10 +18685,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -18647,15 +18697,15 @@
         <v>56.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C3" s="1">
         <v>1.0</v>
@@ -18664,15 +18714,15 @@
         <v>56.0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C4" s="1">
         <v>1.0</v>
@@ -18681,7 +18731,7 @@
         <v>84.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -18701,56 +18751,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="231">
   <si>
     <t>Discards</t>
   </si>
@@ -215,16 +215,17 @@
     <t>Combola 3</t>
   </si>
   <si>
-    <t>Gain 1 points for every two balls that match in color between the Lanes.</t>
+    <t>Gain 1 points for every opposite ball in the other Lane that match in color when it is Scored.</t>
+  </si>
+  <si>
+    <t>Max 5 (2/3)</t>
   </si>
   <si>
     <t>Combola 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 1 point if the first and last ball in a lane is of the same color when it is scored. </t>
-  </si>
-  <si>
-    <t>Max 1</t>
+    <t xml:space="preserve">Gain 1 Point for each Lane whose first ball and last ball are the same color when ANY Lane is scored.
+</t>
   </si>
   <si>
     <t>Combola 5</t>
@@ -331,14 +332,13 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;When Scored:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Yellow if Yellow is the majority Color in this Lane. </t>
+Gain 1 Point if Yellow is the majority Color in this Lane. </t>
   </si>
   <si>
     <t>Ball 2</t>
   </si>
   <si>
-    <t>&lt;b&gt;When Scored:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Channels</t>
+    <t xml:space="preserve">Gain 1 Point when destroyed. </t>
   </si>
   <si>
     <t>Ball 3</t>
@@ -383,320 +383,327 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Yellow for each Yellow ball in the Draw area. </t>
+Gain 1 Point for each Yellow ball in the Draw area. </t>
   </si>
   <si>
     <t>Ball 9</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
+Draw a ball from any Lane.</t>
+  </si>
+  <si>
+    <t>Ball 10</t>
+  </si>
+  <si>
+    <t>Gain 1 Bounces whenever this Collides with a non-Yellow ball.</t>
+  </si>
+  <si>
+    <t>Ball 11</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;When Scored:&lt;/b&gt;&lt;/br&gt;
+Gain 1 Bounces.</t>
+  </si>
+  <si>
+    <t>Ball 12</t>
+  </si>
+  <si>
+    <t>Brittle 2</t>
+  </si>
+  <si>
+    <t>Ball 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel this ball at the start of each Trial. </t>
+  </si>
+  <si>
+    <t>Ball 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjacent balls are Shielded. </t>
+  </si>
+  <si>
+    <t>Ball 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score any ball this Collides with. </t>
+  </si>
+  <si>
+    <t>Ball 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 4 Gold when this is bought. </t>
+  </si>
+  <si>
+    <t>Ball 17</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;</t>
+  </si>
+  <si>
+    <t>Ball 18</t>
+  </si>
+  <si>
+    <t>Ball 19</t>
+  </si>
+  <si>
+    <t>Destroy any ball this lands on.</t>
+  </si>
+  <si>
+    <t>Ball 20</t>
+  </si>
+  <si>
+    <t>Ball 21</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Starting Stamp 1</t>
+  </si>
+  <si>
+    <t>stamp_starter</t>
+  </si>
+  <si>
+    <t>Gain 1 Retains for every 2 Power</t>
+  </si>
+  <si>
+    <t>Starting Stamp 2</t>
+  </si>
+  <si>
+    <t>Draw 1 ball for every 2 Power</t>
+  </si>
+  <si>
+    <t>Starting Stamp 3</t>
+  </si>
+  <si>
+    <t>Gain 1 Channels for each Power</t>
+  </si>
+  <si>
+    <t>Starting Stamp 4</t>
+  </si>
+  <si>
+    <t>Gain 1 Bounces for every 3 Power</t>
+  </si>
+  <si>
+    <t>Starting Stamp 5</t>
+  </si>
+  <si>
+    <t>Shield 1 ball for every 2 Power</t>
+  </si>
+  <si>
+    <t>Stamp 1</t>
+  </si>
+  <si>
+    <t>stamp_deck</t>
+  </si>
+  <si>
+    <t>1 - 2 - 4</t>
+  </si>
+  <si>
+    <t>Gain 2 Retains</t>
+  </si>
+  <si>
+    <t>Stamp 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add 2 temporary Yellow balls to the Combola. </t>
+  </si>
+  <si>
+    <t>Stamp 3</t>
+  </si>
+  <si>
+    <t>Gain 2 Channels</t>
+  </si>
+  <si>
+    <t>Stamp 4</t>
+  </si>
+  <si>
+    <t>Gain 1 Bounces</t>
+  </si>
+  <si>
+    <t>Stamp 5</t>
+  </si>
+  <si>
+    <t>7 - 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play when a Lane explodes. The Lane does not close but balls are still destroyed as normal. </t>
+  </si>
+  <si>
+    <t>Stamp 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 4 balls and increase the size of one Lane by 2. </t>
+  </si>
+  <si>
+    <t>Stamp 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw 3 random Blue balls from the Discard. </t>
+  </si>
+  <si>
+    <t>Stamp 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score a Lane. The Lane then Explodes. </t>
+  </si>
+  <si>
+    <t>Stamp 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard 4 non-black balls from the Combola to gain 1 Key. </t>
+  </si>
+  <si>
+    <t>Stamp 10</t>
+  </si>
+  <si>
+    <t>Gain 3 Health</t>
+  </si>
+  <si>
+    <t>Stamp 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy half of all balls (rounded up) in a Lane. Then Score that Lane. </t>
+  </si>
+  <si>
+    <t>Stamp 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play as a copy of a Stamp of Level 4 or lower 4 times. </t>
+  </si>
+  <si>
+    <t>Stamp 13</t>
+  </si>
+  <si>
+    <t>Gain 1 Point whenever a ball is Destroyed.</t>
+  </si>
+  <si>
+    <t>Stamp 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Combola effects trigger twice. </t>
+  </si>
+  <si>
+    <t>Stamp 15</t>
+  </si>
+  <si>
+    <t>Gain 1 Point whenever Yellow ball is drawn.</t>
+  </si>
+  <si>
+    <t>Stamp 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 1 Point whenever a Blue ball is put in the discard. </t>
+  </si>
+  <si>
+    <t>Black 1</t>
+  </si>
+  <si>
+    <t>trial_deck</t>
+  </si>
+  <si>
+    <t>Gain 1 Key.&lt;/br&gt;&lt;/br&gt;
+Add 1 Black ball to the Combola per Level.</t>
+  </si>
+  <si>
+    <t>Black 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase Lane size by 1.&lt;/br&gt;&lt;/br&gt;
+Increase Damage Taken by 1 for each Level. </t>
+  </si>
+  <si>
+    <t>Black 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lose 1 Power per Level. </t>
+  </si>
+  <si>
+    <t>Black 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black balls are moved to the Combola after they are Scored. </t>
+  </si>
+  <si>
+    <t>Black 5</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>Judgement 1</t>
+  </si>
+  <si>
+    <t>judgement_deck</t>
+  </si>
+  <si>
+    <t>Lose one Key.</t>
+  </si>
+  <si>
+    <t>Judgement 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup:&lt;/br&gt;
+Discard half of all balls in the Combola. Return any discarded Black balls. </t>
+  </si>
+  <si>
+    <t>Judgement 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have an additional Key. </t>
+  </si>
+  <si>
+    <t>Stars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two starts in the Same Lane provides 1 Point before they both are destroyed. </t>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>Rock?</t>
+  </si>
+  <si>
+    <t>Magnetic?</t>
+  </si>
+  <si>
+    <t>Ghost?</t>
+  </si>
+  <si>
+    <t>Explode:</t>
+  </si>
+  <si>
+    <t>Shielded:</t>
+  </si>
+  <si>
+    <t>Can't be destroyed and Brittle isn't reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brittle X: </t>
+  </si>
+  <si>
+    <t>Destroyed after X collisions</t>
+  </si>
+  <si>
+    <t>Stamps</t>
+  </si>
+  <si>
+    <t>Draw a Discarded ball of your choice.</t>
+  </si>
+  <si>
+    <t>Balls</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;
 Reveal a ball. Draw it and repeat this effect if it was Yellow. </t>
   </si>
   <si>
-    <t>Ball 10</t>
-  </si>
-  <si>
-    <t>Gain 1 Bounces whenever this Collides with a Black ball.</t>
-  </si>
-  <si>
-    <t>Ball 11</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;When Scored:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Bounces.</t>
-  </si>
-  <si>
-    <t>Ball 12</t>
-  </si>
-  <si>
-    <t>Brittle 2</t>
-  </si>
-  <si>
-    <t>Ball 13</t>
-  </si>
-  <si>
-    <t>Whenever you open a lane, you must Channel this ball if it is in a lane or in the combola.</t>
-  </si>
-  <si>
-    <t>Ball 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjacent balls are Shielded. </t>
-  </si>
-  <si>
-    <t>Ball 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score any ball this Collides with. </t>
-  </si>
-  <si>
-    <t>Ball 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain 4 Gold when this is bought. </t>
-  </si>
-  <si>
-    <t>Ball 17</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;On Draw:&lt;/b&gt;&lt;/br&gt;</t>
-  </si>
-  <si>
-    <t>Ball 18</t>
-  </si>
-  <si>
-    <t>Ball 19</t>
-  </si>
-  <si>
-    <t>Destroy any ball this lands on.</t>
-  </si>
-  <si>
-    <t>Ball 20</t>
-  </si>
-  <si>
-    <t>Ball 21</t>
-  </si>
-  <si>
-    <t>Requirement</t>
-  </si>
-  <si>
-    <t>Starting Stamp 1</t>
-  </si>
-  <si>
-    <t>stamp_starter</t>
-  </si>
-  <si>
-    <t>Gain 1 Retains for every 2 Power</t>
-  </si>
-  <si>
-    <t>Starting Stamp 2</t>
-  </si>
-  <si>
-    <t>Draw 1 ball for every 2 Power</t>
-  </si>
-  <si>
-    <t>Starting Stamp 3</t>
-  </si>
-  <si>
-    <t>Gain 1 Channels for each Power</t>
-  </si>
-  <si>
-    <t>Starting Stamp 4</t>
-  </si>
-  <si>
-    <t>Gain 1 Bounces for every 3 Power</t>
-  </si>
-  <si>
-    <t>Starting Stamp 5</t>
-  </si>
-  <si>
-    <t>Shield 1 ball for every 2 Power</t>
-  </si>
-  <si>
-    <t>Stamp 1</t>
-  </si>
-  <si>
-    <t>stamp_deck</t>
-  </si>
-  <si>
-    <t>1 - 2 - 4</t>
-  </si>
-  <si>
-    <t>Gain 2 Retains</t>
-  </si>
-  <si>
-    <t>Stamp 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add 2 temporary Yellow balls to the Combola. </t>
-  </si>
-  <si>
-    <t>Stamp 3</t>
-  </si>
-  <si>
-    <t>Gain 2 Channels</t>
-  </si>
-  <si>
-    <t>Stamp 4</t>
-  </si>
-  <si>
-    <t>Gain 1 Bounces</t>
-  </si>
-  <si>
-    <t>Stamp 5</t>
-  </si>
-  <si>
-    <t>7 - 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play when a Lane explodes. The Lane does not close but balls are still destroyed as normal. </t>
-  </si>
-  <si>
-    <t>Stamp 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw 4 balls and increase the size of one Lane by 2. </t>
-  </si>
-  <si>
-    <t>Stamp 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw 3 random Blue balls from the Discard. </t>
-  </si>
-  <si>
-    <t>Stamp 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score a Lane. The Lane then Explodes. </t>
-  </si>
-  <si>
-    <t>Stamp 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discard 4 non-black balls from the Combola to gain 1 Key. </t>
-  </si>
-  <si>
-    <t>Stamp 10</t>
-  </si>
-  <si>
-    <t>Gain 3 Health</t>
-  </si>
-  <si>
-    <t>Stamp 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destroy half of all balls (rounded up) in a Lane. Then Score that Lane. </t>
-  </si>
-  <si>
-    <t>Stamp 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play as a copy of a Stamp of Level 4 or lower five times. </t>
-  </si>
-  <si>
-    <t>Stamp 13</t>
-  </si>
-  <si>
-    <t>Gain 2 Gold</t>
-  </si>
-  <si>
-    <t>Stamp 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score all balls in the Lane with the fewest number of balls. </t>
-  </si>
-  <si>
-    <t>Stamp 15</t>
-  </si>
-  <si>
-    <t>Gain 1 Key and lose 1 Health</t>
-  </si>
-  <si>
-    <t>Stamp 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw all Destroyed balls. </t>
-  </si>
-  <si>
-    <t>Black 1</t>
-  </si>
-  <si>
-    <t>trial_deck</t>
-  </si>
-  <si>
-    <t>Gain 1 Key.&lt;/br&gt;&lt;/br&gt;
-Add 1 Black ball to the Combola per Level.</t>
-  </si>
-  <si>
-    <t>Black 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase Lane size by 1.&lt;/br&gt;&lt;/br&gt;
-Increase Damage Taken by 1 for each Level. </t>
-  </si>
-  <si>
-    <t>Black 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lose 1 Power per Level. </t>
-  </si>
-  <si>
-    <t>Black 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black balls are moved to the Combola after they are Scored. </t>
-  </si>
-  <si>
-    <t>Black 5</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
-    <t>Judgement 1</t>
-  </si>
-  <si>
-    <t>judgement_deck</t>
-  </si>
-  <si>
-    <t>Lose one Key.</t>
-  </si>
-  <si>
-    <t>Judgement 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setup:&lt;/br&gt;
-Discard half of all balls in the Combola. Return any discarded Black balls. </t>
-  </si>
-  <si>
-    <t>Judgement 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You have an additional Key. </t>
-  </si>
-  <si>
-    <t>Stars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two starts in the Same Lane provides 1 Point before they both are destroyed. </t>
-  </si>
-  <si>
-    <t>Freeze</t>
-  </si>
-  <si>
-    <t>Burn</t>
-  </si>
-  <si>
-    <t>Rock?</t>
-  </si>
-  <si>
-    <t>Magnetic?</t>
-  </si>
-  <si>
-    <t>Ghost?</t>
-  </si>
-  <si>
-    <t>Explode:</t>
-  </si>
-  <si>
-    <t>Shielded:</t>
-  </si>
-  <si>
-    <t>Can't be destroyed and Brittle isn't reduced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brittle X: </t>
-  </si>
-  <si>
-    <t>Destroyed after X collisions</t>
-  </si>
-  <si>
-    <t>Stamps</t>
-  </si>
-  <si>
-    <t>Draw a Discarded ball of your choice.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Destroy all balls except 1 in a Lane. </t>
   </si>
   <si>
@@ -705,6 +712,18 @@
   </si>
   <si>
     <t xml:space="preserve">Draw 3 random Discarded balls. </t>
+  </si>
+  <si>
+    <t>Gain 2 Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score all balls in the Lane with the fewest number of balls. </t>
+  </si>
+  <si>
+    <t>Gain 1 Key and lose 1 Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw all Destroyed balls. </t>
   </si>
 </sst>
 </file>
@@ -1356,12 +1375,12 @@
         <v>65</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>59</v>
@@ -1370,10 +1389,10 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -7858,9 +7877,9 @@
         <v>4.0</v>
       </c>
       <c r="G13" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="H13" s="4" t="s">
+        <v>2.0</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J13" s="4"/>
@@ -11604,7 +11623,7 @@
       <c r="G19" s="4">
         <v>16.0</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="1" t="s">
         <v>183</v>
       </c>
       <c r="K19" s="4"/>
@@ -11631,7 +11650,7 @@
       <c r="G20" s="4">
         <v>16.0</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="1" t="s">
         <v>185</v>
       </c>
       <c r="K20" s="4"/>
@@ -11658,7 +11677,7 @@
       <c r="G21" s="4">
         <v>16.0</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="4" t="s">
         <v>187</v>
       </c>
     </row>
@@ -11684,7 +11703,7 @@
       <c r="G22" s="4">
         <v>16.0</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K22" s="4"/>
@@ -18747,6 +18766,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="17.5"/>
+    <col customWidth="1" min="7" max="7" width="36.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18810,20 +18830,46 @@
       <c r="B15" s="1" t="s">
         <v>221</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="249">
   <si>
     <t>Base rules</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>Mist</t>
+  </si>
+  <si>
+    <t>ball_deck_2</t>
   </si>
   <si>
     <t>Uncommon</t>
@@ -7559,7 +7562,7 @@
         <v>73</v>
       </c>
       <c r="C2" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>74</v>
@@ -7579,7 +7582,7 @@
         <v>73</v>
       </c>
       <c r="C3" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>74</v>
@@ -7732,67 +7735,67 @@
         <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2">
         <v>3.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2">
         <v>3.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C12" s="2">
         <v>3.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>81</v>
@@ -7804,22 +7807,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C13" s="2">
         <v>3.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>87</v>
@@ -7831,25 +7834,25 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2">
         <v>3.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H14" s="2">
         <v>1.5</v>
@@ -7858,25 +7861,25 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C15" s="2">
         <v>3.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2">
         <v>1.5</v>
@@ -7885,22 +7888,22 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C16" s="2">
         <v>3.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>81</v>
@@ -7912,22 +7915,22 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C17" s="2">
         <v>3.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2">
         <v>1.5</v>
@@ -7936,46 +7939,46 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C18" s="2">
         <v>3.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C19" s="2">
         <v>3.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>92</v>
@@ -7984,22 +7987,22 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>81</v>
@@ -8011,91 +8014,91 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C24" s="2">
         <v>1.0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>81</v>
@@ -8103,25 +8106,25 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
@@ -11072,10 +11075,10 @@
         <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>39</v>
@@ -11086,10 +11089,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -11109,10 +11112,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -11132,10 +11135,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -11155,10 +11158,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
@@ -11178,10 +11181,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -11201,10 +11204,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="2">
         <v>8.0</v>
@@ -11219,18 +11222,18 @@
         <v>2.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="2">
         <v>8.0</v>
@@ -11245,18 +11248,18 @@
         <v>2.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2">
         <v>8.0</v>
@@ -11271,18 +11274,18 @@
         <v>2.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2">
         <v>8.0</v>
@@ -11297,24 +11300,24 @@
         <v>2.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2">
         <v>2.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>17</v>
@@ -11323,24 +11326,24 @@
         <v>4.0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2">
         <v>2.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
@@ -11349,24 +11352,24 @@
         <v>4.0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" s="2">
         <v>2.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -11375,24 +11378,24 @@
         <v>4.0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2">
         <v>2.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -11401,24 +11404,24 @@
         <v>4.0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -11427,24 +11430,24 @@
         <v>4.0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" s="2">
         <v>2.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -11453,24 +11456,24 @@
         <v>4.0</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="2">
         <v>2.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -11479,24 +11482,24 @@
         <v>4.0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2">
         <v>2.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -11505,24 +11508,24 @@
         <v>4.0</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>17</v>
@@ -11534,22 +11537,22 @@
         <v>16.0</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>17</v>
@@ -11561,22 +11564,22 @@
         <v>16.0</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>17</v>
@@ -11588,21 +11591,21 @@
         <v>16.0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
@@ -11614,7 +11617,7 @@
         <v>16.0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -15532,72 +15535,72 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -18608,7 +18611,7 @@
         <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>39</v>
@@ -18616,10 +18619,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -18628,15 +18631,15 @@
         <v>56.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -18645,15 +18648,15 @@
         <v>56.0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -18662,7 +18665,7 @@
         <v>84.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -18683,104 +18686,104 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="12"/>
     </row>
     <row r="2">
       <c r="B2" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -18801,132 +18804,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19">
@@ -18943,13 +18946,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="256">
   <si>
     <t>Base rules</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t xml:space="preserve">Add X copies of this to the Combola when the card is first gained. </t>
+  </si>
+  <si>
+    <t>Ethereal</t>
+  </si>
+  <si>
+    <t>Does not count toward Lane size</t>
   </si>
   <si>
     <t>Triggers:</t>
@@ -262,18 +268,21 @@
     <t>Common</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart if there is an open Rainbow in the other Lane. Increase this bonus by 1 for each Rainbow pair in play. </t>
+    <t>&lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
+Gain 1 Heart if the other Lane has an open Rainbow. +1 Heart per open Rainbow pair.</t>
   </si>
   <si>
     <t>Reward</t>
   </si>
   <si>
+    <t>1+scaling</t>
+  </si>
+  <si>
     <t>Platypus</t>
   </si>
   <si>
-    <t>&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
-Open a ball in play. If it was a Bomb (black), it detonates.</t>
+    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
+Open a ball in play. </t>
   </si>
   <si>
     <t>Manipulation
@@ -284,7 +293,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
-Select a ball in play and switch place with it. </t>
+Select a closed ball and switch place with it. </t>
   </si>
   <si>
     <t>Manipulation</t>
@@ -314,7 +323,7 @@
     <t xml:space="preserve">&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
 &lt;/br&gt;
 &lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
-Gain 2 Hearts and then destroy this. </t>
+Gain 2 Hearts. </t>
   </si>
   <si>
     <t>Mist</t>
@@ -330,11 +339,17 @@
 Replace the ball immediately above this with a ball from the Combola. Gain 2 Hearts if they were of the same Color. </t>
   </si>
   <si>
+    <t>1+2*x+y</t>
+  </si>
+  <si>
     <t>Lightning</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened or Destroyed:&lt;/b&gt;&lt;/br&gt;
-Open the two last balls in each Lane. </t>
+    <t>&lt;b&gt;When Destroyed:&lt;/b&gt;&lt;/br&gt;
+Gain 1 Heart and then Open the two topmost balls.&lt;/br&gt;
+&lt;/br&gt;
+&lt;b&gt;When Opened:&lt;b&gt;&lt;/br&gt;
+Destroy this.</t>
   </si>
   <si>
     <t>?</t>
@@ -367,26 +382,33 @@
     <t>Red Mage</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Detonate all Bombs (black) above this and gain 1 Heart for each. </t>
+    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
+Destroy a non-bomb (black) ball. Gain 2 Hearts. </t>
   </si>
   <si>
     <t>Starter
 Reward</t>
   </si>
   <si>
+    <t>1+0.5</t>
+  </si>
+  <si>
     <t>Toaster</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Get a Toast trophy and 2 Hearts. Then close this. </t>
+Get a Toast trophy and 1 Heart. Then close this. </t>
   </si>
   <si>
     <t>Snowglobe</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Brittle 2&lt;/b&gt;&lt;/br&gt;&lt;/br&gt;
-Gain 1 Heart each time there is a collision above this. </t>
+&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Gain 1 Heart for each time there was a collision above this ball. </t>
+  </si>
+  <si>
+    <t>Reward, Risk</t>
   </si>
   <si>
     <t>Geode</t>
@@ -401,7 +423,7 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>Glass Bomb</t>
+    <t>Brittle Bomb</t>
   </si>
   <si>
     <t>&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
@@ -409,6 +431,9 @@
 &lt;b&gt;Brittle 4&lt;/b&gt;</t>
   </si>
   <si>
+    <t>High: 3.5</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
@@ -416,31 +441,31 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart for each unique colored ball above this. Count both Lanes separately if in the middle.  </t>
+Gain 1 Heart for each uniquely colored ball above this. Count both Lanes separately if in the middle.  </t>
   </si>
   <si>
     <t>Mr Marshmallow</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 1 Redraw whenever you open a ball above this. </t>
+    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
+Gain 1 Heart.&lt;/br&gt;
+Gain 1 Redraw for each open ball in a Lane. </t>
   </si>
   <si>
     <t>Reward, Safety</t>
   </si>
   <si>
-    <t>Protagonist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Invulnerable&lt;/b&gt;&lt;/br&gt;
-&lt;/br&gt;
-&lt;b&gt;On Collision:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart. </t>
+    <t>Seer</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Gain 3 Redraw. Draw 3 balls and place them one at a time.</t>
   </si>
   <si>
     <t>Combola</t>
   </si>
   <si>
-    <t xml:space="preserve">Whenever you draw and place a ball in this Lane, place a copy of that ball (if you have one) from the Combola in the same Lane. </t>
+    <t>Whenever you place a ball in this Lane, draw a copy of that ball from the Combola, if able. The drawn ball becomes &lt;b&gt;Ethereal&lt;/b&gt;.</t>
   </si>
   <si>
     <t>Jade</t>
@@ -455,10 +480,10 @@
     <t>Uranium</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart for each ball in this Lane. 
+    <t xml:space="preserve">Detonate this Lane whenever you have three or more balls of the same color in the Lane. &lt;/br&gt;
 &lt;/br&gt;
-Destroy all balls in play when this detonates. Detonates whenever you have three or more balls of the same color in this Lane. </t>
+&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Gain 1 Heart for each ball in this Lane. </t>
   </si>
   <si>
     <t>Risk</t>
@@ -822,6 +847,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m-d"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="10.0"/>
@@ -845,12 +873,24 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+        <bgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -865,7 +905,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -890,13 +930,22 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1298,24 +1347,32 @@
         <v>31</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1335,41 +1392,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -1377,10 +1434,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -1389,10 +1446,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
@@ -1401,16 +1458,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -4412,148 +4469,148 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -7524,281 +7581,299 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.38"/>
-    <col customWidth="1" min="6" max="6" width="42.63"/>
+    <col customWidth="1" min="6" max="6" width="44.38"/>
     <col customWidth="1" min="7" max="7" width="15.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2">
         <v>12.0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2">
         <v>4.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2">
         <v>10.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2">
         <v>10.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="2">
         <v>10.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" s="2">
         <v>10.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="H7" s="8">
+        <v>46024.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2">
         <v>10.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2">
         <v>10.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2.0</v>
       </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>98</v>
+      <c r="F10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="C11" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>100</v>
+      <c r="F11" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2">
         <v>1.5</v>
@@ -7807,25 +7882,25 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2">
         <v>1.0</v>
@@ -7834,25 +7909,25 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H14" s="2">
         <v>1.5</v>
@@ -7861,151 +7936,154 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1.5</v>
+        <v>115</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="I15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C16" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C17" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1.5</v>
+        <v>120</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="I17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C18" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C19" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="I19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2">
         <v>3.0</v>
@@ -8014,117 +8092,120 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C24" s="2">
         <v>1.0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27">
@@ -11060,160 +11141,160 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C7" s="2">
         <v>8.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>17</v>
@@ -11222,24 +11303,24 @@
         <v>2.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>147</v>
+        <v>153</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C8" s="2">
         <v>8.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>17</v>
@@ -11248,24 +11329,24 @@
         <v>2.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C9" s="2">
         <v>8.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>17</v>
@@ -11274,24 +11355,24 @@
         <v>2.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="C10" s="2">
         <v>8.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
@@ -11300,24 +11381,24 @@
         <v>2.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="9" t="s">
         <v>153</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2">
         <v>2.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>17</v>
@@ -11326,24 +11407,24 @@
         <v>4.0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>156</v>
+        <v>162</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2">
         <v>2.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
@@ -11352,24 +11433,24 @@
         <v>4.0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2">
         <v>2.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -11378,24 +11459,24 @@
         <v>4.0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C14" s="2">
         <v>2.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -11404,24 +11485,24 @@
         <v>4.0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -11430,24 +11511,24 @@
         <v>4.0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2">
         <v>2.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -11456,24 +11537,24 @@
         <v>4.0</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2">
         <v>2.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -11482,24 +11563,24 @@
         <v>4.0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C18" s="2">
         <v>2.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -11508,24 +11589,24 @@
         <v>4.0</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>170</v>
+        <v>162</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>17</v>
@@ -11536,23 +11617,23 @@
       <c r="G19" s="3">
         <v>16.0</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>172</v>
+      <c r="H19" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="K19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>17</v>
@@ -11563,23 +11644,23 @@
       <c r="G20" s="3">
         <v>16.0</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>174</v>
+      <c r="H20" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="K20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>17</v>
@@ -11590,22 +11671,22 @@
       <c r="G21" s="3">
         <v>16.0</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>176</v>
+      <c r="H21" s="13" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
@@ -11616,8 +11697,8 @@
       <c r="G22" s="3">
         <v>16.0</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>178</v>
+      <c r="H22" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -15518,89 +15599,89 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7">
@@ -18602,27 +18683,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -18631,15 +18712,15 @@
         <v>56.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -18648,15 +18729,15 @@
         <v>56.0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -18665,7 +18746,7 @@
         <v>84.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -18686,104 +18767,104 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
+        <v>205</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2">
-      <c r="B2" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>200</v>
+      <c r="B2" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>202</v>
+      <c r="B3" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>204</v>
+      <c r="B4" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -18804,132 +18885,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19">
@@ -18946,13 +19027,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="236">
   <si>
     <t>Base rules</t>
   </si>
@@ -244,7 +244,7 @@
     <t>Role</t>
   </si>
   <si>
-    <t>Stone</t>
+    <t>Bomb</t>
   </si>
   <si>
     <t>starter_deck</t>
@@ -256,10 +256,13 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Bomb</t>
-  </si>
-  <si>
-    <t>Rainbow</t>
+    <t>Super Bomb</t>
+  </si>
+  <si>
+    <t>Counts as &lt;b&gt;two Bombs&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Cloud</t>
   </si>
   <si>
     <t>ball_deck</t>
@@ -268,170 +271,107 @@
     <t>Common</t>
   </si>
   <si>
-    <t>&lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart if the other Lane has an open Rainbow. +1 Heart per open Rainbow pair.</t>
+    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
+Gain 1 Redraw. </t>
   </si>
   <si>
     <t>Reward</t>
   </si>
   <si>
-    <t>1+scaling</t>
-  </si>
-  <si>
     <t>Platypus</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;b&gt;Power:&lt;/b&gt;&lt;/br&gt;
+Open a ball. </t>
+  </si>
+  <si>
+    <t>Starter
+Safety</t>
+  </si>
+  <si>
+    <t>Ninja Dude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Power:&lt;/b&gt;&lt;/br&gt;
+Select a ball and switch place with it. </t>
+  </si>
+  <si>
+    <t>Manipulation</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Gain 1 additional Heart if this has been in a Collision 3 or more times.</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>ball_deck_2</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Power:&lt;/b&gt;&lt;/br&gt;
+Destroy this and the topmost ball of this Lane. </t>
+  </si>
+  <si>
+    <t>Halo</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
-Open a ball in play. </t>
-  </si>
-  <si>
-    <t>Manipulation
-Starter</t>
-  </si>
-  <si>
-    <t>Ninja Dude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
-Select a closed ball and switch place with it. </t>
-  </si>
-  <si>
-    <t>Manipulation</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart if this has been in a Collision 3 or more times.</t>
-  </si>
-  <si>
-    <t>Granite</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
+Gain 1 Heart. &lt;/br&gt;
 &lt;/br&gt;
-&lt;b&gt;Invulnerable&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>Safety</t>
-  </si>
-  <si>
-    <t>Fireworks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
+&lt;b&gt;Power:&lt;/b&gt;&lt;/br&gt;
+Put this back into the Combola. </t>
+  </si>
+  <si>
+    <t>Cuddle Fish</t>
+  </si>
+  <si>
+    <t>Repeat any Open or Power-effect of adjacent balls as if this is a copy of the original ball.</t>
+  </si>
+  <si>
+    <t>Oblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Switch place of any two balls. Gain 1 Heart if they were of the same color.  </t>
+  </si>
+  <si>
+    <t>Pkm Trainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Draw a random Mascot (green) and place it in any Lane. Then gain 1 Heart for each unique Mascot above this. </t>
+  </si>
+  <si>
+    <t>Chain</t>
+  </si>
+  <si>
+    <t>Dynamite Harry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Destroy the first Bomb (black) ball above this and gain 2 Hearts. </t>
+  </si>
+  <si>
+    <t>Toaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
+Gain 2 Hearts and then close this. </t>
+  </si>
+  <si>
+    <t>Snowglobe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Brittle 2&lt;/b&gt;&lt;/br&gt;&lt;/br&gt;
 &lt;/br&gt;
-&lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
-Gain 2 Hearts. </t>
-  </si>
-  <si>
-    <t>Mist</t>
-  </si>
-  <si>
-    <t>ball_deck_2</t>
-  </si>
-  <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened&lt;/b&gt;&lt;/br&gt;
-Replace the ball immediately above this with a ball from the Combola. Gain 2 Hearts if they were of the same Color. </t>
-  </si>
-  <si>
-    <t>1+2*x+y</t>
-  </si>
-  <si>
-    <t>Lightning</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;When Destroyed:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart and then Open the two topmost balls.&lt;/br&gt;
-&lt;/br&gt;
-&lt;b&gt;When Opened:&lt;b&gt;&lt;/br&gt;
-Destroy this.</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>Cuddle Fish</t>
-  </si>
-  <si>
-    <t>Repeat the Open effect of any ball that is opened adjacent to this as if this was a copy of that ball.</t>
-  </si>
-  <si>
-    <t>Oblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Switch place of any two balls in play. Gain 1 Heart if they were of the same color.  </t>
-  </si>
-  <si>
-    <t>Pkm Trainer</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Draw a random Mascot (green) and place it after this ball. If it was Uncommon, gain 1 Heart. If it was Rare, gain 2 Hearts.</t>
-  </si>
-  <si>
-    <t>Reward
-Chain</t>
-  </si>
-  <si>
-    <t>Red Mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
-Destroy a non-bomb (black) ball. Gain 2 Hearts. </t>
-  </si>
-  <si>
-    <t>Starter
-Reward</t>
-  </si>
-  <si>
-    <t>1+0.5</t>
-  </si>
-  <si>
-    <t>Toaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Get a Toast trophy and 1 Heart. Then close this. </t>
-  </si>
-  <si>
-    <t>Snowglobe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Brittle 2&lt;/b&gt;&lt;/br&gt;&lt;/br&gt;
-&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart for each time there was a collision above this ball. </t>
-  </si>
-  <si>
-    <t>Reward, Risk</t>
-  </si>
-  <si>
-    <t>Geode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
-&lt;/br&gt;
-&lt;b&gt;When Destroyed:&lt;/b&gt;&lt;/br&gt;
-Draw your highest rarity ball. Replace this with the drawn ball. </t>
-  </si>
-  <si>
-    <t>Chain</t>
-  </si>
-  <si>
-    <t>Brittle Bomb</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
-&lt;/br&gt;
-&lt;b&gt;Brittle 4&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>High: 3.5</t>
+Gain 1 Heart whenever there is a collision above this ball. </t>
   </si>
   <si>
     <t>Aurora</t>
@@ -447,46 +387,28 @@
     <t>Mr Marshmallow</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart.&lt;/br&gt;
-Gain 1 Redraw for each open ball in a Lane. </t>
-  </si>
-  <si>
-    <t>Reward, Safety</t>
-  </si>
-  <si>
-    <t>Seer</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Gain 3 Redraw. Draw 3 balls and place them one at a time.</t>
+    <t>&lt;b&gt;When Drawn:&lt;/b&gt;&lt;/br&gt;
+Close all balls and refresh all Powers.</t>
+  </si>
+  <si>
+    <t>Reward, Chain</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Anime Protagonist</t>
+  </si>
+  <si>
+    <t>Gain 1 Heart each time this is in a Collision or would be Destroyed.&lt;/br&gt;
+&lt;/br&gt;
+&lt;b&gt;Invulnerable&lt;b&gt;</t>
   </si>
   <si>
     <t>Combola</t>
   </si>
   <si>
     <t>Whenever you place a ball in this Lane, draw a copy of that ball from the Combola, if able. The drawn ball becomes &lt;b&gt;Ethereal&lt;/b&gt;.</t>
-  </si>
-  <si>
-    <t>Jade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Replacement&lt;/b&gt;&lt;/br&gt;
-&lt;/br&gt;
-&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart for each brown ball above this. </t>
-  </si>
-  <si>
-    <t>Uranium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detonate this Lane whenever you have three or more balls of the same color in the Lane. &lt;/br&gt;
-&lt;/br&gt;
-&lt;b&gt;When Opened:&lt;/b&gt;&lt;/br&gt;
-Gain 1 Heart for each ball in this Lane. </t>
-  </si>
-  <si>
-    <t>Risk</t>
   </si>
   <si>
     <t>Cost</t>
@@ -873,7 +795,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,12 +806,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE599"/>
         <bgColor rgb="FFFFE599"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -905,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -936,16 +852,13 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -7581,7 +7494,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.38"/>
-    <col customWidth="1" min="6" max="6" width="44.38"/>
+    <col customWidth="1" min="6" max="6" width="48.25"/>
     <col customWidth="1" min="7" max="7" width="15.25"/>
   </cols>
   <sheetData>
@@ -7619,13 +7532,13 @@
         <v>75</v>
       </c>
       <c r="C2" s="2">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>77</v>
@@ -7639,7 +7552,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>76</v>
@@ -7648,32 +7561,29 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2">
         <v>10.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" s="2" t="s">
         <v>84</v>
       </c>
     </row>
@@ -7682,13 +7592,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="2">
         <v>10.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>15</v>
@@ -7708,13 +7618,13 @@
         <v>88</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2">
         <v>10.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
@@ -7734,13 +7644,13 @@
         <v>91</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2">
         <v>10.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>19</v>
@@ -7749,7 +7659,7 @@
         <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="8">
         <v>46024.0</v>
@@ -7760,459 +7670,303 @@
         <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2.0</v>
+        <v>98</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2">
         <v>4.0</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>102</v>
+      <c r="G10" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C11" s="2">
         <v>4.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>104</v>
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C12" s="2">
         <v>4.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1.5</v>
+        <v>105</v>
       </c>
       <c r="I12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C13" s="2">
         <v>4.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1.0</v>
+        <v>84</v>
       </c>
       <c r="I13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C14" s="2">
         <v>4.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1.5</v>
+        <v>84</v>
       </c>
       <c r="I14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C15" s="2">
         <v>4.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="I15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C16" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>118</v>
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1.5</v>
+        <v>84</v>
       </c>
       <c r="I16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C17" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>15</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C18" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I18" s="3"/>
+        <v>84</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C19" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="I20" s="3"/>
+        <v>105</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="F21" s="6"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="F22" s="6"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="F23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="F24" s="3"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="F27" s="6"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="28">
-      <c r="F28" s="6"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29">
       <c r="F29" s="3"/>
@@ -8220,17 +7974,23 @@
     <row r="30">
       <c r="F30" s="3"/>
     </row>
-    <row r="31">
-      <c r="F31" s="3"/>
+    <row r="33">
+      <c r="F33" s="6"/>
     </row>
     <row r="34">
-      <c r="F34" s="3"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35">
-      <c r="F35" s="3"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36">
-      <c r="F36" s="3"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37">
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38">
+      <c r="F38" s="6"/>
     </row>
     <row r="39">
       <c r="F39" s="6"/>
@@ -11102,24 +10862,6 @@
     </row>
     <row r="995">
       <c r="F995" s="6"/>
-    </row>
-    <row r="996">
-      <c r="F996" s="6"/>
-    </row>
-    <row r="997">
-      <c r="F997" s="6"/>
-    </row>
-    <row r="998">
-      <c r="F998" s="6"/>
-    </row>
-    <row r="999">
-      <c r="F999" s="6"/>
-    </row>
-    <row r="1000">
-      <c r="F1000" s="6"/>
-    </row>
-    <row r="1001">
-      <c r="F1001" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -11156,10 +10898,10 @@
         <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>144</v>
+        <v>123</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>41</v>
@@ -11170,10 +10912,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -11193,10 +10935,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -11216,10 +10958,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -11239,10 +10981,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
@@ -11262,10 +11004,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -11285,16 +11027,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C7" s="2">
         <v>8.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>17</v>
@@ -11303,24 +11045,24 @@
         <v>2.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>154</v>
+        <v>133</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C8" s="2">
         <v>8.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>17</v>
@@ -11329,24 +11071,24 @@
         <v>2.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>156</v>
+        <v>133</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2">
         <v>8.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>17</v>
@@ -11355,24 +11097,24 @@
         <v>2.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>158</v>
+        <v>133</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2">
         <v>8.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
@@ -11381,24 +11123,24 @@
         <v>2.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>160</v>
+        <v>133</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2">
         <v>2.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>17</v>
@@ -11407,24 +11149,24 @@
         <v>4.0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>163</v>
+        <v>142</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2">
         <v>2.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
@@ -11433,24 +11175,24 @@
         <v>4.0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>165</v>
+        <v>142</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C13" s="2">
         <v>2.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -11459,24 +11201,24 @@
         <v>4.0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>167</v>
+        <v>142</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2">
         <v>2.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -11485,24 +11227,24 @@
         <v>4.0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -11511,24 +11253,24 @@
         <v>4.0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>171</v>
+        <v>142</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2">
         <v>2.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -11537,24 +11279,24 @@
         <v>4.0</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>173</v>
+        <v>142</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2">
         <v>2.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -11563,24 +11305,24 @@
         <v>4.0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>175</v>
+        <v>142</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2">
         <v>2.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -11589,24 +11331,24 @@
         <v>4.0</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>177</v>
+        <v>142</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>17</v>
@@ -11617,23 +11359,23 @@
       <c r="G19" s="3">
         <v>16.0</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>179</v>
+      <c r="H19" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="K19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>17</v>
@@ -11644,23 +11386,23 @@
       <c r="G20" s="3">
         <v>16.0</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>181</v>
+      <c r="H20" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="K20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>17</v>
@@ -11671,22 +11413,22 @@
       <c r="G21" s="3">
         <v>16.0</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>183</v>
+      <c r="H21" s="12" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
@@ -11697,8 +11439,8 @@
       <c r="G22" s="3">
         <v>16.0</v>
       </c>
-      <c r="H22" s="13" t="s">
-        <v>185</v>
+      <c r="H22" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -15616,72 +15358,72 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -18692,7 +18434,7 @@
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>41</v>
@@ -18700,10 +18442,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -18712,15 +18454,15 @@
         <v>56.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -18729,15 +18471,15 @@
         <v>56.0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -18746,7 +18488,7 @@
         <v>84.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -18767,104 +18509,104 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="15"/>
+        <v>185</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="2">
-      <c r="B2" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>207</v>
+      <c r="B2" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>209</v>
+      <c r="B3" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>211</v>
+      <c r="B4" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="2" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -18885,132 +18627,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19">
@@ -19027,13 +18769,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="239">
   <si>
     <t>Base rules</t>
   </si>
@@ -306,17 +306,13 @@
 Gain 1 additional Heart if this has been in a Collision 3 or more times.</t>
   </si>
   <si>
-    <t>Lightning</t>
-  </si>
-  <si>
     <t>ball_deck_2</t>
   </si>
   <si>
     <t>Uncommon</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Power:&lt;/b&gt;&lt;/br&gt;
-Destroy this and the topmost ball of this Lane. </t>
+    <t>SOMETHING THAT SYNERGIZES WITH HALO</t>
   </si>
   <si>
     <t>Halo</t>
@@ -369,12 +365,15 @@
     <t>Snowglobe</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Brittle 2&lt;/b&gt;&lt;/br&gt;&lt;/br&gt;
+    <t xml:space="preserve">&lt;b&gt;Brittle 2&lt;/b&gt;&lt;/br&gt;
 &lt;/br&gt;
 Gain 1 Heart whenever there is a collision above this ball. </t>
   </si>
   <si>
     <t>Aurora</t>
+  </si>
+  <si>
+    <t>ball_deck_3</t>
   </si>
   <si>
     <t>Rare</t>
@@ -649,6 +648,18 @@
     <t>Eclipse</t>
   </si>
   <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Topmost ball</t>
+  </si>
+  <si>
+    <t>Mist</t>
+  </si>
+  <si>
+    <t>Shrouded in mist</t>
+  </si>
+  <si>
     <t>Boba Tea</t>
   </si>
   <si>
@@ -671,10 +682,6 @@
   </si>
   <si>
     <t>Världens längsta pommes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Draw
-Destroy a ball and gain 1 Heart. Bombs (black) can not be destroyed. </t>
   </si>
   <si>
     <t>Theme</t>
@@ -7666,44 +7673,41 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="C8" s="2">
         <v>0.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2">
         <v>4.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>76</v>
@@ -7712,22 +7716,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2">
         <v>4.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>84</v>
@@ -7736,22 +7740,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="2">
         <v>4.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>90</v>
@@ -7760,46 +7764,46 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="2">
         <v>4.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="I12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2">
         <v>4.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>84</v>
@@ -7808,22 +7812,22 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="2">
         <v>4.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>84</v>
@@ -7832,22 +7836,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="2">
         <v>4.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>84</v>
@@ -7856,10 +7860,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
@@ -7883,7 +7887,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -7909,7 +7913,7 @@
         <v>119</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
@@ -7932,7 +7936,7 @@
         <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
@@ -7947,7 +7951,7 @@
         <v>122</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
@@ -11140,7 +11144,7 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>17</v>
@@ -11166,7 +11170,7 @@
         <v>2.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
@@ -11192,7 +11196,7 @@
         <v>2.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -11218,7 +11222,7 @@
         <v>2.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -11244,7 +11248,7 @@
         <v>2.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -11270,7 +11274,7 @@
         <v>2.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -11296,7 +11300,7 @@
         <v>2.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -11322,7 +11326,7 @@
         <v>2.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -18564,49 +18568,60 @@
         <v>197</v>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
     <row r="12">
       <c r="B12" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -18627,132 +18642,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19">
@@ -18769,10 +18784,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>118</v>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -1782,7 +1782,7 @@
         <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="178">
   <si>
     <t>Matches</t>
   </si>
@@ -434,7 +434,7 @@
     <t>Twins Token</t>
   </si>
   <si>
-    <t xml:space="preserve">Gain 1 additional Credit whenever you gain a copy of a Trophy. </t>
+    <t xml:space="preserve">Gain 1 additional Credit whenever you gain a copy of a non-Bomb Trophy. </t>
   </si>
   <si>
     <t>Bag Token</t>
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>Chemists Token</t>
+  </si>
+  <si>
+    <t>token_deck_2</t>
   </si>
   <si>
     <t xml:space="preserve">Increase the number of bombs required for a detonation by 1.&lt;/br&gt;
@@ -5061,7 +5064,7 @@
         <v>113</v>
       </c>
       <c r="C9" s="2">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>65</v>
@@ -5143,7 +5146,7 @@
         <v>137</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C14" s="2">
         <v>1.0</v>
@@ -5152,15 +5155,15 @@
         <v>85</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C15" s="2">
         <v>1.0</v>
@@ -5169,15 +5172,15 @@
         <v>85</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
@@ -5186,15 +5189,15 @@
         <v>85</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -5203,15 +5206,15 @@
         <v>85</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
@@ -5220,15 +5223,15 @@
         <v>85</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
@@ -5237,7 +5240,7 @@
         <v>85</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20">
@@ -8219,17 +8222,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="15"/>
     </row>
     <row r="2">
       <c r="B2" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -8240,36 +8243,36 @@
     </row>
     <row r="4">
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -8277,60 +8280,60 @@
         <v>63</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
@@ -8345,13 +8348,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
@@ -8366,14 +8369,14 @@
         <v>46</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>64</v>
@@ -8388,7 +8391,7 @@
         <v>46</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>55</v>
@@ -8400,7 +8403,7 @@
         <v>39</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
